--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>321</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>306</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.1</v>
+        <v>60.1</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.2</v>
+        <v>45.9</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>306</v>
+        <v>291</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
         <v>5</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>92.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>94.7</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -772,19 +772,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>85.7</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>82.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="8">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
         <v>22</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>76.3</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F9" t="n">
         <v>13</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>81.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>60.9</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="12">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" t="n">
         <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="13">
@@ -996,19 +996,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
         <v>37</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>58.7</v>
+        <v>57.8</v>
       </c>
     </row>
     <row r="14">
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>37.1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>53.7</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="16">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>40.7</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>49.3</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="18">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>29.6</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="19">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
         <v>58</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="21">
@@ -1255,16 +1255,16 @@
         <v>60</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>28.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="22">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>70.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E24" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>71.2</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="25">
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>65.59999999999999</v>
+        <v>66.2</v>
       </c>
     </row>
   </sheetData>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>959.39</v>
+        <v>983.41</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27.36</v>
+        <v>51.38</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-105.5</v>
+        <v>-81.48999999999999</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1319.35</v>
+        <v>1343.36</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>77.5</v>
+        <v>101.51</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>15.79</v>
+        <v>39.8</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>624.36</v>
+        <v>648.37</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>343.45</v>
+        <v>367.46</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>73.59999999999999</v>
+        <v>97.61</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -3470,45 +3470,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-15T14:17:24.794840+00:00</t>
+          <t>2026-10-01T10:17:24.794840+00:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-18T16:55:32.004331+00:00</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-08-21T18:54:38.339110+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-04T12:55:32.004331+00:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>74.64</v>
       </c>
-      <c r="H39" t="n">
-        <v>73.98999999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>148.62</v>
-      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="b">
-        <v>1</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-71.2</v>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3652,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>-45.31</v>
+        <v>-21.3</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3817,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>529.72</v>
+        <v>553.74</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3976,7 +3970,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>-20.49</v>
+        <v>3.52</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4025,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>190.67</v>
+        <v>214.68</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4051,7 +4045,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4064,18 +4058,24 @@
           <t>2026-09-26T03:37:34.055636+00:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-27T18:42:08.324374+00:00</t>
+        </is>
+      </c>
       <c r="G50" t="n">
         <v>34.04</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>39.08</v>
+      </c>
+      <c r="I50" t="n">
+        <v>73.12</v>
+      </c>
       <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>65.48999999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4113,18 +4113,24 @@
           <t>2026-09-22T15:27:52.179860+00:00</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-28T04:34:49.027819+00:00</t>
+        </is>
+      </c>
       <c r="G51" t="n">
         <v>47.42</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>133.12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>180.53</v>
+      </c>
       <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>163.03</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -4722,7 +4728,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>752.08</v>
+        <v>776.1</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4771,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1271.33</v>
+        <v>1295.34</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4875,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>45.27</v>
+        <v>69.28</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4924,7 +4930,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>39.64</v>
+        <v>63.66</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4973,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>-6.74</v>
+        <v>17.28</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5077,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>27.79</v>
+        <v>51.8</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5103,37 +5109,31 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-07T21:30:05.853272+00:00</t>
+          <t>2026-09-30T05:30:05.853272+00:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-08T15:12:48.340790+00:00</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-09-10T03:40:47.932189+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-30T23:12:48.340790+00:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>17.71</v>
       </c>
-      <c r="H70" t="n">
-        <v>36.47</v>
-      </c>
-      <c r="I70" t="n">
-        <v>54.18</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="b">
-        <v>1</v>
-      </c>
-      <c r="K70" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>-42.41</v>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>38.84</v>
+        <v>62.86</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>56.15</v>
+        <v>80.16</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.08</v>
+        <v>20.94</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>-1.23</v>
+        <v>22.79</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>28.15</v>
+        <v>52.16</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>69.75</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>41.99</v>
+        <v>66</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>252.19</v>
+        <v>276.2</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>145.89</v>
+        <v>169.9</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>232.47</v>
+        <v>256.48</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -6826,7 +6826,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>-10.8</v>
+        <v>13.21</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>-97.66</v>
+        <v>-73.65000000000001</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>295.61</v>
+        <v>319.62</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7060,45 +7060,39 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-18T00:43:58.986451+00:00</t>
+          <t>2026-09-29T12:13:28.450598+00:00</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-18T08:53:26.780802+00:00</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-08-23T02:36:03.146300+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-29T20:22:56.244949+00:00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
         <v>8.16</v>
       </c>
-      <c r="H107" t="n">
-        <v>113.71</v>
-      </c>
-      <c r="I107" t="n">
-        <v>121.87</v>
-      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="b">
-        <v>1</v>
-      </c>
-      <c r="K107" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>-25.14</v>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>583.9299999999999</v>
+        <v>607.9400000000001</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -7594,67 +7588,61 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PO-10178</t>
+          <t>PO-10177</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-20T09:53:39.583202+00:00</t>
+          <t>2026-10-02T11:18:49.509655+00:00</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-09-22T07:09:53.716842+00:00</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-09-24T04:28:36.357545+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-03T12:13:16.000836+00:00</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>45.27</v>
-      </c>
-      <c r="H117" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I117" t="n">
-        <v>90.58</v>
-      </c>
+        <v>24.91</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="b">
-        <v>1</v>
-      </c>
-      <c r="K117" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>-96.22</v>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PO-10179</t>
+          <t>PO-10178</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7664,27 +7652,27 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-20T09:31:21.607327+00:00</t>
+          <t>2026-09-05T16:37:43.254327+00:00</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-22T05:22:21.578284+00:00</t>
+          <t>2026-09-06T04:03:22.582674+00:00</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-23T18:02:51.686514+00:00</t>
+          <t>2026-09-07T03:15:06.102054+00:00</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>43.85</v>
+        <v>11.43</v>
       </c>
       <c r="H118" t="n">
-        <v>36.68</v>
+        <v>23.2</v>
       </c>
       <c r="I118" t="n">
-        <v>80.53</v>
+        <v>34.62</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
@@ -7692,24 +7680,24 @@
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PO-10180</t>
+          <t>PO-10179</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7719,27 +7707,27 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-22T14:04:07.705505+00:00</t>
+          <t>2026-08-25T21:40:37.975573+00:00</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-09-23T07:21:27.929347+00:00</t>
+          <t>2026-08-26T18:49:47.365726+00:00</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-25T01:55:53.159642+00:00</t>
+          <t>2026-08-30T15:50:15.580728+00:00</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>17.29</v>
+        <v>21.15</v>
       </c>
       <c r="H119" t="n">
-        <v>42.57</v>
+        <v>93.01000000000001</v>
       </c>
       <c r="I119" t="n">
-        <v>59.86</v>
+        <v>114.16</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
@@ -7747,12 +7735,12 @@
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7752,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PO-10182</t>
+          <t>PO-10181</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7819,7 +7807,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PO-10184</t>
+          <t>PO-10183</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7874,7 +7862,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PO-10186</t>
+          <t>PO-10185</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7902,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>-66.03</v>
+        <v>-42.02</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -7923,7 +7911,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PO-10187</t>
+          <t>PO-10186</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7978,7 +7966,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PO-10188</t>
+          <t>PO-10187</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8033,7 +8021,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PO-10189</t>
+          <t>PO-10188</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8088,7 +8076,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PO-10190</t>
+          <t>PO-10189</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8143,7 +8131,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PO-10192</t>
+          <t>PO-10191</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8198,7 +8186,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PO-10194</t>
+          <t>PO-10193</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8253,7 +8241,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PO-10195</t>
+          <t>PO-10194</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8308,7 +8296,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PO-10196</t>
+          <t>PO-10195</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8363,7 +8351,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PO-10199</t>
+          <t>PO-10198</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8391,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>-72.92</v>
+        <v>-48.9</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8412,7 +8400,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PO-10200</t>
+          <t>PO-10199</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8467,7 +8455,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PO-10203</t>
+          <t>PO-10202</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8495,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>288.23</v>
+        <v>312.24</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -8516,7 +8504,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PO-10204</t>
+          <t>PO-10203</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8571,7 +8559,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PO-10206</t>
+          <t>PO-10205</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8626,7 +8614,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PO-10207</t>
+          <t>PO-10206</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8681,7 +8669,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PO-10208</t>
+          <t>PO-10207</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8709,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>-13.26</v>
+        <v>10.75</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -8730,7 +8718,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PO-10210</t>
+          <t>PO-10209</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8785,7 +8773,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PO-10211</t>
+          <t>PO-10210</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8840,7 +8828,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PO-10212</t>
+          <t>PO-10211</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8895,7 +8883,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PO-10214</t>
+          <t>PO-10213</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8923,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>613.37</v>
+        <v>637.39</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -8944,7 +8932,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PO-10217</t>
+          <t>PO-10216</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8972,7 +8960,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>318.89</v>
+        <v>342.9</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -8993,7 +8981,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PO-10218</t>
+          <t>PO-10217</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9021,7 +9009,7 @@
         <v>0</v>
       </c>
       <c r="K143" t="n">
-        <v>1260.33</v>
+        <v>1284.34</v>
       </c>
       <c r="L143" t="inlineStr">
         <is>
@@ -9042,7 +9030,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PO-10220</t>
+          <t>PO-10219</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9097,7 +9085,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PO-10221</t>
+          <t>PO-10220</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9152,7 +9140,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PO-10223</t>
+          <t>PO-10222</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9207,7 +9195,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PO-10224</t>
+          <t>PO-10223</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9235,7 +9223,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>975.17</v>
+        <v>999.1799999999999</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -9256,7 +9244,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PO-10225</t>
+          <t>PO-10224</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9311,12 +9299,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PO-10226</t>
+          <t>PO-10225</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9329,18 +9317,24 @@
           <t>2026-09-27T05:13:49.767436+00:00</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-28T03:59:46.566157+00:00</t>
+        </is>
+      </c>
       <c r="G149" t="n">
         <v>27.03</v>
       </c>
-      <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
+      <c r="H149" t="n">
+        <v>22.77</v>
+      </c>
+      <c r="I149" t="n">
+        <v>49.79</v>
+      </c>
       <c r="J149" t="b">
-        <v>0</v>
-      </c>
-      <c r="K149" t="n">
-        <v>32.87</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -9355,7 +9349,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9365,132 +9359,120 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-27T17:46:43.586100+00:00</t>
+          <t>2026-09-11T12:59:10.672111+00:00</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-29T08:29:30.606610+00:00</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-01T20:54:50.978774+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-12T07:24:55.956154+00:00</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="n">
-        <v>38.71</v>
-      </c>
-      <c r="H150" t="n">
-        <v>84.42</v>
-      </c>
-      <c r="I150" t="n">
-        <v>123.14</v>
-      </c>
+        <v>18.43</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="b">
-        <v>1</v>
-      </c>
-      <c r="K150" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>406.1</v>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PO-10228</t>
+          <t>PO-10230</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-14T21:46:10.130729+00:00</t>
+          <t>2026-09-11T04:09:06.419305+00:00</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-16T15:25:34.701730+00:00</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-08-18T22:12:33.202566+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-11T07:15:05.545807+00:00</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="n">
-        <v>41.66</v>
-      </c>
-      <c r="H151" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="I151" t="n">
-        <v>96.44</v>
-      </c>
+        <v>3.1</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="b">
-        <v>1</v>
-      </c>
-      <c r="K151" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>414.94</v>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PO-10229</t>
+          <t>PO-10231</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-23T01:51:15.236491+00:00</t>
+          <t>2026-09-27T05:02:13.039854+00:00</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-23T06:02:34.325331+00:00</t>
+          <t>2026-09-28T23:59:44.282440+00:00</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="n">
-        <v>4.19</v>
+        <v>42.96</v>
       </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
@@ -9498,65 +9480,71 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>849.22</v>
+        <v>30.05</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PO-10230</t>
+          <t>PO-10232</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-27T05:02:13.039854+00:00</t>
+          <t>2026-08-09T14:55:21.679944+00:00</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-09-28T23:59:44.282440+00:00</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
+          <t>2026-08-12T14:27:56.693815+00:00</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-15T10:24:22.926225+00:00</t>
+        </is>
+      </c>
       <c r="G153" t="n">
-        <v>42.96</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
+        <v>71.54000000000001</v>
+      </c>
+      <c r="H153" t="n">
+        <v>67.94</v>
+      </c>
+      <c r="I153" t="n">
+        <v>139.48</v>
+      </c>
       <c r="J153" t="b">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>6.04</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9556,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PO-10231</t>
+          <t>PO-10233</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9578,27 +9566,27 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-09T14:55:21.679944+00:00</t>
+          <t>2026-09-07T09:35:03.486270+00:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-12T14:27:56.693815+00:00</t>
+          <t>2026-09-10T16:00:49.370910+00:00</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-15T10:24:22.926225+00:00</t>
+          <t>2026-09-13T11:27:57.448053+00:00</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>71.54000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="H154" t="n">
-        <v>67.94</v>
+        <v>67.45</v>
       </c>
       <c r="I154" t="n">
-        <v>139.48</v>
+        <v>145.88</v>
       </c>
       <c r="J154" t="b">
         <v>1</v>
@@ -9606,24 +9594,24 @@
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PO-10232</t>
+          <t>PO-10234</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9633,27 +9621,27 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-07T09:35:03.486270+00:00</t>
+          <t>2026-08-15T22:34:17.465186+00:00</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-09-10T16:00:49.370910+00:00</t>
+          <t>2026-08-18T15:13:06.986577+00:00</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-09-13T11:27:57.448053+00:00</t>
+          <t>2026-08-19T11:46:13.239653+00:00</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>78.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="H155" t="n">
-        <v>67.45</v>
+        <v>20.55</v>
       </c>
       <c r="I155" t="n">
-        <v>145.88</v>
+        <v>85.2</v>
       </c>
       <c r="J155" t="b">
         <v>1</v>
@@ -9661,108 +9649,108 @@
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PO-10233</t>
+          <t>PO-10236</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-15T22:34:17.465186+00:00</t>
+          <t>2026-09-17T12:18:37.587502+00:00</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-08-18T15:13:06.986577+00:00</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-08-19T11:46:13.239653+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-18T00:54:30.832025+00:00</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="n">
-        <v>64.65000000000001</v>
-      </c>
-      <c r="H156" t="n">
-        <v>20.55</v>
-      </c>
-      <c r="I156" t="n">
-        <v>85.2</v>
-      </c>
+        <v>12.6</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="b">
-        <v>1</v>
-      </c>
-      <c r="K156" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>262.78</v>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PO-10235</t>
+          <t>PO-10237</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-17T12:18:37.587502+00:00</t>
+          <t>2026-09-13T13:14:31.023135+00:00</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-09-18T00:54:30.832025+00:00</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr"/>
+          <t>2026-09-14T04:09:04.551793+00:00</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-15T20:51:37.188657+00:00</t>
+        </is>
+      </c>
       <c r="G157" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
+        <v>14.91</v>
+      </c>
+      <c r="H157" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="I157" t="n">
+        <v>55.62</v>
+      </c>
       <c r="J157" t="b">
-        <v>0</v>
-      </c>
-      <c r="K157" t="n">
-        <v>238.77</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -9770,19 +9758,19 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PO-10236</t>
+          <t>PO-10238</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9792,27 +9780,27 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-13T13:14:31.023135+00:00</t>
+          <t>2026-09-17T07:51:03.004621+00:00</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-09-14T04:09:04.551793+00:00</t>
+          <t>2026-09-17T19:44:48.440880+00:00</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-09-15T20:51:37.188657+00:00</t>
+          <t>2026-09-20T12:23:25.436938+00:00</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>14.91</v>
+        <v>11.9</v>
       </c>
       <c r="H158" t="n">
-        <v>40.71</v>
+        <v>64.64</v>
       </c>
       <c r="I158" t="n">
-        <v>55.62</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="J158" t="b">
         <v>1</v>
@@ -9825,19 +9813,19 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PO-10237</t>
+          <t>PO-10239</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9847,27 +9835,27 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-17T07:51:03.004621+00:00</t>
+          <t>2026-08-15T12:15:05.176968+00:00</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-09-17T19:44:48.440880+00:00</t>
+          <t>2026-08-16T07:55:51.219322+00:00</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-09-20T12:23:25.436938+00:00</t>
+          <t>2026-08-19T02:27:46.045119+00:00</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>11.9</v>
+        <v>19.68</v>
       </c>
       <c r="H159" t="n">
-        <v>64.64</v>
+        <v>66.53</v>
       </c>
       <c r="I159" t="n">
-        <v>76.54000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="J159" t="b">
         <v>1</v>
@@ -9875,24 +9863,24 @@
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PO-10238</t>
+          <t>PO-10241</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9902,27 +9890,27 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-15T12:15:05.176968+00:00</t>
+          <t>2026-08-18T15:32:18.202870+00:00</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-08-16T07:55:51.219322+00:00</t>
+          <t>2026-08-18T21:36:03.019182+00:00</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-19T02:27:46.045119+00:00</t>
+          <t>2026-08-20T12:56:08.089601+00:00</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>19.68</v>
+        <v>6.06</v>
       </c>
       <c r="H160" t="n">
-        <v>66.53</v>
+        <v>39.33</v>
       </c>
       <c r="I160" t="n">
-        <v>86.20999999999999</v>
+        <v>45.4</v>
       </c>
       <c r="J160" t="b">
         <v>1</v>
@@ -9935,19 +9923,19 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PO-10240</t>
+          <t>PO-10242</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -9957,27 +9945,27 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-18T15:32:18.202870+00:00</t>
+          <t>2026-08-31T09:32:25.546311+00:00</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-08-18T21:36:03.019182+00:00</t>
+          <t>2026-09-01T14:25:42.004397+00:00</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-20T12:56:08.089601+00:00</t>
+          <t>2026-09-02T23:17:37.311811+00:00</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>6.06</v>
+        <v>28.89</v>
       </c>
       <c r="H161" t="n">
-        <v>39.33</v>
+        <v>32.87</v>
       </c>
       <c r="I161" t="n">
-        <v>45.4</v>
+        <v>61.75</v>
       </c>
       <c r="J161" t="b">
         <v>1</v>
@@ -9990,19 +9978,19 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PO-10241</t>
+          <t>PO-10243</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10012,27 +10000,27 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-31T09:32:25.546311+00:00</t>
+          <t>2026-09-03T06:21:04.715668+00:00</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-09-01T14:25:42.004397+00:00</t>
+          <t>2026-09-04T21:55:11.127541+00:00</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-02T23:17:37.311811+00:00</t>
+          <t>2026-09-07T04:51:09.453229+00:00</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>28.89</v>
+        <v>39.57</v>
       </c>
       <c r="H162" t="n">
-        <v>32.87</v>
+        <v>54.93</v>
       </c>
       <c r="I162" t="n">
-        <v>61.75</v>
+        <v>94.5</v>
       </c>
       <c r="J162" t="b">
         <v>1</v>
@@ -10040,7 +10028,7 @@
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -10052,12 +10040,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PO-10242</t>
+          <t>PO-10244</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10067,27 +10055,27 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-03T06:21:04.715668+00:00</t>
+          <t>2026-09-14T04:02:39.703255+00:00</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-09-04T21:55:11.127541+00:00</t>
+          <t>2026-09-17T09:51:38.129739+00:00</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-07T04:51:09.453229+00:00</t>
+          <t>2026-09-19T18:29:52.070760+00:00</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>39.57</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="H163" t="n">
-        <v>54.93</v>
+        <v>56.64</v>
       </c>
       <c r="I163" t="n">
-        <v>94.5</v>
+        <v>134.45</v>
       </c>
       <c r="J163" t="b">
         <v>1</v>
@@ -10100,19 +10088,19 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PO-10243</t>
+          <t>PO-10245</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10122,27 +10110,27 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-14T04:02:39.703255+00:00</t>
+          <t>2026-08-30T13:38:10.949224+00:00</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-09-17T09:51:38.129739+00:00</t>
+          <t>2026-08-30T17:07:55.861054+00:00</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-09-19T18:29:52.070760+00:00</t>
+          <t>2026-09-01T03:28:05.267149+00:00</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>77.81999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H164" t="n">
-        <v>56.64</v>
+        <v>34.34</v>
       </c>
       <c r="I164" t="n">
-        <v>134.45</v>
+        <v>37.83</v>
       </c>
       <c r="J164" t="b">
         <v>1</v>
@@ -10150,12 +10138,12 @@
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10155,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PO-10244</t>
+          <t>PO-10246</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10177,27 +10165,27 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-30T13:38:10.949224+00:00</t>
+          <t>2026-09-08T12:30:30.413250+00:00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-08-30T17:07:55.861054+00:00</t>
+          <t>2026-09-09T03:59:35.928030+00:00</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-09-01T03:28:05.267149+00:00</t>
+          <t>2026-09-09T19:52:46.650643+00:00</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>3.5</v>
+        <v>15.48</v>
       </c>
       <c r="H165" t="n">
-        <v>34.34</v>
+        <v>15.89</v>
       </c>
       <c r="I165" t="n">
-        <v>37.83</v>
+        <v>31.37</v>
       </c>
       <c r="J165" t="b">
         <v>1</v>
@@ -10205,12 +10193,12 @@
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -10222,7 +10210,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PO-10245</t>
+          <t>PO-10249</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10232,27 +10220,27 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-08T12:30:30.413250+00:00</t>
+          <t>2026-08-06T13:14:21.949146+00:00</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-09-09T03:59:35.928030+00:00</t>
+          <t>2026-08-07T09:28:41.720911+00:00</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-09-09T19:52:46.650643+00:00</t>
+          <t>2026-08-08T07:48:09.271745+00:00</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>15.48</v>
+        <v>20.24</v>
       </c>
       <c r="H166" t="n">
-        <v>15.89</v>
+        <v>22.32</v>
       </c>
       <c r="I166" t="n">
-        <v>31.37</v>
+        <v>42.56</v>
       </c>
       <c r="J166" t="b">
         <v>1</v>
@@ -10260,67 +10248,61 @@
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PO-10248</t>
+          <t>PO-10250</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-06T13:14:21.949146+00:00</t>
+          <t>2026-09-29T02:04:17.345631+00:00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-08-07T09:28:41.720911+00:00</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-08-08T07:48:09.271745+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-30T04:08:23.850223+00:00</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="H167" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="I167" t="n">
-        <v>42.56</v>
-      </c>
+        <v>26.07</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="b">
-        <v>1</v>
-      </c>
-      <c r="K167" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>-14.98</v>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -10332,56 +10314,62 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PO-10249</t>
+          <t>PO-10252</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-29T02:04:17.345631+00:00</t>
+          <t>2026-08-26T22:26:51.613292+00:00</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>2026-09-30T04:08:23.850223+00:00</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr"/>
+          <t>2026-08-28T06:07:25.113334+00:00</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-08-31T02:27:00.205867+00:00</t>
+        </is>
+      </c>
       <c r="G168" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
+        <v>31.68</v>
+      </c>
+      <c r="H168" t="n">
+        <v>68.33</v>
+      </c>
+      <c r="I168" t="n">
+        <v>100</v>
+      </c>
       <c r="J168" t="b">
-        <v>0</v>
-      </c>
-      <c r="K168" t="n">
-        <v>-38.99</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PO-10251</t>
+          <t>PO-10253</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10391,27 +10379,27 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-26T22:26:51.613292+00:00</t>
+          <t>2026-08-16T18:21:05.974360+00:00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-08-28T06:07:25.113334+00:00</t>
+          <t>2026-08-17T10:34:55.170763+00:00</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-31T02:27:00.205867+00:00</t>
+          <t>2026-08-20T06:29:59.460695+00:00</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>31.68</v>
+        <v>16.23</v>
       </c>
       <c r="H169" t="n">
-        <v>68.33</v>
+        <v>67.92</v>
       </c>
       <c r="I169" t="n">
-        <v>100</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="J169" t="b">
         <v>1</v>
@@ -10424,19 +10412,19 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PO-10252</t>
+          <t>PO-10254</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10446,27 +10434,27 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-16T18:21:05.974360+00:00</t>
+          <t>2026-08-19T16:58:41.600194+00:00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-08-17T10:34:55.170763+00:00</t>
+          <t>2026-08-20T23:01:35.485427+00:00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-20T06:29:59.460695+00:00</t>
+          <t>2026-08-27T00:29:51.570175+00:00</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>16.23</v>
+        <v>30.05</v>
       </c>
       <c r="H170" t="n">
-        <v>67.92</v>
+        <v>145.47</v>
       </c>
       <c r="I170" t="n">
-        <v>84.15000000000001</v>
+        <v>175.52</v>
       </c>
       <c r="J170" t="b">
         <v>1</v>
@@ -10479,19 +10467,19 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PO-10253</t>
+          <t>PO-10255</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10501,27 +10489,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-19T16:58:41.600194+00:00</t>
+          <t>2026-08-10T02:24:14.327452+00:00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-08-20T23:01:35.485427+00:00</t>
+          <t>2026-08-11T10:16:57.206854+00:00</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-27T00:29:51.570175+00:00</t>
+          <t>2026-08-14T01:30:22.810576+00:00</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>30.05</v>
+        <v>31.88</v>
       </c>
       <c r="H171" t="n">
-        <v>145.47</v>
+        <v>63.22</v>
       </c>
       <c r="I171" t="n">
-        <v>175.52</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="J171" t="b">
         <v>1</v>
@@ -10534,7 +10522,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10534,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PO-10254</t>
+          <t>PO-10256</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10556,27 +10544,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-10T02:24:14.327452+00:00</t>
+          <t>2026-08-10T22:47:52.441820+00:00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-08-11T10:16:57.206854+00:00</t>
+          <t>2026-08-11T23:03:39.820856+00:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-14T01:30:22.810576+00:00</t>
+          <t>2026-08-12T04:39:19.461092+00:00</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>31.88</v>
+        <v>24.26</v>
       </c>
       <c r="H172" t="n">
-        <v>63.22</v>
+        <v>5.59</v>
       </c>
       <c r="I172" t="n">
-        <v>95.09999999999999</v>
+        <v>29.86</v>
       </c>
       <c r="J172" t="b">
         <v>1</v>
@@ -10601,7 +10589,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PO-10255</t>
+          <t>PO-10257</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10611,27 +10599,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-10T22:47:52.441820+00:00</t>
+          <t>2026-08-17T21:59:20.702594+00:00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-08-11T23:03:39.820856+00:00</t>
+          <t>2026-08-18T16:35:34.317101+00:00</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-12T04:39:19.461092+00:00</t>
+          <t>2026-08-19T18:54:21.152731+00:00</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>24.26</v>
+        <v>18.6</v>
       </c>
       <c r="H173" t="n">
-        <v>5.59</v>
+        <v>26.31</v>
       </c>
       <c r="I173" t="n">
-        <v>29.86</v>
+        <v>44.92</v>
       </c>
       <c r="J173" t="b">
         <v>1</v>
@@ -10644,19 +10632,19 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PO-10256</t>
+          <t>PO-10258</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10666,27 +10654,27 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-17T21:59:20.702594+00:00</t>
+          <t>2026-08-09T18:05:17.413411+00:00</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-08-18T16:35:34.317101+00:00</t>
+          <t>2026-08-11T13:49:59.470353+00:00</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-19T18:54:21.152731+00:00</t>
+          <t>2026-08-12T02:46:24.585075+00:00</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>18.6</v>
+        <v>43.75</v>
       </c>
       <c r="H174" t="n">
-        <v>26.31</v>
+        <v>12.94</v>
       </c>
       <c r="I174" t="n">
-        <v>44.92</v>
+        <v>56.69</v>
       </c>
       <c r="J174" t="b">
         <v>1</v>
@@ -10699,123 +10687,123 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PO-10257</t>
+          <t>PO-10260</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-09T18:05:17.413411+00:00</t>
+          <t>2026-09-23T18:32:18.130370+00:00</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-08-11T13:49:59.470353+00:00</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-08-12T02:46:24.585075+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-25T14:13:03.457590+00:00</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="n">
-        <v>43.75</v>
-      </c>
-      <c r="H175" t="n">
-        <v>12.94</v>
-      </c>
-      <c r="I175" t="n">
-        <v>56.69</v>
-      </c>
+        <v>43.68</v>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="b">
-        <v>1</v>
-      </c>
-      <c r="K175" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>112.55</v>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PO-10259</t>
+          <t>PO-10261</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-23T18:32:18.130370+00:00</t>
+          <t>2026-08-08T03:33:37.021387+00:00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-09-25T14:13:03.457590+00:00</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr"/>
+          <t>2026-08-08T13:08:16.709433+00:00</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:32:17.832025+00:00</t>
+        </is>
+      </c>
       <c r="G176" t="n">
-        <v>43.68</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
-      <c r="I176" t="inlineStr"/>
+        <v>9.58</v>
+      </c>
+      <c r="H176" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="I176" t="n">
+        <v>89.98</v>
+      </c>
       <c r="J176" t="b">
-        <v>0</v>
-      </c>
-      <c r="K176" t="n">
-        <v>88.54000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PO-10260</t>
+          <t>PO-10262</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10825,27 +10813,27 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-08T03:33:37.021387+00:00</t>
+          <t>2026-09-03T22:30:34.691904+00:00</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2026-08-08T13:08:16.709433+00:00</t>
+          <t>2026-09-06T01:28:48.457326+00:00</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-11T21:32:17.832025+00:00</t>
+          <t>2026-09-10T12:33:41.797459+00:00</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>9.58</v>
+        <v>50.97</v>
       </c>
       <c r="H177" t="n">
-        <v>80.40000000000001</v>
+        <v>107.08</v>
       </c>
       <c r="I177" t="n">
-        <v>89.98</v>
+        <v>158.05</v>
       </c>
       <c r="J177" t="b">
         <v>1</v>
@@ -10853,24 +10841,24 @@
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PO-10261</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10880,27 +10868,27 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-03T22:30:34.691904+00:00</t>
+          <t>2026-08-18T07:56:26.369659+00:00</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>2026-09-06T01:28:48.457326+00:00</t>
+          <t>2026-08-18T17:08:16.086784+00:00</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-09-10T12:33:41.797459+00:00</t>
+          <t>2026-08-22T18:51:14.269803+00:00</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>50.97</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H178" t="n">
-        <v>107.08</v>
+        <v>97.72</v>
       </c>
       <c r="I178" t="n">
-        <v>158.05</v>
+        <v>106.91</v>
       </c>
       <c r="J178" t="b">
         <v>1</v>
@@ -10908,12 +10896,12 @@
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -10925,82 +10913,76 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10262</t>
+          <t>PO-10264</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-18T07:56:26.369659+00:00</t>
+          <t>2026-09-22T19:10:26.859368+00:00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-08-18T17:08:16.086784+00:00</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-08-22T18:51:14.269803+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-23T17:38:35.868236+00:00</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H179" t="n">
-        <v>97.72</v>
-      </c>
-      <c r="I179" t="n">
-        <v>106.91</v>
-      </c>
+        <v>22.47</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="b">
-        <v>1</v>
-      </c>
-      <c r="K179" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>135.92</v>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10263</t>
+          <t>PO-10265</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-09-22T19:10:26.859368+00:00</t>
+          <t>2026-09-29T00:35:21.639230+00:00</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-09-23T17:38:35.868236+00:00</t>
+          <t>2026-09-29T21:51:15.180525+00:00</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>22.47</v>
+        <v>21.26</v>
       </c>
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
@@ -11008,7 +10990,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>111.9</v>
+        <v>-13.5</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -11017,48 +10999,54 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10264</t>
+          <t>PO-10267</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-09-29T00:35:21.639230+00:00</t>
+          <t>2026-09-03T12:36:02.731095+00:00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-09-29T21:51:15.180525+00:00</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>2026-09-03T19:15:17.331225+00:00</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-09-10T16:21:54.120140+00:00</t>
+        </is>
+      </c>
       <c r="G181" t="n">
-        <v>21.26</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
+        <v>6.65</v>
+      </c>
+      <c r="H181" t="n">
+        <v>165.11</v>
+      </c>
+      <c r="I181" t="n">
+        <v>171.76</v>
+      </c>
       <c r="J181" t="b">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-37.51</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -11066,7 +11054,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -11078,7 +11066,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10266</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11088,27 +11076,27 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-03T12:36:02.731095+00:00</t>
+          <t>2026-08-25T12:12:35.271945+00:00</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-09-03T19:15:17.331225+00:00</t>
+          <t>2026-08-27T11:39:51.731798+00:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-10T16:21:54.120140+00:00</t>
+          <t>2026-08-27T20:16:09.414588+00:00</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>6.65</v>
+        <v>47.45</v>
       </c>
       <c r="H182" t="n">
-        <v>165.11</v>
+        <v>8.6</v>
       </c>
       <c r="I182" t="n">
-        <v>171.76</v>
+        <v>56.06</v>
       </c>
       <c r="J182" t="b">
         <v>1</v>
@@ -11116,12 +11104,12 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -11133,7 +11121,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10267</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11143,27 +11131,27 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-25T12:12:35.271945+00:00</t>
+          <t>2026-08-31T04:02:57.860442+00:00</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>2026-08-27T11:39:51.731798+00:00</t>
+          <t>2026-08-31T22:00:30.459000+00:00</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-08-27T20:16:09.414588+00:00</t>
+          <t>2026-09-01T09:42:55.394632+00:00</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>47.45</v>
+        <v>17.96</v>
       </c>
       <c r="H183" t="n">
-        <v>8.6</v>
+        <v>11.71</v>
       </c>
       <c r="I183" t="n">
-        <v>56.06</v>
+        <v>29.67</v>
       </c>
       <c r="J183" t="b">
         <v>1</v>
@@ -11176,7 +11164,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11176,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10268</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11198,27 +11186,27 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-31T04:02:57.860442+00:00</t>
+          <t>2026-09-18T12:04:18.713259+00:00</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>2026-08-31T22:00:30.459000+00:00</t>
+          <t>2026-09-22T05:49:12.768068+00:00</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-09-01T09:42:55.394632+00:00</t>
+          <t>2026-09-23T06:06:14.836856+00:00</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>17.96</v>
+        <v>89.75</v>
       </c>
       <c r="H184" t="n">
-        <v>11.71</v>
+        <v>24.28</v>
       </c>
       <c r="I184" t="n">
-        <v>29.67</v>
+        <v>114.03</v>
       </c>
       <c r="J184" t="b">
         <v>1</v>
@@ -11226,24 +11214,24 @@
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10272</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11253,27 +11241,27 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-18T12:04:18.713259+00:00</t>
+          <t>2026-09-06T17:12:20.934224+00:00</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-09-22T05:49:12.768068+00:00</t>
+          <t>2026-09-07T07:56:37.908605+00:00</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-09-23T06:06:14.836856+00:00</t>
+          <t>2026-09-08T03:38:53.023462+00:00</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>89.75</v>
+        <v>14.74</v>
       </c>
       <c r="H185" t="n">
-        <v>24.28</v>
+        <v>19.7</v>
       </c>
       <c r="I185" t="n">
-        <v>114.03</v>
+        <v>34.44</v>
       </c>
       <c r="J185" t="b">
         <v>1</v>
@@ -11286,19 +11274,19 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10273</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11308,27 +11296,27 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-06T17:12:20.934224+00:00</t>
+          <t>2026-08-15T23:41:02.676112+00:00</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-09-07T07:56:37.908605+00:00</t>
+          <t>2026-08-16T20:08:49.725245+00:00</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-09-08T03:38:53.023462+00:00</t>
+          <t>2026-08-18T08:16:32.068979+00:00</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>14.74</v>
+        <v>20.46</v>
       </c>
       <c r="H186" t="n">
-        <v>19.7</v>
+        <v>36.13</v>
       </c>
       <c r="I186" t="n">
-        <v>34.44</v>
+        <v>56.59</v>
       </c>
       <c r="J186" t="b">
         <v>1</v>
@@ -11336,12 +11324,12 @@
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -11353,91 +11341,91 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10272</t>
+          <t>PO-10276</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-15T23:41:02.676112+00:00</t>
+          <t>2026-09-12T20:59:13.540087+00:00</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>2026-08-16T20:08:49.725245+00:00</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-08-18T08:16:32.068979+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-13T17:55:15.088442+00:00</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="n">
-        <v>20.46</v>
-      </c>
-      <c r="H187" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="I187" t="n">
-        <v>56.59</v>
-      </c>
+        <v>20.93</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="b">
-        <v>1</v>
-      </c>
-      <c r="K187" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>374.1</v>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10275</t>
+          <t>PO-10277</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-12T20:59:13.540087+00:00</t>
+          <t>2026-09-08T00:09:44.035795+00:00</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>2026-09-13T17:55:15.088442+00:00</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr"/>
+          <t>2026-09-08T23:03:00.981536+00:00</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-09-10T04:12:36.340253+00:00</t>
+        </is>
+      </c>
       <c r="G188" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
+        <v>22.89</v>
+      </c>
+      <c r="H188" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="I188" t="n">
+        <v>52.05</v>
+      </c>
       <c r="J188" t="b">
-        <v>0</v>
-      </c>
-      <c r="K188" t="n">
-        <v>350.09</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -11452,151 +11440,145 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10276</t>
+          <t>PO-10278</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-09-08T00:09:44.035795+00:00</t>
+          <t>2026-08-20T00:25:52.086837+00:00</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-09-08T23:03:00.981536+00:00</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-09-10T04:12:36.340253+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-21T09:06:53.967000+00:00</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="H189" t="n">
-        <v>29.16</v>
-      </c>
-      <c r="I189" t="n">
-        <v>52.05</v>
-      </c>
+        <v>32.68</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="b">
-        <v>1</v>
-      </c>
-      <c r="K189" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>946.66</v>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10277</t>
+          <t>PO-10281</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-20T00:25:52.086837+00:00</t>
+          <t>2026-09-20T23:05:10.882474+00:00</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-08-21T09:06:53.967000+00:00</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr"/>
+          <t>2026-09-22T11:59:46.336053+00:00</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-09-24T09:03:02.184439+00:00</t>
+        </is>
+      </c>
       <c r="G190" t="n">
-        <v>32.68</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
+        <v>36.91</v>
+      </c>
+      <c r="H190" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="I190" t="n">
+        <v>81.95999999999999</v>
+      </c>
       <c r="J190" t="b">
-        <v>0</v>
-      </c>
-      <c r="K190" t="n">
-        <v>922.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10280</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-20T23:05:10.882474+00:00</t>
+          <t>2026-09-24T22:44:53.213279+00:00</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-09-22T11:59:46.336053+00:00</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-09-24T09:03:02.184439+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-26T16:30:17.942003+00:00</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="n">
-        <v>36.91</v>
-      </c>
-      <c r="H191" t="n">
-        <v>45.05</v>
-      </c>
-      <c r="I191" t="n">
-        <v>81.95999999999999</v>
-      </c>
+        <v>41.76</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="b">
-        <v>1</v>
-      </c>
-      <c r="K191" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>84.34</v>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -11604,152 +11586,158 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10281</t>
+          <t>PO-10283</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-24T22:44:53.213279+00:00</t>
+          <t>2026-08-26T22:55:09.401426+00:00</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>2026-09-26T16:30:17.942003+00:00</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr"/>
+          <t>2026-08-27T09:04:04.664168+00:00</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-08-29T17:25:00.763910+00:00</t>
+        </is>
+      </c>
       <c r="G192" t="n">
-        <v>41.76</v>
-      </c>
-      <c r="H192" t="inlineStr"/>
-      <c r="I192" t="inlineStr"/>
+        <v>10.15</v>
+      </c>
+      <c r="H192" t="n">
+        <v>56.35</v>
+      </c>
+      <c r="I192" t="n">
+        <v>66.5</v>
+      </c>
       <c r="J192" t="b">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>60.33</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10282</t>
+          <t>PO-10284</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-26T22:55:09.401426+00:00</t>
+          <t>2026-09-07T06:15:49.653533+00:00</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>2026-08-27T09:04:04.664168+00:00</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-08-29T17:25:00.763910+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-08T09:22:41.674507+00:00</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="H193" t="n">
-        <v>56.35</v>
-      </c>
-      <c r="I193" t="n">
-        <v>66.5</v>
-      </c>
+        <v>27.11</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="b">
-        <v>1</v>
-      </c>
-      <c r="K193" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>508.83</v>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10283</t>
+          <t>PO-10287</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-07T06:15:49.653533+00:00</t>
+          <t>2026-09-13T23:00:55.903899+00:00</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>2026-09-08T09:22:41.674507+00:00</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr"/>
+          <t>2026-09-15T20:08:56.955145+00:00</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-09-19T05:00:43.467492+00:00</t>
+        </is>
+      </c>
       <c r="G194" t="n">
-        <v>27.11</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
-      <c r="I194" t="inlineStr"/>
+        <v>45.13</v>
+      </c>
+      <c r="H194" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="I194" t="n">
+        <v>126</v>
+      </c>
       <c r="J194" t="b">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>484.81</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -11769,7 +11757,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11779,27 +11767,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-13T23:00:55.903899+00:00</t>
+          <t>2026-08-28T01:03:53.349047+00:00</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>2026-09-15T20:08:56.955145+00:00</t>
+          <t>2026-08-30T00:34:39.200092+00:00</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>2026-09-19T05:00:43.467492+00:00</t>
+          <t>2026-08-31T08:55:59.015226+00:00</t>
         </is>
       </c>
       <c r="G195" t="n">
-        <v>45.13</v>
+        <v>47.51</v>
       </c>
       <c r="H195" t="n">
-        <v>80.86</v>
+        <v>32.36</v>
       </c>
       <c r="I195" t="n">
-        <v>126</v>
+        <v>79.87</v>
       </c>
       <c r="J195" t="b">
         <v>1</v>
@@ -11807,24 +11795,24 @@
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10287</t>
+          <t>PO-10291</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11834,27 +11822,27 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-28T01:03:53.349047+00:00</t>
+          <t>2026-09-05T17:59:26.540480+00:00</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>2026-08-30T00:34:39.200092+00:00</t>
+          <t>2026-09-07T06:20:31.552530+00:00</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-08-31T08:55:59.015226+00:00</t>
+          <t>2026-09-09T17:34:03.015319+00:00</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>47.51</v>
+        <v>36.35</v>
       </c>
       <c r="H196" t="n">
-        <v>32.36</v>
+        <v>59.23</v>
       </c>
       <c r="I196" t="n">
-        <v>79.87</v>
+        <v>95.58</v>
       </c>
       <c r="J196" t="b">
         <v>1</v>
@@ -11862,24 +11850,24 @@
       <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10290</t>
+          <t>PO-10292</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11889,27 +11877,27 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-05T17:59:26.540480+00:00</t>
+          <t>2026-09-18T17:45:33.256914+00:00</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-09-07T06:20:31.552530+00:00</t>
+          <t>2026-09-19T17:24:24.533869+00:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-09T17:34:03.015319+00:00</t>
+          <t>2026-09-19T23:33:04.258183+00:00</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>36.35</v>
+        <v>23.65</v>
       </c>
       <c r="H197" t="n">
-        <v>59.23</v>
+        <v>6.14</v>
       </c>
       <c r="I197" t="n">
-        <v>95.58</v>
+        <v>29.79</v>
       </c>
       <c r="J197" t="b">
         <v>1</v>
@@ -11922,7 +11910,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -11934,62 +11922,56 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10291</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-18T17:45:33.256914+00:00</t>
+          <t>2026-10-01T11:34:51.023903+00:00</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>2026-09-19T17:24:24.533869+00:00</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-09-19T23:33:04.258183+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-01T16:43:25.865531+00:00</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="H198" t="n">
-        <v>6.14</v>
-      </c>
-      <c r="I198" t="n">
-        <v>29.79</v>
-      </c>
+        <v>5.14</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="b">
-        <v>1</v>
-      </c>
-      <c r="K198" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>-72.48999999999999</v>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10292</t>
+          <t>PO-10295</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11999,27 +11981,27 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-19T11:34:51.023903+00:00</t>
+          <t>2026-09-08T14:24:26.070654+00:00</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>2026-09-19T16:43:25.865531+00:00</t>
+          <t>2026-09-10T11:25:25.411755+00:00</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-23T07:45:50.725155+00:00</t>
+          <t>2026-09-15T13:33:26.885812+00:00</t>
         </is>
       </c>
       <c r="G199" t="n">
-        <v>5.14</v>
+        <v>45.02</v>
       </c>
       <c r="H199" t="n">
-        <v>87.04000000000001</v>
+        <v>122.13</v>
       </c>
       <c r="I199" t="n">
-        <v>92.18000000000001</v>
+        <v>167.15</v>
       </c>
       <c r="J199" t="b">
         <v>1</v>
@@ -12032,19 +12014,19 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10294</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12054,27 +12036,27 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-09-08T14:24:26.070654+00:00</t>
+          <t>2026-08-13T15:50:44.177891+00:00</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>2026-09-10T11:25:25.411755+00:00</t>
+          <t>2026-08-14T10:59:10.299967+00:00</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-09-15T13:33:26.885812+00:00</t>
+          <t>2026-08-19T04:14:48.341133+00:00</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>45.02</v>
+        <v>19.14</v>
       </c>
       <c r="H200" t="n">
-        <v>122.13</v>
+        <v>113.26</v>
       </c>
       <c r="I200" t="n">
-        <v>167.15</v>
+        <v>132.4</v>
       </c>
       <c r="J200" t="b">
         <v>1</v>
@@ -12082,128 +12064,128 @@
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-13T15:50:44.177891+00:00</t>
+          <t>2026-09-15T06:45:49.198774+00:00</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>2026-08-14T10:59:10.299967+00:00</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-08-19T04:14:48.341133+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-17T15:07:14.288723+00:00</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="H201" t="n">
-        <v>113.26</v>
-      </c>
-      <c r="I201" t="n">
-        <v>132.4</v>
-      </c>
+        <v>56.36</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="b">
-        <v>1</v>
-      </c>
-      <c r="K201" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>316.33</v>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10296</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-09-15T06:45:49.198774+00:00</t>
+          <t>2026-08-08T05:04:23.455671+00:00</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>2026-09-17T15:07:14.288723+00:00</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr"/>
+          <t>2026-08-12T00:22:36.885749+00:00</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-08-14T01:26:22.878476+00:00</t>
+        </is>
+      </c>
       <c r="G202" t="n">
-        <v>56.36</v>
-      </c>
-      <c r="H202" t="inlineStr"/>
-      <c r="I202" t="inlineStr"/>
+        <v>91.3</v>
+      </c>
+      <c r="H202" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="I202" t="n">
+        <v>140.37</v>
+      </c>
       <c r="J202" t="b">
-        <v>0</v>
-      </c>
-      <c r="K202" t="n">
-        <v>292.31</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10299</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12213,27 +12195,27 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-08T05:04:23.455671+00:00</t>
+          <t>2026-08-19T18:55:45.655899+00:00</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>2026-08-12T00:22:36.885749+00:00</t>
+          <t>2026-08-20T02:26:16.255413+00:00</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-14T01:26:22.878476+00:00</t>
+          <t>2026-08-24T16:16:54.112517+00:00</t>
         </is>
       </c>
       <c r="G203" t="n">
-        <v>91.3</v>
+        <v>7.51</v>
       </c>
       <c r="H203" t="n">
-        <v>49.06</v>
+        <v>109.84</v>
       </c>
       <c r="I203" t="n">
-        <v>140.37</v>
+        <v>117.35</v>
       </c>
       <c r="J203" t="b">
         <v>1</v>
@@ -12246,19 +12228,19 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10298</t>
+          <t>PO-10300</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12268,27 +12250,27 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-19T18:55:45.655899+00:00</t>
+          <t>2026-08-09T20:51:37.537056+00:00</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-08-20T02:26:16.255413+00:00</t>
+          <t>2026-08-11T11:20:29.232670+00:00</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-24T16:16:54.112517+00:00</t>
+          <t>2026-08-15T08:40:26.809173+00:00</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>7.51</v>
+        <v>38.48</v>
       </c>
       <c r="H204" t="n">
-        <v>109.84</v>
+        <v>93.33</v>
       </c>
       <c r="I204" t="n">
-        <v>117.35</v>
+        <v>131.81</v>
       </c>
       <c r="J204" t="b">
         <v>1</v>
@@ -12301,7 +12283,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -12313,42 +12295,36 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10299</t>
+          <t>PO-10301</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-09T20:51:37.537056+00:00</t>
+          <t>2026-08-02T21:11:51.623800+00:00</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-08-11T11:20:29.232670+00:00</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-08-15T08:40:26.809173+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-04T15:23:38.012075+00:00</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="n">
-        <v>38.48</v>
-      </c>
-      <c r="H205" t="n">
-        <v>93.33</v>
-      </c>
-      <c r="I205" t="n">
-        <v>131.81</v>
-      </c>
+        <v>42.2</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="b">
-        <v>1</v>
-      </c>
-      <c r="K205" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>1357.89</v>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -12356,103 +12332,103 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S31</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10300</t>
+          <t>PO-10302</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-02T21:11:51.623800+00:00</t>
+          <t>2026-09-14T18:54:12.862542+00:00</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-08-04T15:23:38.012075+00:00</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
+          <t>2026-09-15T07:59:32.068592+00:00</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-09-18T03:47:33.625700+00:00</t>
+        </is>
+      </c>
       <c r="G206" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="H206" t="inlineStr"/>
-      <c r="I206" t="inlineStr"/>
+        <v>13.09</v>
+      </c>
+      <c r="H206" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="I206" t="n">
+        <v>80.89</v>
+      </c>
       <c r="J206" t="b">
-        <v>0</v>
-      </c>
-      <c r="K206" t="n">
-        <v>1333.88</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-S31</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-14T18:54:12.862542+00:00</t>
+          <t>2026-09-04T15:59:31.160800+00:00</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>2026-09-15T07:59:32.068592+00:00</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:47:33.625700+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-07T20:39:13.537141+00:00</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="H207" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="I207" t="n">
-        <v>80.89</v>
-      </c>
+        <v>76.66</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="b">
-        <v>1</v>
-      </c>
-      <c r="K207" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>571.1</v>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -12460,48 +12436,54 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-04T15:59:31.160800+00:00</t>
+          <t>2026-09-20T10:54:56.507681+00:00</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>2026-09-07T20:39:13.537141+00:00</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
+          <t>2026-09-21T17:25:30.100123+00:00</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>2026-09-23T01:33:09.789206+00:00</t>
+        </is>
+      </c>
       <c r="G208" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
+        <v>30.51</v>
+      </c>
+      <c r="H208" t="n">
+        <v>32.13</v>
+      </c>
+      <c r="I208" t="n">
+        <v>62.64</v>
+      </c>
       <c r="J208" t="b">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>547.08</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -12509,19 +12491,19 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10303</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12531,27 +12513,27 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-09-20T10:54:56.507681+00:00</t>
+          <t>2026-09-20T12:09:26.201300+00:00</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>2026-09-21T17:25:30.100123+00:00</t>
+          <t>2026-09-20T22:18:08.693377+00:00</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-09-23T01:33:09.789206+00:00</t>
+          <t>2026-09-22T05:44:58.706011+00:00</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>30.51</v>
+        <v>10.15</v>
       </c>
       <c r="H209" t="n">
-        <v>32.13</v>
+        <v>31.45</v>
       </c>
       <c r="I209" t="n">
-        <v>62.64</v>
+        <v>41.59</v>
       </c>
       <c r="J209" t="b">
         <v>1</v>
@@ -12571,12 +12553,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10307</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12586,27 +12568,27 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-09-20T12:09:26.201300+00:00</t>
+          <t>2026-08-07T15:41:41.244254+00:00</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>2026-09-20T22:18:08.693377+00:00</t>
+          <t>2026-08-08T10:11:25.105555+00:00</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-09-22T05:44:58.706011+00:00</t>
+          <t>2026-08-11T10:46:53.905290+00:00</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>10.15</v>
+        <v>18.5</v>
       </c>
       <c r="H210" t="n">
-        <v>31.45</v>
+        <v>72.59</v>
       </c>
       <c r="I210" t="n">
-        <v>41.59</v>
+        <v>91.09</v>
       </c>
       <c r="J210" t="b">
         <v>1</v>
@@ -12614,12 +12596,12 @@
       <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -12631,7 +12613,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10308</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12641,27 +12623,27 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-30T00:03:29.460707+00:00</t>
+          <t>2026-08-05T11:30:55.690167+00:00</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>2026-08-30T21:45:32.423588+00:00</t>
+          <t>2026-08-05T23:39:34.575856+00:00</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-09-02T19:22:06.061277+00:00</t>
+          <t>2026-08-07T18:00:54.405337+00:00</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>21.7</v>
+        <v>12.14</v>
       </c>
       <c r="H211" t="n">
-        <v>69.61</v>
+        <v>42.36</v>
       </c>
       <c r="I211" t="n">
-        <v>91.31</v>
+        <v>54.5</v>
       </c>
       <c r="J211" t="b">
         <v>1</v>
@@ -12674,19 +12656,19 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10307</t>
+          <t>PO-10309</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12696,27 +12678,27 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-09-11T07:03:25.339819+00:00</t>
+          <t>2026-08-21T08:29:45.098520+00:00</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>2026-09-12T06:45:44.608229+00:00</t>
+          <t>2026-08-23T12:58:22.822826+00:00</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-09-13T08:52:43.157843+00:00</t>
+          <t>2026-08-28T08:20:03.136109+00:00</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>23.71</v>
+        <v>52.48</v>
       </c>
       <c r="H212" t="n">
-        <v>26.12</v>
+        <v>115.36</v>
       </c>
       <c r="I212" t="n">
-        <v>49.82</v>
+        <v>167.84</v>
       </c>
       <c r="J212" t="b">
         <v>1</v>
@@ -12724,59 +12706,53 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10308</t>
+          <t>PO-10310</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-09-06T08:05:46.786895+00:00</t>
+          <t>2026-09-03T09:38:43.007658+00:00</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>2026-09-08T12:38:44.693138+00:00</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-09-12T10:25:47.357753+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-04T02:35:59.997228+00:00</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="n">
-        <v>52.55</v>
-      </c>
-      <c r="H213" t="n">
-        <v>93.78</v>
-      </c>
-      <c r="I213" t="n">
-        <v>146.33</v>
-      </c>
+        <v>16.95</v>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="b">
-        <v>1</v>
-      </c>
-      <c r="K213" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>601.4400000000001</v>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -12796,42 +12772,36 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10310</t>
+          <t>PO-10311</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-09-07T00:40:59.958147+00:00</t>
+          <t>2026-09-11T16:13:12.851086+00:00</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>2026-09-09T10:37:56.528387+00:00</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-09-14T11:19:31.622441+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-11T19:51:40.754828+00:00</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr"/>
       <c r="G214" t="n">
-        <v>57.95</v>
-      </c>
-      <c r="H214" t="n">
-        <v>120.69</v>
-      </c>
-      <c r="I214" t="n">
-        <v>178.64</v>
-      </c>
+        <v>3.64</v>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="b">
-        <v>1</v>
-      </c>
-      <c r="K214" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>402.87</v>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -12846,12 +12816,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10311</t>
+          <t>PO-10312</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12861,27 +12831,27 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-11T21:18:34.873685+00:00</t>
+          <t>2026-09-08T13:23:12.404731+00:00</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>2026-08-14T05:25:44.949397+00:00</t>
+          <t>2026-09-10T07:32:19.566100+00:00</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-16T06:46:03.418211+00:00</t>
+          <t>2026-09-13T06:05:11.258122+00:00</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>56.12</v>
+        <v>42.15</v>
       </c>
       <c r="H215" t="n">
-        <v>49.34</v>
+        <v>70.55</v>
       </c>
       <c r="I215" t="n">
-        <v>105.46</v>
+        <v>112.7</v>
       </c>
       <c r="J215" t="b">
         <v>1</v>
@@ -12889,12 +12859,12 @@
       <c r="K215" t="inlineStr"/>
       <c r="L215" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12876,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10312</t>
+          <t>PO-10313</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12916,27 +12886,27 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-29T18:56:30.652201+00:00</t>
+          <t>2026-09-13T15:15:54.110118+00:00</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>2026-08-31T08:43:52.875957+00:00</t>
+          <t>2026-09-15T12:45:51.757777+00:00</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>2026-09-01T20:50:20.409323+00:00</t>
+          <t>2026-09-17T15:12:22.682073+00:00</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>37.79</v>
+        <v>45.5</v>
       </c>
       <c r="H216" t="n">
-        <v>36.11</v>
+        <v>50.44</v>
       </c>
       <c r="I216" t="n">
-        <v>73.90000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="J216" t="b">
         <v>1</v>
@@ -12944,59 +12914,53 @@
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10313</t>
+          <t>PO-10314</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-09-08T19:10:12.277744+00:00</t>
+          <t>2026-09-17T10:06:07.444440+00:00</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>2026-09-10T22:43:26.231132+00:00</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-09-12T03:08:25.602385+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-17T20:41:30.698111+00:00</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="n">
-        <v>51.55</v>
-      </c>
-      <c r="H217" t="n">
-        <v>28.42</v>
-      </c>
-      <c r="I217" t="n">
-        <v>79.97</v>
-      </c>
+        <v>10.59</v>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="b">
-        <v>1</v>
-      </c>
-      <c r="K217" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>264.99</v>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -13004,56 +12968,62 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10315</t>
+          <t>PO-10316</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-10T05:44:28.945479+00:00</t>
+          <t>2026-09-12T16:53:42.233826+00:00</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>2026-08-13T04:08:48.892286+00:00</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
+          <t>2026-09-13T15:07:22.646282+00:00</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:49:55.338934+00:00</t>
+        </is>
+      </c>
       <c r="G218" t="n">
-        <v>70.41</v>
-      </c>
-      <c r="H218" t="inlineStr"/>
-      <c r="I218" t="inlineStr"/>
+        <v>22.23</v>
+      </c>
+      <c r="H218" t="n">
+        <v>69.70999999999999</v>
+      </c>
+      <c r="I218" t="n">
+        <v>91.94</v>
+      </c>
       <c r="J218" t="b">
-        <v>0</v>
-      </c>
-      <c r="K218" t="n">
-        <v>1157.34</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -13075,27 +13045,27 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-09-11T11:10:45.824379+00:00</t>
+          <t>2026-09-09T06:20:29.923191+00:00</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>2026-09-13T20:01:29.700233+00:00</t>
+          <t>2026-09-10T06:06:20.634294+00:00</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-09-16T04:45:34.716319+00:00</t>
+          <t>2026-09-12T13:57:39.782683+00:00</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>56.85</v>
+        <v>23.76</v>
       </c>
       <c r="H219" t="n">
-        <v>56.73</v>
+        <v>55.86</v>
       </c>
       <c r="I219" t="n">
-        <v>113.58</v>
+        <v>79.62</v>
       </c>
       <c r="J219" t="b">
         <v>1</v>
@@ -13115,7 +13085,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13130,27 +13100,27 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-06T10:00:20.627938+00:00</t>
+          <t>2026-09-23T15:11:44.784698+00:00</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>2026-08-07T10:08:31.226833+00:00</t>
+          <t>2026-09-24T18:47:37.780247+00:00</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-08-08T08:57:26.246015+00:00</t>
+          <t>2026-09-25T20:52:53.120905+00:00</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>24.14</v>
+        <v>27.6</v>
       </c>
       <c r="H220" t="n">
-        <v>22.82</v>
+        <v>26.09</v>
       </c>
       <c r="I220" t="n">
-        <v>46.95</v>
+        <v>53.69</v>
       </c>
       <c r="J220" t="b">
         <v>1</v>
@@ -13158,12 +13128,12 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13228,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>657.08</v>
+        <v>681.09</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -13307,7 +13277,7 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>207.33</v>
+        <v>231.34</v>
       </c>
       <c r="L223" t="inlineStr">
         <is>
@@ -13631,7 +13601,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>0.5600000000000001</v>
+        <v>24.57</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13680,7 +13650,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>1166.3</v>
+        <v>1190.32</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -13839,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>5.6</v>
+        <v>29.61</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -13888,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>134.5</v>
+        <v>158.52</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -13937,7 +13907,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>899.22</v>
+        <v>923.23</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -14041,7 +14011,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>760.09</v>
+        <v>784.1</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -14255,7 +14225,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>-8.949999999999999</v>
+        <v>15.07</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -14579,7 +14549,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>408.51</v>
+        <v>432.52</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -14683,7 +14653,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>887.55</v>
+        <v>911.5599999999999</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -14732,7 +14702,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>-19.31</v>
+        <v>4.7</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -15056,7 +15026,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>20.95</v>
+        <v>44.97</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -15270,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>-15.65</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -15319,7 +15289,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>259.68</v>
+        <v>283.69</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -15423,7 +15393,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>399.82</v>
+        <v>423.83</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -15472,7 +15442,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>-101.45</v>
+        <v>-77.44</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -15576,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>192.14</v>
+        <v>216.15</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -16285,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>1031.31</v>
+        <v>1055.32</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -16334,7 +16304,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>1262.56</v>
+        <v>1286.58</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -16383,7 +16353,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>338.48</v>
+        <v>362.49</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -16432,7 +16402,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>74.53</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16481,7 +16451,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>-83.40000000000001</v>
+        <v>-59.39</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -16530,7 +16500,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>818.12</v>
+        <v>842.13</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -16579,7 +16549,7 @@
         <v>0</v>
       </c>
       <c r="K285" t="n">
-        <v>500.69</v>
+        <v>524.7</v>
       </c>
       <c r="L285" t="inlineStr">
         <is>
@@ -17013,7 +16983,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>161.95</v>
+        <v>185.96</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -17392,7 +17362,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>880.3</v>
+        <v>904.3200000000001</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -17418,52 +17388,46 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-08-15T10:09:49.453505+00:00</t>
+          <t>2026-10-01T06:49:53.348731+00:00</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>2026-08-17T11:01:53.389584+00:00</t>
-        </is>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>2026-08-19T16:15:35.870099+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-01T20:39:00.854979+00:00</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
       <c r="G301" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="H301" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I301" t="n">
-        <v>102.1</v>
-      </c>
+        <v>13.82</v>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
       <c r="J301" t="b">
-        <v>1</v>
-      </c>
-      <c r="K301" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>-67.73999999999999</v>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -17478,27 +17442,27 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-08-24T04:06:07.742266+00:00</t>
+          <t>2026-09-06T16:06:57.072656+00:00</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-08-26T06:33:19.996636+00:00</t>
+          <t>2026-09-08T16:19:16.769036+00:00</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-08-29T11:42:28.519921+00:00</t>
+          <t>2026-09-11T08:39:03.002296+00:00</t>
         </is>
       </c>
       <c r="G302" t="n">
-        <v>50.45</v>
+        <v>48.21</v>
       </c>
       <c r="H302" t="n">
-        <v>77.15000000000001</v>
+        <v>64.33</v>
       </c>
       <c r="I302" t="n">
-        <v>127.61</v>
+        <v>112.53</v>
       </c>
       <c r="J302" t="b">
         <v>1</v>
@@ -17506,19 +17470,19 @@
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -17533,27 +17497,27 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-10T06:26:24.489716+00:00</t>
+          <t>2026-09-03T06:36:18.316516+00:00</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>2026-09-12T20:04:27.778683+00:00</t>
+          <t>2026-09-04T22:29:43.964341+00:00</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>2026-09-18T18:26:19.812144+00:00</t>
+          <t>2026-09-08T18:38:08.181120+00:00</t>
         </is>
       </c>
       <c r="G303" t="n">
-        <v>61.63</v>
+        <v>39.89</v>
       </c>
       <c r="H303" t="n">
-        <v>142.36</v>
+        <v>92.14</v>
       </c>
       <c r="I303" t="n">
-        <v>204</v>
+        <v>132.03</v>
       </c>
       <c r="J303" t="b">
         <v>1</v>
@@ -17566,7 +17530,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -17661,7 +17625,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="n">
-        <v>-25.48</v>
+        <v>-1.47</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -17765,7 +17729,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>-50.54</v>
+        <v>-26.53</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -17924,7 +17888,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>70.23</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -18028,7 +17992,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>7.53</v>
+        <v>31.55</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -18077,7 +18041,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>384.55</v>
+        <v>408.56</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -18181,7 +18145,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>451.09</v>
+        <v>475.1</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -18340,7 +18304,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>61.84</v>
+        <v>85.86</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -18554,7 +18518,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>809.8099999999999</v>
+        <v>833.8200000000001</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -18603,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>581.24</v>
+        <v>605.25</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -18817,7 +18781,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>388.5</v>
+        <v>412.51</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -19086,7 +19050,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>-37.11</v>
+        <v>-13.1</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -19410,7 +19374,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>110.83</v>
+        <v>134.84</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -19459,7 +19423,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>701.46</v>
+        <v>725.48</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -19838,7 +19802,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>919.0700000000001</v>
+        <v>943.08</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -19997,7 +19961,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>392.65</v>
+        <v>416.66</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -20046,7 +20010,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>-43.42</v>
+        <v>-19.4</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -20095,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>303.19</v>
+        <v>327.2</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -20364,7 +20328,7 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>35.73</v>
+        <v>59.74</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
@@ -20578,7 +20542,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1140.62</v>
+        <v>1164.64</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -20627,7 +20591,7 @@
         <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>406.5</v>
+        <v>430.52</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -21281,7 +21245,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>-113.16</v>
+        <v>-89.15000000000001</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -21417,7 +21381,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -21430,18 +21394,24 @@
           <t>2026-09-25T19:33:53.057830+00:00</t>
         </is>
       </c>
-      <c r="F376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-09-28T05:32:03.823527+00:00</t>
+        </is>
+      </c>
       <c r="G376" t="n">
         <v>18.72</v>
       </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
+      <c r="H376" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="I376" t="n">
+        <v>76.69</v>
+      </c>
       <c r="J376" t="b">
-        <v>0</v>
-      </c>
-      <c r="K376" t="n">
-        <v>58.23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -21654,7 +21624,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>-27.65</v>
+        <v>-3.64</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -21868,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>-26.11</v>
+        <v>-2.09</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -22027,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>28.88</v>
+        <v>52.89</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -22241,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>-22.51</v>
+        <v>1.51</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -22345,7 +22315,7 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
-        <v>984.78</v>
+        <v>1008.79</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -22394,7 +22364,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>14.62</v>
+        <v>38.63</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -22443,7 +22413,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>50.97</v>
+        <v>74.98</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -22712,7 +22682,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>8.6</v>
+        <v>32.61</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -22871,7 +22841,7 @@
         <v>0</v>
       </c>
       <c r="K403" t="n">
-        <v>65.81999999999999</v>
+        <v>89.84</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.5</v>
+        <v>96.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.6</v>
+        <v>59.7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.8</v>
+        <v>44.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>98.90000000000001</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="4">
@@ -708,19 +708,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>93.90000000000001</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="5">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>96.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="6">
@@ -775,16 +775,16 @@
         <v>60</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>86.7</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
         <v>13</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>83.8</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="8">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
         <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>77.59999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="10">
@@ -903,16 +903,16 @@
         <v>52</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>65.40000000000001</v>
+        <v>63.5</v>
       </c>
     </row>
     <row r="11">
@@ -999,16 +999,16 @@
         <v>63</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>58.7</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="14">
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E14" t="n">
         <v>23</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>40.4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -1060,13 +1060,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E16" t="n">
         <v>34</v>
       </c>
       <c r="F16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>40</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
         <v>34</v>
       </c>
       <c r="F17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E18" t="n">
         <v>16</v>
       </c>
       <c r="F18" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>20.3</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="20">
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" t="n">
         <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>25.3</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>27.4</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="22">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" t="n">
         <v>42</v>
       </c>
       <c r="F22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>75</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="23">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="24">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" t="n">
         <v>23</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>72</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="25">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F25" t="n">
         <v>23</v>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>65.2</v>
+        <v>65.7</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1007.41</v>
+        <v>1031.42</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1936,18 +1936,24 @@
           <t>2026-09-26T19:19:58.661191+00:00</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-09-30T04:41:34.485183+00:00</t>
+        </is>
+      </c>
       <c r="G10" t="n">
         <v>11.62</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>81.36</v>
+      </c>
+      <c r="I10" t="n">
+        <v>92.98</v>
+      </c>
       <c r="J10" t="b">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>75.38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -2270,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>-57.48</v>
+        <v>-33.48</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2429,7 +2435,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1367.37</v>
+        <v>1391.37</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2533,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>125.52</v>
+        <v>149.52</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2637,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>63.81</v>
+        <v>87.81</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2851,7 +2857,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>672.38</v>
+        <v>696.38</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3120,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>391.47</v>
+        <v>415.47</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3499,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>-47.19</v>
+        <v>-23.19</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -3658,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>2.7</v>
+        <v>26.71</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -3817,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>577.74</v>
+        <v>601.74</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3953,7 +3959,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3966,18 +3972,24 @@
           <t>2026-09-29T06:00:38.244553+00:00</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-29T13:24:52.901107+00:00</t>
+        </is>
+      </c>
       <c r="G48" t="n">
         <v>22.45</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I48" t="n">
+        <v>29.85</v>
+      </c>
       <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>27.53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -4025,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>238.69</v>
+        <v>262.69</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4486,117 +4498,105 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PO-10086</t>
+          <t>PO-10085</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-05T15:16:00.584150+00:00</t>
+          <t>2026-10-04T05:58:02.889374+00:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-07T09:44:43.975728+00:00</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-09-10T23:07:41.197096+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-05T23:40:22.639217+00:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>42.48</v>
-      </c>
-      <c r="H58" t="n">
-        <v>85.38</v>
-      </c>
-      <c r="I58" t="n">
-        <v>127.86</v>
-      </c>
+        <v>41.71</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="b">
-        <v>1</v>
-      </c>
-      <c r="K58" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-90.87</v>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PO-10087</t>
+          <t>PO-10086</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-16T18:41:43.526889+00:00</t>
+          <t>2026-08-16T01:48:49.607508+00:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-09-17T17:13:41.022775+00:00</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-09-19T13:04:37.448571+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-18T00:39:58.134919+00:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>22.53</v>
-      </c>
-      <c r="H59" t="n">
-        <v>43.85</v>
-      </c>
-      <c r="I59" t="n">
-        <v>66.38</v>
-      </c>
+        <v>46.85</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="b">
-        <v>1</v>
-      </c>
-      <c r="K59" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1089.29</v>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PO-10088</t>
+          <t>PO-10087</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4606,27 +4606,27 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-16T09:25:45.286317+00:00</t>
+          <t>2026-08-19T02:32:08.683213+00:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-17T08:45:33.688111+00:00</t>
+          <t>2026-08-21T05:04:20.685120+00:00</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-20T07:32:05.919956+00:00</t>
+          <t>2026-08-26T20:09:23.888586+00:00</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>23.33</v>
+        <v>50.54</v>
       </c>
       <c r="H60" t="n">
-        <v>70.78</v>
+        <v>135.08</v>
       </c>
       <c r="I60" t="n">
-        <v>94.11</v>
+        <v>185.62</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
@@ -4639,19 +4639,19 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PO-10089</t>
+          <t>PO-10088</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4661,27 +4661,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-20T23:16:20.036111+00:00</t>
+          <t>2026-09-08T09:47:35.914706+00:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-09-22T21:50:26.987760+00:00</t>
+          <t>2026-09-09T02:41:05.294001+00:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-23T20:24:23.953493+00:00</t>
+          <t>2026-09-10T07:03:14.485228+00:00</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>46.57</v>
+        <v>16.89</v>
       </c>
       <c r="H61" t="n">
-        <v>22.57</v>
+        <v>28.37</v>
       </c>
       <c r="I61" t="n">
-        <v>69.13</v>
+        <v>45.26</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
@@ -4694,19 +4694,19 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PO-10090</t>
+          <t>PO-10089</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4716,17 +4716,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-27T02:59:31.596707+00:00</t>
+          <t>2026-08-24T16:35:49.169048+00:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-28T13:51:12.988765+00:00</t>
+          <t>2026-08-27T18:01:48.064612+00:00</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>34.86</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>800.1</v>
+        <v>882.5</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PO-10092</t>
+          <t>PO-10091</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4783,7 +4783,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>1319.34</v>
+        <v>1343.35</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PO-10094</t>
+          <t>PO-10093</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PO-10097</t>
+          <t>PO-10096</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PO-10099</t>
+          <t>PO-10098</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4942,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>87.66</v>
+        <v>111.67</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PO-10100</t>
+          <t>PO-10099</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>41.28</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PO-10102</t>
+          <t>PO-10101</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PO-10104</t>
+          <t>PO-10103</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5095,7 +5095,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>75.81</v>
+        <v>99.81</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PO-10106</t>
+          <t>PO-10105</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5144,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>-18.41</v>
+        <v>5.6</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PO-10110</t>
+          <t>PO-10109</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5193,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>86.86</v>
+        <v>110.87</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PO-10114</t>
+          <t>PO-10113</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PO-10116</t>
+          <t>PO-10115</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5297,7 +5297,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>104.17</v>
+        <v>128.17</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PO-10117</t>
+          <t>PO-10116</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5346,7 +5346,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>44.94</v>
+        <v>68.95</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PO-10118</t>
+          <t>PO-10117</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PO-10119</t>
+          <t>PO-10118</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PO-10120</t>
+          <t>PO-10119</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PO-10122</t>
+          <t>PO-10121</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PO-10124</t>
+          <t>PO-10123</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>46.79</v>
+        <v>70.8</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PO-10125</t>
+          <t>PO-10124</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PO-10126</t>
+          <t>PO-10125</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PO-10128</t>
+          <t>PO-10127</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PO-10129</t>
+          <t>PO-10128</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PO-10130</t>
+          <t>PO-10129</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PO-10131</t>
+          <t>PO-10130</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5939,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>117.77</v>
+        <v>141.77</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PO-10132</t>
+          <t>PO-10131</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PO-10133</t>
+          <t>PO-10132</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PO-10134</t>
+          <t>PO-10133</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6125,7 +6125,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PO-10136</t>
+          <t>PO-10135</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PO-10137</t>
+          <t>PO-10136</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PO-10139</t>
+          <t>PO-10138</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PO-10141</t>
+          <t>PO-10140</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PO-10142</t>
+          <t>PO-10141</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PO-10143</t>
+          <t>PO-10142</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PO-10144</t>
+          <t>PO-10143</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PO-10145</t>
+          <t>PO-10144</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PO-10146</t>
+          <t>PO-10145</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PO-10149</t>
+          <t>PO-10148</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PO-10153</t>
+          <t>PO-10152</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6703,7 +6703,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>300.21</v>
+        <v>324.21</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PO-10154</t>
+          <t>PO-10153</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PO-10155</t>
+          <t>PO-10154</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>280.49</v>
+        <v>304.49</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PO-10156</t>
+          <t>PO-10155</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6856,7 +6856,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>37.22</v>
+        <v>61.22</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PO-10157</t>
+          <t>PO-10156</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PO-10158</t>
+          <t>PO-10157</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6960,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>-49.64</v>
+        <v>-25.64</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PO-10160</t>
+          <t>PO-10159</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PO-10161</t>
+          <t>PO-10160</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7064,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>343.63</v>
+        <v>367.63</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PO-10162</t>
+          <t>PO-10161</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7113,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>-1.13</v>
+        <v>22.87</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PO-10163</t>
+          <t>PO-10162</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PO-10164</t>
+          <t>PO-10163</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PO-10166</t>
+          <t>PO-10165</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PO-10167</t>
+          <t>PO-10166</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PO-10170</t>
+          <t>PO-10169</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PO-10172</t>
+          <t>PO-10171</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>631.95</v>
+        <v>655.95</v>
       </c>
       <c r="L113" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PO-10173</t>
+          <t>PO-10172</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PO-10174</t>
+          <t>PO-10173</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PO-10177</t>
+          <t>PO-10176</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PO-10179</t>
+          <t>PO-10178</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7678,7 +7678,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PO-10181</t>
+          <t>PO-10180</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PO-10183</t>
+          <t>PO-10182</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PO-10185</t>
+          <t>PO-10184</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PO-10187</t>
+          <t>PO-10186</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7871,7 +7871,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>-18.01</v>
+        <v>5.99</v>
       </c>
       <c r="L121" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PO-10188</t>
+          <t>PO-10187</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PO-10189</t>
+          <t>PO-10188</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PO-10190</t>
+          <t>PO-10189</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8057,7 +8057,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PO-10191</t>
+          <t>PO-10190</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PO-10193</t>
+          <t>PO-10192</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PO-10195</t>
+          <t>PO-10194</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PO-10196</t>
+          <t>PO-10195</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PO-10197</t>
+          <t>PO-10196</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PO-10200</t>
+          <t>PO-10199</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>-24.9</v>
+        <v>-0.89</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PO-10201</t>
+          <t>PO-10200</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PO-10204</t>
+          <t>PO-10203</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8464,7 +8464,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>336.25</v>
+        <v>360.25</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PO-10205</t>
+          <t>PO-10204</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PO-10207</t>
+          <t>PO-10206</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PO-10208</t>
+          <t>PO-10207</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8650,12 +8650,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PO-10209</t>
+          <t>PO-10208</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -8668,18 +8668,24 @@
           <t>2026-09-28T06:48:24.778857+00:00</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-30T03:20:59.337517+00:00</t>
+        </is>
+      </c>
       <c r="G136" t="n">
         <v>6.47</v>
       </c>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+      <c r="H136" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="I136" t="n">
+        <v>51.01</v>
+      </c>
       <c r="J136" t="b">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>34.76</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -8699,7 +8705,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PO-10211</t>
+          <t>PO-10210</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8754,7 +8760,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PO-10212</t>
+          <t>PO-10211</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8809,7 +8815,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PO-10213</t>
+          <t>PO-10212</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8864,7 +8870,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PO-10215</t>
+          <t>PO-10214</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8892,7 +8898,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>661.39</v>
+        <v>685.4</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8913,7 +8919,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PO-10218</t>
+          <t>PO-10217</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8941,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>366.91</v>
+        <v>390.91</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -8962,7 +8968,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PO-10219</t>
+          <t>PO-10218</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8990,7 +8996,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>1308.35</v>
+        <v>1332.35</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -9011,7 +9017,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PO-10221</t>
+          <t>PO-10220</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9066,7 +9072,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PO-10222</t>
+          <t>PO-10221</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9121,7 +9127,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PO-10224</t>
+          <t>PO-10223</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9176,7 +9182,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PO-10225</t>
+          <t>PO-10224</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9204,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>1023.19</v>
+        <v>1047.19</v>
       </c>
       <c r="L146" t="inlineStr">
         <is>
@@ -9225,7 +9231,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PO-10226</t>
+          <t>PO-10225</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9280,7 +9286,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PO-10227</t>
+          <t>PO-10226</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9335,7 +9341,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PO-10229</t>
+          <t>PO-10228</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9363,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>430.11</v>
+        <v>454.11</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9384,7 +9390,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PO-10232</t>
+          <t>PO-10231</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9412,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>438.94</v>
+        <v>462.95</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -9433,7 +9439,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PO-10233</t>
+          <t>PO-10232</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9461,7 +9467,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>54.06</v>
+        <v>78.06</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -9482,7 +9488,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PO-10234</t>
+          <t>PO-10233</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9537,7 +9543,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PO-10235</t>
+          <t>PO-10234</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9592,7 +9598,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PO-10236</t>
+          <t>PO-10235</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9647,7 +9653,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PO-10238</t>
+          <t>PO-10237</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9675,7 +9681,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>286.79</v>
+        <v>310.79</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -9696,7 +9702,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PO-10239</t>
+          <t>PO-10238</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9751,7 +9757,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PO-10240</t>
+          <t>PO-10239</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9806,7 +9812,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PO-10241</t>
+          <t>PO-10240</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9861,7 +9867,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PO-10243</t>
+          <t>PO-10242</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9916,7 +9922,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PO-10244</t>
+          <t>PO-10243</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9971,7 +9977,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PO-10245</t>
+          <t>PO-10244</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10026,7 +10032,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PO-10246</t>
+          <t>PO-10245</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10081,7 +10087,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PO-10247</t>
+          <t>PO-10246</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10136,7 +10142,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PO-10248</t>
+          <t>PO-10247</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10191,7 +10197,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PO-10251</t>
+          <t>PO-10250</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10246,7 +10252,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PO-10252</t>
+          <t>PO-10251</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10274,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>9.02</v>
+        <v>33.03</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -10295,7 +10301,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PO-10254</t>
+          <t>PO-10253</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10350,7 +10356,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PO-10255</t>
+          <t>PO-10254</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10405,7 +10411,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PO-10256</t>
+          <t>PO-10255</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10460,62 +10466,56 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PO-10257</t>
+          <t>PO-10256</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-10T02:24:14.327452+00:00</t>
+          <t>2026-10-03T16:28:20.080805+00:00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-08-11T10:16:57.206854+00:00</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-08-14T01:30:22.810576+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-04T10:36:31.118640+00:00</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="H170" t="n">
-        <v>63.22</v>
-      </c>
-      <c r="I170" t="n">
-        <v>95.09999999999999</v>
-      </c>
+        <v>18.14</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="b">
-        <v>1</v>
-      </c>
-      <c r="K170" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>-77.37</v>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PO-10258</t>
+          <t>PO-10257</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10525,27 +10525,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-10T22:47:52.441820+00:00</t>
+          <t>2026-08-11T04:14:41.794218+00:00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-08-11T23:03:39.820856+00:00</t>
+          <t>2026-08-13T00:04:47.621390+00:00</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-12T04:39:19.461092+00:00</t>
+          <t>2026-08-13T14:00:45.597910+00:00</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>24.26</v>
+        <v>43.83</v>
       </c>
       <c r="H171" t="n">
-        <v>5.59</v>
+        <v>13.93</v>
       </c>
       <c r="I171" t="n">
-        <v>29.86</v>
+        <v>57.77</v>
       </c>
       <c r="J171" t="b">
         <v>1</v>
@@ -10565,12 +10565,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PO-10259</t>
+          <t>PO-10258</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10580,27 +10580,27 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-17T21:59:20.702594+00:00</t>
+          <t>2026-08-05T06:43:59.548298+00:00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-08-18T16:35:34.317101+00:00</t>
+          <t>2026-08-06T08:05:44.861286+00:00</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-19T18:54:21.152731+00:00</t>
+          <t>2026-08-07T19:58:06.217017+00:00</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>18.6</v>
+        <v>25.36</v>
       </c>
       <c r="H172" t="n">
-        <v>26.31</v>
+        <v>35.87</v>
       </c>
       <c r="I172" t="n">
-        <v>44.92</v>
+        <v>61.24</v>
       </c>
       <c r="J172" t="b">
         <v>1</v>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PO-10260</t>
+          <t>PO-10259</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PO-10262</t>
+          <t>PO-10261</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10698,18 +10698,24 @@
           <t>2026-09-25T14:13:03.457590+00:00</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-09-29T20:52:27.398560+00:00</t>
+        </is>
+      </c>
       <c r="G174" t="n">
         <v>43.68</v>
       </c>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
+      <c r="H174" t="n">
+        <v>102.66</v>
+      </c>
+      <c r="I174" t="n">
+        <v>146.34</v>
+      </c>
       <c r="J174" t="b">
-        <v>0</v>
-      </c>
-      <c r="K174" t="n">
-        <v>136.56</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -10729,7 +10735,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PO-10263</t>
+          <t>PO-10262</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10784,7 +10790,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PO-10264</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10839,7 +10845,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PO-10265</t>
+          <t>PO-10264</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10894,7 +10900,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PO-10266</t>
+          <t>PO-10265</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10922,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="K178" t="n">
-        <v>159.92</v>
+        <v>183.92</v>
       </c>
       <c r="L178" t="inlineStr">
         <is>
@@ -10943,7 +10949,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10267</t>
+          <t>PO-10266</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10971,7 +10977,7 @@
         <v>0</v>
       </c>
       <c r="K179" t="n">
-        <v>10.51</v>
+        <v>34.51</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -10992,7 +10998,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11047,7 +11053,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10270</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11102,7 +11108,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11157,7 +11163,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10272</t>
+          <t>PO-10271</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11212,7 +11218,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10274</t>
+          <t>PO-10273</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11267,7 +11273,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10275</t>
+          <t>PO-10274</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11322,7 +11328,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10278</t>
+          <t>PO-10277</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11350,7 +11356,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>398.11</v>
+        <v>422.11</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11371,7 +11377,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10279</t>
+          <t>PO-10278</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11426,7 +11432,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10280</t>
+          <t>PO-10279</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11454,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>970.66</v>
+        <v>994.67</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11475,7 +11481,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10283</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11530,7 +11536,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10284</t>
+          <t>PO-10283</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11558,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>-83.65000000000001</v>
+        <v>-59.65</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -11579,7 +11585,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10285</t>
+          <t>PO-10284</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11634,7 +11640,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10285</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11662,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>532.83</v>
+        <v>556.84</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11683,7 +11689,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10289</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11738,7 +11744,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10290</t>
+          <t>PO-10289</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11793,7 +11799,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10293</t>
+          <t>PO-10292</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11848,7 +11854,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10294</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11903,7 +11909,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10294</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11931,7 +11937,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-48.49</v>
+        <v>-24.48</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -11952,7 +11958,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12007,7 +12013,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10298</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12062,7 +12068,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10299</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12090,7 +12096,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>340.33</v>
+        <v>364.34</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -12111,7 +12117,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10300</t>
+          <t>PO-10299</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12166,7 +12172,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10300</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12221,7 +12227,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10301</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12276,7 +12282,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10303</t>
+          <t>PO-10302</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12304,7 +12310,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>1381.9</v>
+        <v>1405.9</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -12325,7 +12331,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12380,7 +12386,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10305</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12408,7 +12414,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>595.1</v>
+        <v>619.11</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -12429,7 +12435,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12484,7 +12490,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10307</t>
+          <t>PO-10306</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12539,7 +12545,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10309</t>
+          <t>PO-10308</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12594,7 +12600,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10310</t>
+          <t>PO-10309</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12649,7 +12655,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10311</t>
+          <t>PO-10310</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12704,7 +12710,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10312</t>
+          <t>PO-10311</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12732,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>625.45</v>
+        <v>649.45</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -12753,7 +12759,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10313</t>
+          <t>PO-10312</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12781,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="K213" t="n">
-        <v>426.88</v>
+        <v>450.88</v>
       </c>
       <c r="L213" t="inlineStr">
         <is>
@@ -12802,7 +12808,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10314</t>
+          <t>PO-10313</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12857,7 +12863,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10315</t>
+          <t>PO-10314</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12912,7 +12918,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10316</t>
+          <t>PO-10315</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12940,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
-        <v>288.99</v>
+        <v>313</v>
       </c>
       <c r="L216" t="inlineStr">
         <is>
@@ -12961,7 +12967,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10318</t>
+          <t>PO-10317</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13016,7 +13022,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10319</t>
+          <t>PO-10318</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13071,7 +13077,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PO-10320</t>
+          <t>PO-10319</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13126,7 +13132,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PO-10321</t>
+          <t>PO-10320</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13181,7 +13187,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PO-10322</t>
+          <t>PO-10321</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13209,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>705.1</v>
+        <v>729.1</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -13230,7 +13236,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PO-10324</t>
+          <t>PO-10323</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13258,7 +13264,7 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>255.35</v>
+        <v>279.35</v>
       </c>
       <c r="L222" t="inlineStr">
         <is>
@@ -13279,7 +13285,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PO-10326</t>
+          <t>PO-10325</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13334,7 +13340,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PO-10327</t>
+          <t>PO-10326</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13389,7 +13395,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PO-10328</t>
+          <t>PO-10327</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13444,7 +13450,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PO-10329</t>
+          <t>PO-10328</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13499,7 +13505,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PO-10332</t>
+          <t>PO-10331</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13554,7 +13560,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PO-10333</t>
+          <t>PO-10332</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13582,7 +13588,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>48.58</v>
+        <v>72.58</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -13603,7 +13609,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PO-10334</t>
+          <t>PO-10333</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13631,7 +13637,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>1214.32</v>
+        <v>1238.33</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13652,7 +13658,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PO-10335</t>
+          <t>PO-10334</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13707,7 +13713,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PO-10337</t>
+          <t>PO-10336</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13762,7 +13768,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PO-10339</t>
+          <t>PO-10338</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13817,7 +13823,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PO-10341</t>
+          <t>PO-10340</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13845,7 +13851,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>182.52</v>
+        <v>206.53</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -13866,7 +13872,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PO-10343</t>
+          <t>PO-10342</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13894,7 +13900,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>947.24</v>
+        <v>971.24</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -13915,7 +13921,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PO-10344</t>
+          <t>PO-10343</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13970,7 +13976,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PO-10345</t>
+          <t>PO-10344</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -13998,7 +14004,7 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>808.11</v>
+        <v>832.11</v>
       </c>
       <c r="L236" t="inlineStr">
         <is>
@@ -14019,7 +14025,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PO-10346</t>
+          <t>PO-10345</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14074,7 +14080,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PO-10348</t>
+          <t>PO-10347</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14129,7 +14135,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PO-10349</t>
+          <t>PO-10348</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14184,7 +14190,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PO-10350</t>
+          <t>PO-10349</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14212,7 +14218,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>39.07</v>
+        <v>63.08</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -14233,7 +14239,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PO-10353</t>
+          <t>PO-10352</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14288,7 +14294,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PO-10354</t>
+          <t>PO-10353</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14343,7 +14349,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PO-10355</t>
+          <t>PO-10354</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14398,7 +14404,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PO-10357</t>
+          <t>PO-10356</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14453,7 +14459,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PO-10358</t>
+          <t>PO-10357</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14508,7 +14514,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PO-10359</t>
+          <t>PO-10358</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14536,7 +14542,7 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>456.53</v>
+        <v>480.53</v>
       </c>
       <c r="L246" t="inlineStr">
         <is>
@@ -14557,7 +14563,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PO-10360</t>
+          <t>PO-10359</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14612,7 +14618,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PO-10363</t>
+          <t>PO-10362</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14640,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>935.5700000000001</v>
+        <v>959.5700000000001</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -14661,7 +14667,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PO-10364</t>
+          <t>PO-10363</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14689,7 +14695,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>28.71</v>
+        <v>52.71</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -14710,7 +14716,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PO-10368</t>
+          <t>PO-10367</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14765,7 +14771,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PO-10370</t>
+          <t>PO-10369</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14820,7 +14826,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PO-10371</t>
+          <t>PO-10370</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14875,7 +14881,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PO-10372</t>
+          <t>PO-10371</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14930,7 +14936,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PO-10373</t>
+          <t>PO-10372</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14985,12 +14991,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PO-10375</t>
+          <t>PO-10374</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15003,18 +15009,24 @@
           <t>2026-09-27T17:38:35.325044+00:00</t>
         </is>
       </c>
-      <c r="F255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-09-30T01:59:15.299902+00:00</t>
+        </is>
+      </c>
       <c r="G255" t="n">
         <v>27.52</v>
       </c>
-      <c r="H255" t="inlineStr"/>
-      <c r="I255" t="inlineStr"/>
+      <c r="H255" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="I255" t="n">
+        <v>83.87</v>
+      </c>
       <c r="J255" t="b">
-        <v>0</v>
-      </c>
-      <c r="K255" t="n">
-        <v>68.97</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -15034,7 +15046,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PO-10376</t>
+          <t>PO-10375</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15089,7 +15101,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PO-10377</t>
+          <t>PO-10376</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15144,7 +15156,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PO-10378</t>
+          <t>PO-10377</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15199,7 +15211,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PO-10382</t>
+          <t>PO-10381</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15227,7 +15239,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>32.37</v>
+        <v>56.37</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -15248,7 +15260,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PO-10383</t>
+          <t>PO-10382</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15276,7 +15288,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>307.7</v>
+        <v>331.7</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -15297,7 +15309,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PO-10384</t>
+          <t>PO-10383</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15352,7 +15364,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PO-10386</t>
+          <t>PO-10385</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15407,7 +15419,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PO-10387</t>
+          <t>PO-10386</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15462,12 +15474,12 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PO-10388</t>
+          <t>PO-10387</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -15480,18 +15492,24 @@
           <t>2026-09-29T07:36:19.341850+00:00</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-09-30T08:05:31.389980+00:00</t>
+        </is>
+      </c>
       <c r="G264" t="n">
         <v>28.81</v>
       </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
+      <c r="H264" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="I264" t="n">
+        <v>53.3</v>
+      </c>
       <c r="J264" t="b">
-        <v>0</v>
-      </c>
-      <c r="K264" t="n">
-        <v>32.3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -15511,7 +15529,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PO-10389</t>
+          <t>PO-10388</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15566,7 +15584,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PO-10391</t>
+          <t>PO-10390</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15621,7 +15639,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PO-10392</t>
+          <t>PO-10391</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15676,7 +15694,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PO-10393</t>
+          <t>PO-10392</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15731,7 +15749,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PO-10395</t>
+          <t>PO-10394</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15786,7 +15804,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PO-10396</t>
+          <t>PO-10395</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15841,7 +15859,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PO-10397</t>
+          <t>PO-10396</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15896,7 +15914,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PO-10398</t>
+          <t>PO-10397</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15951,7 +15969,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PO-10400</t>
+          <t>PO-10399</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -16006,7 +16024,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PO-10401</t>
+          <t>PO-10400</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16061,7 +16079,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PO-10405</t>
+          <t>PO-10404</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16116,7 +16134,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PO-10407</t>
+          <t>PO-10406</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16171,7 +16189,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PO-10408</t>
+          <t>PO-10407</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16226,7 +16244,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PO-10409</t>
+          <t>PO-10408</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16254,7 +16272,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>1079.33</v>
+        <v>1103.33</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -16275,7 +16293,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PO-10410</t>
+          <t>PO-10409</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16303,7 +16321,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>1310.58</v>
+        <v>1334.59</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -16324,7 +16342,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PO-10413</t>
+          <t>PO-10412</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16352,7 +16370,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>386.5</v>
+        <v>410.5</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -16373,7 +16391,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PO-10414</t>
+          <t>PO-10413</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16401,7 +16419,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>122.55</v>
+        <v>146.55</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -16422,7 +16440,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PO-10416</t>
+          <t>PO-10415</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16450,7 +16468,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>-35.38</v>
+        <v>-11.38</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16471,7 +16489,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PO-10417</t>
+          <t>PO-10416</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16499,7 +16517,7 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>866.13</v>
+        <v>890.14</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
@@ -16520,7 +16538,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PO-10418</t>
+          <t>PO-10417</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16548,7 +16566,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>548.71</v>
+        <v>572.71</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -16569,7 +16587,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PO-10419</t>
+          <t>PO-10418</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16624,7 +16642,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PO-10420</t>
+          <t>PO-10419</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16679,50 +16697,44 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PO-10421</t>
+          <t>PO-10420</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-17T04:41:54.836285+00:00</t>
+          <t>2026-10-03T00:03:38.395046+00:00</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2026-08-17T21:28:42.932075+00:00</t>
-        </is>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>2026-08-20T00:28:11.368019+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-04T11:23:21.831393+00:00</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
       <c r="G287" t="n">
-        <v>16.78</v>
-      </c>
-      <c r="H287" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="I287" t="n">
-        <v>67.77</v>
-      </c>
+        <v>35.33</v>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
       <c r="J287" t="b">
-        <v>1</v>
-      </c>
-      <c r="K287" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>-60.96</v>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16746,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PO-10423</t>
+          <t>PO-10422</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16789,7 +16801,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PO-10424</t>
+          <t>PO-10423</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16844,7 +16856,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PO-10425</t>
+          <t>PO-10424</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16899,7 +16911,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PO-10431</t>
+          <t>PO-10430</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16954,7 +16966,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PO-10432</t>
+          <t>PO-10431</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16982,7 +16994,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>209.97</v>
+        <v>233.97</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -17003,7 +17015,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PO-10433</t>
+          <t>PO-10432</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17058,50 +17070,44 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PO-10434</t>
+          <t>PO-10433</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-14T05:42:50.463914+00:00</t>
+          <t>2026-10-02T04:42:50.463914+00:00</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>2026-08-17T01:05:39.178979+00:00</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>2026-08-17T23:47:34.718227+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-05T00:05:39.178979+00:00</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
       <c r="G294" t="n">
         <v>67.38</v>
       </c>
-      <c r="H294" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="I294" t="n">
-        <v>90.08</v>
-      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
       <c r="J294" t="b">
-        <v>1</v>
-      </c>
-      <c r="K294" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>-41.62</v>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17119,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PO-10436</t>
+          <t>PO-10435</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17168,7 +17174,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PO-10437</t>
+          <t>PO-10436</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17223,7 +17229,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PO-10440</t>
+          <t>PO-10439</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17278,7 +17284,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PO-10441</t>
+          <t>PO-10440</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17333,7 +17339,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PO-10443</t>
+          <t>PO-10442</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17361,7 +17367,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>928.3200000000001</v>
+        <v>952.33</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -17382,7 +17388,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PO-10444</t>
+          <t>PO-10443</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17410,7 +17416,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>-43.74</v>
+        <v>-19.73</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -17431,7 +17437,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PO-10445</t>
+          <t>PO-10444</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17486,7 +17492,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PO-10446</t>
+          <t>PO-10445</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17541,7 +17547,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PO-10447</t>
+          <t>PO-10446</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17596,7 +17602,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PO-10448</t>
+          <t>PO-10447</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17624,7 +17630,7 @@
         <v>0</v>
       </c>
       <c r="K304" t="n">
-        <v>22.54</v>
+        <v>46.54</v>
       </c>
       <c r="L304" t="inlineStr">
         <is>
@@ -17645,7 +17651,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PO-10452</t>
+          <t>PO-10451</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17700,7 +17706,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PO-10453</t>
+          <t>PO-10452</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17728,7 +17734,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>-2.52</v>
+        <v>21.48</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -17749,7 +17755,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PO-10454</t>
+          <t>PO-10453</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17804,7 +17810,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PO-10455</t>
+          <t>PO-10454</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17859,7 +17865,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PO-10456</t>
+          <t>PO-10455</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17914,7 +17920,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PO-10458</t>
+          <t>PO-10457</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17969,7 +17975,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PO-10459</t>
+          <t>PO-10458</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -17997,7 +18003,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>55.55</v>
+        <v>79.56</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -18018,7 +18024,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PO-10461</t>
+          <t>PO-10460</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18046,7 +18052,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>432.56</v>
+        <v>456.57</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -18067,7 +18073,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PO-10465</t>
+          <t>PO-10464</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18122,7 +18128,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PO-10467</t>
+          <t>PO-10466</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18150,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>499.11</v>
+        <v>523.11</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -18171,7 +18177,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10468</t>
+          <t>PO-10467</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18226,7 +18232,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10469</t>
+          <t>PO-10468</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18281,12 +18287,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10470</t>
+          <t>PO-10469</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -18299,18 +18305,24 @@
           <t>2026-09-26T17:22:59.188461+00:00</t>
         </is>
       </c>
-      <c r="F317" t="inlineStr"/>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:53:18.250947+00:00</t>
+        </is>
+      </c>
       <c r="G317" t="n">
         <v>44.15</v>
       </c>
-      <c r="H317" t="inlineStr"/>
-      <c r="I317" t="inlineStr"/>
+      <c r="H317" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I317" t="n">
+        <v>113.65</v>
+      </c>
       <c r="J317" t="b">
-        <v>0</v>
-      </c>
-      <c r="K317" t="n">
-        <v>109.86</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -18330,7 +18342,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10471</t>
+          <t>PO-10470</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18385,7 +18397,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10472</t>
+          <t>PO-10471</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18440,7 +18452,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10473</t>
+          <t>PO-10472</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18495,7 +18507,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10474</t>
+          <t>PO-10473</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18523,7 +18535,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="n">
-        <v>857.83</v>
+        <v>881.83</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -18544,7 +18556,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10475</t>
+          <t>PO-10474</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18572,7 +18584,7 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>629.26</v>
+        <v>653.26</v>
       </c>
       <c r="L322" t="inlineStr">
         <is>
@@ -18593,7 +18605,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10476</t>
+          <t>PO-10475</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18648,7 +18660,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10477</t>
+          <t>PO-10476</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18703,7 +18715,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10477</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18758,7 +18770,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10479</t>
+          <t>PO-10478</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18786,7 +18798,7 @@
         <v>0</v>
       </c>
       <c r="K326" t="n">
-        <v>436.52</v>
+        <v>460.52</v>
       </c>
       <c r="L326" t="inlineStr">
         <is>
@@ -18807,7 +18819,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10482</t>
+          <t>PO-10481</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -18862,7 +18874,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10483</t>
+          <t>PO-10482</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18917,7 +18929,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10485</t>
+          <t>PO-10484</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18972,7 +18984,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10486</t>
+          <t>PO-10485</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19027,12 +19039,12 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PO-10487</t>
+          <t>PO-10486</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -19045,18 +19057,24 @@
           <t>2026-09-29T13:18:28.144176+00:00</t>
         </is>
       </c>
-      <c r="F331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2026-09-29T21:47:37.635505+00:00</t>
+        </is>
+      </c>
       <c r="G331" t="n">
         <v>13.12</v>
       </c>
-      <c r="H331" t="inlineStr"/>
-      <c r="I331" t="inlineStr"/>
+      <c r="H331" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="I331" t="n">
+        <v>21.61</v>
+      </c>
       <c r="J331" t="b">
-        <v>0</v>
-      </c>
-      <c r="K331" t="n">
-        <v>10.91</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -19076,7 +19094,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PO-10489</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19131,7 +19149,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PO-10490</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19186,7 +19204,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10492</t>
+          <t>PO-10491</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19241,7 +19259,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10493</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19296,7 +19314,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10496</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19351,7 +19369,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10497</t>
+          <t>PO-10496</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19379,7 +19397,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>158.85</v>
+        <v>182.85</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -19400,7 +19418,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10498</t>
+          <t>PO-10497</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19428,7 +19446,7 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>749.48</v>
+        <v>773.49</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -19449,7 +19467,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10501</t>
+          <t>PO-10500</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19504,7 +19522,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10502</t>
+          <t>PO-10501</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19559,7 +19577,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10503</t>
+          <t>PO-10502</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19614,7 +19632,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10504</t>
+          <t>PO-10503</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19669,7 +19687,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10505</t>
+          <t>PO-10504</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19724,7 +19742,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10506</t>
+          <t>PO-10505</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19779,7 +19797,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10508</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19807,7 +19825,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>967.09</v>
+        <v>991.09</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -19828,7 +19846,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10509</t>
+          <t>PO-10508</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19883,7 +19901,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10513</t>
+          <t>PO-10512</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19938,7 +19956,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10514</t>
+          <t>PO-10513</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19966,7 +19984,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>440.67</v>
+        <v>464.67</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -19987,7 +20005,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10516</t>
+          <t>PO-10515</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20015,7 +20033,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>4.6</v>
+        <v>28.61</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -20036,7 +20054,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10517</t>
+          <t>PO-10516</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20064,7 +20082,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>351.2</v>
+        <v>375.21</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -20085,7 +20103,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10517</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20140,7 +20158,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10519</t>
+          <t>PO-10518</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20195,7 +20213,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10520</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20250,7 +20268,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20305,7 +20323,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10525</t>
+          <t>PO-10524</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20333,7 +20351,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>83.75</v>
+        <v>107.75</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -20354,7 +20372,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10528</t>
+          <t>PO-10527</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20409,7 +20427,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10528</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20464,7 +20482,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10530</t>
+          <t>PO-10529</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20519,7 +20537,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10531</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20547,7 +20565,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>1188.64</v>
+        <v>1212.65</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -20568,7 +20586,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10532</t>
+          <t>PO-10531</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20596,7 +20614,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>454.52</v>
+        <v>478.52</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -20617,7 +20635,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10533</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20672,7 +20690,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10537</t>
+          <t>PO-10536</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -20727,7 +20745,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10538</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -20782,7 +20800,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10540</t>
+          <t>PO-10539</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20837,7 +20855,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20865,7 +20883,7 @@
         <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>-39.22</v>
+        <v>-15.21</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
@@ -20886,7 +20904,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10542</t>
+          <t>PO-10541</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20941,7 +20959,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10543</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20969,7 +20987,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>54.03</v>
+        <v>78.03</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -20990,7 +21008,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10544</t>
+          <t>PO-10543</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21018,7 +21036,7 @@
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>54.48</v>
+        <v>78.48</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -21039,7 +21057,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10545</t>
+          <t>PO-10544</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21067,7 +21085,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>-86.91</v>
+        <v>-62.91</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -21088,7 +21106,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10546</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21116,7 +21134,7 @@
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>1026.92</v>
+        <v>1050.92</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -21137,7 +21155,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10546</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21192,7 +21210,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10548</t>
+          <t>PO-10547</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21247,7 +21265,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10550</t>
+          <t>PO-10549</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21275,7 +21293,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>-65.14</v>
+        <v>-41.14</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -21296,7 +21314,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10554</t>
+          <t>PO-10553</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21351,7 +21369,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10555</t>
+          <t>PO-10554</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21406,7 +21424,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10557</t>
+          <t>PO-10556</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21461,7 +21479,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10559</t>
+          <t>PO-10558</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21516,7 +21534,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10560</t>
+          <t>PO-10559</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21571,7 +21589,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10561</t>
+          <t>PO-10560</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21626,7 +21644,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10562</t>
+          <t>PO-10561</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21654,7 +21672,7 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
-        <v>20.37</v>
+        <v>44.37</v>
       </c>
       <c r="L380" t="inlineStr">
         <is>
@@ -21675,7 +21693,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10563</t>
+          <t>PO-10562</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21730,7 +21748,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10564</t>
+          <t>PO-10563</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21785,7 +21803,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10565</t>
+          <t>PO-10564</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21840,7 +21858,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10567</t>
+          <t>PO-10566</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -21868,7 +21886,7 @@
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>21.91</v>
+        <v>45.91</v>
       </c>
       <c r="L384" t="inlineStr">
         <is>
@@ -21889,7 +21907,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10568</t>
+          <t>PO-10567</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21944,7 +21962,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10570</t>
+          <t>PO-10569</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -21999,7 +22017,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10572</t>
+          <t>PO-10571</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22027,7 +22045,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>76.90000000000001</v>
+        <v>100.9</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -22048,7 +22066,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10574</t>
+          <t>PO-10573</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22103,7 +22121,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10575</t>
+          <t>PO-10574</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -22158,7 +22176,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10576</t>
+          <t>PO-10575</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -22213,7 +22231,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10577</t>
+          <t>PO-10576</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22241,7 +22259,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>25.51</v>
+        <v>49.52</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -22262,7 +22280,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10581</t>
+          <t>PO-10580</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22317,7 +22335,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10583</t>
+          <t>PO-10582</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22345,7 +22363,7 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
-        <v>1032.8</v>
+        <v>1056.8</v>
       </c>
       <c r="L393" t="inlineStr">
         <is>
@@ -22366,7 +22384,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10584</t>
+          <t>PO-10583</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22394,7 +22412,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>62.64</v>
+        <v>86.64</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -22415,7 +22433,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10585</t>
+          <t>PO-10584</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22470,7 +22488,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10589</t>
+          <t>PO-10588</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22525,7 +22543,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PO-10590</t>
+          <t>PO-10589</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -22580,7 +22598,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PO-10591</t>
+          <t>PO-10590</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -22635,7 +22653,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PO-10592</t>
+          <t>PO-10591</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22690,7 +22708,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PO-10593</t>
+          <t>PO-10592</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -22718,7 +22736,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>56.62</v>
+        <v>80.62</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -22739,50 +22757,44 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10594</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-07T06:30:07.314893+00:00</t>
+          <t>2026-10-05T03:20:27.406840+00:00</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-09-07T22:14:07.936372+00:00</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>2026-09-11T01:08:34.102909+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-05T19:04:28.028319+00:00</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
       <c r="G401" t="n">
         <v>15.73</v>
       </c>
-      <c r="H401" t="n">
-        <v>74.91</v>
-      </c>
-      <c r="I401" t="n">
-        <v>90.64</v>
-      </c>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
       <c r="J401" t="b">
-        <v>1</v>
-      </c>
-      <c r="K401" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K401" t="n">
+        <v>-112.24</v>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -22794,7 +22806,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PO-10596</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -22849,7 +22861,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>PO-10598</t>
+          <t>PO-10597</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -22893,6 +22905,61 @@
       <c r="M403" t="inlineStr">
         <is>
           <t>2026-S39</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Alpha Moda</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PO-10599</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-08-21T01:22:54.855884+00:00</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-08-21T23:41:23.435126+00:00</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-08-22T09:47:48.263323+00:00</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="H404" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="I404" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="J404" t="b">
+        <v>1</v>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>96.5</v>
+        <v>97</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>310</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.8</v>
+        <v>80.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.8</v>
+        <v>71.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.5</v>
+        <v>60.6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>289</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.6</v>
+        <v>26.7</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>276</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>67</v>
+      </c>
+      <c r="E2" t="n">
         <v>65</v>
       </c>
-      <c r="E2" t="n">
-        <v>62</v>
-      </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>95.40000000000001</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E5" t="n">
         <v>72</v>
-      </c>
-      <c r="E5" t="n">
-        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="6">
@@ -772,19 +772,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>86.40000000000001</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>84.59999999999999</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="8">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>75</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F9" t="n">
         <v>15</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>77.3</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="10">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
         <v>18</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>66</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="11">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>56.5</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="12">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>56.8</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="13">
@@ -996,19 +996,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E13" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>58.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="14">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
         <v>34</v>
@@ -1040,7 +1040,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="15">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
         <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>49.4</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="16">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
         <v>53</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>39.1</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
         <v>32</v>
       </c>
       <c r="F17" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>47.8</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="18">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>28.8</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
         <v>14</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>25.9</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E21" t="n">
         <v>18</v>
       </c>
       <c r="F21" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>28.1</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="22">
@@ -1287,16 +1287,16 @@
         <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>72.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" t="n">
         <v>59</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>69.40000000000001</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="25">
@@ -2062,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-10.92</v>
+        <v>13.06</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1294.9</v>
+        <v>1318.88</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-9.470000000000001</v>
+        <v>14.51</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1415.38</v>
+        <v>1439.36</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2468,18 +2468,24 @@
           <t>2026-09-27T00:39:16.889629+00:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:22:55.333927+00:00</t>
+        </is>
+      </c>
       <c r="G20" t="n">
         <v>67.06999999999999</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>129.73</v>
+      </c>
+      <c r="I20" t="n">
+        <v>196.8</v>
+      </c>
       <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>173.53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -2559,7 +2565,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2572,18 +2578,24 @@
           <t>2026-09-29T02:51:50.216902+00:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:27:18.009434+00:00</t>
+        </is>
+      </c>
       <c r="G22" t="n">
         <v>55.58</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>77.59</v>
+      </c>
+      <c r="I22" t="n">
+        <v>133.17</v>
+      </c>
       <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>111.82</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -2796,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>720.39</v>
+        <v>744.37</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3175,7 +3187,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>229.27</v>
+        <v>253.24</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -3224,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1389.2</v>
+        <v>1413.18</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -3438,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.82</v>
+        <v>24.8</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3597,7 +3609,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>50.72</v>
+        <v>74.7</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3678,45 +3690,39 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-09T22:25:40.706812+00:00</t>
+          <t>2026-10-05T23:28:41.696937+00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-10T04:28:17.183184+00:00</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-11T16:04:22.771041+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-06T05:31:18.173309+00:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>6.04</v>
       </c>
-      <c r="H43" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="I43" t="n">
-        <v>41.65</v>
-      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-84.39</v>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>625.76</v>
+        <v>649.73</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3970,7 +3976,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>286.71</v>
+        <v>310.68</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -4459,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>-66.86</v>
+        <v>-42.88</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4508,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1113.3</v>
+        <v>1137.27</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4667,7 +4673,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>906.51</v>
+        <v>930.49</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -4716,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1367.36</v>
+        <v>1391.34</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4875,7 +4881,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>135.68</v>
+        <v>159.65</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4901,7 +4907,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4914,18 +4920,24 @@
           <t>2026-09-28T10:34:41.222399+00:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-10-02T07:53:44.672077+00:00</t>
+        </is>
+      </c>
       <c r="G66" t="n">
         <v>16.77</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>93.31999999999999</v>
+      </c>
+      <c r="I66" t="n">
+        <v>110.08</v>
+      </c>
       <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>89.3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -5028,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>123.82</v>
+        <v>147.8</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -5077,7 +5089,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>29.61</v>
+        <v>53.59</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5103,7 +5115,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5116,18 +5128,24 @@
           <t>2026-09-27T07:23:39.065444+00:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-10-01T22:33:59.238483+00:00</t>
+        </is>
+      </c>
       <c r="G70" t="n">
         <v>35.16</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="I70" t="n">
+        <v>146.33</v>
+      </c>
       <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>134.88</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -5285,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>92.95999999999999</v>
+        <v>116.93</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5389,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>-92.38</v>
+        <v>-68.41</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5548,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>94.81</v>
+        <v>118.78</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -5872,7 +5890,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>165.78</v>
+        <v>189.76</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -6636,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>348.22</v>
+        <v>372.2</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -6722,12 +6740,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-17T18:36:22.389810+00:00</t>
+          <t>2026-10-02T18:36:22.389810+00:00</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-09-18T05:14:05.999230+00:00</t>
+          <t>2026-10-03T05:14:05.999230+00:00</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -6740,16 +6758,16 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>328.5</v>
+        <v>-7.52</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>85.23</v>
+        <v>109.21</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -6893,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>-1.63</v>
+        <v>22.35</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -6997,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>391.64</v>
+        <v>415.62</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -7046,7 +7064,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>46.89</v>
+        <v>70.86</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7370,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>679.96</v>
+        <v>703.9400000000001</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -7804,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>30</v>
+        <v>53.98</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -8128,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-9.289999999999999</v>
+        <v>14.69</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8177,7 +8195,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>-53.55</v>
+        <v>-29.57</v>
       </c>
       <c r="L127" t="inlineStr">
         <is>
@@ -8258,7 +8276,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8271,18 +8289,24 @@
           <t>2026-09-30T19:43:39.259439+00:00</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:10:12.391049+00:00</t>
+        </is>
+      </c>
       <c r="G129" t="n">
         <v>7.73</v>
       </c>
-      <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="H129" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="I129" t="n">
+        <v>36.18</v>
+      </c>
       <c r="J129" t="b">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>23.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -8385,7 +8409,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>384.26</v>
+        <v>408.24</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8819,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>709.41</v>
+        <v>733.39</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -8868,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>414.92</v>
+        <v>438.9</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8917,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1356.36</v>
+        <v>1380.34</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -9131,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>1071.2</v>
+        <v>1095.18</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -9290,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>478.12</v>
+        <v>502.1</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -9339,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>486.96</v>
+        <v>510.94</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9365,7 +9389,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9378,18 +9402,24 @@
           <t>2026-09-28T23:59:44.282440+00:00</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-02T01:19:43.435676+00:00</t>
+        </is>
+      </c>
       <c r="G150" t="n">
         <v>42.96</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>73.33</v>
+      </c>
+      <c r="I150" t="n">
+        <v>116.29</v>
+      </c>
       <c r="J150" t="b">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>102.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -9602,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>334.8</v>
+        <v>358.78</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -10123,52 +10153,46 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-06T13:14:21.949146+00:00</t>
+          <t>2026-10-06T01:40:46.286073+00:00</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-08-07T09:28:41.720911+00:00</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-08-08T07:48:09.271745+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-07T17:05:11.725115+00:00</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="n">
-        <v>20.24</v>
-      </c>
-      <c r="H164" t="n">
-        <v>22.32</v>
-      </c>
-      <c r="I164" t="n">
-        <v>42.56</v>
-      </c>
+        <v>39.41</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="b">
-        <v>1</v>
-      </c>
-      <c r="K164" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>-86.59</v>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10178,51 +10202,57 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-29T02:04:17.345631+00:00</t>
+          <t>2026-08-10T01:55:04.685035+00:00</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-09-30T04:08:23.850223+00:00</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr"/>
+          <t>2026-08-11T07:52:46.764366+00:00</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-17T02:21:21.693144+00:00</t>
+        </is>
+      </c>
       <c r="G165" t="n">
-        <v>26.07</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
+        <v>29.96</v>
+      </c>
+      <c r="H165" t="n">
+        <v>138.48</v>
+      </c>
+      <c r="I165" t="n">
+        <v>168.44</v>
+      </c>
       <c r="J165" t="b">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>57.04</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PO-10256</t>
+          <t>PO-10257</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10232,27 +10262,27 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-26T22:26:51.613292+00:00</t>
+          <t>2026-08-20T02:12:17.791952+00:00</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-08-28T06:07:25.113334+00:00</t>
+          <t>2026-08-21T01:15:41.529315+00:00</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-31T02:27:00.205867+00:00</t>
+          <t>2026-08-23T02:32:57.687537+00:00</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>31.68</v>
+        <v>23.06</v>
       </c>
       <c r="H166" t="n">
-        <v>68.33</v>
+        <v>49.29</v>
       </c>
       <c r="I166" t="n">
-        <v>100</v>
+        <v>72.34</v>
       </c>
       <c r="J166" t="b">
         <v>1</v>
@@ -10265,19 +10295,19 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PO-10257</t>
+          <t>PO-10258</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10287,27 +10317,27 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-16T18:21:05.974360+00:00</t>
+          <t>2026-09-18T11:21:05.974360+00:00</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>2026-08-17T10:34:55.170763+00:00</t>
+          <t>2026-09-19T06:30:00.067414+00:00</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-20T06:29:59.460695+00:00</t>
+          <t>2026-09-22T14:37:43.412998+00:00</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>16.23</v>
+        <v>19.15</v>
       </c>
       <c r="H167" t="n">
-        <v>67.92</v>
+        <v>80.13</v>
       </c>
       <c r="I167" t="n">
-        <v>84.15000000000001</v>
+        <v>99.28</v>
       </c>
       <c r="J167" t="b">
         <v>1</v>
@@ -10315,12 +10345,12 @@
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10362,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PO-10258</t>
+          <t>PO-10259</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10387,7 +10417,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PO-10259</t>
+          <t>PO-10260</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10415,7 +10445,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>-53.36</v>
+        <v>-29.39</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -10436,7 +10466,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PO-10260</t>
+          <t>PO-10261</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10491,7 +10521,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PO-10261</t>
+          <t>PO-10262</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10546,7 +10576,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PO-10262</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10601,7 +10631,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PO-10264</t>
+          <t>PO-10265</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10656,7 +10686,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PO-10265</t>
+          <t>PO-10266</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10711,7 +10741,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PO-10266</t>
+          <t>PO-10267</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10766,7 +10796,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PO-10267</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10821,7 +10851,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PO-10268</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10849,7 +10879,7 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>207.94</v>
+        <v>231.91</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -10870,12 +10900,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -10888,18 +10918,24 @@
           <t>2026-09-29T21:51:15.180525+00:00</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-10-01T23:18:34.610039+00:00</t>
+        </is>
+      </c>
       <c r="G178" t="n">
         <v>21.26</v>
       </c>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
+      <c r="H178" t="n">
+        <v>49.46</v>
+      </c>
+      <c r="I178" t="n">
+        <v>70.72</v>
+      </c>
       <c r="J178" t="b">
-        <v>0</v>
-      </c>
-      <c r="K178" t="n">
-        <v>58.52</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -10919,7 +10955,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10272</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10974,7 +11010,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10272</t>
+          <t>PO-10273</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11029,50 +11065,44 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10273</t>
+          <t>PO-10274</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-31T04:02:57.860442+00:00</t>
+          <t>2026-10-07T02:02:57.860442+00:00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-08-31T22:00:30.459000+00:00</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-09-01T09:42:55.394632+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-07T20:00:30.459000+00:00</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="n">
         <v>17.96</v>
       </c>
-      <c r="H181" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="I181" t="n">
-        <v>29.67</v>
-      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="b">
-        <v>1</v>
-      </c>
-      <c r="K181" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-110.96</v>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11114,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10274</t>
+          <t>PO-10275</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11139,7 +11169,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10276</t>
+          <t>PO-10277</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11194,7 +11224,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10277</t>
+          <t>PO-10278</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11249,7 +11279,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10280</t>
+          <t>PO-10281</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11277,7 +11307,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>446.12</v>
+        <v>470.1</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -11298,7 +11328,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10281</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11353,7 +11383,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10282</t>
+          <t>PO-10283</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11381,7 +11411,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>1018.68</v>
+        <v>1042.66</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -11402,7 +11432,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10285</t>
+          <t>PO-10286</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11457,7 +11487,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10287</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11485,7 +11515,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>-35.64</v>
+        <v>-11.66</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -11506,7 +11536,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10287</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11561,7 +11591,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10288</t>
+          <t>PO-10289</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11589,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>580.85</v>
+        <v>604.8200000000001</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -11610,7 +11640,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10291</t>
+          <t>PO-10292</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11665,7 +11695,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10292</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11720,7 +11750,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11775,7 +11805,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10296</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11830,7 +11860,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11858,7 +11888,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>-0.47</v>
+        <v>23.51</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -11879,7 +11909,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10299</t>
+          <t>PO-10300</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11934,7 +11964,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10300</t>
+          <t>PO-10301</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11989,7 +12019,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10302</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12017,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>388.35</v>
+        <v>412.32</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -12038,7 +12068,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12093,7 +12123,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10303</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12148,7 +12178,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12203,7 +12233,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10305</t>
+          <t>PO-10306</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12231,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>1429.91</v>
+        <v>1453.89</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12252,91 +12282,91 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10307</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-14T18:54:12.862542+00:00</t>
+          <t>2026-10-05T07:42:11.435008+00:00</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>2026-09-15T07:59:32.068592+00:00</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-09-18T03:47:33.625700+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-06T10:05:17.414086+00:00</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="n">
-        <v>13.09</v>
-      </c>
-      <c r="H204" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="I204" t="n">
-        <v>80.89</v>
-      </c>
+        <v>26.38</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="b">
-        <v>1</v>
-      </c>
-      <c r="K204" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>-68.62</v>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10307</t>
+          <t>PO-10308</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-09-04T15:59:31.160800+00:00</t>
+          <t>2026-09-06T21:39:59.170057+00:00</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>2026-09-07T20:39:13.537141+00:00</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr"/>
+          <t>2026-09-07T14:28:57.504614+00:00</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-09-11T15:42:21.924110+00:00</t>
+        </is>
+      </c>
       <c r="G205" t="n">
-        <v>76.66</v>
-      </c>
-      <c r="H205" t="inlineStr"/>
-      <c r="I205" t="inlineStr"/>
+        <v>16.82</v>
+      </c>
+      <c r="H205" t="n">
+        <v>97.22</v>
+      </c>
+      <c r="I205" t="n">
+        <v>114.04</v>
+      </c>
       <c r="J205" t="b">
-        <v>0</v>
-      </c>
-      <c r="K205" t="n">
-        <v>643.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -12356,7 +12386,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10308</t>
+          <t>PO-10309</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12366,17 +12396,17 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-20T10:54:56.507681+00:00</t>
+          <t>2026-09-18T03:19:24.896933+00:00</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>2026-09-21T17:25:30.100123+00:00</t>
+          <t>2026-09-19T09:49:58.489375+00:00</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-09-23T01:33:09.789206+00:00</t>
+          <t>2026-09-20T17:57:38.178458+00:00</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -12411,7 +12441,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10309</t>
+          <t>PO-10310</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12466,7 +12496,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10311</t>
+          <t>PO-10312</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12521,7 +12551,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10312</t>
+          <t>PO-10313</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12576,7 +12606,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10313</t>
+          <t>PO-10314</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12631,7 +12661,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10314</t>
+          <t>PO-10315</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12659,7 +12689,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>673.46</v>
+        <v>697.4400000000001</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -12680,7 +12710,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10315</t>
+          <t>PO-10316</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12708,7 +12738,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>474.89</v>
+        <v>498.87</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -12729,7 +12759,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10316</t>
+          <t>PO-10317</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12784,7 +12814,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10317</t>
+          <t>PO-10318</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12839,7 +12869,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10318</t>
+          <t>PO-10319</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12867,7 +12897,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>337.01</v>
+        <v>360.99</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -12888,7 +12918,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10320</t>
+          <t>PO-10321</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12943,7 +12973,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10321</t>
+          <t>PO-10322</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12998,7 +13028,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10322</t>
+          <t>PO-10323</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13053,7 +13083,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PO-10323</t>
+          <t>PO-10324</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13108,7 +13138,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PO-10324</t>
+          <t>PO-10325</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13136,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>753.11</v>
+        <v>777.09</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -13157,7 +13187,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PO-10326</t>
+          <t>PO-10327</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13185,7 +13215,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>303.36</v>
+        <v>327.34</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -13206,7 +13236,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PO-10328</t>
+          <t>PO-10329</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13261,7 +13291,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PO-10329</t>
+          <t>PO-10330</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13316,7 +13346,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PO-10330</t>
+          <t>PO-10331</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13371,7 +13401,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PO-10331</t>
+          <t>PO-10332</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13426,7 +13456,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PO-10334</t>
+          <t>PO-10335</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13481,7 +13511,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PO-10335</t>
+          <t>PO-10336</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13536,7 +13566,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PO-10336</t>
+          <t>PO-10337</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13564,7 +13594,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>1262.34</v>
+        <v>1286.31</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -13585,7 +13615,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PO-10337</t>
+          <t>PO-10338</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13640,7 +13670,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PO-10339</t>
+          <t>PO-10340</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13695,7 +13725,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PO-10341</t>
+          <t>PO-10342</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13750,7 +13780,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PO-10343</t>
+          <t>PO-10344</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13778,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>230.54</v>
+        <v>254.51</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13799,7 +13829,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PO-10345</t>
+          <t>PO-10346</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13827,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>995.25</v>
+        <v>1019.23</v>
       </c>
       <c r="L233" t="inlineStr">
         <is>
@@ -13848,7 +13878,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PO-10346</t>
+          <t>PO-10347</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13903,7 +13933,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PO-10347</t>
+          <t>PO-10348</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13931,7 +13961,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>856.12</v>
+        <v>880.1</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -13952,7 +13982,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PO-10348</t>
+          <t>PO-10349</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14007,7 +14037,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PO-10350</t>
+          <t>PO-10351</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14062,7 +14092,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PO-10351</t>
+          <t>PO-10352</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14117,7 +14147,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PO-10352</t>
+          <t>PO-10353</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14145,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>87.09</v>
+        <v>111.06</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -14166,7 +14196,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PO-10355</t>
+          <t>PO-10356</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14221,7 +14251,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PO-10356</t>
+          <t>PO-10357</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14276,7 +14306,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PO-10357</t>
+          <t>PO-10358</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14331,7 +14361,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PO-10359</t>
+          <t>PO-10360</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14386,7 +14416,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PO-10360</t>
+          <t>PO-10361</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14441,7 +14471,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PO-10361</t>
+          <t>PO-10362</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14469,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>504.54</v>
+        <v>528.52</v>
       </c>
       <c r="L245" t="inlineStr">
         <is>
@@ -14490,7 +14520,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PO-10362</t>
+          <t>PO-10363</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14545,7 +14575,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PO-10365</t>
+          <t>PO-10366</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14573,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>983.58</v>
+        <v>1007.56</v>
       </c>
       <c r="L247" t="inlineStr">
         <is>
@@ -14594,12 +14624,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PO-10366</t>
+          <t>PO-10367</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14612,18 +14642,24 @@
           <t>2026-09-29T13:21:38.418091+00:00</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-10-01T20:23:49.036603+00:00</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>30.97</v>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
+      <c r="H248" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="I248" t="n">
+        <v>86.01000000000001</v>
+      </c>
       <c r="J248" t="b">
-        <v>0</v>
-      </c>
-      <c r="K248" t="n">
-        <v>76.72</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -14643,7 +14679,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PO-10370</t>
+          <t>PO-10371</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14698,7 +14734,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PO-10372</t>
+          <t>PO-10373</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14753,7 +14789,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PO-10373</t>
+          <t>PO-10374</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14808,7 +14844,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PO-10374</t>
+          <t>PO-10375</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14863,7 +14899,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PO-10375</t>
+          <t>PO-10376</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14918,7 +14954,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PO-10377</t>
+          <t>PO-10378</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14973,50 +15009,44 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PO-10378</t>
+          <t>PO-10379</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-11T02:14:31.207658+00:00</t>
+          <t>2026-10-05T18:36:22.873224+00:00</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-09-14T09:42:56.059057+00:00</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>2026-09-14T18:02:17.331216+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-08T18:32:08.951469+00:00</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
       <c r="G255" t="n">
-        <v>79.47</v>
-      </c>
-      <c r="H255" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="I255" t="n">
-        <v>87.8</v>
-      </c>
+        <v>71.93000000000001</v>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
       <c r="J255" t="b">
-        <v>1</v>
-      </c>
-      <c r="K255" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>-79.52</v>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15058,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PO-10379</t>
+          <t>PO-10380</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15038,27 +15068,27 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-25T05:24:55.068175+00:00</t>
+          <t>2026-08-11T18:22:57.141658+00:00</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-08-26T12:00:56.568902+00:00</t>
+          <t>2026-08-12T05:28:15.465215+00:00</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2026-08-27T22:30:46.179863+00:00</t>
+          <t>2026-08-15T12:44:42.023063+00:00</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>30.6</v>
+        <v>11.09</v>
       </c>
       <c r="H256" t="n">
-        <v>34.5</v>
+        <v>79.27</v>
       </c>
       <c r="I256" t="n">
-        <v>65.09999999999999</v>
+        <v>90.36</v>
       </c>
       <c r="J256" t="b">
         <v>1</v>
@@ -15071,19 +15101,19 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PO-10380</t>
+          <t>PO-10381</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15093,27 +15123,27 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-17T11:08:27.132700+00:00</t>
+          <t>2026-09-20T06:59:16.386510+00:00</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-08-17T17:53:34.280401+00:00</t>
+          <t>2026-09-20T11:56:25.990140+00:00</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>2026-08-20T03:36:03.912050+00:00</t>
+          <t>2026-09-22T06:16:13.001242+00:00</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>6.75</v>
+        <v>4.95</v>
       </c>
       <c r="H257" t="n">
-        <v>57.71</v>
+        <v>42.33</v>
       </c>
       <c r="I257" t="n">
-        <v>64.45999999999999</v>
+        <v>47.28</v>
       </c>
       <c r="J257" t="b">
         <v>1</v>
@@ -15121,12 +15151,12 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -15138,7 +15168,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PO-10384</t>
+          <t>PO-10385</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15193,7 +15223,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PO-10385</t>
+          <t>PO-10386</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15221,7 +15251,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>355.72</v>
+        <v>379.69</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -15242,7 +15272,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PO-10386</t>
+          <t>PO-10387</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15297,7 +15327,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PO-10388</t>
+          <t>PO-10389</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15352,7 +15382,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PO-10389</t>
+          <t>PO-10390</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15407,7 +15437,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PO-10390</t>
+          <t>PO-10391</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15462,7 +15492,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PO-10391</t>
+          <t>PO-10392</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15517,7 +15547,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PO-10393</t>
+          <t>PO-10394</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15572,7 +15602,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PO-10394</t>
+          <t>PO-10395</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15627,7 +15657,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PO-10395</t>
+          <t>PO-10396</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15682,7 +15712,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PO-10397</t>
+          <t>PO-10398</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15737,7 +15767,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PO-10398</t>
+          <t>PO-10399</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15792,7 +15822,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PO-10399</t>
+          <t>PO-10400</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15847,57 +15877,51 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PO-10400</t>
+          <t>PO-10401</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-20T07:35:51.118964+00:00</t>
+          <t>2026-10-05T03:54:26.066066+00:00</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-08-21T06:25:59.213884+00:00</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>2026-08-25T00:56:44.642840+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-07T01:40:09.879960+00:00</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
       <c r="G271" t="n">
-        <v>22.84</v>
-      </c>
-      <c r="H271" t="n">
-        <v>90.51000000000001</v>
-      </c>
-      <c r="I271" t="n">
-        <v>113.35</v>
-      </c>
+        <v>45.76</v>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
       <c r="J271" t="b">
-        <v>1</v>
-      </c>
-      <c r="K271" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>-64.81999999999999</v>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -15912,27 +15936,27 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-28T11:13:11.819187+00:00</t>
+          <t>2026-08-17T06:30:13.021464+00:00</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>2026-08-30T04:11:39.547603+00:00</t>
+          <t>2026-08-18T07:16:03.603156+00:00</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>2026-08-31T11:32:08.683302+00:00</t>
+          <t>2026-08-22T12:11:51.999925+00:00</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>40.97</v>
+        <v>24.76</v>
       </c>
       <c r="H272" t="n">
-        <v>31.34</v>
+        <v>100.93</v>
       </c>
       <c r="I272" t="n">
-        <v>72.31999999999999</v>
+        <v>125.69</v>
       </c>
       <c r="J272" t="b">
         <v>1</v>
@@ -15945,19 +15969,19 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PO-10403</t>
+          <t>PO-10404</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15967,27 +15991,27 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-21T01:03:32.678636+00:00</t>
+          <t>2026-08-06T18:56:03.575526+00:00</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>2026-08-22T13:41:22.932773+00:00</t>
+          <t>2026-08-07T11:27:28.406997+00:00</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>2026-08-24T10:03:51.214342+00:00</t>
+          <t>2026-08-08T12:56:16.822739+00:00</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>36.63</v>
+        <v>16.52</v>
       </c>
       <c r="H273" t="n">
-        <v>44.37</v>
+        <v>25.48</v>
       </c>
       <c r="I273" t="n">
-        <v>81.01000000000001</v>
+        <v>42</v>
       </c>
       <c r="J273" t="b">
         <v>1</v>
@@ -16000,7 +16024,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16036,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PO-10407</t>
+          <t>PO-10408</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16067,7 +16091,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PO-10409</t>
+          <t>PO-10410</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16122,7 +16146,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PO-10410</t>
+          <t>PO-10411</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16177,7 +16201,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PO-10411</t>
+          <t>PO-10412</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16205,7 +16229,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>1127.34</v>
+        <v>1151.32</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -16226,7 +16250,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PO-10412</t>
+          <t>PO-10413</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16254,7 +16278,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>1358.6</v>
+        <v>1382.57</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -16275,7 +16299,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PO-10415</t>
+          <t>PO-10416</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16303,7 +16327,7 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>434.51</v>
+        <v>458.49</v>
       </c>
       <c r="L279" t="inlineStr">
         <is>
@@ -16324,7 +16348,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PO-10416</t>
+          <t>PO-10417</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16352,7 +16376,7 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
-        <v>170.56</v>
+        <v>194.54</v>
       </c>
       <c r="L280" t="inlineStr">
         <is>
@@ -16373,7 +16397,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PO-10418</t>
+          <t>PO-10419</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16401,7 +16425,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>12.64</v>
+        <v>36.61</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -16422,7 +16446,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PO-10419</t>
+          <t>PO-10420</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16450,7 +16474,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>914.15</v>
+        <v>938.13</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16471,7 +16495,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PO-10420</t>
+          <t>PO-10421</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16481,12 +16505,12 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-06T14:23:05.319402+00:00</t>
+          <t>2026-10-05T15:23:05.319402+00:00</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-09-08T11:11:41.342139+00:00</t>
+          <t>2026-10-07T12:11:41.342139+00:00</t>
         </is>
       </c>
       <c r="F283" t="inlineStr"/>
@@ -16499,16 +16523,16 @@
         <v>0</v>
       </c>
       <c r="K283" t="n">
-        <v>596.73</v>
+        <v>-76.3</v>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -16520,7 +16544,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PO-10421</t>
+          <t>PO-10422</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16575,7 +16599,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PO-10422</t>
+          <t>PO-10423</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16630,7 +16654,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PO-10423</t>
+          <t>PO-10424</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16658,7 +16682,7 @@
         <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>-36.95</v>
+        <v>-12.97</v>
       </c>
       <c r="L286" t="inlineStr">
         <is>
@@ -16679,7 +16703,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PO-10425</t>
+          <t>PO-10426</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16734,7 +16758,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PO-10426</t>
+          <t>PO-10427</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16789,7 +16813,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PO-10427</t>
+          <t>PO-10428</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16844,7 +16868,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PO-10433</t>
+          <t>PO-10434</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16899,7 +16923,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PO-10434</t>
+          <t>PO-10435</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16927,7 +16951,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>257.98</v>
+        <v>281.96</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16948,7 +16972,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PO-10435</t>
+          <t>PO-10436</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -17003,7 +17027,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PO-10436</t>
+          <t>PO-10437</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17031,7 +17055,7 @@
         <v>0</v>
       </c>
       <c r="K293" t="n">
-        <v>-17.6</v>
+        <v>6.37</v>
       </c>
       <c r="L293" t="inlineStr">
         <is>
@@ -17052,7 +17076,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PO-10438</t>
+          <t>PO-10439</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17107,7 +17131,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PO-10439</t>
+          <t>PO-10440</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17162,7 +17186,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PO-10442</t>
+          <t>PO-10443</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17217,7 +17241,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PO-10443</t>
+          <t>PO-10444</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17272,7 +17296,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PO-10445</t>
+          <t>PO-10446</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17300,7 +17324,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>976.34</v>
+        <v>1000.31</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -17321,7 +17345,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PO-10446</t>
+          <t>PO-10447</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17349,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
-        <v>4.28</v>
+        <v>28.26</v>
       </c>
       <c r="L299" t="inlineStr">
         <is>
@@ -17370,7 +17394,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PO-10447</t>
+          <t>PO-10448</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17425,7 +17449,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PO-10448</t>
+          <t>PO-10449</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17480,7 +17504,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PO-10449</t>
+          <t>PO-10450</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17535,12 +17559,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PO-10450</t>
+          <t>PO-10451</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -17553,18 +17577,24 @@
           <t>2026-09-30T14:31:51.651151+00:00</t>
         </is>
       </c>
-      <c r="F303" t="inlineStr"/>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:22:45.926736+00:00</t>
+        </is>
+      </c>
       <c r="G303" t="n">
         <v>49.98</v>
       </c>
-      <c r="H303" t="inlineStr"/>
-      <c r="I303" t="inlineStr"/>
+      <c r="H303" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="I303" t="n">
+        <v>83.81999999999999</v>
+      </c>
       <c r="J303" t="b">
-        <v>0</v>
-      </c>
-      <c r="K303" t="n">
-        <v>70.56</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -17584,7 +17614,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PO-10454</t>
+          <t>PO-10455</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17639,12 +17669,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PO-10455</t>
+          <t>PO-10456</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -17657,18 +17687,24 @@
           <t>2026-10-01T16:51:07.710434+00:00</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>2026-10-02T08:26:21.343284+00:00</t>
+        </is>
+      </c>
       <c r="G305" t="n">
         <v>51.24</v>
       </c>
-      <c r="H305" t="inlineStr"/>
-      <c r="I305" t="inlineStr"/>
+      <c r="H305" t="n">
+        <v>15.59</v>
+      </c>
+      <c r="I305" t="n">
+        <v>66.81999999999999</v>
+      </c>
       <c r="J305" t="b">
-        <v>0</v>
-      </c>
-      <c r="K305" t="n">
-        <v>45.49</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K305" t="inlineStr"/>
       <c r="L305" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -17688,7 +17724,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PO-10456</t>
+          <t>PO-10457</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17743,7 +17779,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PO-10457</t>
+          <t>PO-10458</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17798,7 +17834,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PO-10458</t>
+          <t>PO-10459</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17853,7 +17889,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PO-10460</t>
+          <t>PO-10461</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17881,7 +17917,7 @@
         <v>0</v>
       </c>
       <c r="K309" t="n">
-        <v>-66.68000000000001</v>
+        <v>-42.71</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
@@ -17902,7 +17938,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PO-10461</t>
+          <t>PO-10462</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17957,7 +17993,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PO-10463</t>
+          <t>PO-10464</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -17985,7 +18021,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>480.58</v>
+        <v>504.56</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -18006,7 +18042,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PO-10467</t>
+          <t>PO-10468</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18061,7 +18097,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PO-10469</t>
+          <t>PO-10470</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18089,7 +18125,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>547.13</v>
+        <v>571.1</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -18110,7 +18146,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PO-10470</t>
+          <t>PO-10471</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18165,7 +18201,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10471</t>
+          <t>PO-10472</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18220,7 +18256,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10472</t>
+          <t>PO-10473</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18275,7 +18311,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10473</t>
+          <t>PO-10474</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18330,7 +18366,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10474</t>
+          <t>PO-10475</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18385,7 +18421,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10475</t>
+          <t>PO-10476</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18440,7 +18476,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10476</t>
+          <t>PO-10477</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18468,7 +18504,7 @@
         <v>0</v>
       </c>
       <c r="K320" t="n">
-        <v>905.84</v>
+        <v>929.8200000000001</v>
       </c>
       <c r="L320" t="inlineStr">
         <is>
@@ -18489,7 +18525,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10477</t>
+          <t>PO-10478</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18517,7 +18553,7 @@
         <v>0</v>
       </c>
       <c r="K321" t="n">
-        <v>677.27</v>
+        <v>701.25</v>
       </c>
       <c r="L321" t="inlineStr">
         <is>
@@ -18538,7 +18574,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10479</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18593,7 +18629,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10479</t>
+          <t>PO-10480</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18648,7 +18684,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10480</t>
+          <t>PO-10481</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18703,7 +18739,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10481</t>
+          <t>PO-10482</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18731,7 +18767,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>484.53</v>
+        <v>508.51</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -18752,7 +18788,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10484</t>
+          <t>PO-10485</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18802,47 +18838,41 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10485</t>
+          <t>PO-10487</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-08-19T09:53:22.177648+00:00</t>
+          <t>2026-08-19T00:55:46.780265+00:00</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-08-20T05:51:53.283550+00:00</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>2026-08-23T20:43:07.922518+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-21T02:30:47.843695+00:00</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>19.98</v>
-      </c>
-      <c r="H327" t="n">
-        <v>86.84999999999999</v>
-      </c>
-      <c r="I327" t="n">
-        <v>106.83</v>
-      </c>
+        <v>49.58</v>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="b">
-        <v>1</v>
-      </c>
-      <c r="K327" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>1066.16</v>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -18857,12 +18887,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10487</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18872,27 +18902,27 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-08-04T23:28:47.558849+00:00</t>
+          <t>2026-08-12T08:30:30.723409+00:00</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-08-08T02:11:41.743500+00:00</t>
+          <t>2026-08-14T00:40:21.234609+00:00</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-08-09T07:57:12.095994+00:00</t>
+          <t>2026-08-16T19:27:53.135754+00:00</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>74.72</v>
+        <v>40.16</v>
       </c>
       <c r="H328" t="n">
-        <v>29.76</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="I328" t="n">
-        <v>104.47</v>
+        <v>106.96</v>
       </c>
       <c r="J328" t="b">
         <v>1</v>
@@ -18905,7 +18935,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -18917,42 +18947,36 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10488</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-09-02T20:07:43.581569+00:00</t>
+          <t>2026-09-23T12:19:38.213862+00:00</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-09-04T00:25:37.978882+00:00</t>
-        </is>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>2026-09-05T20:45:36.532072+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-26T01:53:00.738608+00:00</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
       <c r="G329" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H329" t="n">
-        <v>44.33</v>
-      </c>
-      <c r="I329" t="n">
-        <v>72.63</v>
-      </c>
+        <v>61.56</v>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr"/>
       <c r="J329" t="b">
-        <v>1</v>
-      </c>
-      <c r="K329" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K329" t="n">
+        <v>214.76</v>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -18960,19 +18984,19 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10489</t>
+          <t>PO-10490</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18982,27 +19006,27 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-09-29T00:11:14.881371+00:00</t>
+          <t>2026-08-19T17:15:07.605584+00:00</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-09-29T13:18:28.144176+00:00</t>
+          <t>2026-08-21T19:28:39.829245+00:00</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>2026-09-29T21:47:37.635505+00:00</t>
+          <t>2026-08-26T04:38:30.998407+00:00</t>
         </is>
       </c>
       <c r="G330" t="n">
-        <v>13.12</v>
+        <v>50.23</v>
       </c>
       <c r="H330" t="n">
-        <v>8.49</v>
+        <v>105.16</v>
       </c>
       <c r="I330" t="n">
-        <v>21.61</v>
+        <v>155.39</v>
       </c>
       <c r="J330" t="b">
         <v>1</v>
@@ -19010,19 +19034,19 @@
       <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -19032,52 +19056,46 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-16T19:12:35.487348+00:00</t>
+          <t>2026-08-21T20:57:59.166000+00:00</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-09-18T09:14:06.977187+00:00</t>
-        </is>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>2026-09-21T07:29:49.760764+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-23T03:40:49.829977+00:00</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>38.03</v>
-      </c>
-      <c r="H331" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="I331" t="n">
-        <v>108.29</v>
-      </c>
+        <v>30.71</v>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr"/>
       <c r="J331" t="b">
-        <v>1</v>
-      </c>
-      <c r="K331" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K331" t="n">
+        <v>998.12</v>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -19092,27 +19110,27 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-04T10:41:45.474895+00:00</t>
+          <t>2026-08-12T22:59:08.192451+00:00</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-09-07T10:22:02.081934+00:00</t>
+          <t>2026-08-13T09:15:07.499586+00:00</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>2026-09-07T22:27:42.436228+00:00</t>
+          <t>2026-08-17T18:14:17.186973+00:00</t>
         </is>
       </c>
       <c r="G332" t="n">
-        <v>71.67</v>
+        <v>10.27</v>
       </c>
       <c r="H332" t="n">
-        <v>12.09</v>
+        <v>104.99</v>
       </c>
       <c r="I332" t="n">
-        <v>83.77</v>
+        <v>115.25</v>
       </c>
       <c r="J332" t="b">
         <v>1</v>
@@ -19120,12 +19138,12 @@
       <c r="K332" t="inlineStr"/>
       <c r="L332" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19348,7 @@
         <v>0</v>
       </c>
       <c r="K336" t="n">
-        <v>206.87</v>
+        <v>230.84</v>
       </c>
       <c r="L336" t="inlineStr">
         <is>
@@ -19379,7 +19397,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>797.5</v>
+        <v>821.47</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -19758,7 +19776,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>1015.1</v>
+        <v>1039.08</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -19917,7 +19935,7 @@
         <v>0</v>
       </c>
       <c r="K347" t="n">
-        <v>488.68</v>
+        <v>512.66</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
@@ -19966,7 +19984,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>52.62</v>
+        <v>76.59</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
@@ -20015,7 +20033,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>399.22</v>
+        <v>423.2</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -20284,7 +20302,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>131.76</v>
+        <v>155.74</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -20498,7 +20516,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>1236.66</v>
+        <v>1260.63</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -20547,7 +20565,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>502.54</v>
+        <v>526.51</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -20816,7 +20834,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>8.800000000000001</v>
+        <v>32.78</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -20975,7 +20993,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>102.5</v>
+        <v>126.47</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -21024,7 +21042,7 @@
         <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>-38.89</v>
+        <v>-14.92</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
@@ -21073,7 +21091,7 @@
         <v>0</v>
       </c>
       <c r="K369" t="n">
-        <v>1074.93</v>
+        <v>1098.91</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
@@ -21232,7 +21250,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>-17.13</v>
+        <v>6.85</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -21831,7 +21849,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>69.93000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -21990,7 +22008,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>124.91</v>
+        <v>148.89</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -22181,7 +22199,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -22194,18 +22212,24 @@
           <t>2026-09-28T23:50:07.769529+00:00</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-10-02T10:36:19.794849+00:00</t>
+        </is>
+      </c>
       <c r="G390" t="n">
         <v>14.25</v>
       </c>
-      <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
+      <c r="H390" t="n">
+        <v>82.77</v>
+      </c>
+      <c r="I390" t="n">
+        <v>97.02</v>
+      </c>
       <c r="J390" t="b">
-        <v>0</v>
-      </c>
-      <c r="K390" t="n">
-        <v>73.53</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22308,7 +22332,7 @@
         <v>0</v>
       </c>
       <c r="K392" t="n">
-        <v>1080.81</v>
+        <v>1104.79</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -22334,7 +22358,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -22347,18 +22371,24 @@
           <t>2026-09-27T19:31:16.868570+00:00</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-10-02T06:40:44.266323+00:00</t>
+        </is>
+      </c>
       <c r="G393" t="n">
         <v>23.06</v>
       </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
+      <c r="H393" t="n">
+        <v>107.16</v>
+      </c>
+      <c r="I393" t="n">
+        <v>130.22</v>
+      </c>
       <c r="J393" t="b">
-        <v>0</v>
-      </c>
-      <c r="K393" t="n">
-        <v>110.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22461,7 +22491,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>-52.62</v>
+        <v>-28.64</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -22675,7 +22705,7 @@
         <v>0</v>
       </c>
       <c r="K399" t="n">
-        <v>104.63</v>
+        <v>128.61</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
@@ -22724,7 +22754,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>-88.23</v>
+        <v>-64.25</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>299</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66.2</v>
+        <v>64.8</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.7</v>
+        <v>25.2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -775,16 +775,16 @@
         <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>85.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>77.90000000000001</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="8">
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E8" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>75.5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>84.90000000000001</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="10">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" t="n">
         <v>17</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>71.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="11">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>59.3</v>
+        <v>55.7</v>
       </c>
     </row>
     <row r="12">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>72.8</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1063,16 +1063,16 @@
         <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="16">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F16" t="n">
         <v>54</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
         <v>30</v>
       </c>
       <c r="F17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>40.5</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="18">
@@ -1159,16 +1159,16 @@
         <v>39</v>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>30.8</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>28.6</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="20">
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
@@ -1232,7 +1232,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>21.9</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>75</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="23">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>79.5</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>84.7</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="25">
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>62.5</v>
+        <v>62.3</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>815.4400000000001</v>
+        <v>839.4299999999999</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>926.5599999999999</v>
+        <v>950.5599999999999</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>50.77</v>
+        <v>74.77</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-78.31999999999999</v>
+        <v>-54.32</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1305.44</v>
+        <v>1329.43</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>125.94</v>
+        <v>149.94</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-78</v>
+        <v>-54.01</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>711.9</v>
+        <v>735.9</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1068.94</v>
+        <v>1092.93</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>-70.89</v>
+        <v>-46.89</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2762,18 +2762,24 @@
           <t>2026-10-05T05:31:44.115275+00:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:09:35.263800+00:00</t>
+        </is>
+      </c>
       <c r="G26" t="n">
         <v>51.82</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>66.63</v>
+      </c>
+      <c r="I26" t="n">
+        <v>118.45</v>
+      </c>
       <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>105.41</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -2931,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>5.49</v>
+        <v>29.48</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3090,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1509.21</v>
+        <v>1533.21</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3161,7 +3167,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3176,27 +3182,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-04T09:18:47.633079+00:00</t>
+          <t>2026-09-28T17:21:23.206225+00:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-04T15:52:28.709737+00:00</t>
+          <t>2026-09-28T21:53:19.887110+00:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-06T17:46:15.345002+00:00</t>
+          <t>2026-09-29T05:53:44.645902+00:00</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>6.56</v>
+        <v>4.53</v>
       </c>
       <c r="H34" t="n">
-        <v>49.9</v>
+        <v>8.01</v>
       </c>
       <c r="I34" t="n">
-        <v>56.46</v>
+        <v>12.54</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
@@ -3204,12 +3210,12 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3227,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PO-10053</t>
+          <t>PO-10052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3276,7 +3282,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PO-10054</t>
+          <t>PO-10053</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3331,7 +3337,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PO-10055</t>
+          <t>PO-10054</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3359,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1080.42</v>
+        <v>1104.42</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3380,7 +3386,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PO-10058</t>
+          <t>PO-10057</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3435,7 +3441,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PO-10059</t>
+          <t>PO-10058</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3490,7 +3496,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PO-10060</t>
+          <t>PO-10059</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3545,7 +3551,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PO-10062</t>
+          <t>PO-10061</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3600,7 +3606,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PO-10063</t>
+          <t>PO-10062</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3655,7 +3661,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PO-10066</t>
+          <t>PO-10065</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3710,7 +3716,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PO-10068</t>
+          <t>PO-10067</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3765,7 +3771,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PO-10073</t>
+          <t>PO-10072</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3820,7 +3826,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PO-10074</t>
+          <t>PO-10073</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3848,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>-28.58</v>
+        <v>-4.58</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3869,7 +3875,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PO-10075</t>
+          <t>PO-10074</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3897,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>433.78</v>
+        <v>457.78</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3918,7 +3924,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PO-10077</t>
+          <t>PO-10076</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3973,7 +3979,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PO-10079</t>
+          <t>PO-10078</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4028,7 +4034,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PO-10080</t>
+          <t>PO-10079</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4083,7 +4089,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PO-10082</t>
+          <t>PO-10081</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4138,7 +4144,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PO-10083</t>
+          <t>PO-10082</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4193,7 +4199,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PO-10084</t>
+          <t>PO-10083</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4221,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>882.41</v>
+        <v>906.41</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4242,7 +4248,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PO-10085</t>
+          <t>PO-10084</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4270,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>48.62</v>
+        <v>72.61</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -4291,7 +4297,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PO-10086</t>
+          <t>PO-10085</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4319,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>916.73</v>
+        <v>940.73</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PO-10087</t>
+          <t>PO-10086</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4395,7 +4401,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PO-10088</t>
+          <t>PO-10087</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4423,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>-1.67</v>
+        <v>22.33</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4444,7 +4450,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PO-10089</t>
+          <t>PO-10088</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4499,7 +4505,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PO-10091</t>
+          <t>PO-10090</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4554,7 +4560,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PO-10092</t>
+          <t>PO-10091</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4582,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>1487.37</v>
+        <v>1511.36</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -4603,7 +4609,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PO-10094</t>
+          <t>PO-10093</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4658,7 +4664,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PO-10095</t>
+          <t>PO-10094</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4713,7 +4719,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PO-10096</t>
+          <t>PO-10095</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4741,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>39.71</v>
+        <v>63.71</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -4762,7 +4768,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PO-10097</t>
+          <t>PO-10096</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4790,7 +4796,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>594.84</v>
+        <v>618.84</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -4811,7 +4817,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PO-10099</t>
+          <t>PO-10098</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4866,7 +4872,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PO-10100</t>
+          <t>PO-10099</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4921,7 +4927,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PO-10101</t>
+          <t>PO-10100</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4976,7 +4982,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PO-10102</t>
+          <t>PO-10101</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5004,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>714.8200000000001</v>
+        <v>738.8200000000001</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -5025,7 +5031,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PO-10103</t>
+          <t>PO-10102</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5053,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>-9.4</v>
+        <v>14.6</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5074,7 +5080,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PO-10104</t>
+          <t>PO-10103</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5129,7 +5135,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PO-10105</t>
+          <t>PO-10104</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5157,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>1105.95</v>
+        <v>1129.94</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5178,7 +5184,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PO-10108</t>
+          <t>PO-10107</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5233,7 +5239,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PO-10110</t>
+          <t>PO-10109</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5288,7 +5294,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PO-10111</t>
+          <t>PO-10110</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5316,7 +5322,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>401.96</v>
+        <v>425.96</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -5337,7 +5343,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PO-10112</t>
+          <t>PO-10111</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5392,7 +5398,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PO-10113</t>
+          <t>PO-10112</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5447,7 +5453,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PO-10114</t>
+          <t>PO-10113</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5502,7 +5508,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PO-10116</t>
+          <t>PO-10115</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5557,7 +5563,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PO-10118</t>
+          <t>PO-10117</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5612,7 +5618,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PO-10120</t>
+          <t>PO-10119</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5667,7 +5673,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PO-10121</t>
+          <t>PO-10120</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5722,7 +5728,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PO-10123</t>
+          <t>PO-10122</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5750,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1334.72</v>
+        <v>1358.72</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -5771,7 +5777,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PO-10124</t>
+          <t>PO-10123</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5826,7 +5832,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PO-10125</t>
+          <t>PO-10124</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5881,7 +5887,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PO-10126</t>
+          <t>PO-10125</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5936,7 +5942,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PO-10128</t>
+          <t>PO-10127</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5991,7 +5997,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PO-10129</t>
+          <t>PO-10128</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6046,7 +6052,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PO-10130</t>
+          <t>PO-10129</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6101,7 +6107,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PO-10134</t>
+          <t>PO-10133</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6156,7 +6162,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PO-10136</t>
+          <t>PO-10135</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6211,7 +6217,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PO-10137</t>
+          <t>PO-10136</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6266,7 +6272,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PO-10138</t>
+          <t>PO-10137</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6321,7 +6327,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PO-10139</t>
+          <t>PO-10138</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6376,7 +6382,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PO-10140</t>
+          <t>PO-10139</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6431,7 +6437,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PO-10141</t>
+          <t>PO-10140</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6486,7 +6492,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PO-10143</t>
+          <t>PO-10142</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6541,7 +6547,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PO-10144</t>
+          <t>PO-10143</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6596,7 +6602,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PO-10145</t>
+          <t>PO-10144</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6651,7 +6657,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PO-10146</t>
+          <t>PO-10145</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6706,7 +6712,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PO-10147</t>
+          <t>PO-10146</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6734,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>70.23999999999999</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -6755,7 +6761,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PO-10148</t>
+          <t>PO-10147</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6810,7 +6816,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PO-10149</t>
+          <t>PO-10148</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6865,7 +6871,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PO-10150</t>
+          <t>PO-10149</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6920,7 +6926,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PO-10151</t>
+          <t>PO-10150</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6975,7 +6981,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PO-10153</t>
+          <t>PO-10152</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7030,7 +7036,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PO-10154</t>
+          <t>PO-10153</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7085,7 +7091,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PO-10155</t>
+          <t>PO-10154</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7140,7 +7146,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PO-10156</t>
+          <t>PO-10155</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7168,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>594.9</v>
+        <v>618.9</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -7189,7 +7195,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PO-10157</t>
+          <t>PO-10156</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7244,7 +7250,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PO-10158</t>
+          <t>PO-10157</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7299,7 +7305,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PO-10161</t>
+          <t>PO-10160</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7354,7 +7360,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PO-10163</t>
+          <t>PO-10162</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7382,7 +7388,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>79.97</v>
+        <v>103.96</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -7403,7 +7409,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PO-10164</t>
+          <t>PO-10163</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7458,7 +7464,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PO-10165</t>
+          <t>PO-10164</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7513,7 +7519,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PO-10166</t>
+          <t>PO-10165</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7568,7 +7574,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PO-10169</t>
+          <t>PO-10168</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7623,7 +7629,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PO-10171</t>
+          <t>PO-10170</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7678,7 +7684,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PO-10173</t>
+          <t>PO-10172</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7733,7 +7739,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PO-10175</t>
+          <t>PO-10174</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7788,7 +7794,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PO-10179</t>
+          <t>PO-10178</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7816,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>497.33</v>
+        <v>521.3200000000001</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -7837,7 +7843,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PO-10180</t>
+          <t>PO-10179</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7892,7 +7898,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PO-10181</t>
+          <t>PO-10180</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7947,7 +7953,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PO-10182</t>
+          <t>PO-10181</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8002,7 +8008,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PO-10183</t>
+          <t>PO-10182</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8030,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>-79.28</v>
+        <v>-55.28</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8051,7 +8057,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PO-10185</t>
+          <t>PO-10184</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8106,7 +8112,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PO-10186</t>
+          <t>PO-10185</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8134,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>904.83</v>
+        <v>928.83</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8155,7 +8161,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PO-10187</t>
+          <t>PO-10186</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8210,7 +8216,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PO-10188</t>
+          <t>PO-10187</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8265,7 +8271,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PO-10190</t>
+          <t>PO-10189</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8293,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>7.72</v>
+        <v>31.72</v>
       </c>
       <c r="L129" t="inlineStr">
         <is>
@@ -8314,7 +8320,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PO-10192</t>
+          <t>PO-10191</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8369,7 +8375,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PO-10193</t>
+          <t>PO-10192</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8424,7 +8430,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PO-10194</t>
+          <t>PO-10193</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8452,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>1326.41</v>
+        <v>1350.4</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -8473,7 +8479,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PO-10198</t>
+          <t>PO-10197</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8501,7 +8507,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>144.6</v>
+        <v>168.6</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -8522,7 +8528,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PO-10200</t>
+          <t>PO-10199</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8577,7 +8583,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PO-10201</t>
+          <t>PO-10200</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8632,7 +8638,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PO-10202</t>
+          <t>PO-10201</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8660,7 +8666,7 @@
         <v>0</v>
       </c>
       <c r="K136" t="n">
-        <v>779.7</v>
+        <v>803.6900000000001</v>
       </c>
       <c r="L136" t="inlineStr">
         <is>
@@ -8681,7 +8687,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PO-10205</t>
+          <t>PO-10204</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8736,7 +8742,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PO-10206</t>
+          <t>PO-10205</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8764,7 +8770,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>267.93</v>
+        <v>291.92</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -8785,7 +8791,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PO-10207</t>
+          <t>PO-10206</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8813,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>248.15</v>
+        <v>272.14</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -8834,7 +8840,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PO-10208</t>
+          <t>PO-10207</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8889,7 +8895,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PO-10209</t>
+          <t>PO-10208</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8944,7 +8950,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PO-10210</t>
+          <t>PO-10209</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8972,7 +8978,7 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>-79.2</v>
+        <v>-55.2</v>
       </c>
       <c r="L142" t="inlineStr">
         <is>
@@ -8993,7 +8999,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PO-10211</t>
+          <t>PO-10210</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9048,7 +9054,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PO-10212</t>
+          <t>PO-10211</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9103,7 +9109,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PO-10214</t>
+          <t>PO-10213</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9158,7 +9164,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PO-10215</t>
+          <t>PO-10214</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9213,7 +9219,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PO-10217</t>
+          <t>PO-10216</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9241,7 +9247,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -9262,7 +9268,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PO-10219</t>
+          <t>PO-10218</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9317,7 +9323,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PO-10220</t>
+          <t>PO-10219</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9372,7 +9378,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PO-10221</t>
+          <t>PO-10220</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9427,7 +9433,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PO-10222</t>
+          <t>PO-10221</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9455,7 +9461,7 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>934.1900000000001</v>
+        <v>958.1799999999999</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -9476,7 +9482,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PO-10223</t>
+          <t>PO-10222</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9531,7 +9537,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PO-10225</t>
+          <t>PO-10224</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9559,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>-49.19</v>
+        <v>-25.2</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PO-10226</t>
+          <t>PO-10225</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9608,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>1112.6</v>
+        <v>1136.59</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -9629,7 +9635,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PO-10227</t>
+          <t>PO-10226</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9684,7 +9690,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PO-10228</t>
+          <t>PO-10227</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9739,7 +9745,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PO-10229</t>
+          <t>PO-10228</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9794,7 +9800,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PO-10230</t>
+          <t>PO-10229</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9822,7 +9828,7 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>49.84</v>
+        <v>73.84</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -9843,7 +9849,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PO-10231</t>
+          <t>PO-10230</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9898,7 +9904,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PO-10232</t>
+          <t>PO-10231</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9953,7 +9959,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PO-10233</t>
+          <t>PO-10232</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10008,7 +10014,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PO-10234</t>
+          <t>PO-10233</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10063,7 +10069,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PO-10235</t>
+          <t>PO-10234</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10091,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>1093.41</v>
+        <v>1117.4</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -10112,7 +10118,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PO-10236</t>
+          <t>PO-10235</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10167,7 +10173,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PO-10237</t>
+          <t>PO-10236</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10195,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>399.31</v>
+        <v>423.3</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10216,7 +10222,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PO-10238</t>
+          <t>PO-10237</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10271,7 +10277,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PO-10241</t>
+          <t>PO-10240</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10326,7 +10332,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PO-10242</t>
+          <t>PO-10241</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10381,7 +10387,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PO-10243</t>
+          <t>PO-10242</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10436,7 +10442,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PO-10244</t>
+          <t>PO-10243</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10464,7 +10470,7 @@
         <v>0</v>
       </c>
       <c r="K170" t="n">
-        <v>904.8099999999999</v>
+        <v>928.8099999999999</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -10485,7 +10491,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PO-10245</t>
+          <t>PO-10244</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10540,7 +10546,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PO-10246</t>
+          <t>PO-10245</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10595,7 +10601,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PO-10247</t>
+          <t>PO-10246</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10650,7 +10656,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PO-10250</t>
+          <t>PO-10249</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10705,7 +10711,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PO-10251</t>
+          <t>PO-10250</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10760,7 +10766,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PO-10252</t>
+          <t>PO-10251</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10815,7 +10821,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PO-10253</t>
+          <t>PO-10252</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10870,7 +10876,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PO-10254</t>
+          <t>PO-10253</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10925,50 +10931,44 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10256</t>
+          <t>PO-10255</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-09-13T12:12:35.271945+00:00</t>
+          <t>2026-10-13T08:12:35.271945+00:00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-09-15T15:47:08.874839+00:00</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-09-18T16:28:26.290275+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-15T11:47:08.874839+00:00</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
         <v>51.58</v>
       </c>
-      <c r="H179" t="n">
-        <v>72.69</v>
-      </c>
-      <c r="I179" t="n">
-        <v>124.26</v>
-      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="b">
-        <v>1</v>
-      </c>
-      <c r="K179" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>-117.1</v>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10257</t>
+          <t>PO-10256</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10258</t>
+          <t>PO-10257</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10260</t>
+          <t>PO-10259</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11118,7 +11118,7 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>-6.09</v>
+        <v>17.91</v>
       </c>
       <c r="L182" t="inlineStr">
         <is>
@@ -11139,7 +11139,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10261</t>
+          <t>PO-10260</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10264</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10265</t>
+          <t>PO-10264</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10266</t>
+          <t>PO-10265</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11332,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>826.6900000000001</v>
+        <v>850.6799999999999</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10270</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11436,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>-32.23</v>
+        <v>-8.23</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10272</t>
+          <t>PO-10271</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11540,7 +11540,7 @@
         <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>1102.97</v>
+        <v>1126.96</v>
       </c>
       <c r="L190" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10273</t>
+          <t>PO-10272</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10274</t>
+          <t>PO-10273</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11644,7 +11644,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1444.9</v>
+        <v>1468.9</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10278</t>
+          <t>PO-10277</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11693,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="K193" t="n">
-        <v>-6.87</v>
+        <v>17.12</v>
       </c>
       <c r="L193" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10280</t>
+          <t>PO-10279</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10283</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10285</t>
+          <t>PO-10284</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10285</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11907,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>1425.17</v>
+        <v>1449.16</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -11928,7 +11928,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10287</t>
+          <t>PO-10286</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10288</t>
+          <t>PO-10287</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12038,7 +12038,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10289</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12066,7 +12066,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>869.09</v>
+        <v>893.09</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10290</t>
+          <t>PO-10289</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10291</t>
+          <t>PO-10290</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12170,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>-26.66</v>
+        <v>-2.66</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10292</t>
+          <t>PO-10291</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>94.47</v>
+        <v>118.46</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10294</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12295,7 +12295,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10294</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10296</t>
+          <t>PO-10295</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10298</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12488,7 +12488,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>97.47</v>
+        <v>121.47</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -12509,7 +12509,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10299</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12564,7 +12564,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10300</t>
+          <t>PO-10299</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10300</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10301</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10305</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12839,7 +12839,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12867,7 +12867,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>-2.09</v>
+        <v>21.91</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10307</t>
+          <t>PO-10306</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10308</t>
+          <t>PO-10307</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10309</t>
+          <t>PO-10308</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>1023.37</v>
+        <v>1047.37</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PO-10310</t>
+          <t>PO-10309</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PO-10313</t>
+          <t>PO-10312</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PO-10316</t>
+          <t>PO-10315</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PO-10318</t>
+          <t>PO-10317</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PO-10319</t>
+          <t>PO-10318</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PO-10320</t>
+          <t>PO-10319</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13350,7 +13350,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>1286.34</v>
+        <v>1310.34</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PO-10321</t>
+          <t>PO-10320</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13426,12 +13426,12 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PO-10323</t>
+          <t>PO-10322</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13444,18 +13444,24 @@
           <t>2026-10-05T04:38:33.163430+00:00</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:55:56.121318+00:00</t>
+        </is>
+      </c>
       <c r="G226" t="n">
         <v>61.1</v>
       </c>
-      <c r="H226" t="inlineStr"/>
-      <c r="I226" t="inlineStr"/>
+      <c r="H226" t="n">
+        <v>61.29</v>
+      </c>
+      <c r="I226" t="n">
+        <v>122.39</v>
+      </c>
       <c r="J226" t="b">
-        <v>0</v>
-      </c>
-      <c r="K226" t="n">
-        <v>115.58</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -13475,7 +13481,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PO-10325</t>
+          <t>PO-10324</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13530,7 +13536,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PO-10326</t>
+          <t>PO-10325</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13558,7 +13564,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>1406.9</v>
+        <v>1430.89</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -13579,7 +13585,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PO-10328</t>
+          <t>PO-10327</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13607,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>731.26</v>
+        <v>755.26</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13628,7 +13634,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PO-10330</t>
+          <t>PO-10329</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13683,7 +13689,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PO-10331</t>
+          <t>PO-10330</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13711,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>26.1</v>
+        <v>50.1</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -13732,7 +13738,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PO-10334</t>
+          <t>PO-10333</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13760,7 +13766,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>1403.8</v>
+        <v>1427.8</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13776,12 +13782,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PO-10336</t>
+          <t>PO-10338</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13791,27 +13797,27 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-09-09T00:51:22.075035+00:00</t>
+          <t>2026-08-02T10:46:21.028488+00:00</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>2026-09-10T00:02:54.427474+00:00</t>
+          <t>2026-08-04T10:49:15.655675+00:00</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-09-12T17:01:28.560670+00:00</t>
+          <t>2026-08-08T02:10:18.538462+00:00</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>23.19</v>
+        <v>48.05</v>
       </c>
       <c r="H233" t="n">
-        <v>64.98</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="I233" t="n">
-        <v>88.17</v>
+        <v>135.4</v>
       </c>
       <c r="J233" t="b">
         <v>1</v>
@@ -13819,12 +13825,12 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S31</t>
         </is>
       </c>
     </row>
@@ -13836,7 +13842,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PO-10338</t>
+          <t>PO-10340</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13891,7 +13897,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PO-10339</t>
+          <t>PO-10341</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13946,7 +13952,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PO-10340</t>
+          <t>PO-10342</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14001,7 +14007,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PO-10342</t>
+          <t>PO-10344</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14029,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>340.15</v>
+        <v>364.14</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -14050,7 +14056,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PO-10343</t>
+          <t>PO-10345</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14078,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>1452.05</v>
+        <v>1476.04</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -14099,7 +14105,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PO-10345</t>
+          <t>PO-10347</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14127,7 +14133,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>10.58</v>
+        <v>34.58</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -14148,7 +14154,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PO-10346</t>
+          <t>PO-10348</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14203,7 +14209,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PO-10348</t>
+          <t>PO-10350</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14258,7 +14264,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PO-10351</t>
+          <t>PO-10353</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14313,7 +14319,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PO-10353</t>
+          <t>PO-10355</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14368,7 +14374,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PO-10354</t>
+          <t>PO-10356</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14423,7 +14429,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PO-10355</t>
+          <t>PO-10357</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14478,7 +14484,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PO-10356</t>
+          <t>PO-10358</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14533,7 +14539,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PO-10357</t>
+          <t>PO-10359</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14583,12 +14589,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PO-10360</t>
+          <t>PO-10363</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14598,27 +14604,27 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-10T20:04:19.140979+00:00</t>
+          <t>2026-09-02T16:46:00.991584+00:00</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>2026-08-13T05:52:54.678092+00:00</t>
+          <t>2026-09-03T03:25:13.457544+00:00</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>2026-08-13T15:57:05.440797+00:00</t>
+          <t>2026-09-04T01:49:00.187409+00:00</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>57.81</v>
+        <v>10.65</v>
       </c>
       <c r="H248" t="n">
-        <v>10.07</v>
+        <v>22.4</v>
       </c>
       <c r="I248" t="n">
-        <v>67.88</v>
+        <v>33.05</v>
       </c>
       <c r="J248" t="b">
         <v>1</v>
@@ -14626,12 +14632,12 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -14643,56 +14649,62 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PO-10361</t>
+          <t>PO-10365</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-10-06T10:25:52.126474+00:00</t>
+          <t>2026-08-20T18:22:57.141658+00:00</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>2026-10-06T23:54:22.521807+00:00</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr"/>
+          <t>2026-08-21T05:28:15.465215+00:00</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>2026-08-24T12:44:42.023063+00:00</t>
+        </is>
+      </c>
       <c r="G249" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="H249" t="inlineStr"/>
-      <c r="I249" t="inlineStr"/>
+        <v>11.09</v>
+      </c>
+      <c r="H249" t="n">
+        <v>79.27</v>
+      </c>
+      <c r="I249" t="n">
+        <v>90.36</v>
+      </c>
       <c r="J249" t="b">
-        <v>0</v>
-      </c>
-      <c r="K249" t="n">
-        <v>24.69</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PO-10362</t>
+          <t>PO-10366</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14702,27 +14714,27 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-20T02:42:34.537640+00:00</t>
+          <t>2026-08-30T11:08:27.132700+00:00</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-08-22T06:33:32.658975+00:00</t>
+          <t>2026-08-30T16:05:36.736330+00:00</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2026-08-23T05:43:51.676108+00:00</t>
+          <t>2026-09-01T10:25:23.747432+00:00</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>51.85</v>
+        <v>4.95</v>
       </c>
       <c r="H250" t="n">
-        <v>23.17</v>
+        <v>42.33</v>
       </c>
       <c r="I250" t="n">
-        <v>75.02</v>
+        <v>47.28</v>
       </c>
       <c r="J250" t="b">
         <v>1</v>
@@ -14735,19 +14747,19 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PO-10363</t>
+          <t>PO-10370</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14757,27 +14769,27 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-15T02:14:00.035703+00:00</t>
+          <t>2026-09-06T10:07:18.157926+00:00</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2026-09-15T20:36:50.530217+00:00</t>
+          <t>2026-09-08T13:28:39.058618+00:00</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2026-09-17T03:49:09.983200+00:00</t>
+          <t>2026-09-09T13:09:29.477957+00:00</t>
         </is>
       </c>
       <c r="G251" t="n">
-        <v>18.38</v>
+        <v>51.36</v>
       </c>
       <c r="H251" t="n">
-        <v>31.21</v>
+        <v>23.68</v>
       </c>
       <c r="I251" t="n">
-        <v>49.59</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="J251" t="b">
         <v>1</v>
@@ -14790,19 +14802,19 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PO-10366</t>
+          <t>PO-10371</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14812,27 +14824,27 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-06T10:07:18.157926+00:00</t>
+          <t>2026-10-04T10:17:28.209232+00:00</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2026-09-08T13:28:39.058618+00:00</t>
+          <t>2026-10-07T16:04:50.016311+00:00</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2026-09-09T13:09:29.477957+00:00</t>
+          <t>2026-10-08T07:08:56.289812+00:00</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>51.36</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="H252" t="n">
-        <v>23.68</v>
+        <v>15.07</v>
       </c>
       <c r="I252" t="n">
-        <v>75.04000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="J252" t="b">
         <v>1</v>
@@ -14840,73 +14852,79 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PO-10367</t>
+          <t>PO-10372</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-10-04T10:17:28.209232+00:00</t>
+          <t>2026-08-18T16:09:14.191751+00:00</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-07T16:04:50.016311+00:00</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr"/>
+          <t>2026-08-19T00:47:47.640722+00:00</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-08-20T13:03:23.330378+00:00</t>
+        </is>
+      </c>
       <c r="G253" t="n">
-        <v>77.79000000000001</v>
-      </c>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
+        <v>8.640000000000001</v>
+      </c>
+      <c r="H253" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="I253" t="n">
+        <v>44.9</v>
+      </c>
       <c r="J253" t="b">
-        <v>0</v>
-      </c>
-      <c r="K253" t="n">
-        <v>72.83</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PO-10368</t>
+          <t>PO-10374</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14916,27 +14934,27 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-18T16:09:14.191751+00:00</t>
+          <t>2026-09-07T05:44:30.371723+00:00</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-08-19T00:47:47.640722+00:00</t>
+          <t>2026-09-09T13:09:40.533384+00:00</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-20T13:03:23.330378+00:00</t>
+          <t>2026-09-10T21:01:07.362758+00:00</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>8.640000000000001</v>
+        <v>55.42</v>
       </c>
       <c r="H254" t="n">
-        <v>36.26</v>
+        <v>31.86</v>
       </c>
       <c r="I254" t="n">
-        <v>44.9</v>
+        <v>87.28</v>
       </c>
       <c r="J254" t="b">
         <v>1</v>
@@ -14944,24 +14962,24 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PO-10370</t>
+          <t>PO-10375</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -14971,27 +14989,27 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-07T05:44:30.371723+00:00</t>
+          <t>2026-09-02T20:17:52.235828+00:00</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>2026-09-09T13:09:40.533384+00:00</t>
+          <t>2026-09-03T01:42:50.926020+00:00</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>2026-09-10T21:01:07.362758+00:00</t>
+          <t>2026-09-05T22:04:21.709720+00:00</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>55.42</v>
+        <v>5.42</v>
       </c>
       <c r="H255" t="n">
-        <v>31.86</v>
+        <v>68.36</v>
       </c>
       <c r="I255" t="n">
-        <v>87.28</v>
+        <v>73.77</v>
       </c>
       <c r="J255" t="b">
         <v>1</v>
@@ -15004,123 +15022,123 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PO-10371</t>
+          <t>PO-10376</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-02T20:17:52.235828+00:00</t>
+          <t>2026-10-07T02:17:21.256685+00:00</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>2026-09-03T01:42:50.926020+00:00</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>2026-09-05T22:04:21.709720+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-08T11:37:54.484728+00:00</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr"/>
       <c r="G256" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="H256" t="n">
-        <v>68.36</v>
-      </c>
-      <c r="I256" t="n">
-        <v>73.77</v>
-      </c>
+        <v>33.34</v>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
       <c r="J256" t="b">
-        <v>1</v>
-      </c>
-      <c r="K256" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>32.83</v>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PO-10372</t>
+          <t>PO-10377</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-10-07T02:17:21.256685+00:00</t>
+          <t>2026-09-22T10:38:34.493772+00:00</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>2026-10-08T11:37:54.484728+00:00</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr"/>
+          <t>2026-09-23T05:39:55.516872+00:00</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:11:54.083981+00:00</t>
+        </is>
+      </c>
       <c r="G257" t="n">
-        <v>33.34</v>
-      </c>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
+        <v>19.02</v>
+      </c>
+      <c r="H257" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="I257" t="n">
+        <v>39.56</v>
+      </c>
       <c r="J257" t="b">
-        <v>0</v>
-      </c>
-      <c r="K257" t="n">
-        <v>8.83</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PO-10373</t>
+          <t>PO-10378</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15130,27 +15148,27 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-22T10:38:34.493772+00:00</t>
+          <t>2026-08-21T09:21:16.432267+00:00</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>2026-09-23T05:39:55.516872+00:00</t>
+          <t>2026-08-21T21:31:24.434892+00:00</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>2026-09-24T02:11:54.083981+00:00</t>
+          <t>2026-08-23T06:49:44.417735+00:00</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>19.02</v>
+        <v>12.17</v>
       </c>
       <c r="H258" t="n">
-        <v>20.53</v>
+        <v>33.31</v>
       </c>
       <c r="I258" t="n">
-        <v>39.56</v>
+        <v>45.47</v>
       </c>
       <c r="J258" t="b">
         <v>1</v>
@@ -15158,134 +15176,122 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PO-10374</t>
+          <t>PO-10379</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-21T09:21:16.432267+00:00</t>
+          <t>2026-10-11T18:27:51.059493+00:00</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>2026-08-21T21:31:24.434892+00:00</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>2026-08-23T06:49:44.417735+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-13T01:52:42.911811+00:00</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr"/>
       <c r="G259" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="H259" t="n">
-        <v>33.31</v>
-      </c>
-      <c r="I259" t="n">
-        <v>45.47</v>
-      </c>
+        <v>31.41</v>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
       <c r="J259" t="b">
-        <v>1</v>
-      </c>
-      <c r="K259" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>-79.34999999999999</v>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PO-10376</t>
+          <t>PO-10382</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-20T02:59:39.987883+00:00</t>
+          <t>2026-10-10T22:23:00.883669+00:00</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>2026-08-21T13:32:20.642339+00:00</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>2026-08-27T08:13:01.413099+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-11T13:28:03.145698+00:00</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
       <c r="G260" t="n">
-        <v>34.54</v>
-      </c>
-      <c r="H260" t="n">
-        <v>138.68</v>
-      </c>
-      <c r="I260" t="n">
-        <v>173.22</v>
-      </c>
+        <v>15.08</v>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
       <c r="J260" t="b">
-        <v>1</v>
-      </c>
-      <c r="K260" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>-59.27</v>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PO-10377</t>
+          <t>PO-10384</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15295,27 +15301,27 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-11T05:13:37.264525+00:00</t>
+          <t>2026-08-07T05:26:47.251342+00:00</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>2026-08-12T23:22:34.344797+00:00</t>
+          <t>2026-08-09T13:22:48.921040+00:00</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>2026-08-14T23:58:58.258158+00:00</t>
+          <t>2026-08-14T00:48:01.159260+00:00</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>42.15</v>
+        <v>55.93</v>
       </c>
       <c r="H261" t="n">
-        <v>48.61</v>
+        <v>107.42</v>
       </c>
       <c r="I261" t="n">
-        <v>90.76000000000001</v>
+        <v>163.35</v>
       </c>
       <c r="J261" t="b">
         <v>1</v>
@@ -15328,7 +15334,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -15340,7 +15346,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PO-10379</t>
+          <t>PO-10385</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15350,27 +15356,27 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-09-02T13:20:49.530023+00:00</t>
+          <t>2026-09-20T19:11:54.018783+00:00</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>2026-09-04T05:48:28.474195+00:00</t>
+          <t>2026-09-21T20:51:30.300879+00:00</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>2026-09-05T17:52:57.277567+00:00</t>
+          <t>2026-09-23T13:14:16.958639+00:00</t>
         </is>
       </c>
       <c r="G262" t="n">
-        <v>40.46</v>
+        <v>25.66</v>
       </c>
       <c r="H262" t="n">
-        <v>36.07</v>
+        <v>40.38</v>
       </c>
       <c r="I262" t="n">
-        <v>76.54000000000001</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="J262" t="b">
         <v>1</v>
@@ -15383,19 +15389,19 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PO-10380</t>
+          <t>PO-10387</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15405,27 +15411,27 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-10-03T01:06:37.667073+00:00</t>
+          <t>2026-09-30T12:01:29.481710+00:00</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>2026-10-04T06:34:00.304853+00:00</t>
+          <t>2026-10-01T11:57:13.385327+00:00</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>2026-10-06T04:03:41.863057+00:00</t>
+          <t>2026-10-01T22:32:54.826916+00:00</t>
         </is>
       </c>
       <c r="G263" t="n">
-        <v>29.46</v>
+        <v>23.93</v>
       </c>
       <c r="H263" t="n">
-        <v>45.49</v>
+        <v>10.59</v>
       </c>
       <c r="I263" t="n">
-        <v>74.95</v>
+        <v>34.52</v>
       </c>
       <c r="J263" t="b">
         <v>1</v>
@@ -15433,7 +15439,7 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -15445,96 +15451,96 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PO-10381</t>
+          <t>PO-10389</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-10-01T16:40:38.016322+00:00</t>
+          <t>2026-09-25T08:10:53.064937+00:00</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>2026-10-04T02:02:59.184044+00:00</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr"/>
+          <t>2026-09-26T17:27:21.741545+00:00</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>2026-10-03T01:18:08.486046+00:00</t>
+        </is>
+      </c>
       <c r="G264" t="n">
-        <v>57.37</v>
-      </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
+        <v>33.27</v>
+      </c>
+      <c r="H264" t="n">
+        <v>151.85</v>
+      </c>
+      <c r="I264" t="n">
+        <v>185.12</v>
+      </c>
       <c r="J264" t="b">
-        <v>0</v>
-      </c>
-      <c r="K264" t="n">
-        <v>138.44</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PO-10382</t>
+          <t>PO-10391</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-09-01T07:04:54.095815+00:00</t>
+          <t>2026-09-01T12:22:47.264797+00:00</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>2026-09-03T09:23:23.079877+00:00</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>2026-09-05T23:29:35.318296+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-04T05:01:29.577976+00:00</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
       <c r="G265" t="n">
-        <v>50.31</v>
-      </c>
-      <c r="H265" t="n">
-        <v>62.1</v>
-      </c>
-      <c r="I265" t="n">
-        <v>112.41</v>
-      </c>
+        <v>64.65000000000001</v>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
       <c r="J265" t="b">
-        <v>1</v>
-      </c>
-      <c r="K265" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>886.73</v>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -15554,62 +15560,56 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PO-10385</t>
+          <t>PO-10393</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-06T18:56:03.575526+00:00</t>
+          <t>2026-09-09T06:58:07.387584+00:00</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>2026-08-07T11:27:28.406997+00:00</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>2026-08-08T12:56:16.822739+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-10T08:17:56.143452+00:00</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
       <c r="G266" t="n">
-        <v>16.52</v>
-      </c>
-      <c r="H266" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="I266" t="n">
-        <v>42</v>
-      </c>
+        <v>25.33</v>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
       <c r="J266" t="b">
-        <v>1</v>
-      </c>
-      <c r="K266" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>700.15</v>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PO-10388</t>
+          <t>PO-10394</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15619,27 +15619,27 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-09-12T13:10:24.346964+00:00</t>
+          <t>2026-08-09T11:43:25.551641+00:00</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>2026-09-12T18:01:11.883364+00:00</t>
+          <t>2026-08-11T02:25:10.397224+00:00</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>2026-09-17T17:53:48.866730+00:00</t>
+          <t>2026-08-11T06:04:47.451364+00:00</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>4.85</v>
+        <v>38.7</v>
       </c>
       <c r="H267" t="n">
-        <v>119.88</v>
+        <v>3.66</v>
       </c>
       <c r="I267" t="n">
-        <v>124.72</v>
+        <v>42.36</v>
       </c>
       <c r="J267" t="b">
         <v>1</v>
@@ -15647,61 +15647,67 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PO-10390</t>
+          <t>PO-10395</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-04T15:41:11.639284+00:00</t>
+          <t>2026-09-17T19:05:55.338531+00:00</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-08-06T20:23:24.599044+00:00</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr"/>
+          <t>2026-09-20T21:04:20.549328+00:00</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>2026-09-22T04:54:45.967642+00:00</t>
+        </is>
+      </c>
       <c r="G268" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H268" t="inlineStr"/>
-      <c r="I268" t="inlineStr"/>
+        <v>73.97</v>
+      </c>
+      <c r="H268" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="I268" t="n">
+        <v>105.81</v>
+      </c>
       <c r="J268" t="b">
-        <v>0</v>
-      </c>
-      <c r="K268" t="n">
-        <v>1531.43</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15719,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PO-10391</t>
+          <t>PO-10396</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15723,27 +15729,27 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-24T03:01:27.905564+00:00</t>
+          <t>2026-08-29T12:36:35.137812+00:00</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>2026-08-26T11:21:45.547399+00:00</t>
+          <t>2026-08-30T06:49:31.955008+00:00</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>2026-08-29T04:02:19.480950+00:00</t>
+          <t>2026-09-02T17:01:42.751821+00:00</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>56.34</v>
+        <v>18.22</v>
       </c>
       <c r="H269" t="n">
-        <v>64.68000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I269" t="n">
-        <v>121.01</v>
+        <v>100.42</v>
       </c>
       <c r="J269" t="b">
         <v>1</v>
@@ -15768,7 +15774,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PO-10393</t>
+          <t>PO-10397</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15796,7 +15802,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1031.35</v>
+        <v>1055.35</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15817,7 +15823,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PO-10394</t>
+          <t>PO-10398</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15845,7 +15851,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>1502.6</v>
+        <v>1526.6</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -15866,7 +15872,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PO-10396</t>
+          <t>PO-10400</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15894,7 +15900,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>131.9</v>
+        <v>155.89</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15915,7 +15921,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PO-10397</t>
+          <t>PO-10401</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15943,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1248.3</v>
+        <v>1272.3</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -15964,7 +15970,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PO-10399</t>
+          <t>PO-10403</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16019,7 +16025,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PO-10400</t>
+          <t>PO-10404</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16047,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>578.16</v>
+        <v>602.15</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16068,7 +16074,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PO-10401</t>
+          <t>PO-10405</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16096,7 +16102,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>-51.27</v>
+        <v>-27.27</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -16117,7 +16123,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PO-10402</t>
+          <t>PO-10406</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16172,7 +16178,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PO-10403</t>
+          <t>PO-10407</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16227,7 +16233,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PO-10404</t>
+          <t>PO-10408</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16282,7 +16288,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PO-10405</t>
+          <t>PO-10409</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16337,7 +16343,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PO-10406</t>
+          <t>PO-10410</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16365,7 +16371,7 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>1421.24</v>
+        <v>1445.24</v>
       </c>
       <c r="L281" t="inlineStr">
         <is>
@@ -16386,7 +16392,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PO-10407</t>
+          <t>PO-10411</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16414,7 +16420,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>-29.45</v>
+        <v>-5.46</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16435,7 +16441,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PO-10413</t>
+          <t>PO-10417</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16490,7 +16496,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PO-10414</t>
+          <t>PO-10418</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16545,7 +16551,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PO-10415</t>
+          <t>PO-10419</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16600,7 +16606,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PO-10416</t>
+          <t>PO-10420</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16655,7 +16661,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PO-10418</t>
+          <t>PO-10422</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16710,7 +16716,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PO-10419</t>
+          <t>PO-10423</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16738,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>-29.83</v>
+        <v>-5.84</v>
       </c>
       <c r="L288" t="inlineStr">
         <is>
@@ -16759,7 +16765,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PO-10422</t>
+          <t>PO-10426</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16814,7 +16820,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PO-10423</t>
+          <t>PO-10427</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16869,7 +16875,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PO-10425</t>
+          <t>PO-10429</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16897,7 +16903,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>712.35</v>
+        <v>736.34</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16918,7 +16924,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PO-10426</t>
+          <t>PO-10430</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16973,7 +16979,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PO-10427</t>
+          <t>PO-10431</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17028,7 +17034,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PO-10428</t>
+          <t>PO-10432</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17083,7 +17089,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PO-10429</t>
+          <t>PO-10433</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17138,7 +17144,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PO-10431</t>
+          <t>PO-10435</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17193,7 +17199,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PO-10432</t>
+          <t>PO-10436</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17221,7 +17227,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>501.52</v>
+        <v>525.52</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -17242,7 +17248,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PO-10433</t>
+          <t>PO-10437</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17297,7 +17303,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PO-10434</t>
+          <t>PO-10438</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17352,7 +17358,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PO-10435</t>
+          <t>PO-10439</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17407,7 +17413,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PO-10436</t>
+          <t>PO-10440</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17462,7 +17468,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PO-10437</t>
+          <t>PO-10441</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17517,7 +17523,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PO-10438</t>
+          <t>PO-10442</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17572,7 +17578,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PO-10439</t>
+          <t>PO-10443</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17627,7 +17633,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PO-10441</t>
+          <t>PO-10445</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17655,7 +17661,7 @@
         <v>0</v>
       </c>
       <c r="K305" t="n">
-        <v>897.71</v>
+        <v>921.71</v>
       </c>
       <c r="L305" t="inlineStr">
         <is>
@@ -17676,7 +17682,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PO-10445</t>
+          <t>PO-10449</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17731,12 +17737,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PO-10447</t>
+          <t>PO-10451</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -17749,18 +17755,24 @@
           <t>2026-10-07T13:27:45.229706+00:00</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr"/>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:45:20.147395+00:00</t>
+        </is>
+      </c>
       <c r="G307" t="n">
         <v>36.51</v>
       </c>
-      <c r="H307" t="inlineStr"/>
-      <c r="I307" t="inlineStr"/>
+      <c r="H307" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I307" t="n">
+        <v>40.81</v>
+      </c>
       <c r="J307" t="b">
-        <v>0</v>
-      </c>
-      <c r="K307" t="n">
-        <v>34.17</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -17780,7 +17792,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PO-10449</t>
+          <t>PO-10453</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17835,7 +17847,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PO-10451</t>
+          <t>PO-10455</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17845,12 +17857,12 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-26T23:57:12.352708+00:00</t>
+          <t>2026-10-12T15:52:28.598326+00:00</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>2026-08-27T19:14:13.820101+00:00</t>
+          <t>2026-10-13T11:09:30.065719+00:00</t>
         </is>
       </c>
       <c r="F309" t="inlineStr"/>
@@ -17863,16 +17875,16 @@
         <v>0</v>
       </c>
       <c r="K309" t="n">
-        <v>995.16</v>
+        <v>-100.76</v>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17896,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PO-10452</t>
+          <t>PO-10456</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17912,7 +17924,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>569.24</v>
+        <v>593.24</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -17933,7 +17945,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PO-10453</t>
+          <t>PO-10457</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -17961,7 +17973,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>24.12</v>
+        <v>48.11</v>
       </c>
       <c r="L311" t="inlineStr">
         <is>
@@ -17982,7 +17994,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PO-10454</t>
+          <t>PO-10458</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18037,7 +18049,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PO-10455</t>
+          <t>PO-10459</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18065,7 +18077,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>641.85</v>
+        <v>665.85</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -18086,7 +18098,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PO-10456</t>
+          <t>PO-10460</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18114,7 +18126,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>101.28</v>
+        <v>125.28</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -18135,7 +18147,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10457</t>
+          <t>PO-10461</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18190,7 +18202,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10458</t>
+          <t>PO-10462</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18245,7 +18257,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10461</t>
+          <t>PO-10465</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18300,7 +18312,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10464</t>
+          <t>PO-10468</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18355,7 +18367,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10465</t>
+          <t>PO-10469</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18410,7 +18422,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10467</t>
+          <t>PO-10471</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18465,7 +18477,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10468</t>
+          <t>PO-10472</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18520,7 +18532,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10469</t>
+          <t>PO-10473</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18575,7 +18587,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10471</t>
+          <t>PO-10475</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18603,7 +18615,7 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>686.15</v>
+        <v>710.15</v>
       </c>
       <c r="L323" t="inlineStr">
         <is>
@@ -18624,7 +18636,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10472</t>
+          <t>PO-10476</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18679,7 +18691,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10474</t>
+          <t>PO-10478</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18734,7 +18746,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10482</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18789,7 +18801,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10479</t>
+          <t>PO-10483</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -18817,7 +18829,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>273.73</v>
+        <v>297.72</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -18838,7 +18850,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10480</t>
+          <t>PO-10484</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18866,7 +18878,7 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>365.51</v>
+        <v>389.5</v>
       </c>
       <c r="L328" t="inlineStr">
         <is>
@@ -18887,7 +18899,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10481</t>
+          <t>PO-10485</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18942,7 +18954,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10482</t>
+          <t>PO-10486</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18970,7 +18982,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>1015.27</v>
+        <v>1039.26</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -18991,7 +19003,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PO-10483</t>
+          <t>PO-10487</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19046,7 +19058,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PO-10484</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19101,7 +19113,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PO-10485</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19156,7 +19168,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10488</t>
+          <t>PO-10492</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19211,7 +19223,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10490</t>
+          <t>PO-10494</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19239,7 +19251,7 @@
         <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>-19.21</v>
+        <v>4.78</v>
       </c>
       <c r="L335" t="inlineStr">
         <is>
@@ -19260,7 +19272,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10491</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19315,7 +19327,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10498</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19370,7 +19382,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10496</t>
+          <t>PO-10500</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19425,7 +19437,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10497</t>
+          <t>PO-10501</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19480,7 +19492,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10499</t>
+          <t>PO-10503</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19535,7 +19547,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10500</t>
+          <t>PO-10504</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19590,7 +19602,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10501</t>
+          <t>PO-10505</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19645,7 +19657,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10502</t>
+          <t>PO-10506</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19700,7 +19712,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10503</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19755,7 +19767,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10507</t>
+          <t>PO-10511</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19810,7 +19822,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10509</t>
+          <t>PO-10513</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19838,7 +19850,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>-32.31</v>
+        <v>-8.32</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -19859,7 +19871,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10510</t>
+          <t>PO-10514</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19914,7 +19926,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10511</t>
+          <t>PO-10515</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19969,7 +19981,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10512</t>
+          <t>PO-10516</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -19997,7 +20009,7 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>1212.66</v>
+        <v>1236.66</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
@@ -20018,7 +20030,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10514</t>
+          <t>PO-10518</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20046,7 +20058,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>438.45</v>
+        <v>462.45</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -20067,7 +20079,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10515</t>
+          <t>PO-10519</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20095,7 +20107,7 @@
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>135.89</v>
+        <v>159.89</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -20116,7 +20128,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10516</t>
+          <t>PO-10520</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20144,7 +20156,7 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>37.28</v>
+        <v>61.28</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -20165,7 +20177,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10517</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20220,50 +20232,44 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10522</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-09-07T08:25:04.559072+00:00</t>
+          <t>2026-10-12T07:25:04.559072+00:00</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-09-08T11:27:14.088287+00:00</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>2026-09-08T23:27:01.241095+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-13T10:27:14.088287+00:00</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
         <v>27.04</v>
       </c>
-      <c r="H354" t="n">
-        <v>12</v>
-      </c>
-      <c r="I354" t="n">
-        <v>39.03</v>
-      </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr"/>
       <c r="J354" t="b">
-        <v>1</v>
-      </c>
-      <c r="K354" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
+        <v>-92.3</v>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -20275,7 +20281,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10519</t>
+          <t>PO-10523</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20303,7 +20309,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>1375.35</v>
+        <v>1399.34</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -20324,7 +20330,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10525</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20379,7 +20385,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10526</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20407,7 +20413,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>1393.82</v>
+        <v>1417.81</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -20428,7 +20434,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10525</t>
+          <t>PO-10529</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20483,7 +20489,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10526</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20511,7 +20517,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>1247.58</v>
+        <v>1271.58</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -20532,7 +20538,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10527</t>
+          <t>PO-10531</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20587,7 +20593,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10528</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20642,7 +20648,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10533</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -20697,7 +20703,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10530</t>
+          <t>PO-10534</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -20725,7 +20731,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>729.45</v>
+        <v>753.4400000000001</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -20746,7 +20752,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10532</t>
+          <t>PO-10536</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20801,7 +20807,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10533</t>
+          <t>PO-10537</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20856,7 +20862,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10536</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20911,7 +20917,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10538</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20966,7 +20972,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10543</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21021,7 +21027,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10540</t>
+          <t>PO-10544</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21076,7 +21082,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21131,7 +21137,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10544</t>
+          <t>PO-10548</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21186,7 +21192,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10546</t>
+          <t>PO-10550</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21241,7 +21247,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10551</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21296,7 +21302,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10548</t>
+          <t>PO-10552</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21351,7 +21357,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10549</t>
+          <t>PO-10553</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21406,7 +21412,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10553</t>
+          <t>PO-10557</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21461,7 +21467,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10554</t>
+          <t>PO-10558</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21516,7 +21522,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10556</t>
+          <t>PO-10560</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21571,7 +21577,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10557</t>
+          <t>PO-10561</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21626,7 +21632,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10561</t>
+          <t>PO-10565</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21681,7 +21687,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10562</t>
+          <t>PO-10566</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21709,7 +21715,7 @@
         <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>1018.95</v>
+        <v>1042.94</v>
       </c>
       <c r="L381" t="inlineStr">
         <is>
@@ -21730,7 +21736,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10563</t>
+          <t>PO-10567</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21785,7 +21791,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10564</t>
+          <t>PO-10568</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21840,7 +21846,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10568</t>
+          <t>PO-10572</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -21895,7 +21901,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10570</t>
+          <t>PO-10574</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21923,7 +21929,7 @@
         <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>646.74</v>
+        <v>670.74</v>
       </c>
       <c r="L385" t="inlineStr">
         <is>
@@ -21944,7 +21950,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10571</t>
+          <t>PO-10575</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -21972,7 +21978,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>777.34</v>
+        <v>801.34</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -21993,7 +21999,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10572</t>
+          <t>PO-10576</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22048,7 +22054,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10575</t>
+          <t>PO-10579</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22076,7 +22082,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="n">
-        <v>4.62</v>
+        <v>28.61</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -22097,7 +22103,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10576</t>
+          <t>PO-10580</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -22152,7 +22158,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10579</t>
+          <t>PO-10583</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -22207,7 +22213,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10580</t>
+          <t>PO-10584</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22262,7 +22268,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10583</t>
+          <t>PO-10587</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22290,7 +22296,7 @@
         <v>0</v>
       </c>
       <c r="K392" t="n">
-        <v>250.81</v>
+        <v>274.81</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
@@ -22311,7 +22317,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10584</t>
+          <t>PO-10588</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22366,7 +22372,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10585</t>
+          <t>PO-10589</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22421,7 +22427,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10589</t>
+          <t>PO-10593</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22449,7 +22455,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>827.45</v>
+        <v>851.4400000000001</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -22470,7 +22476,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10591</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22525,7 +22531,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PO-10592</t>
+          <t>PO-10596</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -22580,7 +22586,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PO-10594</t>
+          <t>PO-10598</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -22635,7 +22641,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10599</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22679,226 +22685,6 @@
       <c r="M399" t="inlineStr">
         <is>
           <t>2026-S36</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Fluxo Denim</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>PO-10596</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>2026-08-25T00:36:56.096295+00:00</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>2026-08-25T22:55:42.840833+00:00</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-08-28T16:05:18.710307+00:00</t>
-        </is>
-      </c>
-      <c r="G400" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="H400" t="n">
-        <v>65.16</v>
-      </c>
-      <c r="I400" t="n">
-        <v>87.47</v>
-      </c>
-      <c r="J400" t="b">
-        <v>1</v>
-      </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>2026-S35</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Delta Sports</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>PO-10597</t>
-        </is>
-      </c>
-      <c r="C401" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>2026-09-20T15:04:30.893700+00:00</t>
-        </is>
-      </c>
-      <c r="E401" t="inlineStr">
-        <is>
-          <t>2026-09-21T12:21:21.838950+00:00</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>2026-09-27T07:53:01.185675+00:00</t>
-        </is>
-      </c>
-      <c r="G401" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H401" t="n">
-        <v>139.53</v>
-      </c>
-      <c r="I401" t="n">
-        <v>160.81</v>
-      </c>
-      <c r="J401" t="b">
-        <v>1</v>
-      </c>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M401" t="inlineStr">
-        <is>
-          <t>2026-S38</t>
-        </is>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Delta Sports</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>PO-10598</t>
-        </is>
-      </c>
-      <c r="C402" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>2026-09-21T02:01:34.280043+00:00</t>
-        </is>
-      </c>
-      <c r="E402" t="inlineStr">
-        <is>
-          <t>2026-09-22T02:01:16.127104+00:00</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>2026-09-27T00:17:00.385352+00:00</t>
-        </is>
-      </c>
-      <c r="G402" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H402" t="n">
-        <v>118.26</v>
-      </c>
-      <c r="I402" t="n">
-        <v>142.26</v>
-      </c>
-      <c r="J402" t="b">
-        <v>1</v>
-      </c>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M402" t="inlineStr">
-        <is>
-          <t>2026-S39</t>
-        </is>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Fluxo Denim</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>PO-10599</t>
-        </is>
-      </c>
-      <c r="C403" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>2026-08-26T17:05:31.538533+00:00</t>
-        </is>
-      </c>
-      <c r="E403" t="inlineStr">
-        <is>
-          <t>2026-08-29T00:38:08.544159+00:00</t>
-        </is>
-      </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>2026-08-30T11:19:55.215232+00:00</t>
-        </is>
-      </c>
-      <c r="G403" t="n">
-        <v>55.54</v>
-      </c>
-      <c r="H403" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="I403" t="n">
-        <v>90.23999999999999</v>
-      </c>
-      <c r="J403" t="b">
-        <v>1</v>
-      </c>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="M403" t="inlineStr">
-        <is>
-          <t>2026-S35</t>
         </is>
       </c>
     </row>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>93</v>
+        <v>92.2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.7</v>
+        <v>75.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.4</v>
+        <v>47.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7">
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>222</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>90</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="3">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>96.3</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="4">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>91.2</v>
+        <v>91.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>86.2</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>76.5</v>
+        <v>76.90000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F8" t="n">
         <v>22</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>76.59999999999999</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>86.09999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="10">
@@ -900,19 +900,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>53.2</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="12">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E12" t="n">
         <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>70.09999999999999</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>52.3</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="16">
@@ -1092,10 +1092,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F16" t="n">
         <v>55</v>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1124,10 +1124,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F17" t="n">
         <v>45</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>41.6</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="18">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>24.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>31.1</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="20">
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E20" t="n">
         <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="22">
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>63.4</v>
+        <v>66.7</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M403"/>
+  <dimension ref="A1:M407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>863.4299999999999</v>
+        <v>887.39</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>974.55</v>
+        <v>998.52</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>98.76000000000001</v>
+        <v>122.73</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-98.5</v>
+        <v>-74.54000000000001</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1353.43</v>
+        <v>1377.39</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>173.93</v>
+        <v>197.9</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-30.01</v>
+        <v>-6.05</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>759.89</v>
+        <v>783.86</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1116.93</v>
+        <v>1140.89</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>-22.89</v>
+        <v>1.07</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>53.48</v>
+        <v>77.44</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1557.2</v>
+        <v>1581.17</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>1128.41</v>
+        <v>1152.38</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>-83.14</v>
+        <v>-59.17</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>-59.67</v>
+        <v>-35.71</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>930.4</v>
+        <v>954.37</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>964.72</v>
+        <v>988.6900000000001</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>46.33</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>1535.36</v>
+        <v>1559.32</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>642.84</v>
+        <v>666.8</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>762.8099999999999</v>
+        <v>786.78</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>38.59</v>
+        <v>62.56</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1153.94</v>
+        <v>1177.9</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>449.96</v>
+        <v>473.92</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>1382.71</v>
+        <v>1406.68</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>118.24</v>
+        <v>142.2</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>642.89</v>
+        <v>666.86</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>127.96</v>
+        <v>151.93</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -7944,7 +7944,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>545.3200000000001</v>
+        <v>569.28</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-31.29</v>
+        <v>-7.32</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>952.8200000000001</v>
+        <v>976.79</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>-96.88</v>
+        <v>-72.92</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1374.4</v>
+        <v>1398.36</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>192.59</v>
+        <v>216.56</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>827.6900000000001</v>
+        <v>851.65</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>315.92</v>
+        <v>339.88</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>296.14</v>
+        <v>320.1</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>-31.2</v>
+        <v>-7.24</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>153.99</v>
+        <v>177.96</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>982.1799999999999</v>
+        <v>1006.14</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -9687,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>-1.2</v>
+        <v>22.76</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>1160.59</v>
+        <v>1184.55</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>97.84</v>
+        <v>121.8</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>1141.4</v>
+        <v>1165.36</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>447.3</v>
+        <v>471.26</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>952.8</v>
+        <v>976.77</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -10938,12 +10938,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10250</t>
+          <t>PO-10252</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10953,27 +10953,27 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-09T23:13:24.949546+00:00</t>
+          <t>2026-09-04T00:02:04.725108+00:00</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>2026-08-10T13:24:04.045714+00:00</t>
+          <t>2026-09-05T08:36:21.549728+00:00</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-08-12T11:03:42.634137+00:00</t>
+          <t>2026-09-08T05:36:19.523297+00:00</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>14.18</v>
+        <v>32.57</v>
       </c>
       <c r="H179" t="n">
-        <v>45.66</v>
+        <v>69</v>
       </c>
       <c r="I179" t="n">
-        <v>59.84</v>
+        <v>101.57</v>
       </c>
       <c r="J179" t="b">
         <v>1</v>
@@ -10981,128 +10981,128 @@
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10251</t>
+          <t>PO-10253</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-09-12T02:18:03.728636+00:00</t>
+          <t>2026-10-11T04:28:11.734790+00:00</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>2026-09-14T11:25:02.436542+00:00</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-09-20T00:07:23.526153+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-11T14:15:47.985891+00:00</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="n">
-        <v>57.12</v>
-      </c>
-      <c r="H180" t="n">
-        <v>132.71</v>
-      </c>
-      <c r="I180" t="n">
-        <v>189.82</v>
-      </c>
+        <v>9.789999999999999</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="b">
-        <v>1</v>
-      </c>
-      <c r="K180" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>-17.39</v>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10253</t>
+          <t>PO-10254</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-10-13T08:12:35.271945+00:00</t>
+          <t>2026-08-18T02:39:55.837748+00:00</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-10-15T11:47:08.874839+00:00</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr"/>
+          <t>2026-08-19T13:50:35.060165+00:00</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-19T20:13:18.481815+00:00</t>
+        </is>
+      </c>
       <c r="G181" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
+        <v>35.18</v>
+      </c>
+      <c r="H181" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="I181" t="n">
+        <v>41.56</v>
+      </c>
       <c r="J181" t="b">
-        <v>0</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-93.09999999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10254</t>
+          <t>PO-10255</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11112,27 +11112,27 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-25T05:02:57.860442+00:00</t>
+          <t>2026-09-24T04:02:57.860442+00:00</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>2026-08-25T16:40:21.833202+00:00</t>
+          <t>2026-09-24T22:00:30.459000+00:00</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-08-26T00:14:58.564190+00:00</t>
+          <t>2026-09-25T09:42:55.394632+00:00</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>11.62</v>
+        <v>17.96</v>
       </c>
       <c r="H182" t="n">
-        <v>7.58</v>
+        <v>11.71</v>
       </c>
       <c r="I182" t="n">
-        <v>19.2</v>
+        <v>29.67</v>
       </c>
       <c r="J182" t="b">
         <v>1</v>
@@ -11140,12 +11140,12 @@
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10255</t>
+          <t>PO-10256</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10257</t>
+          <t>PO-10258</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10258</t>
+          <t>PO-10259</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10261</t>
+          <t>PO-10262</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11377,7 +11377,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10262</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11432,7 +11432,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10263</t>
+          <t>PO-10264</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11460,7 +11460,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>874.6799999999999</v>
+        <v>898.64</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10266</t>
+          <t>PO-10267</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10267</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -11554,18 +11554,24 @@
           <t>2026-10-09T10:37:57.398024+00:00</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-10-10T10:07:48.719998+00:00</t>
+        </is>
+      </c>
       <c r="G190" t="n">
         <v>15.28</v>
       </c>
-      <c r="H190" t="inlineStr"/>
-      <c r="I190" t="inlineStr"/>
+      <c r="H190" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="I190" t="n">
+        <v>38.78</v>
+      </c>
       <c r="J190" t="b">
-        <v>0</v>
-      </c>
-      <c r="K190" t="n">
-        <v>15.76</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -11585,7 +11591,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10268</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11640,7 +11646,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11668,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1150.96</v>
+        <v>1174.92</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11689,7 +11695,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10270</t>
+          <t>PO-10271</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11744,7 +11750,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10272</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11772,7 +11778,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1492.89</v>
+        <v>1516.86</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -11793,7 +11799,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10275</t>
+          <t>PO-10276</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11821,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>41.12</v>
+        <v>65.08</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -11842,7 +11848,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10277</t>
+          <t>PO-10278</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11897,7 +11903,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10280</t>
+          <t>PO-10281</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11925,7 +11931,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-75.3</v>
+        <v>-51.33</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -11946,7 +11952,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10281</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12001,7 +12007,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10282</t>
+          <t>PO-10283</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12029,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>1302.86</v>
+        <v>1326.82</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -12050,7 +12056,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10283</t>
+          <t>PO-10284</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12105,7 +12111,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10284</t>
+          <t>PO-10285</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12160,7 +12166,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10285</t>
+          <t>PO-10286</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12215,7 +12221,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10287</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12243,7 +12249,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>1621.91</v>
+        <v>1645.88</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12264,7 +12270,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10287</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12292,7 +12298,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>-83.16</v>
+        <v>-59.19</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -12313,7 +12319,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10288</t>
+          <t>PO-10289</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12368,7 +12374,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10289</t>
+          <t>PO-10290</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12423,7 +12429,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10290</t>
+          <t>PO-10291</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12478,7 +12484,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10291</t>
+          <t>PO-10292</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12533,7 +12539,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10292</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12588,7 +12594,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10293</t>
+          <t>PO-10294</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12643,7 +12649,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10294</t>
+          <t>PO-10295</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12671,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>145.46</v>
+        <v>169.43</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -12692,7 +12698,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12747,7 +12753,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10296</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12802,7 +12808,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12830,7 +12836,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>-63</v>
+        <v>-39.03</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -12851,7 +12857,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10298</t>
+          <t>PO-10299</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12906,7 +12912,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10300</t>
+          <t>PO-10301</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12961,7 +12967,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10302</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13016,7 +13022,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13044,7 +13050,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>45.9</v>
+        <v>69.87</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -13065,7 +13071,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PO-10303</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13120,7 +13126,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13148,7 +13154,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>-51.86</v>
+        <v>-27.89</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -13169,7 +13175,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PO-10305</t>
+          <t>PO-10306</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13197,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>1071.36</v>
+        <v>1095.33</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -13218,7 +13224,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10307</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13273,7 +13279,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PO-10309</t>
+          <t>PO-10310</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13328,7 +13334,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PO-10312</t>
+          <t>PO-10313</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13383,7 +13389,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PO-10314</t>
+          <t>PO-10315</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13438,7 +13444,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PO-10315</t>
+          <t>PO-10316</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13493,7 +13499,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PO-10316</t>
+          <t>PO-10317</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13521,7 +13527,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>1334.34</v>
+        <v>1358.3</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -13542,7 +13548,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PO-10317</t>
+          <t>PO-10318</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13597,7 +13603,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PO-10319</t>
+          <t>PO-10320</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13652,7 +13658,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PO-10321</t>
+          <t>PO-10322</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13707,7 +13713,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PO-10322</t>
+          <t>PO-10323</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13735,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>1454.89</v>
+        <v>1478.85</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -13756,7 +13762,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PO-10324</t>
+          <t>PO-10325</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13784,7 +13790,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>779.25</v>
+        <v>803.22</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13805,7 +13811,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PO-10326</t>
+          <t>PO-10327</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13860,7 +13866,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PO-10327</t>
+          <t>PO-10328</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13888,7 +13894,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>74.09</v>
+        <v>98.06</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -13909,7 +13915,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PO-10330</t>
+          <t>PO-10331</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13937,7 +13943,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>1451.79</v>
+        <v>1475.76</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -13958,7 +13964,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PO-10335</t>
+          <t>PO-10336</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14013,7 +14019,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PO-10337</t>
+          <t>PO-10338</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14068,7 +14074,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PO-10338</t>
+          <t>PO-10339</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14123,7 +14129,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PO-10339</t>
+          <t>PO-10340</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14178,7 +14184,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PO-10341</t>
+          <t>PO-10342</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14206,7 +14212,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>388.14</v>
+        <v>412.11</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -14227,7 +14233,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PO-10342</t>
+          <t>PO-10343</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14255,7 +14261,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>1500.04</v>
+        <v>1524</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -14276,7 +14282,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PO-10344</t>
+          <t>PO-10345</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14304,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>58.57</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -14325,7 +14331,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PO-10345</t>
+          <t>PO-10346</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14380,7 +14386,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PO-10347</t>
+          <t>PO-10348</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14435,7 +14441,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PO-10350</t>
+          <t>PO-10351</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14490,7 +14496,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PO-10352</t>
+          <t>PO-10353</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14545,7 +14551,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PO-10353</t>
+          <t>PO-10354</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14600,7 +14606,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PO-10354</t>
+          <t>PO-10355</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14655,7 +14661,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PO-10355</t>
+          <t>PO-10356</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14710,50 +14716,44 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PO-10356</t>
+          <t>PO-10357</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-09T16:18:38.716909+00:00</t>
+          <t>2026-10-13T08:02:56.855874+00:00</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2026-08-09T21:54:20.922269+00:00</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>2026-08-12T07:53:39.142365+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-13T13:38:39.061234+00:00</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr"/>
       <c r="G250" t="n">
         <v>5.6</v>
       </c>
-      <c r="H250" t="n">
-        <v>57.99</v>
-      </c>
-      <c r="I250" t="n">
-        <v>63.58</v>
-      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
       <c r="J250" t="b">
-        <v>1</v>
-      </c>
-      <c r="K250" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>-68.97</v>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PO-10360</t>
+          <t>PO-10361</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PO-10362</t>
+          <t>PO-10363</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14875,7 +14875,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PO-10363</t>
+          <t>PO-10364</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PO-10367</t>
+          <t>PO-10368</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14985,7 +14985,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PO-10368</t>
+          <t>PO-10369</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15040,7 +15040,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PO-10369</t>
+          <t>PO-10370</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PO-10371</t>
+          <t>PO-10372</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PO-10372</t>
+          <t>PO-10373</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PO-10373</t>
+          <t>PO-10374</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15233,7 +15233,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>56.82</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PO-10374</t>
+          <t>PO-10375</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15309,7 +15309,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PO-10375</t>
+          <t>PO-10376</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15364,7 +15364,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PO-10376</t>
+          <t>PO-10377</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15392,7 +15392,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>-55.35</v>
+        <v>-31.39</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PO-10379</t>
+          <t>PO-10380</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15441,7 +15441,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>-35.27</v>
+        <v>-11.31</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PO-10381</t>
+          <t>PO-10382</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PO-10382</t>
+          <t>PO-10383</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PO-10384</t>
+          <t>PO-10385</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PO-10386</t>
+          <t>PO-10387</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PO-10388</t>
+          <t>PO-10389</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15710,7 +15710,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>910.73</v>
+        <v>934.7</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PO-10392</t>
+          <t>PO-10393</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15786,7 +15786,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PO-10394</t>
+          <t>PO-10395</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15814,7 +15814,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1579.42</v>
+        <v>1603.39</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PO-10395</t>
+          <t>PO-10396</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15890,7 +15890,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PO-10397</t>
+          <t>PO-10398</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15918,7 +15918,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>1079.34</v>
+        <v>1103.31</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PO-10398</t>
+          <t>PO-10399</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15967,7 +15967,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1550.6</v>
+        <v>1574.56</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PO-10400</t>
+          <t>PO-10401</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16016,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>179.89</v>
+        <v>203.85</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PO-10401</t>
+          <t>PO-10402</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16065,7 +16065,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>1296.29</v>
+        <v>1320.26</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PO-10403</t>
+          <t>PO-10404</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16141,7 +16141,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PO-10404</t>
+          <t>PO-10405</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>626.15</v>
+        <v>650.11</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PO-10405</t>
+          <t>PO-10406</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>-3.28</v>
+        <v>20.69</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PO-10406</t>
+          <t>PO-10407</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16294,7 +16294,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PO-10407</t>
+          <t>PO-10408</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PO-10408</t>
+          <t>PO-10409</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PO-10409</t>
+          <t>PO-10410</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16459,7 +16459,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PO-10413</t>
+          <t>PO-10414</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16514,7 +16514,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PO-10415</t>
+          <t>PO-10416</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16542,7 +16542,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>1085.12</v>
+        <v>1109.08</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PO-10416</t>
+          <t>PO-10417</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16618,7 +16618,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PO-10417</t>
+          <t>PO-10418</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16673,7 +16673,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PO-10418</t>
+          <t>PO-10419</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16728,7 +16728,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PO-10419</t>
+          <t>PO-10420</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16783,7 +16783,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PO-10420</t>
+          <t>PO-10421</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16838,7 +16838,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PO-10422</t>
+          <t>PO-10423</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PO-10423</t>
+          <t>PO-10424</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16921,7 +16921,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>18.16</v>
+        <v>42.13</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PO-10426</t>
+          <t>PO-10427</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PO-10427</t>
+          <t>PO-10428</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -17052,7 +17052,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PO-10429</t>
+          <t>PO-10430</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17080,7 +17080,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>760.34</v>
+        <v>784.3</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PO-10430</t>
+          <t>PO-10431</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PO-10431</t>
+          <t>PO-10432</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PO-10432</t>
+          <t>PO-10433</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PO-10433</t>
+          <t>PO-10434</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PO-10435</t>
+          <t>PO-10436</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PO-10436</t>
+          <t>PO-10437</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17386,12 +17386,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:52.422117+00:00</t>
+          <t>2026-10-14T15:35:52.422117+00:00</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-09-18T22:25:39.492220+00:00</t>
+          <t>2026-10-17T00:25:39.492220+00:00</t>
         </is>
       </c>
       <c r="F300" t="inlineStr"/>
@@ -17404,16 +17404,16 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>549.51</v>
+        <v>-100.52</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PO-10437</t>
+          <t>PO-10438</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PO-10438</t>
+          <t>PO-10439</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17535,7 +17535,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PO-10439</t>
+          <t>PO-10440</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17590,7 +17590,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PO-10440</t>
+          <t>PO-10441</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PO-10441</t>
+          <t>PO-10442</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17700,7 +17700,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PO-10442</t>
+          <t>PO-10443</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PO-10443</t>
+          <t>PO-10444</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17810,7 +17810,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PO-10445</t>
+          <t>PO-10446</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17838,7 +17838,7 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>945.71</v>
+        <v>969.67</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PO-10449</t>
+          <t>PO-10450</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17914,42 +17914,36 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PO-10451</t>
+          <t>PO-10452</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-10-06T00:56:58.613835+00:00</t>
+          <t>2026-10-13T15:59:03.723755+00:00</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-10-07T13:27:45.229706+00:00</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>2026-10-07T17:45:20.147395+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-14T06:40:47.231404+00:00</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
       <c r="G310" t="n">
-        <v>36.51</v>
-      </c>
-      <c r="H310" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="I310" t="n">
-        <v>40.81</v>
-      </c>
+        <v>14.7</v>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr"/>
       <c r="J310" t="b">
-        <v>1</v>
-      </c>
-      <c r="K310" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>-76.91</v>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -17957,14 +17951,14 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -17979,27 +17973,27 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-09-09T05:36:23.112124+00:00</t>
+          <t>2026-09-25T16:43:56.069414+00:00</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>2026-09-10T18:38:22.076987+00:00</t>
+          <t>2026-09-26T16:20:11.569651+00:00</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>2026-09-11T10:09:52.894498+00:00</t>
+          <t>2026-09-27T16:02:05.244478+00:00</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>37.03</v>
+        <v>23.6</v>
       </c>
       <c r="H311" t="n">
-        <v>15.53</v>
+        <v>23.7</v>
       </c>
       <c r="I311" t="n">
-        <v>52.56</v>
+        <v>47.3</v>
       </c>
       <c r="J311" t="b">
         <v>1</v>
@@ -18012,137 +18006,149 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PO-10455</t>
+          <t>PO-10454</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-10-12T15:52:28.598326+00:00</t>
+          <t>2026-08-28T21:54:55.090250+00:00</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>2026-10-13T11:09:30.065719+00:00</t>
-        </is>
-      </c>
-      <c r="F312" t="inlineStr"/>
+          <t>2026-08-30T16:35:31.917495+00:00</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>2026-08-31T19:29:05.331256+00:00</t>
+        </is>
+      </c>
       <c r="G312" t="n">
-        <v>19.28</v>
-      </c>
-      <c r="H312" t="inlineStr"/>
-      <c r="I312" t="inlineStr"/>
+        <v>42.68</v>
+      </c>
+      <c r="H312" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="I312" t="n">
+        <v>69.56999999999999</v>
+      </c>
       <c r="J312" t="b">
-        <v>0</v>
-      </c>
-      <c r="K312" t="n">
-        <v>-76.77</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PO-10456</t>
+          <t>PO-10455</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-09-13T17:52:44.136131+00:00</t>
+          <t>2026-08-22T14:34:25.872656+00:00</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-09-14T16:28:29.443874+00:00</t>
-        </is>
-      </c>
-      <c r="F313" t="inlineStr"/>
+          <t>2026-08-24T10:43:23.948377+00:00</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>2026-08-27T08:13:43.010863+00:00</t>
+        </is>
+      </c>
       <c r="G313" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="H313" t="inlineStr"/>
-      <c r="I313" t="inlineStr"/>
+        <v>44.15</v>
+      </c>
+      <c r="H313" t="n">
+        <v>69.51000000000001</v>
+      </c>
+      <c r="I313" t="n">
+        <v>113.65</v>
+      </c>
       <c r="J313" t="b">
-        <v>0</v>
-      </c>
-      <c r="K313" t="n">
-        <v>617.23</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PO-10457</t>
+          <t>PO-10456</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-10-06T11:00:08.408805+00:00</t>
+          <t>2026-08-19T10:46:00.279259+00:00</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-10-08T12:58:59.313451+00:00</t>
+          <t>2026-08-21T02:56:36.828247+00:00</t>
         </is>
       </c>
       <c r="F314" t="inlineStr"/>
       <c r="G314" t="n">
-        <v>49.98</v>
+        <v>40.18</v>
       </c>
       <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr"/>
@@ -18150,112 +18156,112 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>72.11</v>
+        <v>1248.31</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10458</t>
+          <t>PO-10457</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-04T06:38:28.762292+00:00</t>
+          <t>2026-10-13T07:28:19.509306+00:00</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-09-06T06:18:34.463310+00:00</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>2026-09-09T18:41:23.294334+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-15T14:36:40.746522+00:00</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
       <c r="G315" t="n">
-        <v>47.67</v>
-      </c>
-      <c r="H315" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="I315" t="n">
-        <v>132.05</v>
-      </c>
+        <v>55.14</v>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr"/>
       <c r="J315" t="b">
-        <v>1</v>
-      </c>
-      <c r="K315" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>-68.40000000000001</v>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10459</t>
+          <t>PO-10458</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-09-10T17:16:09.095754+00:00</t>
+          <t>2026-09-09T04:38:28.762292+00:00</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-09-11T12:43:58.441650+00:00</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
+          <t>2026-09-11T10:08:31.535489+00:00</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:50:48.456109+00:00</t>
+        </is>
+      </c>
       <c r="G316" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
+        <v>53.5</v>
+      </c>
+      <c r="H316" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="I316" t="n">
+        <v>148.21</v>
+      </c>
       <c r="J316" t="b">
-        <v>0</v>
-      </c>
-      <c r="K316" t="n">
-        <v>689.84</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -18270,32 +18276,32 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10460</t>
+          <t>PO-10459</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-10-03T05:50:17.284863+00:00</t>
+          <t>2026-09-10T17:16:09.095754+00:00</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-10-04T10:34:24.997077+00:00</t>
+          <t>2026-09-11T12:43:58.441650+00:00</t>
         </is>
       </c>
       <c r="F317" t="inlineStr"/>
       <c r="G317" t="n">
-        <v>28.74</v>
+        <v>19.46</v>
       </c>
       <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr"/>
@@ -18303,83 +18309,77 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>149.27</v>
+        <v>713.8099999999999</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10461</t>
+          <t>PO-10460</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-31T20:52:16.144491+00:00</t>
+          <t>2026-10-03T05:50:17.284863+00:00</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-09-02T08:25:46.933379+00:00</t>
-        </is>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>2026-09-07T06:25:58.665124+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-04T10:34:24.997077+00:00</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
       <c r="G318" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="H318" t="n">
-        <v>118</v>
-      </c>
-      <c r="I318" t="n">
-        <v>153.56</v>
-      </c>
+        <v>28.74</v>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr"/>
       <c r="J318" t="b">
-        <v>1</v>
-      </c>
-      <c r="K318" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>173.24</v>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10462</t>
+          <t>PO-10461</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18389,27 +18389,27 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-27T18:33:42.716838+00:00</t>
+          <t>2026-08-31T20:52:16.144491+00:00</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-08-28T04:07:06.483584+00:00</t>
+          <t>2026-09-02T08:25:46.933379+00:00</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>2026-08-29T11:51:58.988558+00:00</t>
+          <t>2026-09-07T06:25:58.665124+00:00</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>9.56</v>
+        <v>35.56</v>
       </c>
       <c r="H319" t="n">
-        <v>31.75</v>
+        <v>118</v>
       </c>
       <c r="I319" t="n">
-        <v>41.3</v>
+        <v>153.56</v>
       </c>
       <c r="J319" t="b">
         <v>1</v>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10465</t>
+          <t>PO-10462</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18444,27 +18444,27 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-08-23T00:23:19.885250+00:00</t>
+          <t>2026-08-27T18:33:42.716838+00:00</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-08-23T19:17:35.180209+00:00</t>
+          <t>2026-08-28T04:07:06.483584+00:00</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2026-08-24T18:39:42.550195+00:00</t>
+          <t>2026-08-29T11:51:58.988558+00:00</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>18.9</v>
+        <v>9.56</v>
       </c>
       <c r="H320" t="n">
-        <v>23.37</v>
+        <v>31.75</v>
       </c>
       <c r="I320" t="n">
-        <v>42.27</v>
+        <v>41.3</v>
       </c>
       <c r="J320" t="b">
         <v>1</v>
@@ -18477,19 +18477,19 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10468</t>
+          <t>PO-10465</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18499,27 +18499,27 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-20T16:16:07.583755+00:00</t>
+          <t>2026-08-23T00:23:19.885250+00:00</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-08-22T08:41:06.002334+00:00</t>
+          <t>2026-08-23T19:17:35.180209+00:00</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>2026-08-24T08:55:41.794772+00:00</t>
+          <t>2026-08-24T18:39:42.550195+00:00</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>40.42</v>
+        <v>18.9</v>
       </c>
       <c r="H321" t="n">
-        <v>48.24</v>
+        <v>23.37</v>
       </c>
       <c r="I321" t="n">
-        <v>88.66</v>
+        <v>42.27</v>
       </c>
       <c r="J321" t="b">
         <v>1</v>
@@ -18539,12 +18539,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10469</t>
+          <t>PO-10468</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18554,27 +18554,27 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-09-02T09:53:22.177648+00:00</t>
+          <t>2026-08-20T16:16:07.583755+00:00</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2026-09-03T05:51:53.283550+00:00</t>
+          <t>2026-08-22T08:41:06.002334+00:00</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>2026-09-06T20:43:07.922518+00:00</t>
+          <t>2026-08-24T08:55:41.794772+00:00</t>
         </is>
       </c>
       <c r="G322" t="n">
-        <v>19.98</v>
+        <v>40.42</v>
       </c>
       <c r="H322" t="n">
-        <v>86.84999999999999</v>
+        <v>48.24</v>
       </c>
       <c r="I322" t="n">
-        <v>106.83</v>
+        <v>88.66</v>
       </c>
       <c r="J322" t="b">
         <v>1</v>
@@ -18582,24 +18582,24 @@
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10471</t>
+          <t>PO-10469</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18609,27 +18609,27 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-08-05T23:28:47.558849+00:00</t>
+          <t>2026-09-02T09:53:22.177648+00:00</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-08-09T02:11:41.743500+00:00</t>
+          <t>2026-09-03T05:51:53.283550+00:00</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2026-08-10T07:57:12.095994+00:00</t>
+          <t>2026-09-06T20:43:07.922518+00:00</t>
         </is>
       </c>
       <c r="G323" t="n">
-        <v>74.72</v>
+        <v>19.98</v>
       </c>
       <c r="H323" t="n">
-        <v>29.76</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="I323" t="n">
-        <v>104.47</v>
+        <v>106.83</v>
       </c>
       <c r="J323" t="b">
         <v>1</v>
@@ -18637,24 +18637,24 @@
       <c r="K323" t="inlineStr"/>
       <c r="L323" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10472</t>
+          <t>PO-10471</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18664,27 +18664,27 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-09-30T20:07:43.581569+00:00</t>
+          <t>2026-08-05T23:28:47.558849+00:00</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2026-10-02T00:25:37.978882+00:00</t>
+          <t>2026-08-09T02:11:41.743500+00:00</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>2026-10-03T20:45:36.532072+00:00</t>
+          <t>2026-08-10T07:57:12.095994+00:00</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>28.3</v>
+        <v>74.72</v>
       </c>
       <c r="H324" t="n">
-        <v>44.33</v>
+        <v>29.76</v>
       </c>
       <c r="I324" t="n">
-        <v>72.63</v>
+        <v>104.47</v>
       </c>
       <c r="J324" t="b">
         <v>1</v>
@@ -18692,24 +18692,24 @@
       <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10473</t>
+          <t>PO-10472</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18719,27 +18719,27 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-09-11T20:08:49.970662+00:00</t>
+          <t>2026-09-30T20:07:43.581569+00:00</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-09-12T13:12:55.897133+00:00</t>
+          <t>2026-10-02T00:25:37.978882+00:00</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2026-09-16T08:45:17.054435+00:00</t>
+          <t>2026-10-03T20:45:36.532072+00:00</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>17.07</v>
+        <v>28.3</v>
       </c>
       <c r="H325" t="n">
-        <v>91.54000000000001</v>
+        <v>44.33</v>
       </c>
       <c r="I325" t="n">
-        <v>108.61</v>
+        <v>72.63</v>
       </c>
       <c r="J325" t="b">
         <v>1</v>
@@ -18752,48 +18752,54 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10475</t>
+          <t>PO-10473</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-09-08T20:57:59.166000+00:00</t>
+          <t>2026-09-11T20:08:49.970662+00:00</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2026-09-10T03:40:49.829977+00:00</t>
-        </is>
-      </c>
-      <c r="F326" t="inlineStr"/>
+          <t>2026-09-12T13:12:55.897133+00:00</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>2026-09-16T08:45:17.054435+00:00</t>
+        </is>
+      </c>
       <c r="G326" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="H326" t="inlineStr"/>
-      <c r="I326" t="inlineStr"/>
+        <v>17.07</v>
+      </c>
+      <c r="H326" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="I326" t="n">
+        <v>108.61</v>
+      </c>
       <c r="J326" t="b">
-        <v>0</v>
-      </c>
-      <c r="K326" t="n">
-        <v>734.14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -18808,67 +18814,61 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10476</t>
+          <t>PO-10475</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-08-19T22:59:08.192451+00:00</t>
+          <t>2026-09-08T20:57:59.166000+00:00</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-08-20T09:15:07.499586+00:00</t>
-        </is>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>2026-08-24T18:14:17.186973+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-10T03:40:49.829977+00:00</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
       <c r="G327" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="H327" t="n">
-        <v>104.99</v>
-      </c>
-      <c r="I327" t="n">
-        <v>115.25</v>
-      </c>
+        <v>30.71</v>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr"/>
       <c r="J327" t="b">
-        <v>1</v>
-      </c>
-      <c r="K327" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>758.11</v>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10476</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18878,27 +18878,27 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-01T17:59:42.722496+00:00</t>
+          <t>2026-08-19T22:59:08.192451+00:00</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2026-09-03T17:28:58.754724+00:00</t>
+          <t>2026-08-20T09:15:07.499586+00:00</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>2026-09-04T18:03:39.182610+00:00</t>
+          <t>2026-08-24T18:14:17.186973+00:00</t>
         </is>
       </c>
       <c r="G328" t="n">
-        <v>47.49</v>
+        <v>10.27</v>
       </c>
       <c r="H328" t="n">
-        <v>24.58</v>
+        <v>104.99</v>
       </c>
       <c r="I328" t="n">
-        <v>72.06999999999999</v>
+        <v>115.25</v>
       </c>
       <c r="J328" t="b">
         <v>1</v>
@@ -18906,12 +18906,12 @@
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -18923,7 +18923,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10482</t>
+          <t>PO-10478</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18933,27 +18933,27 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-06T07:09:20.823958+00:00</t>
+          <t>2026-09-01T17:59:42.722496+00:00</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>2026-08-08T09:09:52.832565+00:00</t>
+          <t>2026-09-03T17:28:58.754724+00:00</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>2026-08-12T00:51:09.739836+00:00</t>
+          <t>2026-09-04T18:03:39.182610+00:00</t>
         </is>
       </c>
       <c r="G329" t="n">
-        <v>50.01</v>
+        <v>47.49</v>
       </c>
       <c r="H329" t="n">
-        <v>87.69</v>
+        <v>24.58</v>
       </c>
       <c r="I329" t="n">
-        <v>137.7</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="J329" t="b">
         <v>1</v>
@@ -18961,61 +18961,67 @@
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10483</t>
+          <t>PO-10482</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-09-26T01:23:24.001471+00:00</t>
+          <t>2026-08-06T07:09:20.823958+00:00</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>2026-09-27T10:46:57.411417+00:00</t>
-        </is>
-      </c>
-      <c r="F330" t="inlineStr"/>
+          <t>2026-08-08T09:09:52.832565+00:00</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>2026-08-12T00:51:09.739836+00:00</t>
+        </is>
+      </c>
       <c r="G330" t="n">
-        <v>33.39</v>
-      </c>
-      <c r="H330" t="inlineStr"/>
-      <c r="I330" t="inlineStr"/>
+        <v>50.01</v>
+      </c>
+      <c r="H330" t="n">
+        <v>87.69</v>
+      </c>
+      <c r="I330" t="n">
+        <v>137.7</v>
+      </c>
       <c r="J330" t="b">
-        <v>0</v>
-      </c>
-      <c r="K330" t="n">
-        <v>321.72</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -19027,27 +19033,27 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PO-10484</t>
+          <t>PO-10483</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-22T05:36:44.850986+00:00</t>
+          <t>2026-09-26T01:23:24.001471+00:00</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>2026-09-23T02:20:36.105704+00:00</t>
+          <t>2026-09-27T10:46:57.411417+00:00</t>
         </is>
       </c>
       <c r="F331" t="inlineStr"/>
       <c r="G331" t="n">
-        <v>20.73</v>
+        <v>33.39</v>
       </c>
       <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr"/>
@@ -19055,7 +19061,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>413.5</v>
+        <v>345.69</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -19071,47 +19077,41 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PO-10485</t>
+          <t>PO-10484</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-14T22:17:09.101831+00:00</t>
+          <t>2026-09-22T05:36:44.850986+00:00</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-09-17T00:42:15.695767+00:00</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2026-09-18T02:05:10.458762+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-23T02:20:36.105704+00:00</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
       <c r="G332" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="H332" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="I332" t="n">
-        <v>75.8</v>
-      </c>
+        <v>20.73</v>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr"/>
       <c r="J332" t="b">
-        <v>1</v>
-      </c>
-      <c r="K332" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K332" t="n">
+        <v>437.46</v>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -19119,111 +19119,111 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PO-10486</t>
+          <t>PO-10485</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-26T03:50:58.864173+00:00</t>
+          <t>2026-09-14T22:17:09.101831+00:00</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2026-08-27T06:21:25.808022+00:00</t>
-        </is>
-      </c>
-      <c r="F333" t="inlineStr"/>
+          <t>2026-09-17T00:42:15.695767+00:00</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>2026-09-18T02:05:10.458762+00:00</t>
+        </is>
+      </c>
       <c r="G333" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="H333" t="inlineStr"/>
-      <c r="I333" t="inlineStr"/>
+        <v>50.42</v>
+      </c>
+      <c r="H333" t="n">
+        <v>25.38</v>
+      </c>
+      <c r="I333" t="n">
+        <v>75.8</v>
+      </c>
       <c r="J333" t="b">
-        <v>0</v>
-      </c>
-      <c r="K333" t="n">
-        <v>1063.26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
       <c r="L333" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10487</t>
+          <t>PO-10486</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-09-19T01:52:16.212326+00:00</t>
+          <t>2026-08-26T03:50:58.864173+00:00</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-09-20T02:22:59.430445+00:00</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>2026-09-24T14:10:29.868179+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-27T06:21:25.808022+00:00</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
-        <v>24.51</v>
-      </c>
-      <c r="H334" t="n">
-        <v>107.79</v>
-      </c>
-      <c r="I334" t="n">
-        <v>132.3</v>
-      </c>
+        <v>26.51</v>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
       <c r="J334" t="b">
-        <v>1</v>
-      </c>
-      <c r="K334" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>1087.23</v>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -19235,7 +19235,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10488</t>
+          <t>PO-10487</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19245,27 +19245,27 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-19T18:27:37.821516+00:00</t>
+          <t>2026-09-19T01:52:16.212326+00:00</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-08-23T05:06:12.426176+00:00</t>
+          <t>2026-09-20T02:22:59.430445+00:00</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>2026-08-28T22:05:28.981580+00:00</t>
+          <t>2026-09-24T14:10:29.868179+00:00</t>
         </is>
       </c>
       <c r="G335" t="n">
-        <v>82.64</v>
+        <v>24.51</v>
       </c>
       <c r="H335" t="n">
-        <v>136.99</v>
+        <v>107.79</v>
       </c>
       <c r="I335" t="n">
-        <v>219.63</v>
+        <v>132.3</v>
       </c>
       <c r="J335" t="b">
         <v>1</v>
@@ -19273,24 +19273,24 @@
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10489</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19300,27 +19300,27 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-08-17T02:44:59.622168+00:00</t>
+          <t>2026-08-19T18:27:37.821516+00:00</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-08-19T04:28:49.068780+00:00</t>
+          <t>2026-08-23T05:06:12.426176+00:00</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-08-25T02:55:53.600196+00:00</t>
+          <t>2026-08-28T22:05:28.981580+00:00</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>49.73</v>
+        <v>82.64</v>
       </c>
       <c r="H336" t="n">
-        <v>142.45</v>
+        <v>136.99</v>
       </c>
       <c r="I336" t="n">
-        <v>192.18</v>
+        <v>219.63</v>
       </c>
       <c r="J336" t="b">
         <v>1</v>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10492</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19355,27 +19355,27 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-08-09T21:32:15.767073+00:00</t>
+          <t>2026-08-17T02:44:59.622168+00:00</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-08-10T09:39:03.862803+00:00</t>
+          <t>2026-08-19T04:28:49.068780+00:00</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>2026-08-11T16:15:08.874292+00:00</t>
+          <t>2026-08-25T02:55:53.600196+00:00</t>
         </is>
       </c>
       <c r="G337" t="n">
-        <v>12.11</v>
+        <v>49.73</v>
       </c>
       <c r="H337" t="n">
-        <v>30.6</v>
+        <v>142.45</v>
       </c>
       <c r="I337" t="n">
-        <v>42.71</v>
+        <v>192.18</v>
       </c>
       <c r="J337" t="b">
         <v>1</v>
@@ -19388,56 +19388,62 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10492</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-10-08T06:19:53.378460+00:00</t>
+          <t>2026-08-09T21:32:15.767073+00:00</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-10-10T05:16:07.339986+00:00</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr"/>
+          <t>2026-08-10T09:39:03.862803+00:00</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>2026-08-11T16:15:08.874292+00:00</t>
+        </is>
+      </c>
       <c r="G338" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="H338" t="inlineStr"/>
-      <c r="I338" t="inlineStr"/>
+        <v>12.11</v>
+      </c>
+      <c r="H338" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="I338" t="n">
+        <v>42.71</v>
+      </c>
       <c r="J338" t="b">
-        <v>0</v>
-      </c>
-      <c r="K338" t="n">
-        <v>28.78</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -19449,62 +19455,56 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10495</t>
+          <t>PO-10494</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-30T04:08:07.198697+00:00</t>
+          <t>2026-10-08T06:19:53.378460+00:00</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-08-30T10:30:08.904663+00:00</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>2026-09-02T16:32:14.750148+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-10T05:16:07.339986+00:00</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="H339" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="I339" t="n">
-        <v>84.40000000000001</v>
-      </c>
+        <v>46.94</v>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
       <c r="J339" t="b">
-        <v>1</v>
-      </c>
-      <c r="K339" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K339" t="n">
+        <v>52.74</v>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10498</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19514,27 +19514,27 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-09-28T11:14:25.063087+00:00</t>
+          <t>2026-08-30T04:08:07.198697+00:00</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-09-28T15:49:16.866453+00:00</t>
+          <t>2026-08-30T10:30:08.904663+00:00</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>2026-09-30T13:49:09.557627+00:00</t>
+          <t>2026-09-02T16:32:14.750148+00:00</t>
         </is>
       </c>
       <c r="G340" t="n">
-        <v>4.58</v>
+        <v>6.37</v>
       </c>
       <c r="H340" t="n">
-        <v>46</v>
+        <v>78.03</v>
       </c>
       <c r="I340" t="n">
-        <v>50.58</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="J340" t="b">
         <v>1</v>
@@ -19542,24 +19542,24 @@
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10500</t>
+          <t>PO-10498</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19569,27 +19569,27 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-25T11:21:13.896916+00:00</t>
+          <t>2026-09-28T11:14:25.063087+00:00</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-08-28T06:08:31.892871+00:00</t>
+          <t>2026-09-28T15:49:16.866453+00:00</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-08-30T17:09:32.875510+00:00</t>
+          <t>2026-09-30T13:49:09.557627+00:00</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>66.79000000000001</v>
+        <v>4.58</v>
       </c>
       <c r="H341" t="n">
-        <v>59.02</v>
+        <v>46</v>
       </c>
       <c r="I341" t="n">
-        <v>125.81</v>
+        <v>50.58</v>
       </c>
       <c r="J341" t="b">
         <v>1</v>
@@ -19597,24 +19597,24 @@
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10501</t>
+          <t>PO-10500</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19624,27 +19624,27 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-03T22:29:54.738689+00:00</t>
+          <t>2026-08-25T11:21:13.896916+00:00</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-09-05T11:53:12.439478+00:00</t>
+          <t>2026-08-28T06:08:31.892871+00:00</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>2026-09-07T16:03:03.695045+00:00</t>
+          <t>2026-08-30T17:09:32.875510+00:00</t>
         </is>
       </c>
       <c r="G342" t="n">
-        <v>37.39</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="H342" t="n">
-        <v>52.16</v>
+        <v>59.02</v>
       </c>
       <c r="I342" t="n">
-        <v>89.55</v>
+        <v>125.81</v>
       </c>
       <c r="J342" t="b">
         <v>1</v>
@@ -19652,12 +19652,12 @@
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10503</t>
+          <t>PO-10501</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19679,27 +19679,27 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-01T16:10:57.796010+00:00</t>
+          <t>2026-09-03T22:29:54.738689+00:00</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-09-02T18:34:29.173140+00:00</t>
+          <t>2026-09-05T11:53:12.439478+00:00</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2026-09-06T00:42:22.481813+00:00</t>
+          <t>2026-09-07T16:03:03.695045+00:00</t>
         </is>
       </c>
       <c r="G343" t="n">
-        <v>26.39</v>
+        <v>37.39</v>
       </c>
       <c r="H343" t="n">
-        <v>78.13</v>
+        <v>52.16</v>
       </c>
       <c r="I343" t="n">
-        <v>104.52</v>
+        <v>89.55</v>
       </c>
       <c r="J343" t="b">
         <v>1</v>
@@ -19724,7 +19724,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10504</t>
+          <t>PO-10503</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19734,27 +19734,27 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-06T15:17:25.257644+00:00</t>
+          <t>2026-09-01T16:10:57.796010+00:00</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-08-06T23:16:28.392964+00:00</t>
+          <t>2026-09-02T18:34:29.173140+00:00</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>2026-08-09T22:22:18.161310+00:00</t>
+          <t>2026-09-06T00:42:22.481813+00:00</t>
         </is>
       </c>
       <c r="G344" t="n">
-        <v>7.98</v>
+        <v>26.39</v>
       </c>
       <c r="H344" t="n">
-        <v>71.09999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="I344" t="n">
-        <v>79.08</v>
+        <v>104.52</v>
       </c>
       <c r="J344" t="b">
         <v>1</v>
@@ -19762,12 +19762,12 @@
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -19779,7 +19779,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10505</t>
+          <t>PO-10504</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19789,27 +19789,27 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-12T21:36:25.918953+00:00</t>
+          <t>2026-08-06T15:17:25.257644+00:00</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-08-14T00:18:23.475181+00:00</t>
+          <t>2026-08-06T23:16:28.392964+00:00</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-08-16T16:17:04.216594+00:00</t>
+          <t>2026-08-09T22:22:18.161310+00:00</t>
         </is>
       </c>
       <c r="G345" t="n">
-        <v>26.7</v>
+        <v>7.98</v>
       </c>
       <c r="H345" t="n">
-        <v>63.98</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I345" t="n">
-        <v>90.68000000000001</v>
+        <v>79.08</v>
       </c>
       <c r="J345" t="b">
         <v>1</v>
@@ -19822,19 +19822,19 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10506</t>
+          <t>PO-10505</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19844,27 +19844,27 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-03T11:25:33.495098+00:00</t>
+          <t>2026-08-12T21:36:25.918953+00:00</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-09-03T16:38:32.266915+00:00</t>
+          <t>2026-08-14T00:18:23.475181+00:00</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:10.888701+00:00</t>
+          <t>2026-08-16T16:17:04.216594+00:00</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>5.22</v>
+        <v>26.7</v>
       </c>
       <c r="H346" t="n">
-        <v>114.61</v>
+        <v>63.98</v>
       </c>
       <c r="I346" t="n">
-        <v>119.83</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="J346" t="b">
         <v>1</v>
@@ -19872,24 +19872,24 @@
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10507</t>
+          <t>PO-10506</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19899,27 +19899,27 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-18T12:27:20.859241+00:00</t>
+          <t>2026-09-03T11:25:33.495098+00:00</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-09-18T15:45:07.848708+00:00</t>
+          <t>2026-09-03T16:38:32.266915+00:00</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-09-22T00:28:12.771882+00:00</t>
+          <t>2026-09-08T11:15:10.888701+00:00</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>3.3</v>
+        <v>5.22</v>
       </c>
       <c r="H347" t="n">
-        <v>80.72</v>
+        <v>114.61</v>
       </c>
       <c r="I347" t="n">
-        <v>84.01000000000001</v>
+        <v>119.83</v>
       </c>
       <c r="J347" t="b">
         <v>1</v>
@@ -19932,19 +19932,19 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10511</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19954,27 +19954,27 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-04T20:17:44.545188+00:00</t>
+          <t>2026-09-18T12:27:20.859241+00:00</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-09-05T10:10:40.749824+00:00</t>
+          <t>2026-09-18T15:45:07.848708+00:00</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-09-08T02:48:51.034616+00:00</t>
+          <t>2026-09-22T00:28:12.771882+00:00</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>13.88</v>
+        <v>3.3</v>
       </c>
       <c r="H348" t="n">
-        <v>64.64</v>
+        <v>80.72</v>
       </c>
       <c r="I348" t="n">
-        <v>78.52</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="J348" t="b">
         <v>1</v>
@@ -19987,123 +19987,123 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10513</t>
+          <t>PO-10511</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-10-08T19:25:58.442739+00:00</t>
+          <t>2026-09-04T20:17:44.545188+00:00</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-10-10T04:23:28.455671+00:00</t>
-        </is>
-      </c>
-      <c r="F349" t="inlineStr"/>
+          <t>2026-09-05T10:10:40.749824+00:00</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>2026-09-08T02:48:51.034616+00:00</t>
+        </is>
+      </c>
       <c r="G349" t="n">
-        <v>32.96</v>
-      </c>
-      <c r="H349" t="inlineStr"/>
-      <c r="I349" t="inlineStr"/>
+        <v>13.88</v>
+      </c>
+      <c r="H349" t="n">
+        <v>64.64</v>
+      </c>
+      <c r="I349" t="n">
+        <v>78.52</v>
+      </c>
       <c r="J349" t="b">
-        <v>0</v>
-      </c>
-      <c r="K349" t="n">
-        <v>15.68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10514</t>
+          <t>PO-10513</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-28T12:35:00.419074+00:00</t>
+          <t>2026-10-08T19:25:58.442739+00:00</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-08-30T18:07:11.901792+00:00</t>
-        </is>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>2026-08-30T23:33:48.431347+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-10T04:23:28.455671+00:00</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
       <c r="G350" t="n">
-        <v>53.54</v>
-      </c>
-      <c r="H350" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="I350" t="n">
-        <v>58.98</v>
-      </c>
+        <v>32.96</v>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr"/>
       <c r="J350" t="b">
-        <v>1</v>
-      </c>
-      <c r="K350" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
+        <v>39.64</v>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10515</t>
+          <t>PO-10514</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20113,27 +20113,27 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-25T09:27:22.946834+00:00</t>
+          <t>2026-08-28T12:35:00.419074+00:00</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-09-26T15:01:10.819219+00:00</t>
+          <t>2026-08-30T18:07:11.901792+00:00</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-09-28T09:45:20.374206+00:00</t>
+          <t>2026-08-30T23:33:48.431347+00:00</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>29.56</v>
+        <v>53.54</v>
       </c>
       <c r="H351" t="n">
-        <v>42.74</v>
+        <v>5.44</v>
       </c>
       <c r="I351" t="n">
-        <v>72.3</v>
+        <v>58.98</v>
       </c>
       <c r="J351" t="b">
         <v>1</v>
@@ -20141,73 +20141,79 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10516</t>
+          <t>PO-10515</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-08-17T22:27:11.867127+00:00</t>
+          <t>2026-09-25T09:27:22.946834+00:00</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-08-20T09:21:31.781331+00:00</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr"/>
+          <t>2026-09-26T15:01:10.819219+00:00</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>2026-09-28T09:45:20.374206+00:00</t>
+        </is>
+      </c>
       <c r="G352" t="n">
-        <v>58.91</v>
-      </c>
-      <c r="H352" t="inlineStr"/>
-      <c r="I352" t="inlineStr"/>
+        <v>29.56</v>
+      </c>
+      <c r="H352" t="n">
+        <v>42.74</v>
+      </c>
+      <c r="I352" t="n">
+        <v>72.3</v>
+      </c>
       <c r="J352" t="b">
-        <v>0</v>
-      </c>
-      <c r="K352" t="n">
-        <v>1260.66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10517</t>
+          <t>PO-10516</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20217,17 +20223,17 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-10-12T17:06:21.615195+00:00</t>
+          <t>2026-08-17T22:27:11.867127+00:00</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-10-13T14:42:57.412543+00:00</t>
+          <t>2026-08-20T09:21:31.781331+00:00</t>
         </is>
       </c>
       <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>21.61</v>
+        <v>58.91</v>
       </c>
       <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr"/>
@@ -20235,16 +20241,16 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>-78</v>
+        <v>1284.62</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -20256,27 +20262,27 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10517</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-10-01T19:13:45.683677+00:00</t>
+          <t>2026-10-12T17:06:21.615195+00:00</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-10-04T07:25:33.582465+00:00</t>
+          <t>2026-10-13T14:42:57.412543+00:00</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>60.2</v>
+        <v>21.61</v>
       </c>
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
@@ -20284,7 +20290,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>183.88</v>
+        <v>-54.03</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -20293,19 +20299,19 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10519</t>
+          <t>PO-10518</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20315,17 +20321,17 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-10-05T21:50:20.734144+00:00</t>
+          <t>2026-10-01T19:13:45.683677+00:00</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-07T17:40:13.163466+00:00</t>
+          <t>2026-10-04T07:25:33.582465+00:00</t>
         </is>
       </c>
       <c r="F355" t="inlineStr"/>
       <c r="G355" t="n">
-        <v>43.83</v>
+        <v>60.2</v>
       </c>
       <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr"/>
@@ -20333,7 +20339,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>85.27</v>
+        <v>207.85</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -20342,19 +20348,19 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10520</t>
+          <t>PO-10519</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20364,27 +20370,27 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-06T12:28:31.557626+00:00</t>
+          <t>2026-10-05T21:50:20.734144+00:00</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-08-08T22:34:29.902721+00:00</t>
+          <t>2026-10-07T17:40:13.163466+00:00</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-08-10T13:55:47.178696+00:00</t>
+          <t>2026-10-09T19:45:48.589802+00:00</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>58.1</v>
+        <v>43.83</v>
       </c>
       <c r="H356" t="n">
-        <v>39.35</v>
+        <v>50.09</v>
       </c>
       <c r="I356" t="n">
-        <v>97.45</v>
+        <v>93.92</v>
       </c>
       <c r="J356" t="b">
         <v>1</v>
@@ -20392,73 +20398,79 @@
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10520</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-10-12T07:25:04.559072+00:00</t>
+          <t>2026-08-06T12:28:31.557626+00:00</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-10-13T10:27:14.088287+00:00</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr"/>
+          <t>2026-08-08T22:34:29.902721+00:00</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>2026-08-10T13:55:47.178696+00:00</t>
+        </is>
+      </c>
       <c r="G357" t="n">
-        <v>27.04</v>
-      </c>
-      <c r="H357" t="inlineStr"/>
-      <c r="I357" t="inlineStr"/>
+        <v>58.1</v>
+      </c>
+      <c r="H357" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="I357" t="n">
+        <v>97.45</v>
+      </c>
       <c r="J357" t="b">
-        <v>0</v>
-      </c>
-      <c r="K357" t="n">
-        <v>-68.31</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20468,17 +20480,17 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-08-11T03:46:13.881420+00:00</t>
+          <t>2026-10-12T07:25:04.559072+00:00</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-08-12T15:53:25.625643+00:00</t>
+          <t>2026-10-13T10:27:14.088287+00:00</t>
         </is>
       </c>
       <c r="F358" t="inlineStr"/>
       <c r="G358" t="n">
-        <v>36.12</v>
+        <v>27.04</v>
       </c>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr"/>
@@ -20486,16 +20498,16 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>1423.34</v>
+        <v>-44.34</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -20507,42 +20519,36 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10524</t>
+          <t>PO-10522</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-08-18T13:52:22.507142+00:00</t>
+          <t>2026-08-11T03:46:13.881420+00:00</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-08-21T13:56:45.271649+00:00</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2026-08-21T23:12:45.771375+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-12T15:53:25.625643+00:00</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>72.06999999999999</v>
-      </c>
-      <c r="H359" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="I359" t="n">
-        <v>81.34</v>
-      </c>
+        <v>36.12</v>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
       <c r="J359" t="b">
-        <v>1</v>
-      </c>
-      <c r="K359" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K359" t="n">
+        <v>1447.3</v>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -20550,48 +20556,54 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10525</t>
+          <t>PO-10524</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-10T09:18:03.411993+00:00</t>
+          <t>2026-08-18T13:52:22.507142+00:00</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-08-12T16:20:47.711713+00:00</t>
-        </is>
-      </c>
-      <c r="F360" t="inlineStr"/>
+          <t>2026-08-21T13:56:45.271649+00:00</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>2026-08-21T23:12:45.771375+00:00</t>
+        </is>
+      </c>
       <c r="G360" t="n">
-        <v>55.05</v>
-      </c>
-      <c r="H360" t="inlineStr"/>
-      <c r="I360" t="inlineStr"/>
+        <v>72.06999999999999</v>
+      </c>
+      <c r="H360" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="I360" t="n">
+        <v>81.34</v>
+      </c>
       <c r="J360" t="b">
-        <v>0</v>
-      </c>
-      <c r="K360" t="n">
-        <v>1441.81</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -20599,54 +20611,48 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10528</t>
+          <t>PO-10525</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-16T02:01:54.885863+00:00</t>
+          <t>2026-08-10T09:18:03.411993+00:00</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-08-16T21:09:23.207688+00:00</t>
-        </is>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>2026-08-18T02:22:56.590571+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-12T16:20:47.711713+00:00</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="H361" t="n">
-        <v>29.23</v>
-      </c>
-      <c r="I361" t="n">
-        <v>48.35</v>
-      </c>
+        <v>55.05</v>
+      </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr"/>
       <c r="J361" t="b">
-        <v>1</v>
-      </c>
-      <c r="K361" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K361" t="n">
+        <v>1465.77</v>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -20666,36 +20672,42 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10528</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-16T11:32:17.062607+00:00</t>
+          <t>2026-08-16T02:01:54.885863+00:00</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-08-18T13:57:29.497866+00:00</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr"/>
+          <t>2026-08-16T21:09:23.207688+00:00</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2026-08-18T02:22:56.590571+00:00</t>
+        </is>
+      </c>
       <c r="G362" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="H362" t="inlineStr"/>
-      <c r="I362" t="inlineStr"/>
+        <v>19.12</v>
+      </c>
+      <c r="H362" t="n">
+        <v>29.23</v>
+      </c>
+      <c r="I362" t="n">
+        <v>48.35</v>
+      </c>
       <c r="J362" t="b">
-        <v>0</v>
-      </c>
-      <c r="K362" t="n">
-        <v>1295.57</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -20710,55 +20722,49 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10530</t>
+          <t>PO-10529</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-10-02T03:06:52.204713+00:00</t>
+          <t>2026-08-16T11:32:17.062607+00:00</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-10-03T05:43:54.768920+00:00</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>2026-10-04T21:41:22.411968+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-18T13:57:29.497866+00:00</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr"/>
       <c r="G363" t="n">
-        <v>26.62</v>
-      </c>
-      <c r="H363" t="n">
-        <v>39.96</v>
-      </c>
-      <c r="I363" t="n">
-        <v>66.58</v>
-      </c>
+        <v>50.42</v>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr"/>
       <c r="J363" t="b">
-        <v>1</v>
-      </c>
-      <c r="K363" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K363" t="n">
+        <v>1319.54</v>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -20770,7 +20776,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10531</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20780,27 +20786,27 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-08-13T11:41:12.939185+00:00</t>
+          <t>2026-10-02T03:06:52.204713+00:00</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-08-13T14:54:56.715542+00:00</t>
+          <t>2026-10-03T05:43:54.768920+00:00</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>2026-08-15T04:52:53.625014+00:00</t>
+          <t>2026-10-04T21:41:22.411968+00:00</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>3.23</v>
+        <v>26.62</v>
       </c>
       <c r="H364" t="n">
-        <v>37.97</v>
+        <v>39.96</v>
       </c>
       <c r="I364" t="n">
-        <v>41.19</v>
+        <v>66.58</v>
       </c>
       <c r="J364" t="b">
         <v>1</v>
@@ -20808,12 +20814,12 @@
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -20825,7 +20831,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10532</t>
+          <t>PO-10531</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20835,27 +20841,27 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-09-27T20:19:57.430213+00:00</t>
+          <t>2026-08-13T11:41:12.939185+00:00</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-09-28T02:04:57.914534+00:00</t>
+          <t>2026-08-13T14:54:56.715542+00:00</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>2026-09-30T05:37:24.861343+00:00</t>
+          <t>2026-08-15T04:52:53.625014+00:00</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>5.75</v>
+        <v>3.23</v>
       </c>
       <c r="H365" t="n">
-        <v>51.54</v>
+        <v>37.97</v>
       </c>
       <c r="I365" t="n">
-        <v>57.29</v>
+        <v>41.19</v>
       </c>
       <c r="J365" t="b">
         <v>1</v>
@@ -20863,53 +20869,59 @@
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10533</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-09-07T01:40:13.965224+00:00</t>
+          <t>2026-09-27T20:19:57.430213+00:00</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-09-08T11:42:04.638687+00:00</t>
-        </is>
-      </c>
-      <c r="F366" t="inlineStr"/>
+          <t>2026-09-28T02:04:57.914534+00:00</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>2026-09-30T05:37:24.861343+00:00</t>
+        </is>
+      </c>
       <c r="G366" t="n">
-        <v>34.03</v>
-      </c>
-      <c r="H366" t="inlineStr"/>
-      <c r="I366" t="inlineStr"/>
+        <v>5.75</v>
+      </c>
+      <c r="H366" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="I366" t="n">
+        <v>57.29</v>
+      </c>
       <c r="J366" t="b">
-        <v>0</v>
-      </c>
-      <c r="K366" t="n">
-        <v>777.4400000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -20917,54 +20929,48 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10535</t>
+          <t>PO-10533</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-09-26T08:48:56.678519+00:00</t>
+          <t>2026-09-07T01:40:13.965224+00:00</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-09-28T11:17:18.629658+00:00</t>
-        </is>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>2026-09-29T18:54:01.738390+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-08T11:42:04.638687+00:00</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr"/>
       <c r="G367" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="H367" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="I367" t="n">
-        <v>82.08</v>
-      </c>
+        <v>34.03</v>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr"/>
       <c r="J367" t="b">
-        <v>1</v>
-      </c>
-      <c r="K367" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>801.4</v>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -20972,19 +20978,19 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10536</t>
+          <t>PO-10535</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20994,27 +21000,27 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-23T06:12:07.616449+00:00</t>
+          <t>2026-09-26T08:48:56.678519+00:00</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-09-24T15:52:37.551670+00:00</t>
+          <t>2026-09-28T11:17:18.629658+00:00</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-09-27T00:23:00.657506+00:00</t>
+          <t>2026-09-29T18:54:01.738390+00:00</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>33.67</v>
+        <v>50.47</v>
       </c>
       <c r="H368" t="n">
-        <v>56.51</v>
+        <v>31.61</v>
       </c>
       <c r="I368" t="n">
-        <v>90.18000000000001</v>
+        <v>82.08</v>
       </c>
       <c r="J368" t="b">
         <v>1</v>
@@ -21034,12 +21040,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10536</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21049,27 +21055,27 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-12T15:10:11.725791+00:00</t>
+          <t>2026-09-23T06:12:07.616449+00:00</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-08-14T01:18:09.047021+00:00</t>
+          <t>2026-09-24T15:52:37.551670+00:00</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2026-08-16T16:12:40.195622+00:00</t>
+          <t>2026-09-27T00:23:00.657506+00:00</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>34.13</v>
+        <v>33.67</v>
       </c>
       <c r="H369" t="n">
-        <v>62.91</v>
+        <v>56.51</v>
       </c>
       <c r="I369" t="n">
-        <v>97.04000000000001</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="J369" t="b">
         <v>1</v>
@@ -21077,12 +21083,12 @@
       <c r="K369" t="inlineStr"/>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -21094,62 +21100,56 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10538</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-09-25T12:05:30.837880+00:00</t>
+          <t>2026-10-14T09:59:13.458924+00:00</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-09-27T00:38:46.824642+00:00</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>2026-09-27T04:52:36.343634+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-15T16:47:55.886881+00:00</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr"/>
       <c r="G370" t="n">
-        <v>36.55</v>
-      </c>
-      <c r="H370" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="I370" t="n">
-        <v>40.78</v>
-      </c>
+        <v>30.81</v>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr"/>
       <c r="J370" t="b">
-        <v>1</v>
-      </c>
-      <c r="K370" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>-94.91</v>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10542</t>
+          <t>PO-10539</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21159,27 +21159,27 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-03T04:13:50.299988+00:00</t>
+          <t>2026-09-30T16:51:26.731151+00:00</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-09-04T00:23:54.815814+00:00</t>
+          <t>2026-10-04T07:32:29.826345+00:00</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-09-06T03:42:54.298807+00:00</t>
+          <t>2026-10-07T06:32:54.729961+00:00</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>20.17</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="H371" t="n">
-        <v>51.32</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="I371" t="n">
-        <v>71.48</v>
+        <v>157.69</v>
       </c>
       <c r="J371" t="b">
         <v>1</v>
@@ -21192,117 +21192,105 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10543</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-08-23T22:36:27.710601+00:00</t>
+          <t>2026-10-09T10:15:44.580551+00:00</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-08-24T22:18:54.011474+00:00</t>
-        </is>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>2026-08-25T20:54:28.750229+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-10T00:07:58.109611+00:00</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr"/>
       <c r="G372" t="n">
-        <v>23.71</v>
-      </c>
-      <c r="H372" t="n">
-        <v>22.59</v>
-      </c>
-      <c r="I372" t="n">
-        <v>46.3</v>
-      </c>
+        <v>13.87</v>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr"/>
       <c r="J372" t="b">
-        <v>1</v>
-      </c>
-      <c r="K372" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>24.81</v>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10544</t>
+          <t>PO-10541</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-09-08T13:05:55.781125+00:00</t>
+          <t>2026-10-07T09:57:50.147511+00:00</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-09-09T21:16:32.627073+00:00</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>2026-09-15T09:19:04.986914+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-09T11:39:59.246568+00:00</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
-        <v>32.18</v>
-      </c>
-      <c r="H373" t="n">
-        <v>132.04</v>
-      </c>
-      <c r="I373" t="n">
-        <v>164.22</v>
-      </c>
+        <v>49.7</v>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
       <c r="J373" t="b">
-        <v>1</v>
-      </c>
-      <c r="K373" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K373" t="n">
+        <v>73.11</v>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -21314,42 +21302,36 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-09-18T06:05:14.732667+00:00</t>
+          <t>2026-09-15T17:04:16.078411+00:00</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-09-20T18:51:07.315001+00:00</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>2026-09-22T09:53:07.941793+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-17T07:04:14.427206+00:00</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr"/>
       <c r="G374" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="H374" t="n">
-        <v>39.03</v>
-      </c>
-      <c r="I374" t="n">
-        <v>99.8</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr"/>
       <c r="J374" t="b">
-        <v>1</v>
-      </c>
-      <c r="K374" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
+        <v>594</v>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -21364,12 +21346,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10549</t>
+          <t>PO-10543</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21379,27 +21361,27 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-25T10:48:32.733828+00:00</t>
+          <t>2026-08-28T06:27:56.812254+00:00</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-08-26T21:43:48.732261+00:00</t>
+          <t>2026-08-31T12:20:00.151268+00:00</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>2026-08-27T21:54:57.128563+00:00</t>
+          <t>2026-09-03T08:09:46.557253+00:00</t>
         </is>
       </c>
       <c r="G375" t="n">
-        <v>34.92</v>
+        <v>77.87</v>
       </c>
       <c r="H375" t="n">
-        <v>24.19</v>
+        <v>67.83</v>
       </c>
       <c r="I375" t="n">
-        <v>59.11</v>
+        <v>145.7</v>
       </c>
       <c r="J375" t="b">
         <v>1</v>
@@ -21424,56 +21406,62 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10550</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-10-13T03:02:49.669800+00:00</t>
+          <t>2026-09-18T06:05:14.732667+00:00</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-10-14T14:15:28.972878+00:00</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr"/>
+          <t>2026-09-20T18:51:07.315001+00:00</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-09-22T09:53:07.941793+00:00</t>
+        </is>
+      </c>
       <c r="G376" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
+        <v>60.76</v>
+      </c>
+      <c r="H376" t="n">
+        <v>39.03</v>
+      </c>
+      <c r="I376" t="n">
+        <v>99.8</v>
+      </c>
       <c r="J376" t="b">
-        <v>0</v>
-      </c>
-      <c r="K376" t="n">
-        <v>-87.94</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10551</t>
+          <t>PO-10547</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21483,27 +21471,27 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-10-01T01:34:58.328543+00:00</t>
+          <t>2026-08-25T10:48:32.733828+00:00</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-10-01T08:49:19.134062+00:00</t>
+          <t>2026-08-26T21:43:48.732261+00:00</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>2026-10-01T22:37:14.930137+00:00</t>
+          <t>2026-08-27T21:54:57.128563+00:00</t>
         </is>
       </c>
       <c r="G377" t="n">
-        <v>7.24</v>
+        <v>34.92</v>
       </c>
       <c r="H377" t="n">
-        <v>13.8</v>
+        <v>24.19</v>
       </c>
       <c r="I377" t="n">
-        <v>21.04</v>
+        <v>59.11</v>
       </c>
       <c r="J377" t="b">
         <v>1</v>
@@ -21511,79 +21499,73 @@
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10552</t>
+          <t>PO-10548</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-09-29T07:38:45.123436+00:00</t>
+          <t>2026-10-13T03:02:49.669800+00:00</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-10-01T02:19:46.942968+00:00</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>2026-10-04T15:16:49.058324+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-14T14:15:28.972878+00:00</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" t="n">
-        <v>42.68</v>
-      </c>
-      <c r="H378" t="n">
-        <v>84.95</v>
-      </c>
-      <c r="I378" t="n">
-        <v>127.63</v>
-      </c>
+        <v>35.21</v>
+      </c>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
       <c r="J378" t="b">
-        <v>1</v>
-      </c>
-      <c r="K378" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K378" t="n">
+        <v>-63.97</v>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10556</t>
+          <t>PO-10549</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21593,27 +21575,27 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-08-18T08:18:23.601518+00:00</t>
+          <t>2026-10-01T01:34:58.328543+00:00</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-08-20T04:18:48.318982+00:00</t>
+          <t>2026-10-01T08:49:19.134062+00:00</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-08-23T08:15:22.520821+00:00</t>
+          <t>2026-10-01T22:37:14.930137+00:00</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>44.01</v>
+        <v>7.24</v>
       </c>
       <c r="H379" t="n">
-        <v>75.94</v>
+        <v>13.8</v>
       </c>
       <c r="I379" t="n">
-        <v>119.95</v>
+        <v>21.04</v>
       </c>
       <c r="J379" t="b">
         <v>1</v>
@@ -21621,24 +21603,24 @@
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10557</t>
+          <t>PO-10550</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21648,27 +21630,27 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-21T01:10:17.136890+00:00</t>
+          <t>2026-09-29T07:38:45.123436+00:00</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-08-22T23:02:34.077777+00:00</t>
+          <t>2026-10-01T02:19:46.942968+00:00</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-08-24T10:24:44.895786+00:00</t>
+          <t>2026-10-04T15:16:49.058324+00:00</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>45.87</v>
+        <v>42.68</v>
       </c>
       <c r="H380" t="n">
-        <v>35.37</v>
+        <v>84.95</v>
       </c>
       <c r="I380" t="n">
-        <v>81.23999999999999</v>
+        <v>127.63</v>
       </c>
       <c r="J380" t="b">
         <v>1</v>
@@ -21676,24 +21658,24 @@
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10559</t>
+          <t>PO-10554</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21703,27 +21685,27 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-09-29T01:31:35.007610+00:00</t>
+          <t>2026-08-18T08:18:23.601518+00:00</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-09-29T13:24:00.117735+00:00</t>
+          <t>2026-08-20T04:18:48.318982+00:00</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-10-01T06:55:42.864711+00:00</t>
+          <t>2026-08-23T08:15:22.520821+00:00</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>11.87</v>
+        <v>44.01</v>
       </c>
       <c r="H381" t="n">
-        <v>41.53</v>
+        <v>75.94</v>
       </c>
       <c r="I381" t="n">
-        <v>53.4</v>
+        <v>119.95</v>
       </c>
       <c r="J381" t="b">
         <v>1</v>
@@ -21731,12 +21713,12 @@
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -21748,7 +21730,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10560</t>
+          <t>PO-10555</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21758,27 +21740,27 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-09-16T07:28:51.601950+00:00</t>
+          <t>2026-08-21T01:10:17.136890+00:00</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-09-17T19:46:15.585581+00:00</t>
+          <t>2026-08-22T23:02:34.077777+00:00</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-09-20T18:38:43.283997+00:00</t>
+          <t>2026-08-24T10:24:44.895786+00:00</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>36.29</v>
+        <v>45.87</v>
       </c>
       <c r="H382" t="n">
-        <v>70.87</v>
+        <v>35.37</v>
       </c>
       <c r="I382" t="n">
-        <v>107.16</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="J382" t="b">
         <v>1</v>
@@ -21786,24 +21768,24 @@
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10564</t>
+          <t>PO-10557</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21813,27 +21795,27 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-22T22:49:57.786697+00:00</t>
+          <t>2026-09-29T01:31:35.007610+00:00</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-09-24T10:41:20.139185+00:00</t>
+          <t>2026-09-29T13:24:00.117735+00:00</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>2026-09-29T04:10:36.889140+00:00</t>
+          <t>2026-10-01T06:55:42.864711+00:00</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>35.86</v>
+        <v>11.87</v>
       </c>
       <c r="H383" t="n">
-        <v>113.49</v>
+        <v>41.53</v>
       </c>
       <c r="I383" t="n">
-        <v>149.34</v>
+        <v>53.4</v>
       </c>
       <c r="J383" t="b">
         <v>1</v>
@@ -21846,68 +21828,74 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10565</t>
+          <t>PO-10558</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-08-26T00:10:17.513362+00:00</t>
+          <t>2026-09-16T07:28:51.601950+00:00</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-08-26T17:02:14.582750+00:00</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr"/>
+          <t>2026-09-17T19:46:15.585581+00:00</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-09-20T18:38:43.283997+00:00</t>
+        </is>
+      </c>
       <c r="G384" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
+        <v>36.29</v>
+      </c>
+      <c r="H384" t="n">
+        <v>70.87</v>
+      </c>
+      <c r="I384" t="n">
+        <v>107.16</v>
+      </c>
       <c r="J384" t="b">
-        <v>0</v>
-      </c>
-      <c r="K384" t="n">
-        <v>1066.94</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10566</t>
+          <t>PO-10562</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21917,27 +21905,27 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-08T11:15:58.813417+00:00</t>
+          <t>2026-09-22T22:49:57.786697+00:00</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-08-08T14:56:53.887078+00:00</t>
+          <t>2026-09-24T10:41:20.139185+00:00</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>2026-08-10T21:10:27.076616+00:00</t>
+          <t>2026-09-29T04:10:36.889140+00:00</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>3.68</v>
+        <v>35.86</v>
       </c>
       <c r="H385" t="n">
-        <v>54.23</v>
+        <v>113.49</v>
       </c>
       <c r="I385" t="n">
-        <v>57.91</v>
+        <v>149.34</v>
       </c>
       <c r="J385" t="b">
         <v>1</v>
@@ -21945,79 +21933,73 @@
       <c r="K385" t="inlineStr"/>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10567</t>
+          <t>PO-10563</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-09T03:48:36.013567+00:00</t>
+          <t>2026-08-26T00:10:17.513362+00:00</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-09-11T04:29:50.524995+00:00</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>2026-09-14T02:58:22.220455+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-26T17:02:14.582750+00:00</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
       <c r="G386" t="n">
-        <v>48.69</v>
-      </c>
-      <c r="H386" t="n">
-        <v>70.48</v>
-      </c>
-      <c r="I386" t="n">
-        <v>119.16</v>
-      </c>
+        <v>16.87</v>
+      </c>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
       <c r="J386" t="b">
-        <v>1</v>
-      </c>
-      <c r="K386" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K386" t="n">
+        <v>1090.9</v>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10571</t>
+          <t>PO-10564</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22027,27 +22009,27 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-17T14:30:34.313777+00:00</t>
+          <t>2026-08-08T11:15:58.813417+00:00</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-09-19T07:06:39.336574+00:00</t>
+          <t>2026-08-08T14:56:53.887078+00:00</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-09-21T05:03:03.900005+00:00</t>
+          <t>2026-08-10T21:10:27.076616+00:00</t>
         </is>
       </c>
       <c r="G387" t="n">
-        <v>40.6</v>
+        <v>3.68</v>
       </c>
       <c r="H387" t="n">
-        <v>45.94</v>
+        <v>54.23</v>
       </c>
       <c r="I387" t="n">
-        <v>86.54000000000001</v>
+        <v>57.91</v>
       </c>
       <c r="J387" t="b">
         <v>1</v>
@@ -22055,53 +22037,59 @@
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10573</t>
+          <t>PO-10565</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-10T12:22:28.845322+00:00</t>
+          <t>2026-09-09T03:48:36.013567+00:00</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-09-10T18:43:53.991861+00:00</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr"/>
+          <t>2026-09-11T04:29:50.524995+00:00</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>2026-09-14T02:58:22.220455+00:00</t>
+        </is>
+      </c>
       <c r="G388" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="H388" t="inlineStr"/>
-      <c r="I388" t="inlineStr"/>
+        <v>48.69</v>
+      </c>
+      <c r="H388" t="n">
+        <v>70.48</v>
+      </c>
+      <c r="I388" t="n">
+        <v>119.16</v>
+      </c>
       <c r="J388" t="b">
-        <v>0</v>
-      </c>
-      <c r="K388" t="n">
-        <v>694.73</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22116,41 +22104,47 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10574</t>
+          <t>PO-10569</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-05T01:46:42.783345+00:00</t>
+          <t>2026-09-17T14:30:34.313777+00:00</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-09-05T23:00:42.432096+00:00</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr"/>
+          <t>2026-09-19T07:06:39.336574+00:00</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-09-21T05:03:03.900005+00:00</t>
+        </is>
+      </c>
       <c r="G389" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="H389" t="inlineStr"/>
-      <c r="I389" t="inlineStr"/>
+        <v>40.6</v>
+      </c>
+      <c r="H389" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="I389" t="n">
+        <v>86.54000000000001</v>
+      </c>
       <c r="J389" t="b">
-        <v>0</v>
-      </c>
-      <c r="K389" t="n">
-        <v>825.33</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22158,54 +22152,48 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10575</t>
+          <t>PO-10571</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-17T19:20:11.795162+00:00</t>
+          <t>2026-09-10T12:22:28.845322+00:00</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-09-20T02:55:18.519980+00:00</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>2026-09-24T17:37:09.196078+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-10T18:43:53.991861+00:00</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
       <c r="G390" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="H390" t="n">
-        <v>110.7</v>
-      </c>
-      <c r="I390" t="n">
-        <v>166.28</v>
-      </c>
+        <v>6.36</v>
+      </c>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
       <c r="J390" t="b">
-        <v>1</v>
-      </c>
-      <c r="K390" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K390" t="n">
+        <v>718.7</v>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22213,7 +22201,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -22225,27 +22213,27 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10578</t>
+          <t>PO-10572</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-10-07T06:30:07.314893+00:00</t>
+          <t>2026-09-05T01:46:42.783345+00:00</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-10-07T22:14:07.936372+00:00</t>
+          <t>2026-09-05T23:00:42.432096+00:00</t>
         </is>
       </c>
       <c r="F391" t="inlineStr"/>
       <c r="G391" t="n">
-        <v>15.73</v>
+        <v>21.23</v>
       </c>
       <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr"/>
@@ -22253,16 +22241,16 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>52.61</v>
+        <v>849.3</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -22274,7 +22262,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10579</t>
+          <t>PO-10573</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22284,27 +22272,27 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-16T22:32:09.599556+00:00</t>
+          <t>2026-09-17T19:20:11.795162+00:00</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-09-18T18:42:54.145985+00:00</t>
+          <t>2026-09-20T02:55:18.519980+00:00</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>2026-09-21T08:13:42.147403+00:00</t>
+          <t>2026-09-24T17:37:09.196078+00:00</t>
         </is>
       </c>
       <c r="G392" t="n">
-        <v>44.18</v>
+        <v>55.59</v>
       </c>
       <c r="H392" t="n">
-        <v>61.51</v>
+        <v>110.7</v>
       </c>
       <c r="I392" t="n">
-        <v>105.69</v>
+        <v>166.28</v>
       </c>
       <c r="J392" t="b">
         <v>1</v>
@@ -22324,67 +22312,61 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10582</t>
+          <t>PO-10576</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-23T00:23:09.845408+00:00</t>
+          <t>2026-10-07T06:30:07.314893+00:00</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-08-24T13:57:23.901980+00:00</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>2026-08-25T12:08:11.844181+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-07T22:14:07.936372+00:00</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
       <c r="G393" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="H393" t="n">
-        <v>22.18</v>
-      </c>
-      <c r="I393" t="n">
-        <v>59.75</v>
-      </c>
+        <v>15.73</v>
+      </c>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
       <c r="J393" t="b">
-        <v>1</v>
-      </c>
-      <c r="K393" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>76.56999999999999</v>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10583</t>
+          <t>PO-10577</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22394,27 +22376,27 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-06T01:22:54.855884+00:00</t>
+          <t>2026-09-16T22:32:09.599556+00:00</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-09-06T23:41:23.435126+00:00</t>
+          <t>2026-09-18T18:42:54.145985+00:00</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-09-07T09:47:48.263323+00:00</t>
+          <t>2026-09-21T08:13:42.147403+00:00</t>
         </is>
       </c>
       <c r="G394" t="n">
-        <v>22.31</v>
+        <v>44.18</v>
       </c>
       <c r="H394" t="n">
-        <v>10.11</v>
+        <v>61.51</v>
       </c>
       <c r="I394" t="n">
-        <v>32.41</v>
+        <v>105.69</v>
       </c>
       <c r="J394" t="b">
         <v>1</v>
@@ -22427,68 +22409,74 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10586</t>
+          <t>PO-10580</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-09-27T00:18:24.785515+00:00</t>
+          <t>2026-08-23T00:23:09.845408+00:00</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-09-27T09:52:49.421779+00:00</t>
-        </is>
-      </c>
-      <c r="F395" t="inlineStr"/>
+          <t>2026-08-24T13:57:23.901980+00:00</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2026-08-25T12:08:11.844181+00:00</t>
+        </is>
+      </c>
       <c r="G395" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="H395" t="inlineStr"/>
-      <c r="I395" t="inlineStr"/>
+        <v>37.57</v>
+      </c>
+      <c r="H395" t="n">
+        <v>22.18</v>
+      </c>
+      <c r="I395" t="n">
+        <v>59.75</v>
+      </c>
       <c r="J395" t="b">
-        <v>0</v>
-      </c>
-      <c r="K395" t="n">
-        <v>298.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10587</t>
+          <t>PO-10581</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22498,27 +22486,27 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-10-02T06:47:57.340763+00:00</t>
+          <t>2026-09-06T01:22:54.855884+00:00</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-10-02T15:48:19.434701+00:00</t>
+          <t>2026-09-06T23:41:23.435126+00:00</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-10-04T19:16:20.346680+00:00</t>
+          <t>2026-09-07T09:47:48.263323+00:00</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>9.01</v>
+        <v>22.31</v>
       </c>
       <c r="H396" t="n">
-        <v>51.47</v>
+        <v>10.11</v>
       </c>
       <c r="I396" t="n">
-        <v>60.47</v>
+        <v>32.41</v>
       </c>
       <c r="J396" t="b">
         <v>1</v>
@@ -22526,128 +22514,128 @@
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PO-10588</t>
+          <t>PO-10584</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-06T16:57:58.427622+00:00</t>
+          <t>2026-09-27T00:18:24.785515+00:00</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-08-08T15:30:51.105814+00:00</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>2026-08-11T03:49:20.271959+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-27T09:52:49.421779+00:00</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
-        <v>46.55</v>
-      </c>
-      <c r="H397" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="I397" t="n">
-        <v>106.86</v>
-      </c>
+        <v>9.57</v>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
       <c r="J397" t="b">
-        <v>1</v>
-      </c>
-      <c r="K397" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>322.77</v>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PO-10592</t>
+          <t>PO-10585</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-02T23:40:14.276060+00:00</t>
+          <t>2026-10-02T06:47:57.340763+00:00</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-09-03T14:16:36.045318+00:00</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr"/>
+          <t>2026-10-02T15:48:19.434701+00:00</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-10-04T19:16:20.346680+00:00</t>
+        </is>
+      </c>
       <c r="G398" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
+        <v>9.01</v>
+      </c>
+      <c r="H398" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="I398" t="n">
+        <v>60.47</v>
+      </c>
       <c r="J398" t="b">
-        <v>0</v>
-      </c>
-      <c r="K398" t="n">
-        <v>875.4400000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PO-10594</t>
+          <t>PO-10586</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22657,27 +22645,27 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-04T09:04:04.231838+00:00</t>
+          <t>2026-08-06T16:57:58.427622+00:00</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-09-07T23:15:30.642690+00:00</t>
+          <t>2026-08-08T15:30:51.105814+00:00</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>2026-09-12T21:07:36.636639+00:00</t>
+          <t>2026-08-11T03:49:20.271959+00:00</t>
         </is>
       </c>
       <c r="G399" t="n">
-        <v>86.19</v>
+        <v>46.55</v>
       </c>
       <c r="H399" t="n">
-        <v>117.87</v>
+        <v>60.31</v>
       </c>
       <c r="I399" t="n">
-        <v>204.06</v>
+        <v>106.86</v>
       </c>
       <c r="J399" t="b">
         <v>1</v>
@@ -22685,59 +22673,53 @@
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10590</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-18T13:20:17.190626+00:00</t>
+          <t>2026-09-02T23:40:14.276060+00:00</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-09-20T03:13:36.941066+00:00</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-09-22T14:33:45.250899+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-03T14:16:36.045318+00:00</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
       <c r="G400" t="n">
-        <v>37.89</v>
-      </c>
-      <c r="H400" t="n">
-        <v>59.34</v>
-      </c>
-      <c r="I400" t="n">
-        <v>97.22</v>
-      </c>
+        <v>14.61</v>
+      </c>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
       <c r="J400" t="b">
-        <v>1</v>
-      </c>
-      <c r="K400" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K400" t="n">
+        <v>899.4</v>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22745,19 +22727,19 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PO-10597</t>
+          <t>PO-10592</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -22767,27 +22749,27 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-30T07:21:55.275141+00:00</t>
+          <t>2026-09-04T09:04:04.231838+00:00</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-10-01T08:50:53.580538+00:00</t>
+          <t>2026-09-07T23:15:30.642690+00:00</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>2026-10-02T07:51:46.146475+00:00</t>
+          <t>2026-09-12T21:07:36.636639+00:00</t>
         </is>
       </c>
       <c r="G401" t="n">
-        <v>25.48</v>
+        <v>86.19</v>
       </c>
       <c r="H401" t="n">
-        <v>23.01</v>
+        <v>117.87</v>
       </c>
       <c r="I401" t="n">
-        <v>48.5</v>
+        <v>204.06</v>
       </c>
       <c r="J401" t="b">
         <v>1</v>
@@ -22800,19 +22782,19 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PO-10598</t>
+          <t>PO-10593</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -22822,27 +22804,27 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-31T09:13:28.604479+00:00</t>
+          <t>2026-09-18T13:20:17.190626+00:00</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-09-02T20:15:42.822032+00:00</t>
+          <t>2026-09-20T03:13:36.941066+00:00</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>2026-09-05T09:26:18.675009+00:00</t>
+          <t>2026-09-22T14:33:45.250899+00:00</t>
         </is>
       </c>
       <c r="G402" t="n">
-        <v>59.04</v>
+        <v>37.89</v>
       </c>
       <c r="H402" t="n">
-        <v>61.18</v>
+        <v>59.34</v>
       </c>
       <c r="I402" t="n">
-        <v>120.21</v>
+        <v>97.22</v>
       </c>
       <c r="J402" t="b">
         <v>1</v>
@@ -22850,24 +22832,24 @@
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>PO-10599</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -22877,27 +22859,27 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-08-25T00:36:56.096295+00:00</t>
+          <t>2026-09-30T07:21:55.275141+00:00</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-08-25T22:55:42.840833+00:00</t>
+          <t>2026-10-01T08:50:53.580538+00:00</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>2026-08-28T16:05:18.710307+00:00</t>
+          <t>2026-10-02T07:51:46.146475+00:00</t>
         </is>
       </c>
       <c r="G403" t="n">
-        <v>22.31</v>
+        <v>25.48</v>
       </c>
       <c r="H403" t="n">
-        <v>65.16</v>
+        <v>23.01</v>
       </c>
       <c r="I403" t="n">
-        <v>87.47</v>
+        <v>48.5</v>
       </c>
       <c r="J403" t="b">
         <v>1</v>
@@ -22905,12 +22887,232 @@
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-S40</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Delta Sports</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PO-10596</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-08-31T09:13:28.604479+00:00</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-09-02T20:15:42.822032+00:00</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>2026-09-05T09:26:18.675009+00:00</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>59.04</v>
+      </c>
+      <c r="H404" t="n">
+        <v>61.18</v>
+      </c>
+      <c r="I404" t="n">
+        <v>120.21</v>
+      </c>
+      <c r="J404" t="b">
+        <v>1</v>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="M403" t="inlineStr">
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-S36</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Fluxo Denim</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>PO-10597</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-08-25T00:36:56.096295+00:00</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>2026-08-25T22:55:42.840833+00:00</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>2026-08-28T16:05:18.710307+00:00</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="H405" t="n">
+        <v>65.16</v>
+      </c>
+      <c r="I405" t="n">
+        <v>87.47</v>
+      </c>
+      <c r="J405" t="b">
+        <v>1</v>
+      </c>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
         <is>
           <t>2026-S35</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Delta Sports</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>PO-10598</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-09-20T15:04:30.893700+00:00</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>2026-09-21T12:21:21.838950+00:00</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>2026-09-27T07:53:01.185675+00:00</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="H406" t="n">
+        <v>139.53</v>
+      </c>
+      <c r="I406" t="n">
+        <v>160.81</v>
+      </c>
+      <c r="J406" t="b">
+        <v>1</v>
+      </c>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-S38</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Delta Sports</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>PO-10599</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Aprovado</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-09-21T02:01:34.280043+00:00</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:01:16.127104+00:00</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>2026-09-27T00:17:00.385352+00:00</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="H407" t="n">
+        <v>118.26</v>
+      </c>
+      <c r="I407" t="n">
+        <v>142.26</v>
+      </c>
+      <c r="J407" t="b">
+        <v>1</v>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>92.2</v>
+        <v>92.3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>292</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>289</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>345</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24.6</v>
+        <v>25.3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -644,19 +644,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>90.2</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -711,16 +711,16 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>94.40000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="5">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>91.40000000000001</v>
+        <v>92.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -772,19 +772,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>76.90000000000001</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="8">
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E8" t="n">
         <v>68</v>
       </c>
       <c r="F8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>75.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>85.5</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="10">
@@ -903,16 +903,16 @@
         <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>70.40000000000001</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="11">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>53.9</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="12">
@@ -967,16 +967,16 @@
         <v>86</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>70.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F13" t="n">
         <v>25</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>60.9</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="14">
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
         <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>43.3</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="15">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E15" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>54.4</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="16">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E16" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" t="n">
         <v>33</v>
       </c>
       <c r="F17" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>42.3</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="18">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>25</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>32.8</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="20">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>18.9</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="22">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>74.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="23">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E23" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>78.7</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="24">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F24" t="n">
         <v>14</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>82.5</v>
+        <v>83.90000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F25" t="n">
         <v>24</v>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>66.7</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M407"/>
+  <dimension ref="A1:M405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>887.39</v>
+        <v>911.4</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>998.52</v>
+        <v>1022.52</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>122.73</v>
+        <v>146.73</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-74.54000000000001</v>
+        <v>-50.53</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1377.39</v>
+        <v>1401.4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>197.9</v>
+        <v>221.91</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.05</v>
+        <v>17.96</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>783.86</v>
+        <v>807.86</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1140.89</v>
+        <v>1164.9</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2470,62 +2470,56 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PO-10031</t>
+          <t>PO-10033</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-31T01:27:10.137032+00:00</t>
+          <t>2026-10-10T13:19:32.175536+00:00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-09-01T12:24:14.156516+00:00</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-09-04T04:05:26.409146+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-12T10:11:27.407818+00:00</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
-        <v>34.95</v>
-      </c>
-      <c r="H21" t="n">
-        <v>63.69</v>
-      </c>
-      <c r="I21" t="n">
-        <v>98.64</v>
-      </c>
+        <v>44.87</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21.75</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2540,27 +2534,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-14T11:50:45.888006+00:00</t>
+          <t>2026-09-12T14:34:16.760354+00:00</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-17T15:16:48.590090+00:00</t>
+          <t>2026-09-13T10:49:13.490162+00:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-23T22:52:35.147499+00:00</t>
+          <t>2026-09-16T00:14:29.599563+00:00</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>75.43000000000001</v>
+        <v>20.25</v>
       </c>
       <c r="H22" t="n">
-        <v>151.6</v>
+        <v>61.42</v>
       </c>
       <c r="I22" t="n">
-        <v>227.03</v>
+        <v>81.67</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
@@ -2568,12 +2562,12 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2579,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PO-10035</t>
+          <t>PO-10036</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2595,27 +2589,27 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-01T03:29:16.676846+00:00</t>
+          <t>2026-08-20T09:58:53.560171+00:00</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-09-01T18:31:38.140672+00:00</t>
+          <t>2026-08-22T09:56:32.685397+00:00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-02T13:19:26.714376+00:00</t>
+          <t>2026-08-28T16:24:13.140882+00:00</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>15.04</v>
+        <v>47.96</v>
       </c>
       <c r="H23" t="n">
-        <v>18.8</v>
+        <v>150.46</v>
       </c>
       <c r="I23" t="n">
-        <v>33.84</v>
+        <v>198.42</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
@@ -2623,12 +2617,12 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2634,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PO-10036</t>
+          <t>PO-10037</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2650,27 +2644,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-31T21:46:45.285264+00:00</t>
+          <t>2026-08-23T10:32:14.200075+00:00</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-09-02T03:36:05.383035+00:00</t>
+          <t>2026-08-24T00:09:28.628525+00:00</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-04T00:04:33.384699+00:00</t>
+          <t>2026-08-27T21:25:04.869937+00:00</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>29.82</v>
+        <v>13.62</v>
       </c>
       <c r="H24" t="n">
-        <v>44.47</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>74.3</v>
+        <v>106.88</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
@@ -2683,39 +2677,39 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PO-10037</t>
+          <t>PO-10040</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-10T10:00:14.933190+00:00</t>
+          <t>2026-09-30T17:16:41.320387+00:00</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-10-11T13:17:46.289092+00:00</t>
+          <t>2026-10-01T10:58:53.841207+00:00</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
-        <v>27.29</v>
+        <v>17.7</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2723,28 +2717,28 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1.07</v>
+        <v>257.8</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PO-10038</t>
+          <t>PO-10042</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2754,27 +2748,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-10-03T01:42:37.963001+00:00</t>
+          <t>2026-09-05T05:11:20.608807+00:00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-10-05T05:31:44.115275+00:00</t>
+          <t>2026-09-06T04:37:13.935541+00:00</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-08T00:09:35.263800+00:00</t>
+          <t>2026-09-06T09:46:15.590939+00:00</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>51.82</v>
+        <v>23.43</v>
       </c>
       <c r="H26" t="n">
-        <v>66.63</v>
+        <v>5.15</v>
       </c>
       <c r="I26" t="n">
-        <v>118.45</v>
+        <v>28.58</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
@@ -2782,79 +2776,73 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PO-10039</t>
+          <t>PO-10043</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-14T05:52:41.801526+00:00</t>
+          <t>2026-10-09T05:00:20.850698+00:00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-14T20:47:26.506443+00:00</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-16T13:32:18.995061+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-09T11:09:48.784993+00:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
-        <v>14.91</v>
-      </c>
-      <c r="H27" t="n">
-        <v>40.75</v>
-      </c>
-      <c r="I27" t="n">
-        <v>55.66</v>
-      </c>
+        <v>6.16</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>54.07</v>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PO-10040</t>
+          <t>PO-10046</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2864,27 +2852,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-26T05:48:26.615041+00:00</t>
+          <t>2026-08-27T04:51:43.057547+00:00</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-09-26T21:48:45.738402+00:00</t>
+          <t>2026-08-27T23:36:23.870291+00:00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-30T08:14:41.322960+00:00</t>
+          <t>2026-09-02T09:54:39.079213+00:00</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>16.01</v>
+        <v>18.74</v>
       </c>
       <c r="H28" t="n">
-        <v>82.43000000000001</v>
+        <v>130.3</v>
       </c>
       <c r="I28" t="n">
-        <v>98.44</v>
+        <v>149.05</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
@@ -2892,108 +2880,108 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PO-10041</t>
+          <t>PO-10047</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-07T05:37:49.432844+00:00</t>
+          <t>2026-09-25T09:47:33.007259+00:00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-10-09T01:07:41.097172+00:00</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>2026-09-26T05:33:30.301331+00:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-28T23:04:56.648847+00:00</t>
+        </is>
+      </c>
       <c r="G29" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+        <v>19.77</v>
+      </c>
+      <c r="H29" t="n">
+        <v>65.52</v>
+      </c>
+      <c r="I29" t="n">
+        <v>85.29000000000001</v>
+      </c>
       <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>77.44</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PO-10043</t>
+          <t>PO-10050</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-27T04:51:43.057547+00:00</t>
+          <t>2026-08-05T13:54:28.115263+00:00</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-27T23:36:23.870291+00:00</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-02T09:54:39.079213+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-07T13:00:18.666721+00:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="H30" t="n">
-        <v>130.3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>149.05</v>
-      </c>
+        <v>47.1</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-      <c r="K30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1605.17</v>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -3001,19 +2989,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PO-10044</t>
+          <t>PO-10052</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3023,27 +3011,27 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-25T09:47:33.007259+00:00</t>
+          <t>2026-08-27T19:57:13.568066+00:00</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-09-26T05:33:30.301331+00:00</t>
+          <t>2026-08-28T14:20:02.425767+00:00</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-28T23:04:56.648847+00:00</t>
+          <t>2026-08-30T07:13:30.492961+00:00</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>19.77</v>
+        <v>18.38</v>
       </c>
       <c r="H31" t="n">
-        <v>65.52</v>
+        <v>40.89</v>
       </c>
       <c r="I31" t="n">
-        <v>85.29000000000001</v>
+        <v>59.27</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
@@ -3051,12 +3039,12 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -3068,56 +3056,62 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PO-10047</t>
+          <t>PO-10054</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-05T13:54:28.115263+00:00</t>
+          <t>2026-09-28T17:21:23.206225+00:00</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-07T13:00:18.666721+00:00</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>2026-09-28T21:53:19.887110+00:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-29T05:53:44.645902+00:00</t>
+        </is>
+      </c>
       <c r="G32" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+        <v>4.53</v>
+      </c>
+      <c r="H32" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="I32" t="n">
+        <v>12.54</v>
+      </c>
       <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1581.17</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PO-10049</t>
+          <t>PO-10055</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3127,27 +3121,27 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-27T19:57:13.568066+00:00</t>
+          <t>2026-08-30T04:24:42.798805+00:00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-28T14:20:02.425767+00:00</t>
+          <t>2026-08-30T23:33:55.244451+00:00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-30T07:13:30.492961+00:00</t>
+          <t>2026-09-01T01:58:10.642788+00:00</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>18.38</v>
+        <v>19.15</v>
       </c>
       <c r="H33" t="n">
-        <v>40.89</v>
+        <v>26.4</v>
       </c>
       <c r="I33" t="n">
-        <v>59.27</v>
+        <v>45.56</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
@@ -3167,12 +3161,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PO-10051</t>
+          <t>PO-10056</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3182,27 +3176,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-28T17:21:23.206225+00:00</t>
+          <t>2026-09-19T06:56:52.382590+00:00</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-09-28T21:53:19.887110+00:00</t>
+          <t>2026-09-19T16:06:36.216907+00:00</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-29T05:53:44.645902+00:00</t>
+          <t>2026-09-21T16:46:01.897816+00:00</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4.53</v>
+        <v>9.16</v>
       </c>
       <c r="H34" t="n">
-        <v>8.01</v>
+        <v>48.66</v>
       </c>
       <c r="I34" t="n">
-        <v>12.54</v>
+        <v>57.82</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
@@ -3215,54 +3209,48 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PO-10052</t>
+          <t>PO-10057</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-30T04:24:42.798805+00:00</t>
+          <t>2026-08-23T10:41:52.646057+00:00</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-30T23:33:55.244451+00:00</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-09-01T01:58:10.642788+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-24T20:33:23.949441+00:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
-        <v>19.15</v>
-      </c>
-      <c r="H35" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="I35" t="n">
-        <v>45.56</v>
-      </c>
+        <v>33.86</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="b">
-        <v>1</v>
-      </c>
-      <c r="K35" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>1176.38</v>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -3270,19 +3258,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PO-10053</t>
+          <t>PO-10060</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3292,27 +3280,27 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-19T06:56:52.382590+00:00</t>
+          <t>2026-08-09T19:37:45.249180+00:00</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-09-19T16:06:36.216907+00:00</t>
+          <t>2026-08-11T23:53:30.448716+00:00</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-21T16:46:01.897816+00:00</t>
+          <t>2026-08-13T20:41:00.154093+00:00</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9.16</v>
+        <v>52.26</v>
       </c>
       <c r="H36" t="n">
-        <v>48.66</v>
+        <v>44.79</v>
       </c>
       <c r="I36" t="n">
-        <v>57.82</v>
+        <v>97.05</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
@@ -3320,53 +3308,59 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PO-10054</t>
+          <t>PO-10061</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-08-23T10:41:52.646057+00:00</t>
+          <t>2026-08-28T06:37:41.341446+00:00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-24T20:33:23.949441+00:00</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>2026-08-28T12:37:01.573460+00:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-01T07:43:45.051426+00:00</t>
+        </is>
+      </c>
       <c r="G37" t="n">
-        <v>33.86</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>5.99</v>
+      </c>
+      <c r="H37" t="n">
+        <v>91.11</v>
+      </c>
+      <c r="I37" t="n">
+        <v>97.09999999999999</v>
+      </c>
       <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1152.38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -3374,19 +3368,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PO-10057</t>
+          <t>PO-10062</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3396,27 +3390,27 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-09T19:37:45.249180+00:00</t>
+          <t>2026-08-30T11:38:25.267645+00:00</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-11T23:53:30.448716+00:00</t>
+          <t>2026-09-01T05:45:46.114066+00:00</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13T20:41:00.154093+00:00</t>
+          <t>2026-09-03T05:32:55.278197+00:00</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>52.26</v>
+        <v>42.12</v>
       </c>
       <c r="H38" t="n">
-        <v>44.79</v>
+        <v>47.79</v>
       </c>
       <c r="I38" t="n">
-        <v>97.05</v>
+        <v>89.91</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
@@ -3429,19 +3423,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PO-10058</t>
+          <t>PO-10064</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3451,27 +3445,27 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-08-28T06:37:41.341446+00:00</t>
+          <t>2026-09-08T04:23:12.341350+00:00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-28T12:37:01.573460+00:00</t>
+          <t>2026-09-09T20:26:47.396657+00:00</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01T07:43:45.051426+00:00</t>
+          <t>2026-09-13T03:18:51.723206+00:00</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>5.99</v>
+        <v>40.06</v>
       </c>
       <c r="H39" t="n">
-        <v>91.11</v>
+        <v>78.87</v>
       </c>
       <c r="I39" t="n">
-        <v>97.09999999999999</v>
+        <v>118.93</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
@@ -3479,24 +3473,24 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PO-10059</t>
+          <t>PO-10065</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3506,27 +3500,27 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-30T11:38:25.267645+00:00</t>
+          <t>2026-09-12T05:47:41.425507+00:00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-09-01T05:45:46.114066+00:00</t>
+          <t>2026-09-13T22:56:35.400229+00:00</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-03T05:32:55.278197+00:00</t>
+          <t>2026-09-15T04:01:41.415203+00:00</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>42.12</v>
+        <v>41.15</v>
       </c>
       <c r="H40" t="n">
-        <v>47.79</v>
+        <v>29.09</v>
       </c>
       <c r="I40" t="n">
-        <v>89.91</v>
+        <v>70.23</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
@@ -3534,24 +3528,24 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PO-10061</t>
+          <t>PO-10068</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3561,27 +3555,27 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-08T04:23:12.341350+00:00</t>
+          <t>2026-08-12T02:44:57.118522+00:00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-09-09T20:26:47.396657+00:00</t>
+          <t>2026-08-12T17:21:58.407100+00:00</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-13T03:18:51.723206+00:00</t>
+          <t>2026-08-15T15:31:27.911980+00:00</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>40.06</v>
+        <v>14.62</v>
       </c>
       <c r="H41" t="n">
-        <v>78.87</v>
+        <v>70.16</v>
       </c>
       <c r="I41" t="n">
-        <v>118.93</v>
+        <v>84.78</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
@@ -3589,79 +3583,73 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PO-10062</t>
+          <t>PO-10069</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-12T05:47:41.425507+00:00</t>
+          <t>2026-10-12T22:14:55.467509+00:00</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-09-13T22:56:35.400229+00:00</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-15T04:01:41.415203+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-14T15:56:33.906417+00:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>41.15</v>
-      </c>
-      <c r="H42" t="n">
-        <v>29.09</v>
-      </c>
-      <c r="I42" t="n">
-        <v>70.23</v>
-      </c>
+        <v>41.69</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-35.17</v>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PO-10065</t>
+          <t>PO-10071</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3671,27 +3659,27 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-12T02:44:57.118522+00:00</t>
+          <t>2026-09-15T15:48:43.385650+00:00</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-12T17:21:58.407100+00:00</t>
+          <t>2026-09-17T22:12:52.293642+00:00</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-15T15:31:27.911980+00:00</t>
+          <t>2026-09-18T05:25:51.427391+00:00</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>14.62</v>
+        <v>54.4</v>
       </c>
       <c r="H43" t="n">
-        <v>70.16</v>
+        <v>7.22</v>
       </c>
       <c r="I43" t="n">
-        <v>84.78</v>
+        <v>61.62</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
@@ -3699,61 +3687,67 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PO-10066</t>
+          <t>PO-10072</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-10-12T22:14:55.467509+00:00</t>
+          <t>2026-08-24T09:19:15.526604+00:00</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-10-14T15:56:33.906417+00:00</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>2026-08-24T23:15:31.056086+00:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-25T23:53:07.145997+00:00</t>
+        </is>
+      </c>
       <c r="G44" t="n">
-        <v>41.69</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+        <v>13.94</v>
+      </c>
+      <c r="H44" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="I44" t="n">
+        <v>38.56</v>
+      </c>
       <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-59.17</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3759,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PO-10068</t>
+          <t>PO-10073</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3775,27 +3769,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-15T15:48:43.385650+00:00</t>
+          <t>2026-08-14T17:35:03.513068+00:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-17T22:12:52.293642+00:00</t>
+          <t>2026-08-16T15:59:37.005047+00:00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-18T05:25:51.427391+00:00</t>
+          <t>2026-08-18T21:15:58.622794+00:00</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>54.4</v>
+        <v>46.41</v>
       </c>
       <c r="H45" t="n">
-        <v>7.22</v>
+        <v>53.27</v>
       </c>
       <c r="I45" t="n">
-        <v>61.62</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
@@ -3803,12 +3797,12 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3814,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PO-10069</t>
+          <t>PO-10074</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3830,27 +3824,27 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-24T09:19:15.526604+00:00</t>
+          <t>2026-08-07T16:12:10.116200+00:00</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-24T23:15:31.056086+00:00</t>
+          <t>2026-08-11T09:10:38.112075+00:00</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-25T23:53:07.145997+00:00</t>
+          <t>2026-08-17T23:42:35.113759+00:00</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13.94</v>
+        <v>88.97</v>
       </c>
       <c r="H46" t="n">
-        <v>24.63</v>
+        <v>158.53</v>
       </c>
       <c r="I46" t="n">
-        <v>38.56</v>
+        <v>247.51</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
@@ -3863,19 +3857,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PO-10070</t>
+          <t>PO-10075</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3885,27 +3879,27 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-14T17:35:03.513068+00:00</t>
+          <t>2026-08-25T06:29:09.674689+00:00</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-16T15:59:37.005047+00:00</t>
+          <t>2026-08-27T10:05:16.260389+00:00</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-18T21:15:58.622794+00:00</t>
+          <t>2026-08-30T19:02:33.619103+00:00</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>46.41</v>
+        <v>51.6</v>
       </c>
       <c r="H47" t="n">
-        <v>53.27</v>
+        <v>80.95</v>
       </c>
       <c r="I47" t="n">
-        <v>99.68000000000001</v>
+        <v>132.56</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
@@ -3918,74 +3912,68 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PO-10071</t>
+          <t>PO-10077</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-08-07T16:12:10.116200+00:00</t>
+          <t>2026-10-11T22:46:48.802792+00:00</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-11T09:10:38.112075+00:00</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-17T23:42:35.113759+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-12T13:23:58.131636+00:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>88.97</v>
-      </c>
-      <c r="H48" t="n">
-        <v>158.53</v>
-      </c>
-      <c r="I48" t="n">
-        <v>247.51</v>
-      </c>
+        <v>14.62</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="b">
-        <v>1</v>
-      </c>
-      <c r="K48" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-11.7</v>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PO-10072</t>
+          <t>PO-10079</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3995,27 +3983,27 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-25T06:29:09.674689+00:00</t>
+          <t>2026-08-30T20:07:26.828948+00:00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-27T10:05:16.260389+00:00</t>
+          <t>2026-08-30T23:13:12.783104+00:00</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-30T19:02:33.619103+00:00</t>
+          <t>2026-09-02T10:00:47.797213+00:00</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>51.6</v>
+        <v>3.1</v>
       </c>
       <c r="H49" t="n">
-        <v>80.95</v>
+        <v>58.79</v>
       </c>
       <c r="I49" t="n">
-        <v>132.56</v>
+        <v>61.89</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -4035,61 +4023,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PO-10074</t>
+          <t>PO-10080</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-10-11T22:46:48.802792+00:00</t>
+          <t>2026-09-06T14:44:41.224872+00:00</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-10-12T13:23:58.131636+00:00</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>2026-09-07T07:24:15.872071+00:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:55:54.397957+00:00</t>
+        </is>
+      </c>
       <c r="G50" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+        <v>16.66</v>
+      </c>
+      <c r="H50" t="n">
+        <v>77.53</v>
+      </c>
+      <c r="I50" t="n">
+        <v>94.19</v>
+      </c>
       <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-35.71</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PO-10076</t>
+          <t>PO-10082</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4099,27 +4093,27 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-30T20:07:26.828948+00:00</t>
+          <t>2026-08-05T12:58:14.092749+00:00</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-30T23:13:12.783104+00:00</t>
+          <t>2026-08-08T08:25:18.478307+00:00</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-02T10:00:47.797213+00:00</t>
+          <t>2026-08-11T01:51:59.456435+00:00</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3.1</v>
+        <v>67.45</v>
       </c>
       <c r="H51" t="n">
-        <v>58.79</v>
+        <v>65.44</v>
       </c>
       <c r="I51" t="n">
-        <v>61.89</v>
+        <v>132.9</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
@@ -4132,7 +4126,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4138,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PO-10077</t>
+          <t>PO-10083</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4154,27 +4148,27 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-06T14:44:41.224872+00:00</t>
+          <t>2026-09-19T13:42:56.866609+00:00</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-09-07T07:24:15.872071+00:00</t>
+          <t>2026-09-21T22:56:42.574822+00:00</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-10T12:55:54.397957+00:00</t>
+          <t>2026-09-22T20:16:24.319062+00:00</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>16.66</v>
+        <v>57.23</v>
       </c>
       <c r="H52" t="n">
-        <v>77.53</v>
+        <v>21.33</v>
       </c>
       <c r="I52" t="n">
-        <v>94.19</v>
+        <v>78.56</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
@@ -4187,54 +4181,48 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PO-10079</t>
+          <t>PO-10084</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-05T12:58:14.092749+00:00</t>
+          <t>2026-08-31T16:42:22.522388+00:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-08T08:25:18.478307+00:00</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-11T01:51:59.456435+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-02T10:29:50.162793+00:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>67.45</v>
-      </c>
-      <c r="H53" t="n">
-        <v>65.44</v>
-      </c>
-      <c r="I53" t="n">
-        <v>132.9</v>
-      </c>
+        <v>41.79</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="b">
-        <v>1</v>
-      </c>
-      <c r="K53" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>978.37</v>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -4242,19 +4230,19 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PO-10080</t>
+          <t>PO-10085</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4264,27 +4252,27 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-19T13:42:56.866609+00:00</t>
+          <t>2026-10-05T10:30:09.399534+00:00</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-09-21T22:56:42.574822+00:00</t>
+          <t>2026-10-06T15:50:54.830850+00:00</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-22T20:16:24.319062+00:00</t>
+          <t>2026-10-09T01:01:52.876514+00:00</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>57.23</v>
+        <v>29.35</v>
       </c>
       <c r="H54" t="n">
-        <v>21.33</v>
+        <v>57.18</v>
       </c>
       <c r="I54" t="n">
-        <v>78.56</v>
+        <v>86.53</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
@@ -4292,24 +4280,24 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PO-10081</t>
+          <t>PO-10086</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4319,17 +4307,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-31T16:42:22.522388+00:00</t>
+          <t>2026-08-30T06:23:05.817553+00:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-09-02T10:29:50.162793+00:00</t>
+          <t>2026-08-30T12:18:34.407863+00:00</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>41.79</v>
+        <v>5.92</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
@@ -4337,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>954.37</v>
+        <v>1012.69</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4346,19 +4334,19 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PO-10082</t>
+          <t>PO-10087</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4368,27 +4356,27 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-10-05T10:30:09.399534+00:00</t>
+          <t>2026-09-12T11:41:21.630539+00:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-10-06T15:50:54.830850+00:00</t>
+          <t>2026-09-14T15:23:10.750146+00:00</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-09T01:01:52.876514+00:00</t>
+          <t>2026-09-18T10:03:05.672248+00:00</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>29.35</v>
+        <v>51.7</v>
       </c>
       <c r="H56" t="n">
-        <v>57.18</v>
+        <v>90.67</v>
       </c>
       <c r="I56" t="n">
-        <v>86.53</v>
+        <v>142.36</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
@@ -4396,73 +4384,79 @@
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PO-10083</t>
+          <t>PO-10088</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-30T06:23:05.817553+00:00</t>
+          <t>2026-10-07T12:46:59.687237+00:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-30T12:18:34.407863+00:00</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
+          <t>2026-10-07T17:40:09.631932+00:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-10-10T14:14:22.494602+00:00</t>
+        </is>
+      </c>
       <c r="G57" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+        <v>4.89</v>
+      </c>
+      <c r="H57" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="I57" t="n">
+        <v>73.45999999999999</v>
+      </c>
       <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>988.6900000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PO-10084</t>
+          <t>PO-10089</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4472,27 +4466,27 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-12T11:41:21.630539+00:00</t>
+          <t>2026-09-21T12:41:06.804743+00:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-09-14T15:23:10.750146+00:00</t>
+          <t>2026-09-22T23:40:04.222486+00:00</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-18T10:03:05.672248+00:00</t>
+          <t>2026-09-24T02:47:11.324482+00:00</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>51.7</v>
+        <v>34.98</v>
       </c>
       <c r="H58" t="n">
-        <v>90.67</v>
+        <v>27.12</v>
       </c>
       <c r="I58" t="n">
-        <v>142.36</v>
+        <v>62.1</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
@@ -4505,123 +4499,123 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PO-10085</t>
+          <t>PO-10091</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-10-07T12:46:59.687237+00:00</t>
+          <t>2026-08-13T16:50:05.428262+00:00</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-10-07T17:40:09.631932+00:00</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>2026-08-14T06:16:13.586391+00:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-08-14T19:00:59.713217+00:00</t>
+        </is>
+      </c>
       <c r="G59" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+        <v>13.44</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="I59" t="n">
+        <v>26.18</v>
+      </c>
       <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>70.29000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PO-10086</t>
+          <t>PO-10092</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-21T12:41:06.804743+00:00</t>
+          <t>2026-08-06T11:45:05.928880+00:00</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-09-22T23:40:04.222486+00:00</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-09-24T02:47:11.324482+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-07T23:12:39.210253+00:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>34.98</v>
-      </c>
-      <c r="H60" t="n">
-        <v>27.12</v>
-      </c>
-      <c r="I60" t="n">
-        <v>62.1</v>
-      </c>
+        <v>35.46</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="b">
-        <v>1</v>
-      </c>
-      <c r="K60" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1583.33</v>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PO-10088</t>
+          <t>PO-10094</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4631,27 +4625,27 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-13T16:50:05.428262+00:00</t>
+          <t>2026-08-22T07:57:58.724495+00:00</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-14T06:16:13.586391+00:00</t>
+          <t>2026-08-24T15:02:49.781108+00:00</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14T19:00:59.713217+00:00</t>
+          <t>2026-08-28T00:07:22.273345+00:00</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>13.44</v>
+        <v>55.08</v>
       </c>
       <c r="H61" t="n">
-        <v>12.75</v>
+        <v>81.08</v>
       </c>
       <c r="I61" t="n">
-        <v>26.18</v>
+        <v>136.16</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
@@ -4664,48 +4658,54 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PO-10089</t>
+          <t>PO-10095</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-06T11:45:05.928880+00:00</t>
+          <t>2026-08-14T21:21:05.853422+00:00</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-07T23:12:39.210253+00:00</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>2026-08-16T06:38:13.300291+00:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-20T01:17:02.194752+00:00</t>
+        </is>
+      </c>
       <c r="G62" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+        <v>33.29</v>
+      </c>
+      <c r="H62" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="I62" t="n">
+        <v>123.93</v>
+      </c>
       <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1559.32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -4713,19 +4713,19 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PO-10091</t>
+          <t>PO-10096</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4735,27 +4735,27 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-22T07:57:58.724495+00:00</t>
+          <t>2026-10-05T19:24:29.949258+00:00</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-24T15:02:49.781108+00:00</t>
+          <t>2026-10-08T17:46:30.320625+00:00</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-28T00:07:22.273345+00:00</t>
+          <t>2026-10-09T01:56:48.212269+00:00</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>55.08</v>
+        <v>70.37</v>
       </c>
       <c r="H63" t="n">
-        <v>81.08</v>
+        <v>8.17</v>
       </c>
       <c r="I63" t="n">
-        <v>136.16</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
@@ -4763,79 +4763,73 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PO-10092</t>
+          <t>PO-10097</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-14T21:21:05.853422+00:00</t>
+          <t>2026-09-12T16:16:25.964847+00:00</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-16T06:38:13.300291+00:00</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-20T01:17:02.194752+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-13T20:45:31.064297+00:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>33.29</v>
-      </c>
-      <c r="H64" t="n">
-        <v>90.65000000000001</v>
-      </c>
-      <c r="I64" t="n">
-        <v>123.93</v>
-      </c>
+        <v>28.48</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="b">
-        <v>1</v>
-      </c>
-      <c r="K64" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>690.8099999999999</v>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PO-10093</t>
+          <t>PO-10099</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4845,27 +4839,27 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-05T19:24:29.949258+00:00</t>
+          <t>2026-09-12T03:09:06.695033+00:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-08T17:46:30.320625+00:00</t>
+          <t>2026-09-13T08:03:20.180702+00:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-10-09T01:56:48.212269+00:00</t>
+          <t>2026-09-15T17:51:58.724535+00:00</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>70.37</v>
+        <v>28.9</v>
       </c>
       <c r="H65" t="n">
-        <v>8.17</v>
+        <v>57.81</v>
       </c>
       <c r="I65" t="n">
-        <v>78.54000000000001</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
@@ -4873,73 +4867,79 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PO-10094</t>
+          <t>PO-10100</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-12T16:16:25.964847+00:00</t>
+          <t>2026-08-27T20:57:24.371230+00:00</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-09-13T20:45:31.064297+00:00</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>2026-08-29T06:09:03.703133+00:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-30T04:49:06.476414+00:00</t>
+        </is>
+      </c>
       <c r="G66" t="n">
-        <v>28.48</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+        <v>33.19</v>
+      </c>
+      <c r="H66" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="I66" t="n">
+        <v>55.86</v>
+      </c>
       <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>666.8</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PO-10096</t>
+          <t>PO-10101</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4949,27 +4949,27 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-12T03:09:06.695033+00:00</t>
+          <t>2026-08-31T04:41:22.502957+00:00</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-09-13T08:03:20.180702+00:00</t>
+          <t>2026-09-03T02:33:13.194543+00:00</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-15T17:51:58.724535+00:00</t>
+          <t>2026-09-08T16:20:38.553173+00:00</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>28.9</v>
+        <v>69.86</v>
       </c>
       <c r="H67" t="n">
-        <v>57.81</v>
+        <v>133.79</v>
       </c>
       <c r="I67" t="n">
-        <v>86.70999999999999</v>
+        <v>203.65</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
@@ -4977,203 +4977,197 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PO-10097</t>
+          <t>PO-10102</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-27T20:57:24.371230+00:00</t>
+          <t>2026-09-07T16:17:42.089303+00:00</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-29T06:09:03.703133+00:00</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-08-30T04:49:06.476414+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-09T07:56:32.669779+00:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
-        <v>33.19</v>
-      </c>
-      <c r="H68" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="I68" t="n">
-        <v>55.86</v>
-      </c>
+        <v>39.65</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="b">
-        <v>1</v>
-      </c>
-      <c r="K68" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>810.78</v>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PO-10098</t>
+          <t>PO-10103</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-31T04:41:22.502957+00:00</t>
+          <t>2026-10-07T20:30:55.820208+00:00</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-09-03T02:33:13.194543+00:00</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-09-08T16:20:38.553173+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-10T11:03:09.626743+00:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
-        <v>69.86</v>
-      </c>
-      <c r="H69" t="n">
-        <v>133.79</v>
-      </c>
-      <c r="I69" t="n">
-        <v>203.65</v>
-      </c>
+        <v>62.54</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="b">
-        <v>1</v>
-      </c>
-      <c r="K69" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>86.56</v>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PO-10099</t>
+          <t>PO-10104</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-07T16:17:42.089303+00:00</t>
+          <t>2026-08-29T16:16:03.454472+00:00</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-09-09T07:56:32.669779+00:00</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
+          <t>2026-08-30T03:18:05.195687+00:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-30T13:34:32.979649+00:00</t>
+        </is>
+      </c>
       <c r="G70" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+        <v>11.03</v>
+      </c>
+      <c r="H70" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="I70" t="n">
+        <v>21.31</v>
+      </c>
       <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>786.78</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PO-10100</t>
+          <t>PO-10105</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-10-07T20:30:55.820208+00:00</t>
+          <t>2026-10-13T03:31:52.231355+00:00</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-10-10T11:03:09.626743+00:00</t>
+          <t>2026-10-15T02:16:22.896982+00:00</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
-        <v>62.54</v>
+        <v>46.74</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -5181,7 +5175,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>62.56</v>
+        <v>-40.45</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -5190,19 +5184,19 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PO-10101</t>
+          <t>PO-10107</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5212,27 +5206,27 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-29T16:16:03.454472+00:00</t>
+          <t>2026-08-19T10:44:15.122633+00:00</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-30T03:18:05.195687+00:00</t>
+          <t>2026-08-20T03:18:51.382023+00:00</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-30T13:34:32.979649+00:00</t>
+          <t>2026-08-23T12:19:59.932181+00:00</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>11.03</v>
+        <v>16.58</v>
       </c>
       <c r="H72" t="n">
-        <v>10.27</v>
+        <v>81.02</v>
       </c>
       <c r="I72" t="n">
-        <v>21.31</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
@@ -5245,39 +5239,39 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PO-10102</t>
+          <t>PO-10109</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-22T09:10:19.661040+00:00</t>
+          <t>2026-10-07T20:00:09.564377+00:00</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-22T17:31:34.441585+00:00</t>
+          <t>2026-10-08T04:04:31.478309+00:00</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
-        <v>8.35</v>
+        <v>8.07</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
@@ -5285,28 +5279,28 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>1177.9</v>
+        <v>87.08</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PO-10105</t>
+          <t>PO-10110</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5316,27 +5310,27 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-08-07T04:43:04.594304+00:00</t>
+          <t>2026-09-10T09:14:24.124746+00:00</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-07T11:21:14.434617+00:00</t>
+          <t>2026-09-11T04:40:29.313776+00:00</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-09T22:55:16.429748+00:00</t>
+          <t>2026-09-14T12:04:46.617295+00:00</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>6.64</v>
+        <v>19.43</v>
       </c>
       <c r="H74" t="n">
-        <v>59.57</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>66.2</v>
+        <v>98.84</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
@@ -5344,12 +5338,12 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5355,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PO-10107</t>
+          <t>PO-10111</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5371,27 +5365,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-18T02:55:33.410438+00:00</t>
+          <t>2026-08-10T05:55:39.902442+00:00</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-09-18T18:03:18.211830+00:00</t>
+          <t>2026-08-12T23:49:26.945438+00:00</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-24T10:18:06.777567+00:00</t>
+          <t>2026-08-19T00:27:57.450694+00:00</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>15.13</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="H75" t="n">
-        <v>136.25</v>
+        <v>144.64</v>
       </c>
       <c r="I75" t="n">
-        <v>151.38</v>
+        <v>210.54</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
@@ -5399,116 +5393,116 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PO-10108</t>
+          <t>PO-10112</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-20T17:09:12.761730+00:00</t>
+          <t>2026-08-10T07:20:08.989579+00:00</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-09-20T21:13:26.087800+00:00</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
+          <t>2026-08-10T10:54:54.163815+00:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-13T06:16:34.188428+00:00</t>
+        </is>
+      </c>
       <c r="G76" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+        <v>3.58</v>
+      </c>
+      <c r="H76" t="n">
+        <v>67.36</v>
+      </c>
+      <c r="I76" t="n">
+        <v>70.94</v>
+      </c>
       <c r="J76" t="b">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>473.92</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PO-10109</t>
+          <t>PO-10113</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-07T05:32:27.546435+00:00</t>
+          <t>2026-10-12T11:41:38.102314+00:00</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-09-07T15:35:45.400767+00:00</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-09-10T15:46:20.540589+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-15T02:08:30.014001+00:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="H77" t="n">
-        <v>72.18000000000001</v>
-      </c>
-      <c r="I77" t="n">
-        <v>82.23</v>
-      </c>
+        <v>62.45</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="b">
-        <v>1</v>
-      </c>
-      <c r="K77" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>-24.61</v>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5514,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PO-10110</t>
+          <t>PO-10114</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5530,27 +5524,27 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-22T17:37:30.851805+00:00</t>
+          <t>2026-09-15T16:14:04.125435+00:00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-09-23T01:52:43.027159+00:00</t>
+          <t>2026-09-16T20:08:49.115934+00:00</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-09-24T07:43:45.569952+00:00</t>
+          <t>2026-09-18T14:32:56.816608+00:00</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>8.25</v>
+        <v>27.91</v>
       </c>
       <c r="H78" t="n">
-        <v>29.85</v>
+        <v>42.4</v>
       </c>
       <c r="I78" t="n">
-        <v>38.1</v>
+        <v>70.31</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
@@ -5563,19 +5557,19 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PO-10111</t>
+          <t>PO-10116</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5585,27 +5579,27 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-06T19:27:22.144938+00:00</t>
+          <t>2026-10-03T21:16:42.665361+00:00</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-08T09:38:03.463682+00:00</t>
+          <t>2026-10-04T18:32:53.915424+00:00</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-12T00:46:06.663312+00:00</t>
+          <t>2026-10-06T19:54:25.107013+00:00</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>38.18</v>
+        <v>21.27</v>
       </c>
       <c r="H79" t="n">
-        <v>87.13</v>
+        <v>49.36</v>
       </c>
       <c r="I79" t="n">
-        <v>125.31</v>
+        <v>70.63</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
@@ -5613,24 +5607,24 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PO-10113</t>
+          <t>PO-10118</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5640,27 +5634,27 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-03T21:16:42.665361+00:00</t>
+          <t>2026-09-03T10:44:22.044790+00:00</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-10-04T18:32:53.915424+00:00</t>
+          <t>2026-09-05T02:32:59.171526+00:00</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-06T19:54:25.107013+00:00</t>
+          <t>2026-09-06T13:18:36.658950+00:00</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>21.27</v>
+        <v>39.81</v>
       </c>
       <c r="H80" t="n">
-        <v>49.36</v>
+        <v>34.76</v>
       </c>
       <c r="I80" t="n">
-        <v>70.63</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
@@ -5668,24 +5662,24 @@
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PO-10115</t>
+          <t>PO-10120</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5695,27 +5689,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-03T10:44:22.044790+00:00</t>
+          <t>2026-09-08T08:19:32.513818+00:00</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-09-05T02:32:59.171526+00:00</t>
+          <t>2026-09-09T10:41:33.281194+00:00</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-06T13:18:36.658950+00:00</t>
+          <t>2026-09-12T21:39:41.979025+00:00</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>39.81</v>
+        <v>26.37</v>
       </c>
       <c r="H81" t="n">
-        <v>34.76</v>
+        <v>82.97</v>
       </c>
       <c r="I81" t="n">
-        <v>74.56999999999999</v>
+        <v>109.34</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
@@ -5728,19 +5722,19 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PO-10117</t>
+          <t>PO-10121</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5750,27 +5744,27 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-08T08:19:32.513818+00:00</t>
+          <t>2026-09-15T06:11:01.963544+00:00</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-09-09T10:41:33.281194+00:00</t>
+          <t>2026-09-15T10:36:00.218732+00:00</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-12T21:39:41.979025+00:00</t>
+          <t>2026-09-19T10:55:02.737898+00:00</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>26.37</v>
+        <v>4.42</v>
       </c>
       <c r="H82" t="n">
-        <v>82.97</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>109.34</v>
+        <v>100.73</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
@@ -5783,7 +5777,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -5795,91 +5789,91 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PO-10118</t>
+          <t>PO-10123</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-15T06:11:01.963544+00:00</t>
+          <t>2026-08-12T20:23:43.074041+00:00</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-09-15T10:36:00.218732+00:00</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-09-19T10:55:02.737898+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-13T17:19:42.646492+00:00</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="H83" t="n">
-        <v>96.31999999999999</v>
-      </c>
-      <c r="I83" t="n">
-        <v>100.73</v>
-      </c>
+        <v>20.93</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="b">
-        <v>1</v>
-      </c>
-      <c r="K83" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1430.68</v>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PO-10120</t>
+          <t>PO-10124</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-12T20:23:43.074041+00:00</t>
+          <t>2026-08-27T07:53:51.919786+00:00</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-13T17:19:42.646492+00:00</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>2026-08-30T00:50:33.407051+00:00</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-30T08:10:15.157887+00:00</t>
+        </is>
+      </c>
       <c r="G84" t="n">
-        <v>20.93</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+        <v>64.94</v>
+      </c>
+      <c r="H84" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="I84" t="n">
+        <v>72.27</v>
+      </c>
       <c r="J84" t="b">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>1406.68</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -5887,7 +5881,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5893,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PO-10121</t>
+          <t>PO-10126</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5909,27 +5903,27 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-27T07:53:51.919786+00:00</t>
+          <t>2026-08-22T00:03:44.994983+00:00</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-30T00:50:33.407051+00:00</t>
+          <t>2026-08-24T19:04:36.314896+00:00</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-30T08:10:15.157887+00:00</t>
+          <t>2026-08-26T04:48:14.747975+00:00</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>64.94</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="H85" t="n">
-        <v>7.33</v>
+        <v>33.73</v>
       </c>
       <c r="I85" t="n">
-        <v>72.27</v>
+        <v>100.74</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
@@ -5942,7 +5936,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5948,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PO-10122</t>
+          <t>PO-10127</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5964,27 +5958,27 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-05T17:28:53.552886+00:00</t>
+          <t>2026-08-17T17:57:13.666676+00:00</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-06T06:05:00.086351+00:00</t>
+          <t>2026-08-18T14:04:25.693151+00:00</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-09T22:56:28.606271+00:00</t>
+          <t>2026-08-22T20:58:02.698105+00:00</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>12.6</v>
+        <v>20.12</v>
       </c>
       <c r="H86" t="n">
-        <v>88.86</v>
+        <v>102.89</v>
       </c>
       <c r="I86" t="n">
-        <v>101.46</v>
+        <v>123.01</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
@@ -5997,19 +5991,19 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PO-10123</t>
+          <t>PO-10128</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6019,27 +6013,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-13T08:03:06.026907+00:00</t>
+          <t>2026-09-05T19:56:42.427816+00:00</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-14T21:36:50.569924+00:00</t>
+          <t>2026-09-06T12:02:14.217395+00:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-16T14:10:59.300439+00:00</t>
+          <t>2026-09-09T15:36:04.628908+00:00</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>37.56</v>
+        <v>16.09</v>
       </c>
       <c r="H87" t="n">
-        <v>40.57</v>
+        <v>75.56</v>
       </c>
       <c r="I87" t="n">
-        <v>78.13</v>
+        <v>91.66</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -6047,79 +6041,73 @@
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PO-10125</t>
+          <t>PO-10129</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-05T19:56:42.427816+00:00</t>
+          <t>2026-10-13T21:04:45.756055+00:00</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-09-06T12:02:14.217395+00:00</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-09-09T15:36:04.628908+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-14T10:46:52.388000+00:00</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="H88" t="n">
-        <v>75.56</v>
-      </c>
-      <c r="I88" t="n">
-        <v>91.66</v>
-      </c>
+        <v>13.7</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="b">
-        <v>1</v>
-      </c>
-      <c r="K88" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>-58</v>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PO-10126</t>
+          <t>PO-10131</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6129,27 +6117,27 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-04T13:54:26.967607+00:00</t>
+          <t>2026-09-30T03:33:13.216058+00:00</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-09-05T16:08:12.692328+00:00</t>
+          <t>2026-10-01T12:09:19.876475+00:00</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-07T17:30:16.165436+00:00</t>
+          <t>2026-10-02T12:18:20.190696+00:00</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>26.23</v>
+        <v>32.6</v>
       </c>
       <c r="H89" t="n">
-        <v>49.37</v>
+        <v>24.15</v>
       </c>
       <c r="I89" t="n">
-        <v>75.59999999999999</v>
+        <v>56.75</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
@@ -6162,74 +6150,68 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PO-10127</t>
+          <t>PO-10132</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-12T19:17:56.050115+00:00</t>
+          <t>2026-10-08T06:58:28.530358+00:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-12T23:23:30.130182+00:00</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-13T16:37:00.123884+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-08T21:47:13.248758+00:00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="H90" t="n">
-        <v>17.22</v>
-      </c>
-      <c r="I90" t="n">
-        <v>21.32</v>
-      </c>
+        <v>14.81</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="b">
-        <v>1</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>76.11</v>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PO-10131</t>
+          <t>PO-10133</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6239,27 +6221,27 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-27T14:35:11.001621+00:00</t>
+          <t>2026-09-27T01:20:42.418399+00:00</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-28T16:09:00.159554+00:00</t>
+          <t>2026-09-28T05:22:26.348139+00:00</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-30T08:51:59.344756+00:00</t>
+          <t>2026-09-29T22:59:36.421338+00:00</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>25.56</v>
+        <v>28.03</v>
       </c>
       <c r="H91" t="n">
-        <v>40.72</v>
+        <v>41.62</v>
       </c>
       <c r="I91" t="n">
-        <v>66.28</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
@@ -6267,12 +6249,12 @@
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6266,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PO-10133</t>
+          <t>PO-10135</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6339,7 +6321,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PO-10134</t>
+          <t>PO-10136</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6394,7 +6376,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PO-10135</t>
+          <t>PO-10137</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6449,7 +6431,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PO-10136</t>
+          <t>PO-10138</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6504,7 +6486,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PO-10137</t>
+          <t>PO-10139</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6559,7 +6541,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PO-10138</t>
+          <t>PO-10140</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6614,7 +6596,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PO-10140</t>
+          <t>PO-10142</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6669,7 +6651,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PO-10141</t>
+          <t>PO-10143</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6724,7 +6706,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PO-10142</t>
+          <t>PO-10144</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6779,7 +6761,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PO-10143</t>
+          <t>PO-10145</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6834,7 +6816,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PO-10144</t>
+          <t>PO-10146</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6862,7 +6844,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>142.2</v>
+        <v>166.21</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -6883,7 +6865,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>PO-10145</t>
+          <t>PO-10147</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6938,7 +6920,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>PO-10146</t>
+          <t>PO-10148</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6993,7 +6975,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>PO-10147</t>
+          <t>PO-10149</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7048,7 +7030,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PO-10148</t>
+          <t>PO-10150</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7103,7 +7085,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>PO-10150</t>
+          <t>PO-10152</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7158,7 +7140,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>PO-10151</t>
+          <t>PO-10153</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7213,7 +7195,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>PO-10152</t>
+          <t>PO-10154</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7268,7 +7250,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>PO-10153</t>
+          <t>PO-10155</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7296,7 +7278,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>666.86</v>
+        <v>690.86</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7317,7 +7299,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PO-10154</t>
+          <t>PO-10156</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7372,7 +7354,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PO-10155</t>
+          <t>PO-10157</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7427,7 +7409,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>PO-10158</t>
+          <t>PO-10160</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7482,7 +7464,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PO-10160</t>
+          <t>PO-10162</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7510,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>151.93</v>
+        <v>175.93</v>
       </c>
       <c r="L114" t="inlineStr">
         <is>
@@ -7531,7 +7513,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>PO-10161</t>
+          <t>PO-10163</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7586,7 +7568,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>PO-10162</t>
+          <t>PO-10164</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7641,7 +7623,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PO-10163</t>
+          <t>PO-10165</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7696,7 +7678,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>PO-10166</t>
+          <t>PO-10168</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7751,7 +7733,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>PO-10168</t>
+          <t>PO-10170</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7806,7 +7788,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PO-10170</t>
+          <t>PO-10172</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7861,7 +7843,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PO-10172</t>
+          <t>PO-10174</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7916,7 +7898,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PO-10176</t>
+          <t>PO-10178</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7926,12 +7908,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-16T17:47:35.030641+00:00</t>
+          <t>2026-10-13T04:24:59.716614+00:00</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-09-19T13:44:59.387532+00:00</t>
+          <t>2026-10-16T00:22:24.073505+00:00</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
@@ -7944,16 +7926,16 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>569.28</v>
+        <v>-41.34</v>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7947,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PO-10177</t>
+          <t>PO-10179</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8020,7 +8002,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PO-10178</t>
+          <t>PO-10180</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8075,7 +8057,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PO-10179</t>
+          <t>PO-10181</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8130,7 +8112,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PO-10180</t>
+          <t>PO-10182</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8158,7 +8140,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>-7.32</v>
+        <v>16.68</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8179,7 +8161,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PO-10182</t>
+          <t>PO-10184</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8234,7 +8216,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PO-10183</t>
+          <t>PO-10185</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8262,7 +8244,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>976.79</v>
+        <v>1000.8</v>
       </c>
       <c r="L128" t="inlineStr">
         <is>
@@ -8283,7 +8265,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PO-10184</t>
+          <t>PO-10186</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8338,7 +8320,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PO-10185</t>
+          <t>PO-10187</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8393,7 +8375,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PO-10187</t>
+          <t>PO-10189</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8421,7 +8403,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>-72.92</v>
+        <v>-48.91</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8442,7 +8424,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PO-10189</t>
+          <t>PO-10191</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8497,7 +8479,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PO-10190</t>
+          <t>PO-10192</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8552,7 +8534,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PO-10191</t>
+          <t>PO-10193</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8580,7 +8562,7 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1398.36</v>
+        <v>1422.37</v>
       </c>
       <c r="L134" t="inlineStr">
         <is>
@@ -8601,7 +8583,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PO-10195</t>
+          <t>PO-10197</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8629,7 +8611,7 @@
         <v>0</v>
       </c>
       <c r="K135" t="n">
-        <v>216.56</v>
+        <v>240.56</v>
       </c>
       <c r="L135" t="inlineStr">
         <is>
@@ -8650,7 +8632,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>PO-10197</t>
+          <t>PO-10199</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8705,7 +8687,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>PO-10198</t>
+          <t>PO-10200</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8760,7 +8742,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>PO-10199</t>
+          <t>PO-10201</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8788,7 +8770,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>851.65</v>
+        <v>875.66</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -8809,7 +8791,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>PO-10202</t>
+          <t>PO-10204</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8864,7 +8846,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>PO-10203</t>
+          <t>PO-10205</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8892,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>339.88</v>
+        <v>363.89</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -8913,7 +8895,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>PO-10204</t>
+          <t>PO-10206</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -8941,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>320.1</v>
+        <v>344.11</v>
       </c>
       <c r="L141" t="inlineStr">
         <is>
@@ -8962,7 +8944,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>PO-10205</t>
+          <t>PO-10207</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9017,7 +8999,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PO-10206</t>
+          <t>PO-10208</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9072,7 +9054,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PO-10207</t>
+          <t>PO-10209</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9100,7 +9082,7 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>-7.24</v>
+        <v>16.77</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -9121,7 +9103,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PO-10208</t>
+          <t>PO-10210</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9176,7 +9158,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PO-10209</t>
+          <t>PO-10211</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9231,7 +9213,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PO-10211</t>
+          <t>PO-10213</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9286,7 +9268,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PO-10212</t>
+          <t>PO-10214</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9341,7 +9323,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PO-10214</t>
+          <t>PO-10216</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9369,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>177.96</v>
+        <v>201.97</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9390,7 +9372,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PO-10216</t>
+          <t>PO-10218</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9445,7 +9427,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>PO-10217</t>
+          <t>PO-10219</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9500,7 +9482,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>PO-10218</t>
+          <t>PO-10220</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9555,7 +9537,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>PO-10219</t>
+          <t>PO-10221</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9583,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>1006.14</v>
+        <v>1030.15</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -9604,7 +9586,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PO-10220</t>
+          <t>PO-10222</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9659,7 +9641,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PO-10222</t>
+          <t>PO-10224</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9687,7 +9669,7 @@
         <v>0</v>
       </c>
       <c r="K155" t="n">
-        <v>22.76</v>
+        <v>46.77</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -9708,7 +9690,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PO-10223</t>
+          <t>PO-10225</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9736,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>1184.55</v>
+        <v>1208.56</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -9757,7 +9739,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PO-10224</t>
+          <t>PO-10226</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -9812,7 +9794,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PO-10225</t>
+          <t>PO-10227</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -9867,7 +9849,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PO-10226</t>
+          <t>PO-10228</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -9922,7 +9904,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PO-10227</t>
+          <t>PO-10229</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -9950,7 +9932,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>121.8</v>
+        <v>145.81</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -9971,7 +9953,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PO-10228</t>
+          <t>PO-10230</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10026,7 +10008,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PO-10229</t>
+          <t>PO-10231</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10081,7 +10063,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>PO-10230</t>
+          <t>PO-10232</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10136,7 +10118,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>PO-10231</t>
+          <t>PO-10233</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10191,7 +10173,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PO-10232</t>
+          <t>PO-10234</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10219,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>1165.36</v>
+        <v>1189.37</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10240,7 +10222,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>PO-10233</t>
+          <t>PO-10235</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10295,7 +10277,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>PO-10234</t>
+          <t>PO-10236</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10323,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>471.26</v>
+        <v>495.27</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -10344,7 +10326,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>PO-10235</t>
+          <t>PO-10237</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10394,67 +10376,61 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PO-10238</t>
+          <t>PO-10239</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-19T07:25:15.563402+00:00</t>
+          <t>2026-10-15T20:16:54.608075+00:00</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-09-19T23:24:30.220921+00:00</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-09-23T21:34:03.934201+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-17T14:12:04.838679+00:00</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="H169" t="n">
-        <v>94.16</v>
-      </c>
-      <c r="I169" t="n">
-        <v>110.15</v>
-      </c>
+        <v>41.92</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="b">
-        <v>1</v>
-      </c>
-      <c r="K169" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>-105.2</v>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>PO-10239</t>
+          <t>PO-10241</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10464,27 +10440,27 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-18T10:40:29.166662+00:00</t>
+          <t>2026-08-25T07:53:47.719852+00:00</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-08-19T21:38:55.061437+00:00</t>
+          <t>2026-08-26T11:17:15.357058+00:00</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-21T02:37:03.999003+00:00</t>
+          <t>2026-08-30T04:07:35.854346+00:00</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>34.97</v>
+        <v>27.39</v>
       </c>
       <c r="H170" t="n">
-        <v>28.97</v>
+        <v>88.84</v>
       </c>
       <c r="I170" t="n">
-        <v>63.94</v>
+        <v>116.23</v>
       </c>
       <c r="J170" t="b">
         <v>1</v>
@@ -10497,54 +10473,48 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>PO-10240</t>
+          <t>PO-10242</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-29T22:57:53.100483+00:00</t>
+          <t>2026-08-24T03:13:47.427658+00:00</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>2026-08-30T06:18:28.768835+00:00</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-09-01T13:53:55.274215+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-24T05:57:15.998345+00:00</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="H171" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I171" t="n">
-        <v>62.93</v>
-      </c>
+        <v>2.72</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="b">
-        <v>1</v>
-      </c>
-      <c r="K171" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1159.85</v>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -10564,56 +10534,62 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PO-10241</t>
+          <t>PO-10243</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-30T18:18:27.619156+00:00</t>
+          <t>2026-10-01T17:22:34.645812+00:00</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>2026-09-01T13:20:17.052603+00:00</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr"/>
+          <t>2026-10-02T00:59:30.373282+00:00</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-10-03T15:04:43.288892+00:00</t>
+        </is>
+      </c>
       <c r="G172" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
-      <c r="I172" t="inlineStr"/>
+        <v>7.62</v>
+      </c>
+      <c r="H172" t="n">
+        <v>38.09</v>
+      </c>
+      <c r="I172" t="n">
+        <v>45.7</v>
+      </c>
       <c r="J172" t="b">
-        <v>0</v>
-      </c>
-      <c r="K172" t="n">
-        <v>976.77</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PO-10242</t>
+          <t>PO-10244</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -10623,27 +10599,27 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-25T06:53:37.520110+00:00</t>
+          <t>2026-09-14T01:30:26.199034+00:00</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>2026-08-25T11:03:45.164723+00:00</t>
+          <t>2026-09-15T10:21:56.250928+00:00</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-28T14:45:01.098524+00:00</t>
+          <t>2026-09-16T01:42:51.669031+00:00</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>4.17</v>
+        <v>32.86</v>
       </c>
       <c r="H173" t="n">
-        <v>75.69</v>
+        <v>15.35</v>
       </c>
       <c r="I173" t="n">
-        <v>79.86</v>
+        <v>48.21</v>
       </c>
       <c r="J173" t="b">
         <v>1</v>
@@ -10651,24 +10627,24 @@
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>PO-10243</t>
+          <t>PO-10246</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -10678,27 +10654,27 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-19T11:27:45.458854+00:00</t>
+          <t>2026-09-21T21:32:18.130370+00:00</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>2026-09-21T22:02:19.926343+00:00</t>
+          <t>2026-09-23T17:13:03.457590+00:00</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-25T05:07:30.156964+00:00</t>
+          <t>2026-09-27T23:52:27.398560+00:00</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>58.58</v>
+        <v>43.68</v>
       </c>
       <c r="H174" t="n">
-        <v>79.09</v>
+        <v>102.66</v>
       </c>
       <c r="I174" t="n">
-        <v>137.66</v>
+        <v>146.34</v>
       </c>
       <c r="J174" t="b">
         <v>1</v>
@@ -10711,19 +10687,19 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>PO-10244</t>
+          <t>PO-10247</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -10733,27 +10709,27 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-22T09:36:54.099413+00:00</t>
+          <t>2026-08-11T03:33:37.021387+00:00</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>2026-08-24T10:18:08.645911+00:00</t>
+          <t>2026-08-11T13:08:16.709433+00:00</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-28T15:32:07.650865+00:00</t>
+          <t>2026-08-14T21:32:17.832025+00:00</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>48.69</v>
+        <v>9.58</v>
       </c>
       <c r="H175" t="n">
-        <v>101.23</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I175" t="n">
-        <v>149.92</v>
+        <v>89.98</v>
       </c>
       <c r="J175" t="b">
         <v>1</v>
@@ -10766,7 +10742,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10754,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>PO-10247</t>
+          <t>PO-10248</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -10788,17 +10764,17 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-01T21:30:34.691904+00:00</t>
+          <t>2026-10-03T22:30:34.691904+00:00</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2026-09-04T00:28:48.457326+00:00</t>
+          <t>2026-10-06T01:28:48.457326+00:00</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-09-08T11:33:41.797459+00:00</t>
+          <t>2026-10-10T12:33:41.797459+00:00</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -10816,12 +10792,12 @@
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10809,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>PO-10248</t>
+          <t>PO-10249</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -10888,7 +10864,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>PO-10249</t>
+          <t>PO-10250</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -10943,7 +10919,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>PO-10252</t>
+          <t>PO-10253</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -10998,7 +10974,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>PO-10253</t>
+          <t>PO-10254</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11026,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>-17.39</v>
+        <v>6.61</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -11047,7 +11023,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>PO-10254</t>
+          <t>PO-10255</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11102,7 +11078,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>PO-10255</t>
+          <t>PO-10256</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11157,7 +11133,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>PO-10256</t>
+          <t>PO-10257</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11212,7 +11188,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>PO-10258</t>
+          <t>PO-10259</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11267,7 +11243,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>PO-10259</t>
+          <t>PO-10260</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11322,7 +11298,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>PO-10262</t>
+          <t>PO-10263</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11377,7 +11353,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>PO-10263</t>
+          <t>PO-10264</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11432,7 +11408,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>PO-10264</t>
+          <t>PO-10265</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11460,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>898.64</v>
+        <v>922.65</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11481,7 +11457,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>PO-10267</t>
+          <t>PO-10268</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11536,7 +11512,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>PO-10268</t>
+          <t>PO-10269</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -11591,7 +11567,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>PO-10269</t>
+          <t>PO-10270</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -11646,7 +11622,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>PO-10270</t>
+          <t>PO-10271</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -11674,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>1174.92</v>
+        <v>1198.93</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11695,7 +11671,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PO-10271</t>
+          <t>PO-10272</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -11750,7 +11726,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>PO-10272</t>
+          <t>PO-10273</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -11778,7 +11754,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>1516.86</v>
+        <v>1540.86</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -11799,7 +11775,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>PO-10276</t>
+          <t>PO-10277</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -11827,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>65.08</v>
+        <v>89.09</v>
       </c>
       <c r="L195" t="inlineStr">
         <is>
@@ -11848,7 +11824,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>PO-10278</t>
+          <t>PO-10279</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -11903,7 +11879,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>PO-10281</t>
+          <t>PO-10282</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -11931,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>-51.33</v>
+        <v>-27.33</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
@@ -11952,7 +11928,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>PO-10282</t>
+          <t>PO-10283</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12007,7 +11983,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PO-10283</t>
+          <t>PO-10284</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12035,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
-        <v>1326.82</v>
+        <v>1350.83</v>
       </c>
       <c r="L199" t="inlineStr">
         <is>
@@ -12056,7 +12032,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>PO-10284</t>
+          <t>PO-10285</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12111,7 +12087,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>PO-10285</t>
+          <t>PO-10286</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12166,7 +12142,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PO-10286</t>
+          <t>PO-10287</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12221,7 +12197,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>PO-10287</t>
+          <t>PO-10288</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12249,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>1645.88</v>
+        <v>1669.88</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12270,7 +12246,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>PO-10288</t>
+          <t>PO-10289</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12298,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>-59.19</v>
+        <v>-35.19</v>
       </c>
       <c r="L204" t="inlineStr">
         <is>
@@ -12319,7 +12295,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>PO-10289</t>
+          <t>PO-10290</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12374,7 +12350,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>PO-10290</t>
+          <t>PO-10291</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -12429,7 +12405,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>PO-10291</t>
+          <t>PO-10292</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -12484,7 +12460,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>PO-10292</t>
+          <t>PO-10293</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -12539,7 +12515,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>PO-10293</t>
+          <t>PO-10294</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -12594,7 +12570,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>PO-10294</t>
+          <t>PO-10295</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12649,7 +12625,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>PO-10295</t>
+          <t>PO-10296</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -12677,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>169.43</v>
+        <v>193.43</v>
       </c>
       <c r="L211" t="inlineStr">
         <is>
@@ -12698,7 +12674,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PO-10296</t>
+          <t>PO-10297</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -12753,7 +12729,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>PO-10297</t>
+          <t>PO-10298</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -12808,7 +12784,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>PO-10298</t>
+          <t>PO-10299</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -12836,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>-39.03</v>
+        <v>-15.03</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -12857,7 +12833,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>PO-10299</t>
+          <t>PO-10300</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -12912,7 +12888,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>PO-10301</t>
+          <t>PO-10302</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -12967,7 +12943,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>PO-10302</t>
+          <t>PO-10303</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13022,7 +12998,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>PO-10303</t>
+          <t>PO-10304</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13050,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>69.87</v>
+        <v>93.87</v>
       </c>
       <c r="L218" t="inlineStr">
         <is>
@@ -13071,7 +13047,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>PO-10304</t>
+          <t>PO-10305</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13126,7 +13102,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>PO-10305</t>
+          <t>PO-10306</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13154,7 +13130,7 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>-27.89</v>
+        <v>-3.88</v>
       </c>
       <c r="L220" t="inlineStr">
         <is>
@@ -13175,7 +13151,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>PO-10306</t>
+          <t>PO-10307</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13203,7 +13179,7 @@
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>1095.33</v>
+        <v>1119.33</v>
       </c>
       <c r="L221" t="inlineStr">
         <is>
@@ -13224,7 +13200,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>PO-10307</t>
+          <t>PO-10308</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13279,7 +13255,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>PO-10310</t>
+          <t>PO-10311</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -13334,7 +13310,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>PO-10313</t>
+          <t>PO-10314</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -13389,7 +13365,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>PO-10315</t>
+          <t>PO-10316</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -13444,7 +13420,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>PO-10316</t>
+          <t>PO-10317</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -13499,7 +13475,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PO-10317</t>
+          <t>PO-10318</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -13527,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>1358.3</v>
+        <v>1382.31</v>
       </c>
       <c r="L227" t="inlineStr">
         <is>
@@ -13548,7 +13524,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PO-10318</t>
+          <t>PO-10319</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -13603,7 +13579,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PO-10320</t>
+          <t>PO-10321</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -13658,7 +13634,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>PO-10322</t>
+          <t>PO-10323</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -13713,7 +13689,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>PO-10323</t>
+          <t>PO-10324</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -13741,7 +13717,7 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>1478.85</v>
+        <v>1502.86</v>
       </c>
       <c r="L231" t="inlineStr">
         <is>
@@ -13762,7 +13738,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>PO-10325</t>
+          <t>PO-10326</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -13790,7 +13766,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>803.22</v>
+        <v>827.22</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13811,7 +13787,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PO-10327</t>
+          <t>PO-10328</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -13866,7 +13842,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>PO-10328</t>
+          <t>PO-10329</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -13894,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="K234" t="n">
-        <v>98.06</v>
+        <v>122.06</v>
       </c>
       <c r="L234" t="inlineStr">
         <is>
@@ -13915,7 +13891,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>PO-10331</t>
+          <t>PO-10332</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -13943,7 +13919,7 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>1475.76</v>
+        <v>1499.76</v>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -13964,7 +13940,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>PO-10336</t>
+          <t>PO-10337</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14019,7 +13995,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>PO-10338</t>
+          <t>PO-10339</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14074,7 +14050,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>PO-10339</t>
+          <t>PO-10340</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14129,7 +14105,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>PO-10340</t>
+          <t>PO-10341</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -14184,7 +14160,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>PO-10342</t>
+          <t>PO-10343</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -14212,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>412.11</v>
+        <v>436.11</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -14233,7 +14209,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>PO-10343</t>
+          <t>PO-10344</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -14261,7 +14237,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>1524</v>
+        <v>1548.01</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -14282,7 +14258,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>PO-10345</t>
+          <t>PO-10346</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -14310,7 +14286,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>82.54000000000001</v>
+        <v>106.54</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -14331,7 +14307,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PO-10346</t>
+          <t>PO-10347</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -14386,7 +14362,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>PO-10348</t>
+          <t>PO-10349</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -14441,7 +14417,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>PO-10351</t>
+          <t>PO-10352</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -14496,7 +14472,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PO-10353</t>
+          <t>PO-10354</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -14551,7 +14527,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>PO-10354</t>
+          <t>PO-10355</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -14606,7 +14582,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>PO-10355</t>
+          <t>PO-10356</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -14661,7 +14637,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>PO-10356</t>
+          <t>PO-10357</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -14716,7 +14692,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>PO-10357</t>
+          <t>PO-10358</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -14744,7 +14720,7 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>-68.97</v>
+        <v>-44.97</v>
       </c>
       <c r="L250" t="inlineStr">
         <is>
@@ -14765,7 +14741,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>PO-10361</t>
+          <t>PO-10362</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -14820,7 +14796,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>PO-10363</t>
+          <t>PO-10364</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -14875,7 +14851,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>PO-10364</t>
+          <t>PO-10365</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -14930,7 +14906,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>PO-10368</t>
+          <t>PO-10369</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -14985,7 +14961,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>PO-10369</t>
+          <t>PO-10370</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -15040,7 +15016,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>PO-10370</t>
+          <t>PO-10371</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -15095,7 +15071,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>PO-10372</t>
+          <t>PO-10373</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -15150,7 +15126,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>PO-10373</t>
+          <t>PO-10374</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -15205,7 +15181,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PO-10374</t>
+          <t>PO-10375</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -15233,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>80.79000000000001</v>
+        <v>104.79</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -15254,7 +15230,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>PO-10375</t>
+          <t>PO-10376</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -15309,7 +15285,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>PO-10376</t>
+          <t>PO-10377</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -15364,7 +15340,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>PO-10377</t>
+          <t>PO-10378</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -15392,7 +15368,7 @@
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>-31.39</v>
+        <v>-7.38</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -15413,7 +15389,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>PO-10380</t>
+          <t>PO-10381</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -15441,7 +15417,7 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>-11.31</v>
+        <v>12.7</v>
       </c>
       <c r="L263" t="inlineStr">
         <is>
@@ -15462,7 +15438,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>PO-10382</t>
+          <t>PO-10383</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -15517,7 +15493,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>PO-10383</t>
+          <t>PO-10384</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -15572,7 +15548,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PO-10385</t>
+          <t>PO-10386</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -15627,7 +15603,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>PO-10387</t>
+          <t>PO-10388</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -15682,7 +15658,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>PO-10389</t>
+          <t>PO-10390</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -15710,7 +15686,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>934.7</v>
+        <v>958.7</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -15731,7 +15707,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>PO-10393</t>
+          <t>PO-10394</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -15786,7 +15762,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>PO-10395</t>
+          <t>PO-10396</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -15814,7 +15790,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1603.39</v>
+        <v>1627.39</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15835,7 +15811,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>PO-10396</t>
+          <t>PO-10397</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -15890,7 +15866,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>PO-10398</t>
+          <t>PO-10399</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -15918,7 +15894,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>1103.31</v>
+        <v>1127.31</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15939,7 +15915,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>PO-10399</t>
+          <t>PO-10400</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -15967,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1574.56</v>
+        <v>1598.57</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -15988,7 +15964,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>PO-10401</t>
+          <t>PO-10402</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -16016,7 +15992,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>203.85</v>
+        <v>227.86</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -16037,7 +16013,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>PO-10402</t>
+          <t>PO-10403</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -16065,7 +16041,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>1320.26</v>
+        <v>1344.26</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16086,7 +16062,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>PO-10404</t>
+          <t>PO-10405</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -16141,7 +16117,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>PO-10405</t>
+          <t>PO-10406</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -16169,7 +16145,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>650.11</v>
+        <v>674.12</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -16190,7 +16166,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>PO-10406</t>
+          <t>PO-10407</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16218,7 +16194,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>20.69</v>
+        <v>44.7</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -16239,7 +16215,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>PO-10407</t>
+          <t>PO-10408</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -16294,7 +16270,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>PO-10408</t>
+          <t>PO-10409</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -16349,7 +16325,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>PO-10409</t>
+          <t>PO-10410</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -16404,7 +16380,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>PO-10410</t>
+          <t>PO-10411</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -16459,7 +16435,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>PO-10414</t>
+          <t>PO-10415</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -16514,7 +16490,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>PO-10416</t>
+          <t>PO-10417</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -16542,7 +16518,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>1109.08</v>
+        <v>1133.09</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -16563,7 +16539,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>PO-10417</t>
+          <t>PO-10418</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -16618,7 +16594,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>PO-10418</t>
+          <t>PO-10419</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -16673,7 +16649,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>PO-10419</t>
+          <t>PO-10420</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -16728,7 +16704,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>PO-10420</t>
+          <t>PO-10421</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -16783,7 +16759,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>PO-10421</t>
+          <t>PO-10422</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -16838,7 +16814,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>PO-10423</t>
+          <t>PO-10424</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -16893,7 +16869,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>PO-10424</t>
+          <t>PO-10425</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -16921,7 +16897,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>42.13</v>
+        <v>66.13</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16942,7 +16918,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>PO-10427</t>
+          <t>PO-10428</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -16997,50 +16973,44 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>PO-10428</t>
+          <t>PO-10429</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-27T00:07:18.909102+00:00</t>
+          <t>2026-10-13T23:07:18.909102+00:00</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-09-28T09:12:27.462496+00:00</t>
-        </is>
-      </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>2026-10-02T05:12:08.411296+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-15T08:12:27.462496+00:00</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
       <c r="G293" t="n">
         <v>33.09</v>
       </c>
-      <c r="H293" t="n">
-        <v>91.98999999999999</v>
-      </c>
-      <c r="I293" t="n">
-        <v>125.08</v>
-      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
       <c r="J293" t="b">
-        <v>1</v>
-      </c>
-      <c r="K293" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>-60.04</v>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17022,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>PO-10430</t>
+          <t>PO-10431</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -17080,7 +17050,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>784.3</v>
+        <v>808.3099999999999</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -17101,7 +17071,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>PO-10431</t>
+          <t>PO-10432</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -17156,7 +17126,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PO-10432</t>
+          <t>PO-10433</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -17211,7 +17181,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>PO-10433</t>
+          <t>PO-10434</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17266,7 +17236,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>PO-10434</t>
+          <t>PO-10435</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -17321,7 +17291,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>PO-10436</t>
+          <t>PO-10437</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -17376,7 +17346,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PO-10437</t>
+          <t>PO-10438</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -17404,7 +17374,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>-100.52</v>
+        <v>-76.52</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -17425,7 +17395,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>PO-10438</t>
+          <t>PO-10439</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -17480,7 +17450,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PO-10439</t>
+          <t>PO-10440</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -17535,7 +17505,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>PO-10440</t>
+          <t>PO-10441</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -17590,7 +17560,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>PO-10441</t>
+          <t>PO-10442</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -17645,7 +17615,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>PO-10442</t>
+          <t>PO-10443</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -17700,7 +17670,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>PO-10443</t>
+          <t>PO-10444</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -17755,7 +17725,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>PO-10444</t>
+          <t>PO-10445</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -17810,7 +17780,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>PO-10446</t>
+          <t>PO-10447</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -17820,12 +17790,12 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-08-31T01:24:14.974740+00:00</t>
+          <t>2026-10-16T10:31:52.404171+00:00</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-08-31T12:26:48.060070+00:00</t>
+          <t>2026-10-16T21:34:25.489501+00:00</t>
         </is>
       </c>
       <c r="F308" t="inlineStr"/>
@@ -17838,16 +17808,16 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>969.67</v>
+        <v>-119.45</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17829,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>PO-10450</t>
+          <t>PO-10451</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -17914,7 +17884,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PO-10452</t>
+          <t>PO-10453</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -17942,7 +17912,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>-76.91</v>
+        <v>-52.9</v>
       </c>
       <c r="L310" t="inlineStr">
         <is>
@@ -17963,7 +17933,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>PO-10453</t>
+          <t>PO-10454</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -18018,7 +17988,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>PO-10454</t>
+          <t>PO-10455</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -18073,7 +18043,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>PO-10455</t>
+          <t>PO-10456</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -18128,7 +18098,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>PO-10456</t>
+          <t>PO-10457</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -18156,7 +18126,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>1248.31</v>
+        <v>1272.31</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -18177,7 +18147,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10457</t>
+          <t>PO-10458</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -18205,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>-68.40000000000001</v>
+        <v>-44.39</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -18226,7 +18196,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10458</t>
+          <t>PO-10459</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -18281,7 +18251,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10459</t>
+          <t>PO-10460</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -18309,7 +18279,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>713.8099999999999</v>
+        <v>737.8099999999999</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -18330,7 +18300,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10460</t>
+          <t>PO-10461</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18358,7 +18328,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>173.24</v>
+        <v>197.24</v>
       </c>
       <c r="L318" t="inlineStr">
         <is>
@@ -18379,7 +18349,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10461</t>
+          <t>PO-10462</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18434,7 +18404,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10462</t>
+          <t>PO-10463</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18489,7 +18459,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10465</t>
+          <t>PO-10466</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18544,7 +18514,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10468</t>
+          <t>PO-10469</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18599,7 +18569,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10469</t>
+          <t>PO-10470</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18654,7 +18624,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10471</t>
+          <t>PO-10472</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18709,7 +18679,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10472</t>
+          <t>PO-10473</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18764,7 +18734,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10473</t>
+          <t>PO-10474</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18819,7 +18789,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10475</t>
+          <t>PO-10476</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -18847,7 +18817,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>758.11</v>
+        <v>782.11</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -18868,7 +18838,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10476</t>
+          <t>PO-10477</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18923,7 +18893,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10479</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18978,7 +18948,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10482</t>
+          <t>PO-10483</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -19033,7 +19003,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PO-10483</t>
+          <t>PO-10484</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19061,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>345.69</v>
+        <v>369.69</v>
       </c>
       <c r="L331" t="inlineStr">
         <is>
@@ -19082,7 +19052,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PO-10484</t>
+          <t>PO-10485</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19110,7 +19080,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>437.46</v>
+        <v>461.47</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -19131,7 +19101,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PO-10485</t>
+          <t>PO-10486</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19186,7 +19156,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10486</t>
+          <t>PO-10487</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -19214,7 +19184,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>1087.23</v>
+        <v>1111.23</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -19235,7 +19205,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10487</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19290,7 +19260,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10488</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19345,7 +19315,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10489</t>
+          <t>PO-10490</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19400,7 +19370,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10492</t>
+          <t>PO-10493</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19455,7 +19425,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19483,7 +19453,7 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>52.74</v>
+        <v>76.75</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -19504,7 +19474,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10495</t>
+          <t>PO-10496</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19559,7 +19529,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10498</t>
+          <t>PO-10500</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19614,7 +19584,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10500</t>
+          <t>PO-10502</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19669,7 +19639,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10501</t>
+          <t>PO-10503</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19724,7 +19694,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10503</t>
+          <t>PO-10505</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19779,7 +19749,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10504</t>
+          <t>PO-10506</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19834,7 +19804,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10505</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19889,7 +19859,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10506</t>
+          <t>PO-10508</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19944,7 +19914,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10507</t>
+          <t>PO-10509</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19999,7 +19969,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10511</t>
+          <t>PO-10513</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -20054,7 +20024,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10513</t>
+          <t>PO-10515</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20082,7 +20052,7 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>39.64</v>
+        <v>63.65</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
@@ -20103,7 +20073,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10514</t>
+          <t>PO-10516</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20158,7 +20128,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10515</t>
+          <t>PO-10517</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20213,7 +20183,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10516</t>
+          <t>PO-10518</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20241,7 +20211,7 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>1284.62</v>
+        <v>1308.63</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -20262,7 +20232,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10517</t>
+          <t>PO-10519</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20290,7 +20260,7 @@
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>-54.03</v>
+        <v>-30.03</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
@@ -20311,7 +20281,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10520</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20339,7 +20309,7 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>207.85</v>
+        <v>231.85</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
@@ -20360,7 +20330,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10519</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20415,7 +20385,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10520</t>
+          <t>PO-10522</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20470,7 +20440,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10523</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20498,7 +20468,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>-44.34</v>
+        <v>-20.34</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -20519,7 +20489,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10524</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20547,7 +20517,7 @@
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>1447.3</v>
+        <v>1471.31</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -20568,7 +20538,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10524</t>
+          <t>PO-10526</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20623,7 +20593,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10525</t>
+          <t>PO-10527</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20651,7 +20621,7 @@
         <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>1465.77</v>
+        <v>1489.78</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
@@ -20672,7 +20642,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10528</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -20727,7 +20697,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10531</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -20755,7 +20725,7 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>1319.54</v>
+        <v>1343.54</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
@@ -20776,7 +20746,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10530</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20831,7 +20801,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10531</t>
+          <t>PO-10533</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20886,7 +20856,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10532</t>
+          <t>PO-10534</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20941,7 +20911,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10533</t>
+          <t>PO-10535</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20969,7 +20939,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>801.4</v>
+        <v>825.41</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -20990,7 +20960,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10535</t>
+          <t>PO-10537</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -21045,7 +21015,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10536</t>
+          <t>PO-10538</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21100,7 +21070,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10538</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21110,12 +21080,12 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-10-14T09:59:13.458924+00:00</t>
+          <t>2026-10-15T14:59:13.458924+00:00</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-10-15T16:47:55.886881+00:00</t>
+          <t>2026-10-16T21:47:55.886881+00:00</t>
         </is>
       </c>
       <c r="F370" t="inlineStr"/>
@@ -21128,7 +21098,7 @@
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>-94.91</v>
+        <v>-99.91</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
@@ -21149,7 +21119,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10541</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21204,7 +21174,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10540</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21232,7 +21202,7 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>24.81</v>
+        <v>48.82</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
@@ -21253,7 +21223,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10543</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21281,7 +21251,7 @@
         <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>73.11</v>
+        <v>97.12</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -21302,7 +21272,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10542</t>
+          <t>PO-10544</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21330,7 +21300,7 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>594</v>
+        <v>618.01</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
@@ -21351,7 +21321,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10543</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21406,7 +21376,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10545</t>
+          <t>PO-10547</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21461,7 +21431,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10549</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21516,7 +21486,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10548</t>
+          <t>PO-10550</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21544,7 +21514,7 @@
         <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>-63.97</v>
+        <v>-39.97</v>
       </c>
       <c r="L378" t="inlineStr">
         <is>
@@ -21565,7 +21535,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10549</t>
+          <t>PO-10551</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21620,7 +21590,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10550</t>
+          <t>PO-10552</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21675,7 +21645,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10554</t>
+          <t>PO-10556</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21730,7 +21700,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10555</t>
+          <t>PO-10557</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21785,7 +21755,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10557</t>
+          <t>PO-10559</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21840,7 +21810,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10558</t>
+          <t>PO-10560</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -21895,7 +21865,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10562</t>
+          <t>PO-10564</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21950,7 +21920,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10563</t>
+          <t>PO-10565</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -21978,7 +21948,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>1090.9</v>
+        <v>1114.91</v>
       </c>
       <c r="L386" t="inlineStr">
         <is>
@@ -21999,7 +21969,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10564</t>
+          <t>PO-10566</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -22054,7 +22024,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10565</t>
+          <t>PO-10567</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22109,7 +22079,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10569</t>
+          <t>PO-10571</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -22164,7 +22134,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10571</t>
+          <t>PO-10573</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -22192,7 +22162,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="n">
-        <v>718.7</v>
+        <v>742.71</v>
       </c>
       <c r="L390" t="inlineStr">
         <is>
@@ -22213,7 +22183,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10572</t>
+          <t>PO-10574</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22241,7 +22211,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>849.3</v>
+        <v>873.3</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -22262,7 +22232,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10573</t>
+          <t>PO-10575</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22317,12 +22287,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10576</t>
+          <t>PO-10578</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -22335,18 +22305,24 @@
           <t>2026-10-07T22:14:07.936372+00:00</t>
         </is>
       </c>
-      <c r="F393" t="inlineStr"/>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:08:34.102909+00:00</t>
+        </is>
+      </c>
       <c r="G393" t="n">
         <v>15.73</v>
       </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
+      <c r="H393" t="n">
+        <v>74.91</v>
+      </c>
+      <c r="I393" t="n">
+        <v>90.64</v>
+      </c>
       <c r="J393" t="b">
-        <v>0</v>
-      </c>
-      <c r="K393" t="n">
-        <v>76.56999999999999</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -22366,7 +22342,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10577</t>
+          <t>PO-10579</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22421,7 +22397,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10580</t>
+          <t>PO-10582</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22476,7 +22452,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10581</t>
+          <t>PO-10583</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22531,7 +22507,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PO-10584</t>
+          <t>PO-10586</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -22559,7 +22535,7 @@
         <v>0</v>
       </c>
       <c r="K397" t="n">
-        <v>322.77</v>
+        <v>346.77</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
@@ -22580,7 +22556,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PO-10585</t>
+          <t>PO-10587</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -22635,7 +22611,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PO-10586</t>
+          <t>PO-10588</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -22690,7 +22666,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>PO-10590</t>
+          <t>PO-10592</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -22718,7 +22694,7 @@
         <v>0</v>
       </c>
       <c r="K400" t="n">
-        <v>899.4</v>
+        <v>923.41</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
@@ -22739,7 +22715,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PO-10592</t>
+          <t>PO-10594</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -22794,7 +22770,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PO-10593</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -22849,7 +22825,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10597</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -22904,7 +22880,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PO-10596</t>
+          <t>PO-10598</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -22959,7 +22935,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PO-10597</t>
+          <t>PO-10599</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -23003,116 +22979,6 @@
       <c r="M405" t="inlineStr">
         <is>
           <t>2026-S35</t>
-        </is>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Delta Sports</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>PO-10598</t>
-        </is>
-      </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>2026-09-20T15:04:30.893700+00:00</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>2026-09-21T12:21:21.838950+00:00</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr">
-        <is>
-          <t>2026-09-27T07:53:01.185675+00:00</t>
-        </is>
-      </c>
-      <c r="G406" t="n">
-        <v>21.28</v>
-      </c>
-      <c r="H406" t="n">
-        <v>139.53</v>
-      </c>
-      <c r="I406" t="n">
-        <v>160.81</v>
-      </c>
-      <c r="J406" t="b">
-        <v>1</v>
-      </c>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>2026-S38</t>
-        </is>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Delta Sports</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>PO-10599</t>
-        </is>
-      </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>2026-09-21T02:01:34.280043+00:00</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>2026-09-22T02:01:16.127104+00:00</t>
-        </is>
-      </c>
-      <c r="F407" t="inlineStr">
-        <is>
-          <t>2026-09-27T00:17:00.385352+00:00</t>
-        </is>
-      </c>
-      <c r="G407" t="n">
-        <v>23.99</v>
-      </c>
-      <c r="H407" t="n">
-        <v>118.26</v>
-      </c>
-      <c r="I407" t="n">
-        <v>142.26</v>
-      </c>
-      <c r="J407" t="b">
-        <v>1</v>
-      </c>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M407" t="inlineStr">
-        <is>
-          <t>2026-S39</t>
         </is>
       </c>
     </row>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.40000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82.5</v>
+        <v>82.3</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73</v>
+        <v>72.8</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.1</v>
+        <v>60.4</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.6</v>
+        <v>25.2</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="4">
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>94.59999999999999</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>83.3</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E7" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>85.2</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="8">
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>84.5</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -900,10 +900,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
         <v>19</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>62.7</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -932,19 +932,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>52.9</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="12">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>63.7</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F13" t="n">
         <v>21</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1031,16 +1031,16 @@
         <v>69</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>36.2</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="15">
@@ -1095,16 +1095,16 @@
         <v>105</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="17">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="n">
         <v>35</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>27.1</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="19">
@@ -1191,16 +1191,16 @@
         <v>67</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>28.4</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="20">
@@ -1223,16 +1223,16 @@
         <v>77</v>
       </c>
       <c r="E20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>29.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="21">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
@@ -1296,7 +1296,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E23" t="n">
         <v>60</v>
       </c>
       <c r="F23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>73.2</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="24">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E24" t="n">
         <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>83.7</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="25">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>27</v>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>64.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M397"/>
+  <dimension ref="A1:M396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>983.64</v>
+        <v>1007.62</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1094.76</v>
+        <v>1118.75</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>218.97</v>
+        <v>242.96</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21.71</v>
+        <v>45.69</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1473.64</v>
+        <v>1497.63</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>294.14</v>
+        <v>318.13</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-10T17:07:19.707982+00:00</t>
+          <t>2026-10-17T21:33:54.969945+00:00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-12T16:22:49.581282+00:00</t>
+          <t>2026-10-19T20:49:24.843245+00:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>90.2</v>
+        <v>-58.26</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>880.1</v>
+        <v>904.09</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1237.14</v>
+        <v>1261.12</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>93.98999999999999</v>
+        <v>117.98</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>330.04</v>
+        <v>354.03</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1677.41</v>
+        <v>1701.4</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>-31.92</v>
+        <v>-7.93</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.84</v>
+        <v>20.14</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>417.62</v>
+        <v>441.61</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>601.98</v>
+        <v>625.97</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1050.61</v>
+        <v>1074.6</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1084.93</v>
+        <v>1108.92</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>-46.46</v>
+        <v>-22.48</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>-82.86</v>
+        <v>-58.87</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1655.57</v>
+        <v>1679.55</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>763.04</v>
+        <v>787.03</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>-16.37</v>
+        <v>7.62</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>883.02</v>
+        <v>907.01</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4943,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>158.8</v>
+        <v>182.79</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>31.79</v>
+        <v>55.77</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47.62</v>
+        <v>71.61</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1502.92</v>
+        <v>1526.91</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>14.24</v>
+        <v>38.23</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6000,22 +6000,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-10-01T12:09:19.876475+00:00</t>
+          <t>2026-10-01T03:43:15.853702+00:00</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-02T12:18:20.190696+00:00</t>
+          <t>2026-10-01T21:37:23.769557+00:00</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>32.6</v>
+        <v>24.17</v>
       </c>
       <c r="H87" t="n">
-        <v>24.15</v>
+        <v>17.9</v>
       </c>
       <c r="I87" t="n">
-        <v>56.75</v>
+        <v>42.07</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-65.23</v>
+        <v>-41.24</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1444.89</v>
+        <v>1468.88</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1096.3</v>
+        <v>1120.29</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>191.71</v>
+        <v>215.7</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>763.1</v>
+        <v>787.09</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>248.17</v>
+        <v>272.16</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>30.9</v>
+        <v>54.89</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7886,18 +7886,24 @@
           <t>2026-10-12T13:09:15.202202+00:00</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-10-15T10:50:37.894047+00:00</t>
+        </is>
+      </c>
       <c r="G122" t="n">
         <v>42.76</v>
       </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="H122" t="n">
+        <v>69.69</v>
+      </c>
+      <c r="I122" t="n">
+        <v>112.45</v>
+      </c>
       <c r="J122" t="b">
-        <v>0</v>
-      </c>
-      <c r="K122" t="n">
-        <v>88.92</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -8000,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1073.03</v>
+        <v>1097.02</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8136,7 +8142,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8149,18 +8155,24 @@
           <t>2026-10-13T18:53:04.059609+00:00</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-10-14T20:13:34.548338+00:00</t>
+        </is>
+      </c>
       <c r="G127" t="n">
         <v>6.89</v>
       </c>
-      <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="H127" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="I127" t="n">
+        <v>32.23</v>
+      </c>
       <c r="J127" t="b">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>23.32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -8318,7 +8330,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1494.61</v>
+        <v>1518.59</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -8367,7 +8379,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>312.8</v>
+        <v>336.79</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8416,7 +8428,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>-101.67</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -8685,7 +8697,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1175.13</v>
+        <v>1199.12</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -8734,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1668.57</v>
+        <v>1692.56</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -8815,7 +8827,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8828,18 +8840,24 @@
           <t>2026-10-13T02:09:19.393552+00:00</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-10-15T03:13:51.990655+00:00</t>
+        </is>
+      </c>
       <c r="G140" t="n">
         <v>55.84</v>
       </c>
-      <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr"/>
+      <c r="H140" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="I140" t="n">
+        <v>104.92</v>
+      </c>
       <c r="J140" t="b">
-        <v>0</v>
-      </c>
-      <c r="K140" t="n">
-        <v>89.01000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -9107,7 +9125,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>274.2</v>
+        <v>298.19</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -9321,7 +9339,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>1.73</v>
+        <v>25.72</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9755,7 +9773,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>593.95</v>
+        <v>617.9400000000001</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -9859,7 +9877,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>381.88</v>
+        <v>405.86</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -9963,7 +9981,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1261.61</v>
+        <v>1285.59</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -10067,7 +10085,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>567.51</v>
+        <v>591.49</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -10171,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>-32.96</v>
+        <v>-8.98</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10275,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>1232.09</v>
+        <v>1256.08</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -10654,7 +10672,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>1168.2</v>
+        <v>1192.19</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -11198,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>994.89</v>
+        <v>1018.87</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -11302,7 +11320,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>-14.35</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11406,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>125.05</v>
+        <v>149.04</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11565,7 +11583,7 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
-        <v>71.27</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L191" t="inlineStr">
         <is>
@@ -11614,7 +11632,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>-99.83</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11718,7 +11736,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>44.91</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -11822,7 +11840,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1423.07</v>
+        <v>1447.06</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -12036,7 +12054,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>1742.12</v>
+        <v>1766.11</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -12085,7 +12103,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>-46.44</v>
+        <v>-22.46</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -12134,7 +12152,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>235.33</v>
+        <v>259.31</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -12458,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>265.67</v>
+        <v>289.66</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -12507,7 +12525,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>-18.71</v>
+        <v>5.28</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -12556,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>45.93</v>
+        <v>69.92</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -12660,7 +12678,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>1335.43</v>
+        <v>1359.41</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -12764,7 +12782,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>4.98</v>
+        <v>28.96</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -12813,7 +12831,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>1064.78</v>
+        <v>1088.77</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -13027,7 +13045,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>-34.8</v>
+        <v>-10.81</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -13296,7 +13314,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>1454.54</v>
+        <v>1478.53</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -13400,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>-49.88</v>
+        <v>-25.9</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -13504,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>1575.1</v>
+        <v>1599.08</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -13553,7 +13571,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>899.46</v>
+        <v>923.45</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13712,7 +13730,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>1572</v>
+        <v>1595.99</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13981,7 +13999,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>508.35</v>
+        <v>532.34</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -14030,7 +14048,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>1620.25</v>
+        <v>1644.24</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -14079,7 +14097,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>178.78</v>
+        <v>202.77</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -14238,7 +14256,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>-63.08</v>
+        <v>-39.1</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -14562,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>27.27</v>
+        <v>51.26</v>
       </c>
       <c r="L248" t="inlineStr">
         <is>
@@ -14808,37 +14826,31 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-10-04T10:17:28.209232+00:00</t>
+          <t>2026-10-18T13:23:39.846226+00:00</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2026-10-07T16:04:50.016311+00:00</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>2026-10-08T07:08:56.289812+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-20T08:55:43.732851+00:00</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
       <c r="G253" t="n">
-        <v>77.79000000000001</v>
-      </c>
-      <c r="H253" t="n">
-        <v>15.07</v>
-      </c>
-      <c r="I253" t="n">
-        <v>92.86</v>
-      </c>
+        <v>43.53</v>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
       <c r="J253" t="b">
-        <v>1</v>
-      </c>
-      <c r="K253" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>-74.09</v>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -14846,7 +14858,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -14868,27 +14880,27 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-18T16:09:14.191751+00:00</t>
+          <t>2026-09-15T06:53:05.711425+00:00</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>2026-08-19T00:47:47.640722+00:00</t>
+          <t>2026-09-16T17:28:04.173575+00:00</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>2026-08-20T13:03:23.330378+00:00</t>
+          <t>2026-09-17T16:26:34.154727+00:00</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>8.640000000000001</v>
+        <v>34.58</v>
       </c>
       <c r="H254" t="n">
-        <v>36.26</v>
+        <v>22.97</v>
       </c>
       <c r="I254" t="n">
-        <v>44.9</v>
+        <v>57.56</v>
       </c>
       <c r="J254" t="b">
         <v>1</v>
@@ -14896,12 +14908,12 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
@@ -15216,7 +15228,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>64.84999999999999</v>
+        <v>88.84</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -15265,7 +15277,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>84.94</v>
+        <v>108.92</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -15534,7 +15546,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>1030.94</v>
+        <v>1054.93</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -15638,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>1699.63</v>
+        <v>1723.62</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -15742,7 +15754,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1199.55</v>
+        <v>1223.54</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15791,7 +15803,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>1670.8</v>
+        <v>1694.79</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -15840,7 +15852,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>300.1</v>
+        <v>324.08</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15889,7 +15901,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1416.5</v>
+        <v>1440.49</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -15993,7 +16005,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>746.36</v>
+        <v>770.34</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16042,7 +16054,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>116.93</v>
+        <v>140.92</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -16366,7 +16378,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>1205.33</v>
+        <v>1229.31</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16722,7 +16734,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -16735,18 +16747,24 @@
           <t>2026-10-10T13:59:28.879122+00:00</t>
         </is>
       </c>
-      <c r="F289" t="inlineStr"/>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>2026-10-14T20:19:41.163147+00:00</t>
+        </is>
+      </c>
       <c r="G289" t="n">
         <v>45.04</v>
       </c>
-      <c r="H289" t="inlineStr"/>
-      <c r="I289" t="inlineStr"/>
+      <c r="H289" t="n">
+        <v>102.34</v>
+      </c>
+      <c r="I289" t="n">
+        <v>147.38</v>
+      </c>
       <c r="J289" t="b">
-        <v>0</v>
-      </c>
-      <c r="K289" t="n">
-        <v>138.37</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -16849,7 +16867,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>12.2</v>
+        <v>36.18</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16898,7 +16916,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>880.55</v>
+        <v>904.53</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -17034,52 +17052,46 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-08-28T02:08:47.489081+00:00</t>
+          <t>2026-10-17T06:26:24.489716+00:00</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-08-31T13:57:00.431691+00:00</t>
-        </is>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>2026-09-01T21:54:10.546246+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-19T20:04:27.778683+00:00</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
       <c r="G295" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="H295" t="n">
-        <v>31.95</v>
-      </c>
-      <c r="I295" t="n">
-        <v>115.76</v>
-      </c>
+        <v>61.63</v>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
       <c r="J295" t="b">
-        <v>1</v>
-      </c>
-      <c r="K295" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>-43.13</v>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -17094,27 +17106,27 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-30T23:05:37.510801+00:00</t>
+          <t>2026-08-19T02:04:08.877497+00:00</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-10-01T07:10:56.849290+00:00</t>
+          <t>2026-08-19T11:36:43.537712+00:00</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>2026-10-01T19:31:49.038306+00:00</t>
+          <t>2026-08-20T02:10:47.718408+00:00</t>
         </is>
       </c>
       <c r="G296" t="n">
-        <v>8.09</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H296" t="n">
-        <v>12.35</v>
+        <v>14.57</v>
       </c>
       <c r="I296" t="n">
-        <v>20.44</v>
+        <v>24.11</v>
       </c>
       <c r="J296" t="b">
         <v>1</v>
@@ -17122,12 +17134,12 @@
       <c r="K296" t="inlineStr"/>
       <c r="L296" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -17222,7 +17234,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>-4.28</v>
+        <v>19.71</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -17656,7 +17668,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>-47.21</v>
+        <v>-23.23</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -17980,7 +17992,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>1344.55</v>
+        <v>1368.54</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -18029,7 +18041,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>27.85</v>
+        <v>51.83</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -18055,198 +18067,198 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-09-09T04:38:28.762292+00:00</t>
+          <t>2026-10-18T18:21:40.554627+00:00</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-09-11T10:08:31.535489+00:00</t>
-        </is>
-      </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>2026-09-15T08:50:48.456109+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-19T08:58:32.107455+00:00</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
       <c r="G314" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="H314" t="n">
-        <v>94.7</v>
-      </c>
-      <c r="I314" t="n">
-        <v>148.21</v>
-      </c>
+        <v>14.61</v>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr"/>
       <c r="J314" t="b">
-        <v>1</v>
-      </c>
-      <c r="K314" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>-79.06</v>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>PO-10464</t>
+          <t>PO-10465</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-10T17:16:09.095754+00:00</t>
+          <t>2026-08-18T20:42:52.634346+00:00</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>2026-09-11T12:43:58.441650+00:00</t>
-        </is>
-      </c>
-      <c r="F315" t="inlineStr"/>
+          <t>2026-08-20T14:27:28.706475+00:00</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>2026-08-24T15:23:27.948638+00:00</t>
+        </is>
+      </c>
       <c r="G315" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="H315" t="inlineStr"/>
-      <c r="I315" t="inlineStr"/>
+        <v>41.74</v>
+      </c>
+      <c r="H315" t="n">
+        <v>96.93000000000001</v>
+      </c>
+      <c r="I315" t="n">
+        <v>138.68</v>
+      </c>
       <c r="J315" t="b">
-        <v>0</v>
-      </c>
-      <c r="K315" t="n">
-        <v>810.05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>PO-10465</t>
+          <t>PO-10466</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-10-03T05:50:17.284863+00:00</t>
+          <t>2026-08-25T18:47:47.606509+00:00</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>2026-10-04T10:34:24.997077+00:00</t>
-        </is>
-      </c>
-      <c r="F316" t="inlineStr"/>
+          <t>2026-08-27T01:13:05.052293+00:00</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>2026-08-29T15:33:53.862577+00:00</t>
+        </is>
+      </c>
       <c r="G316" t="n">
-        <v>28.74</v>
-      </c>
-      <c r="H316" t="inlineStr"/>
-      <c r="I316" t="inlineStr"/>
+        <v>30.42</v>
+      </c>
+      <c r="H316" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="I316" t="n">
+        <v>92.77</v>
+      </c>
       <c r="J316" t="b">
-        <v>0</v>
-      </c>
-      <c r="K316" t="n">
-        <v>269.48</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>PO-10466</t>
+          <t>PO-10467</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-31T20:52:16.144491+00:00</t>
+          <t>2026-09-13T07:19:41.643302+00:00</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>2026-09-02T08:25:46.933379+00:00</t>
-        </is>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>2026-09-07T06:25:58.665124+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-13T12:44:32.693349+00:00</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
       <c r="G317" t="n">
-        <v>35.56</v>
-      </c>
-      <c r="H317" t="n">
-        <v>118</v>
-      </c>
-      <c r="I317" t="n">
-        <v>153.56</v>
-      </c>
+        <v>5.41</v>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
       <c r="J317" t="b">
-        <v>1</v>
-      </c>
-      <c r="K317" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>771.98</v>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
@@ -18258,7 +18270,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>PO-10467</t>
+          <t>PO-10468</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -18313,7 +18325,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>PO-10470</t>
+          <t>PO-10471</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -18368,7 +18380,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>PO-10473</t>
+          <t>PO-10474</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -18423,7 +18435,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>PO-10474</t>
+          <t>PO-10475</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -18478,7 +18490,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>PO-10476</t>
+          <t>PO-10477</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -18533,7 +18545,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>PO-10477</t>
+          <t>PO-10478</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -18588,7 +18600,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>PO-10478</t>
+          <t>PO-10479</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -18643,7 +18655,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>PO-10480</t>
+          <t>PO-10481</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -18671,7 +18683,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>854.35</v>
+        <v>878.34</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -18692,7 +18704,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PO-10481</t>
+          <t>PO-10482</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -18747,7 +18759,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>PO-10483</t>
+          <t>PO-10484</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -18802,7 +18814,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>PO-10487</t>
+          <t>PO-10488</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -18857,7 +18869,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>PO-10488</t>
+          <t>PO-10489</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -18885,7 +18897,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>441.93</v>
+        <v>465.92</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -18906,7 +18918,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>PO-10489</t>
+          <t>PO-10490</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -18934,7 +18946,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>533.71</v>
+        <v>557.6900000000001</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -18955,7 +18967,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>PO-10490</t>
+          <t>PO-10491</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -19010,7 +19022,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>PO-10491</t>
+          <t>PO-10492</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -19038,7 +19050,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>1183.47</v>
+        <v>1207.46</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -19059,7 +19071,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>PO-10492</t>
+          <t>PO-10493</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -19087,7 +19099,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>-40.55</v>
+        <v>-16.57</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -19108,50 +19120,44 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10493</t>
+          <t>PO-10494</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-19T18:27:37.821516+00:00</t>
+          <t>2026-10-20T15:15:50.765955+00:00</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-08-23T05:06:12.426176+00:00</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>2026-08-28T22:05:28.981580+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-24T01:54:25.370615+00:00</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr"/>
       <c r="G334" t="n">
         <v>82.64</v>
       </c>
-      <c r="H334" t="n">
-        <v>136.99</v>
-      </c>
-      <c r="I334" t="n">
-        <v>219.63</v>
-      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr"/>
       <c r="J334" t="b">
-        <v>1</v>
-      </c>
-      <c r="K334" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
+        <v>-123.96</v>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
@@ -19163,7 +19169,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -19218,7 +19224,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10497</t>
+          <t>PO-10498</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19273,7 +19279,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10499</t>
+          <t>PO-10500</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -19301,7 +19307,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>148.99</v>
+        <v>172.97</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -19322,7 +19328,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10500</t>
+          <t>PO-10501</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19377,7 +19383,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10504</t>
+          <t>PO-10505</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -19432,7 +19438,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10505</t>
+          <t>PO-10506</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -19460,7 +19466,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>-87.11</v>
+        <v>-63.12</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -19481,7 +19487,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10506</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19509,7 +19515,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>-76.66</v>
+        <v>-52.67</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -19530,7 +19536,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10507</t>
+          <t>PO-10508</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -19585,7 +19591,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10508</t>
+          <t>PO-10509</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -19640,7 +19646,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10510</t>
+          <t>PO-10511</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -19695,7 +19701,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10511</t>
+          <t>PO-10512</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -19750,7 +19756,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10512</t>
+          <t>PO-10513</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19805,7 +19811,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10516</t>
+          <t>PO-10517</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19860,12 +19866,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10519</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -19878,18 +19884,24 @@
           <t>2026-10-10T04:23:28.455671+00:00</t>
         </is>
       </c>
-      <c r="F348" t="inlineStr"/>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>2026-10-15T08:31:19.903061+00:00</t>
+        </is>
+      </c>
       <c r="G348" t="n">
         <v>32.96</v>
       </c>
-      <c r="H348" t="inlineStr"/>
-      <c r="I348" t="inlineStr"/>
+      <c r="H348" t="n">
+        <v>124.13</v>
+      </c>
+      <c r="I348" t="n">
+        <v>157.09</v>
+      </c>
       <c r="J348" t="b">
-        <v>0</v>
-      </c>
-      <c r="K348" t="n">
-        <v>135.89</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -19909,7 +19921,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10519</t>
+          <t>PO-10520</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -19964,7 +19976,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10520</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20019,7 +20031,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10522</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20047,7 +20059,7 @@
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>1380.87</v>
+        <v>1404.85</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -20068,7 +20080,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10523</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20096,7 +20108,7 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>-49.26</v>
+        <v>-25.27</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -20117,7 +20129,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10523</t>
+          <t>PO-10524</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -20145,7 +20157,7 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>-38.63</v>
+        <v>-14.64</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -20166,7 +20178,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10527</t>
+          <t>PO-10528</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20221,7 +20233,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -20276,7 +20288,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10531</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20331,7 +20343,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10532</t>
+          <t>PO-10533</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20359,7 +20371,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>1375.58</v>
+        <v>1399.57</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -20380,7 +20392,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10534</t>
+          <t>PO-10535</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20408,7 +20420,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>1562.02</v>
+        <v>1586</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -20429,7 +20441,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10537</t>
+          <t>PO-10538</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -20484,7 +20496,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10538</t>
+          <t>PO-10539</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -20512,7 +20524,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1415.78</v>
+        <v>1439.77</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -20533,7 +20545,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20588,7 +20600,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10540</t>
+          <t>PO-10541</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -20643,7 +20655,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -20698,7 +20710,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10542</t>
+          <t>PO-10543</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -20726,7 +20738,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>897.65</v>
+        <v>921.64</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -20747,7 +20759,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10544</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -20802,7 +20814,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10545</t>
+          <t>PO-10546</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20857,7 +20869,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10548</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20885,7 +20897,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>-27.67</v>
+        <v>-3.68</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -20906,7 +20918,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10548</t>
+          <t>PO-10549</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20961,7 +20973,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10549</t>
+          <t>PO-10550</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -21016,7 +21028,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10550</t>
+          <t>PO-10551</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -21071,7 +21083,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10551</t>
+          <t>PO-10552</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21099,7 +21111,7 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>690.25</v>
+        <v>714.23</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -21120,7 +21132,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10552</t>
+          <t>PO-10553</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21175,7 +21187,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10554</t>
+          <t>PO-10555</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -21230,7 +21242,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10556</t>
+          <t>PO-10557</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -21285,7 +21297,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10557</t>
+          <t>PO-10558</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -21313,7 +21325,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>32.27</v>
+        <v>56.26</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -21334,7 +21346,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10558</t>
+          <t>PO-10559</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -21389,7 +21401,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10559</t>
+          <t>PO-10560</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -21444,7 +21456,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10563</t>
+          <t>PO-10564</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -21499,7 +21511,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10564</t>
+          <t>PO-10565</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21554,7 +21566,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10566</t>
+          <t>PO-10567</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21609,7 +21621,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10567</t>
+          <t>PO-10568</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21664,7 +21676,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10571</t>
+          <t>PO-10572</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21719,7 +21731,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10572</t>
+          <t>PO-10573</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -21747,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>1187.15</v>
+        <v>1211.13</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -21768,7 +21780,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10573</t>
+          <t>PO-10574</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -21823,7 +21835,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10574</t>
+          <t>PO-10575</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -21878,7 +21890,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10578</t>
+          <t>PO-10579</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -21933,7 +21945,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10580</t>
+          <t>PO-10581</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -21961,7 +21973,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>814.9400000000001</v>
+        <v>838.9299999999999</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -21982,7 +21994,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10581</t>
+          <t>PO-10582</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22010,7 +22022,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="n">
-        <v>945.54</v>
+        <v>969.53</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -22031,7 +22043,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10582</t>
+          <t>PO-10583</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -22086,7 +22098,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10585</t>
+          <t>PO-10586</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -22141,7 +22153,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10586</t>
+          <t>PO-10587</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22196,7 +22208,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10589</t>
+          <t>PO-10590</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -22251,7 +22263,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10590</t>
+          <t>PO-10591</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -22306,7 +22318,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10593</t>
+          <t>PO-10594</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22334,7 +22346,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>419.01</v>
+        <v>443</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -22355,7 +22367,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10594</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22383,7 +22395,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>-65.63</v>
+        <v>-41.65</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
@@ -22404,7 +22416,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10596</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22448,55 +22460,6 @@
       <c r="M396" t="inlineStr">
         <is>
           <t>2026-S38</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Bravo Casa</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>PO-10599</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>2026-09-02T23:40:14.276060+00:00</t>
-        </is>
-      </c>
-      <c r="E397" t="inlineStr">
-        <is>
-          <t>2026-09-03T14:16:36.045318+00:00</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr"/>
-      <c r="G397" t="n">
-        <v>14.61</v>
-      </c>
-      <c r="H397" t="inlineStr"/>
-      <c r="I397" t="inlineStr"/>
-      <c r="J397" t="b">
-        <v>0</v>
-      </c>
-      <c r="K397" t="n">
-        <v>995.65</v>
-      </c>
-      <c r="L397" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M397" t="inlineStr">
-        <is>
-          <t>2026-S36</t>
         </is>
       </c>
     </row>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60.4</v>
+        <v>60.6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6">
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -656,7 +656,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>96</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -720,7 +720,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>93.90000000000001</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>82.8</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -804,10 +804,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -816,7 +816,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="9">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="10">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
         <v>51</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>64.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
         <v>48</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>45.5</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="16">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E16" t="n">
         <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>46.7</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="17">
@@ -1156,19 +1156,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>25.5</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
       </c>
       <c r="F19" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="20">
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="22">
@@ -1284,19 +1284,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E22" t="n">
         <v>48</v>
       </c>
       <c r="F22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F23" t="n">
         <v>23</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>72.3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
         <v>15</v>
@@ -1360,7 +1360,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>82.8</v>
+        <v>82.59999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1380,19 +1380,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
         <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>65.40000000000001</v>
+        <v>66.2</v>
       </c>
     </row>
   </sheetData>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1007.62</v>
+        <v>1031.63</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1118.75</v>
+        <v>1142.75</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>242.96</v>
+        <v>266.96</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>45.69</v>
+        <v>69.7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1497.63</v>
+        <v>1521.63</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>318.13</v>
+        <v>342.13</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-58.26</v>
+        <v>-34.26</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>904.09</v>
+        <v>928.09</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1261.12</v>
+        <v>1285.13</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2493,18 +2493,24 @@
           <t>2026-10-12T10:11:27.407818+00:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-16T02:47:42.147096+00:00</t>
+        </is>
+      </c>
       <c r="G21" t="n">
         <v>44.87</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>133.47</v>
+      </c>
       <c r="J21" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>117.98</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -2717,7 +2723,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>354.03</v>
+        <v>378.03</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -2986,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>1701.4</v>
+        <v>1725.4</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3420,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.93</v>
+        <v>16.07</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3524,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>20.14</v>
+        <v>44.15</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -3573,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>441.61</v>
+        <v>465.61</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3764,22 +3770,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-19T09:20:01.939484+00:00</t>
+          <t>2026-10-18T20:04:34.183434+00:00</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-09-19T19:55:30.753710+00:00</t>
+          <t>2026-10-21T20:08:35.710620+00:00</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>10.59</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -3787,16 +3793,16 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>625.97</v>
+        <v>-56.77</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3814,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PO-10078</t>
+          <t>PO-10079</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3863,7 +3869,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>PO-10080</t>
+          <t>PO-10081</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3918,7 +3924,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PO-10081</t>
+          <t>PO-10082</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3973,7 +3979,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PO-10083</t>
+          <t>PO-10084</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4028,7 +4034,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PO-10084</t>
+          <t>PO-10085</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4083,7 +4089,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PO-10085</t>
+          <t>PO-10086</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4111,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1074.6</v>
+        <v>1098.6</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -4132,7 +4138,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PO-10086</t>
+          <t>PO-10087</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4187,7 +4193,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PO-10087</t>
+          <t>PO-10088</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4215,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>1108.92</v>
+        <v>1132.92</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -4236,7 +4242,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PO-10088</t>
+          <t>PO-10089</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4291,7 +4297,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PO-10089</t>
+          <t>PO-10090</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4319,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>-22.48</v>
+        <v>1.53</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4340,7 +4346,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PO-10090</t>
+          <t>PO-10091</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4390,7 +4396,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4400,22 +4406,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-10-17T22:10:39.562579+00:00</t>
+          <t>2026-10-19T05:07:32.546408+00:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-10-18T11:36:47.720708+00:00</t>
+          <t>2026-10-19T15:10:19.810830+00:00</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>13.44</v>
+        <v>10.05</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
@@ -4423,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>-58.87</v>
+        <v>-65.81999999999999</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4432,14 +4438,14 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4449,31 +4455,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-06T11:45:05.928880+00:00</t>
+          <t>2026-08-31T05:37:58.813763+00:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-07T23:12:39.210253+00:00</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>2026-08-31T21:00:15.569141+00:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-03T00:32:29.255896+00:00</t>
+        </is>
+      </c>
       <c r="G58" t="n">
-        <v>35.46</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+        <v>15.37</v>
+      </c>
+      <c r="H58" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="I58" t="n">
+        <v>66.91</v>
+      </c>
       <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>1679.55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -4481,7 +4493,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>787.03</v>
+        <v>811.03</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4827,12 +4839,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-10-15T03:41:22.502957+00:00</t>
+          <t>2026-10-18T09:41:22.502957+00:00</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-10-18T01:33:13.194543+00:00</t>
+          <t>2026-10-21T07:33:13.194543+00:00</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -4845,7 +4857,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>7.62</v>
+        <v>-46.38</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4894,7 +4906,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>907.01</v>
+        <v>931.01</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4943,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>182.79</v>
+        <v>206.79</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5047,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>55.77</v>
+        <v>79.78</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5348,7 +5360,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5361,18 +5373,24 @@
           <t>2026-10-15T02:08:30.014001+00:00</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-10-16T02:18:06.920590+00:00</t>
+        </is>
+      </c>
       <c r="G75" t="n">
         <v>62.45</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>24.16</v>
+      </c>
+      <c r="I75" t="n">
+        <v>86.61</v>
+      </c>
       <c r="J75" t="b">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>71.61</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -5695,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1526.91</v>
+        <v>1550.91</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -5964,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>38.23</v>
+        <v>62.23</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -6270,12 +6288,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-10-17T04:32:58.761059+00:00</t>
+          <t>2026-10-17T22:25:00.168390+00:00</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-10-17T17:06:53.316047+00:00</t>
+          <t>2026-10-18T10:58:54.723378+00:00</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -6288,7 +6306,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>-41.24</v>
+        <v>-35.11</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -6337,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1468.88</v>
+        <v>1492.88</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -6386,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>1120.29</v>
+        <v>1144.29</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -6600,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>215.7</v>
+        <v>239.7</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -7034,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>787.09</v>
+        <v>811.09</v>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -7248,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>272.16</v>
+        <v>296.16</v>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -7682,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>54.89</v>
+        <v>78.89</v>
       </c>
       <c r="L118" t="inlineStr">
         <is>
@@ -8006,7 +8024,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1097.02</v>
+        <v>1121.02</v>
       </c>
       <c r="L124" t="inlineStr">
         <is>
@@ -8330,7 +8348,7 @@
         <v>0</v>
       </c>
       <c r="K130" t="n">
-        <v>1518.59</v>
+        <v>1542.6</v>
       </c>
       <c r="L130" t="inlineStr">
         <is>
@@ -8379,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>336.79</v>
+        <v>360.79</v>
       </c>
       <c r="L131" t="inlineStr">
         <is>
@@ -8428,7 +8446,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>-77.68000000000001</v>
+        <v>-53.68</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -8697,7 +8715,7 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1199.12</v>
+        <v>1223.12</v>
       </c>
       <c r="L137" t="inlineStr">
         <is>
@@ -8746,7 +8764,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>1692.56</v>
+        <v>1716.56</v>
       </c>
       <c r="L138" t="inlineStr">
         <is>
@@ -9125,7 +9143,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>298.19</v>
+        <v>322.19</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -9339,7 +9357,7 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>25.72</v>
+        <v>49.72</v>
       </c>
       <c r="L149" t="inlineStr">
         <is>
@@ -9585,45 +9603,39 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-10T11:39:00.739162+00:00</t>
+          <t>2026-10-19T04:54:40.480553+00:00</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-09-11T10:41:21.171244+00:00</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-12T09:13:36.713937+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-20T03:57:00.912635+00:00</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="n">
         <v>23.04</v>
       </c>
-      <c r="H154" t="n">
-        <v>22.54</v>
-      </c>
-      <c r="I154" t="n">
-        <v>45.58</v>
-      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="b">
-        <v>1</v>
-      </c>
-      <c r="K154" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>-65.59999999999999</v>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9785,7 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>617.9400000000001</v>
+        <v>641.9400000000001</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -9877,7 +9889,7 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
-        <v>405.86</v>
+        <v>429.87</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -9981,7 +9993,7 @@
         <v>0</v>
       </c>
       <c r="K161" t="n">
-        <v>1285.59</v>
+        <v>1309.6</v>
       </c>
       <c r="L161" t="inlineStr">
         <is>
@@ -10085,7 +10097,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>591.49</v>
+        <v>615.5</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -10189,7 +10201,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>-8.98</v>
+        <v>15.03</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10293,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>1256.08</v>
+        <v>1280.08</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -10672,7 +10684,7 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>1192.19</v>
+        <v>1216.19</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -11216,7 +11228,7 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>1018.87</v>
+        <v>1042.88</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -11320,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>9.640000000000001</v>
+        <v>33.64</v>
       </c>
       <c r="L186" t="inlineStr">
         <is>
@@ -11424,7 +11436,7 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>149.04</v>
+        <v>173.04</v>
       </c>
       <c r="L188" t="inlineStr">
         <is>
@@ -11560,7 +11572,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11573,18 +11585,24 @@
           <t>2026-10-13T16:04:56.078166+00:00</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-10-16T01:14:59.802480+00:00</t>
+        </is>
+      </c>
       <c r="G191" t="n">
         <v>52.04</v>
       </c>
-      <c r="H191" t="inlineStr"/>
-      <c r="I191" t="inlineStr"/>
+      <c r="H191" t="n">
+        <v>57.17</v>
+      </c>
+      <c r="I191" t="n">
+        <v>109.2</v>
+      </c>
       <c r="J191" t="b">
-        <v>0</v>
-      </c>
-      <c r="K191" t="n">
-        <v>95.26000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -11632,7 +11650,7 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>-75.84999999999999</v>
+        <v>-51.84</v>
       </c>
       <c r="L192" t="inlineStr">
         <is>
@@ -11736,7 +11754,7 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>68.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L194" t="inlineStr">
         <is>
@@ -11840,7 +11858,7 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>1447.06</v>
+        <v>1471.06</v>
       </c>
       <c r="L196" t="inlineStr">
         <is>
@@ -12054,7 +12072,7 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>1766.11</v>
+        <v>1790.11</v>
       </c>
       <c r="L200" t="inlineStr">
         <is>
@@ -12103,7 +12121,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>-22.46</v>
+        <v>1.55</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -12152,7 +12170,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>259.31</v>
+        <v>283.32</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -12476,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>289.66</v>
+        <v>313.66</v>
       </c>
       <c r="L208" t="inlineStr">
         <is>
@@ -12525,7 +12543,7 @@
         <v>0</v>
       </c>
       <c r="K209" t="n">
-        <v>5.28</v>
+        <v>29.28</v>
       </c>
       <c r="L209" t="inlineStr">
         <is>
@@ -12574,7 +12592,7 @@
         <v>0</v>
       </c>
       <c r="K210" t="n">
-        <v>69.92</v>
+        <v>93.92</v>
       </c>
       <c r="L210" t="inlineStr">
         <is>
@@ -12678,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>1359.41</v>
+        <v>1383.42</v>
       </c>
       <c r="L212" t="inlineStr">
         <is>
@@ -12782,7 +12800,7 @@
         <v>0</v>
       </c>
       <c r="K214" t="n">
-        <v>28.96</v>
+        <v>52.97</v>
       </c>
       <c r="L214" t="inlineStr">
         <is>
@@ -12831,7 +12849,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>1088.77</v>
+        <v>1112.77</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -13045,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>-10.81</v>
+        <v>13.19</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -13314,7 +13332,7 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>1478.53</v>
+        <v>1502.53</v>
       </c>
       <c r="L224" t="inlineStr">
         <is>
@@ -13418,7 +13436,7 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>-25.9</v>
+        <v>-1.89</v>
       </c>
       <c r="L226" t="inlineStr">
         <is>
@@ -13522,7 +13540,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>1599.08</v>
+        <v>1623.09</v>
       </c>
       <c r="L228" t="inlineStr">
         <is>
@@ -13571,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>923.45</v>
+        <v>947.45</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13730,7 +13748,7 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>1595.99</v>
+        <v>1619.99</v>
       </c>
       <c r="L232" t="inlineStr">
         <is>
@@ -13999,7 +14017,7 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>532.34</v>
+        <v>556.34</v>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -14048,7 +14066,7 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>1644.24</v>
+        <v>1668.24</v>
       </c>
       <c r="L238" t="inlineStr">
         <is>
@@ -14097,7 +14115,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>202.77</v>
+        <v>226.77</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -14256,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>-39.1</v>
+        <v>-15.09</v>
       </c>
       <c r="L242" t="inlineStr">
         <is>
@@ -14557,7 +14575,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -14570,18 +14588,24 @@
           <t>2026-10-13T13:38:39.061234+00:00</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr"/>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>2026-10-15T23:37:57.281330+00:00</t>
+        </is>
+      </c>
       <c r="G248" t="n">
         <v>5.6</v>
       </c>
-      <c r="H248" t="inlineStr"/>
-      <c r="I248" t="inlineStr"/>
+      <c r="H248" t="n">
+        <v>57.99</v>
+      </c>
+      <c r="I248" t="n">
+        <v>63.58</v>
+      </c>
       <c r="J248" t="b">
-        <v>0</v>
-      </c>
-      <c r="K248" t="n">
-        <v>51.26</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -14849,7 +14873,7 @@
         <v>0</v>
       </c>
       <c r="K253" t="n">
-        <v>-74.09</v>
+        <v>-50.09</v>
       </c>
       <c r="L253" t="inlineStr">
         <is>
@@ -15228,7 +15252,7 @@
         <v>0</v>
       </c>
       <c r="K260" t="n">
-        <v>88.84</v>
+        <v>112.84</v>
       </c>
       <c r="L260" t="inlineStr">
         <is>
@@ -15277,7 +15301,7 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>108.92</v>
+        <v>132.92</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -15546,7 +15570,7 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>1054.93</v>
+        <v>1078.93</v>
       </c>
       <c r="L266" t="inlineStr">
         <is>
@@ -15650,7 +15674,7 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
-        <v>1723.62</v>
+        <v>1747.62</v>
       </c>
       <c r="L268" t="inlineStr">
         <is>
@@ -15754,7 +15778,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1223.54</v>
+        <v>1247.54</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15803,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>1694.79</v>
+        <v>1718.79</v>
       </c>
       <c r="L271" t="inlineStr">
         <is>
@@ -15852,7 +15876,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>324.08</v>
+        <v>348.09</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15901,7 +15925,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1440.49</v>
+        <v>1464.49</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -16005,7 +16029,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>770.34</v>
+        <v>794.35</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16054,7 +16078,7 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>140.92</v>
+        <v>164.92</v>
       </c>
       <c r="L276" t="inlineStr">
         <is>
@@ -16378,7 +16402,7 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>1229.31</v>
+        <v>1253.32</v>
       </c>
       <c r="L282" t="inlineStr">
         <is>
@@ -16867,7 +16891,7 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
-        <v>36.18</v>
+        <v>60.19</v>
       </c>
       <c r="L291" t="inlineStr">
         <is>
@@ -16916,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="K292" t="n">
-        <v>904.53</v>
+        <v>928.54</v>
       </c>
       <c r="L292" t="inlineStr">
         <is>
@@ -17075,7 +17099,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>-43.13</v>
+        <v>-19.13</v>
       </c>
       <c r="L295" t="inlineStr">
         <is>
@@ -17234,7 +17258,7 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>19.71</v>
+        <v>43.71</v>
       </c>
       <c r="L298" t="inlineStr">
         <is>
@@ -17668,7 +17692,7 @@
         <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>-23.23</v>
+        <v>0.78</v>
       </c>
       <c r="L306" t="inlineStr">
         <is>
@@ -17992,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>1368.54</v>
+        <v>1392.54</v>
       </c>
       <c r="L312" t="inlineStr">
         <is>
@@ -18041,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>51.83</v>
+        <v>75.84</v>
       </c>
       <c r="L313" t="inlineStr">
         <is>
@@ -18090,7 +18114,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>-79.06</v>
+        <v>-55.05</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -18249,7 +18273,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>771.98</v>
+        <v>795.98</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -18683,7 +18707,7 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>878.34</v>
+        <v>902.34</v>
       </c>
       <c r="L325" t="inlineStr">
         <is>
@@ -18897,7 +18921,7 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>465.92</v>
+        <v>489.92</v>
       </c>
       <c r="L329" t="inlineStr">
         <is>
@@ -18946,7 +18970,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>557.6900000000001</v>
+        <v>581.7</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -19050,7 +19074,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>1207.46</v>
+        <v>1231.46</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -19099,7 +19123,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>-16.57</v>
+        <v>7.44</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -19148,7 +19172,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>-123.96</v>
+        <v>-99.95999999999999</v>
       </c>
       <c r="L334" t="inlineStr">
         <is>
@@ -19307,7 +19331,7 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>172.97</v>
+        <v>196.98</v>
       </c>
       <c r="L337" t="inlineStr">
         <is>
@@ -19466,7 +19490,7 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>-63.12</v>
+        <v>-39.12</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -19515,7 +19539,7 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>-52.67</v>
+        <v>-28.67</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -20059,7 +20083,7 @@
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>1404.85</v>
+        <v>1428.86</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
@@ -20108,7 +20132,7 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>-25.27</v>
+        <v>-1.27</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
@@ -20157,7 +20181,7 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>-14.64</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
@@ -20371,7 +20395,7 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>1399.57</v>
+        <v>1423.57</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
@@ -20420,7 +20444,7 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>1586</v>
+        <v>1610.01</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
@@ -20524,7 +20548,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1439.77</v>
+        <v>1463.77</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -20738,7 +20762,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>921.64</v>
+        <v>945.64</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -20897,7 +20921,7 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>-3.68</v>
+        <v>20.32</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
@@ -21111,7 +21135,7 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
-        <v>714.23</v>
+        <v>738.24</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
@@ -21325,7 +21349,7 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>56.26</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -21759,7 +21783,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>1211.13</v>
+        <v>1235.14</v>
       </c>
       <c r="L383" t="inlineStr">
         <is>
@@ -21973,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="K387" t="n">
-        <v>838.9299999999999</v>
+        <v>862.9299999999999</v>
       </c>
       <c r="L387" t="inlineStr">
         <is>
@@ -22022,7 +22046,7 @@
         <v>0</v>
       </c>
       <c r="K388" t="n">
-        <v>969.53</v>
+        <v>993.53</v>
       </c>
       <c r="L388" t="inlineStr">
         <is>
@@ -22346,7 +22370,7 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="L394" t="inlineStr">
         <is>
@@ -22395,7 +22419,7 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
-        <v>-41.65</v>
+        <v>-17.64</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>

--- a/dados/status_atual.xlsx
+++ b/dados/status_atual.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>95.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>83.8</v>
+        <v>84</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>324</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.2</v>
+        <v>72.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -505,7 +505,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.3</v>
+        <v>59.7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45.9</v>
+        <v>45.5</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -547,7 +547,7 @@
         <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>317</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7">
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>28.3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -740,19 +740,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>94.7</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -772,10 +772,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E6" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>88.90000000000001</v>
+        <v>89.2</v>
       </c>
     </row>
     <row r="7">
@@ -804,19 +804,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>79.2</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>83.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -935,16 +935,16 @@
         <v>74</v>
       </c>
       <c r="E11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>54.1</v>
+        <v>56.8</v>
       </c>
     </row>
     <row r="12">
@@ -967,16 +967,16 @@
         <v>81</v>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="13">
@@ -999,16 +999,16 @@
         <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>56.7</v>
+        <v>58.2</v>
       </c>
     </row>
     <row r="14">
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>42.2</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="15">
@@ -1060,19 +1060,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>46.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="16">
@@ -1092,19 +1092,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E16" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>46.4</v>
+        <v>45.7</v>
       </c>
     </row>
     <row r="17">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="18">
@@ -1156,10 +1156,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
@@ -1168,7 +1168,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>31.2</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="19">
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>29.4</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="20">
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="21">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
         <v>11</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="22">
@@ -1287,16 +1287,16 @@
         <v>61</v>
       </c>
       <c r="E22" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>68.90000000000001</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="23">
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E23" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
         <v>23</v>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="24">
@@ -1348,19 +1348,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>84.5</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="25">
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M400"/>
+  <dimension ref="A1:M398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1203.87</v>
+        <v>1226.49</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1314.99</v>
+        <v>1337.62</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>439.2</v>
+        <v>461.83</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1693.87</v>
+        <v>1716.49</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>514.38</v>
+        <v>537</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1100.33</v>
+        <v>1122.96</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1457.37</v>
+        <v>1479.99</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>32.97</v>
+        <v>55.59</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-50.08</v>
+        <v>-27.46</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>70.73</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-62.74</v>
+        <v>-40.12</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-31.73</v>
+        <v>-9.1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>1897.64</v>
+        <v>1920.27</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1468.85</v>
+        <v>1491.48</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>-41.03</v>
+        <v>-18.41</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>257.3</v>
+        <v>279.93</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>-93.95999999999999</v>
+        <v>-71.34</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1173.58</v>
+        <v>1196.21</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>910.95</v>
+        <v>933.58</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1875.8</v>
+        <v>1898.42</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>983.28</v>
+        <v>1005.9</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>125.86</v>
+        <v>148.49</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>1103.26</v>
+        <v>1125.88</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>379.04</v>
+        <v>401.66</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>252.02</v>
+        <v>274.64</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1723.16</v>
+        <v>1745.78</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>89.3</v>
+        <v>111.93</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -6167,45 +6167,39 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-07T16:13:04.914106+00:00</t>
+          <t>2026-10-24T20:13:04.914106+00:00</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-09-08T19:53:06.336866+00:00</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-09-10T14:48:54.639006+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-25T23:53:06.336866+00:00</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>27.67</v>
       </c>
-      <c r="H90" t="n">
-        <v>42.93</v>
-      </c>
-      <c r="I90" t="n">
-        <v>70.59999999999999</v>
-      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="b">
-        <v>1</v>
-      </c>
-      <c r="K90" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>-6.04</v>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>-23.46</v>
+        <v>-0.84</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -6624,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>-71.34</v>
+        <v>-48.71</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -6728,7 +6722,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>411.94</v>
+        <v>434.57</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -6942,7 +6936,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>32.23</v>
+        <v>54.85</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -7101,7 +7095,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
-        <v>-38.6</v>
+        <v>-15.97</v>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -7150,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>983.33</v>
+        <v>1005.96</v>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -7364,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>468.4</v>
+        <v>491.02</v>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -7798,7 +7792,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>251.13</v>
+        <v>273.76</v>
       </c>
       <c r="L120" t="inlineStr">
         <is>
@@ -8122,7 +8116,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1293.27</v>
+        <v>1315.89</v>
       </c>
       <c r="L126" t="inlineStr">
         <is>
@@ -8446,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>1714.84</v>
+        <v>1737.46</v>
       </c>
       <c r="L132" t="inlineStr">
         <is>
@@ -8467,7 +8461,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PO-10205</t>
+          <t>PO-10203</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8477,17 +8471,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-10-01T10:31:01.808106+00:00</t>
+          <t>2026-10-28T12:22:37.582224+00:00</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-10-03T08:16:10.904843+00:00</t>
+          <t>2026-10-29T10:50:29.524529+00:00</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
-        <v>45.75</v>
+        <v>22.46</v>
       </c>
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
@@ -8495,7 +8489,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>533.03</v>
+        <v>-94.2</v>
       </c>
       <c r="L133" t="inlineStr">
         <is>
@@ -8504,56 +8498,62 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S44</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PO-10207</t>
+          <t>PO-10204</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-18T16:59:17.615226+00:00</t>
+          <t>2026-09-06T20:55:00.825283+00:00</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-10-21T20:33:48.093809+00:00</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
+          <t>2026-09-07T11:52:40.069788+00:00</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-10T09:02:50.742874+00:00</t>
+        </is>
+      </c>
       <c r="G134" t="n">
-        <v>75.58</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+        <v>14.96</v>
+      </c>
+      <c r="H134" t="n">
+        <v>69.17</v>
+      </c>
+      <c r="I134" t="n">
+        <v>84.13</v>
+      </c>
       <c r="J134" t="b">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>118.56</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>PO-10208</t>
+          <t>PO-10206</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8575,27 +8575,27 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-10-08T10:57:18.539968+00:00</t>
+          <t>2026-10-07T19:21:38.935011+00:00</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-10-08T22:05:17.733242+00:00</t>
+          <t>2026-10-10T05:27:24.452254+00:00</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-10-11T13:41:03.845005+00:00</t>
+          <t>2026-10-13T23:30:41.762375+00:00</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>11.13</v>
+        <v>58.1</v>
       </c>
       <c r="H135" t="n">
-        <v>63.6</v>
+        <v>90.05</v>
       </c>
       <c r="I135" t="n">
-        <v>74.73</v>
+        <v>148.15</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
@@ -8615,7 +8615,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8630,27 +8630,27 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-29T06:16:46.208495+00:00</t>
+          <t>2026-10-21T14:46:44.428154+00:00</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-31T22:51:17.994256+00:00</t>
+          <t>2026-10-23T09:21:27.617570+00:00</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-02T00:15:37.209469+00:00</t>
+          <t>2026-10-24T02:06:32.398916+00:00</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>64.58</v>
+        <v>42.58</v>
       </c>
       <c r="H136" t="n">
-        <v>25.41</v>
+        <v>16.75</v>
       </c>
       <c r="I136" t="n">
-        <v>89.98</v>
+        <v>59.33</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
@@ -8658,12 +8658,12 @@
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>-36.64</v>
+        <v>-14.01</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>1888.8</v>
+        <v>1911.43</v>
       </c>
       <c r="L140" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>494.44</v>
+        <v>517.0599999999999</v>
       </c>
       <c r="L147" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -9390,18 +9390,24 @@
           <t>2026-10-22T09:07:25.576636+00:00</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-10-23T17:22:40.120768+00:00</t>
+        </is>
+      </c>
       <c r="G150" t="n">
         <v>33.96</v>
       </c>
-      <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+      <c r="H150" t="n">
+        <v>32.25</v>
+      </c>
+      <c r="I150" t="n">
+        <v>66.22</v>
+      </c>
       <c r="J150" t="b">
-        <v>0</v>
-      </c>
-      <c r="K150" t="n">
-        <v>64.39</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -9559,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>3.46</v>
+        <v>26.08</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -9608,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>2.31</v>
+        <v>24.93</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -9712,7 +9718,7 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>810.24</v>
+        <v>832.87</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -9926,7 +9932,7 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>951.97</v>
+        <v>974.59</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -10085,7 +10091,7 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>1700.39</v>
+        <v>1723.02</v>
       </c>
       <c r="L163" t="inlineStr">
         <is>
@@ -10134,7 +10140,7 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>813.83</v>
+        <v>836.46</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -10183,7 +10189,7 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>1407.29</v>
+        <v>1429.92</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -10287,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>954.58</v>
+        <v>977.21</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -10391,7 +10397,7 @@
         <v>0</v>
       </c>
       <c r="K169" t="n">
-        <v>948.49</v>
+        <v>971.11</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -10495,7 +10501,7 @@
         <v>0</v>
       </c>
       <c r="K171" t="n">
-        <v>-32.41</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="L171" t="inlineStr">
         <is>
@@ -10709,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>1729.29</v>
+        <v>1751.92</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -11143,7 +11149,7 @@
         <v>0</v>
       </c>
       <c r="K183" t="n">
-        <v>18.56</v>
+        <v>41.19</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -11247,7 +11253,7 @@
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>1215.12</v>
+        <v>1237.74</v>
       </c>
       <c r="L185" t="inlineStr">
         <is>
@@ -11351,7 +11357,7 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
-        <v>205.89</v>
+        <v>228.51</v>
       </c>
       <c r="L187" t="inlineStr">
         <is>
@@ -11455,7 +11461,7 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>345.29</v>
+        <v>367.91</v>
       </c>
       <c r="L189" t="inlineStr">
         <is>
@@ -11646,7 +11652,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -11659,18 +11665,24 @@
           <t>2026-10-19T17:31:47.610946+00:00</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-10-24T01:49:40.800770+00:00</t>
+        </is>
+      </c>
       <c r="G193" t="n">
         <v>26.38</v>
       </c>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
+      <c r="H193" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="I193" t="n">
+        <v>130.68</v>
+      </c>
       <c r="J193" t="b">
-        <v>0</v>
-      </c>
-      <c r="K193" t="n">
-        <v>120.4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -11865,12 +11877,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-16T04:15:01.695869+00:00</t>
+          <t>2026-10-27T06:45:49.198774+00:00</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>2026-08-18T12:36:26.785818+00:00</t>
+          <t>2026-10-29T15:07:14.288723+00:00</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
@@ -11883,16 +11895,16 @@
         <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>1643.3</v>
+        <v>-64.59</v>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S44</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12109,7 @@
         <v>0</v>
       </c>
       <c r="K201" t="n">
-        <v>1962.35</v>
+        <v>1984.98</v>
       </c>
       <c r="L201" t="inlineStr">
         <is>
@@ -12146,7 +12158,7 @@
         <v>0</v>
       </c>
       <c r="K202" t="n">
-        <v>-51.35</v>
+        <v>-28.73</v>
       </c>
       <c r="L202" t="inlineStr">
         <is>
@@ -12195,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>455.56</v>
+        <v>478.18</v>
       </c>
       <c r="L203" t="inlineStr">
         <is>
@@ -12354,7 +12366,7 @@
         <v>0</v>
       </c>
       <c r="K206" t="n">
-        <v>114</v>
+        <v>136.63</v>
       </c>
       <c r="L206" t="inlineStr">
         <is>
@@ -12843,7 +12855,7 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
-        <v>319.51</v>
+        <v>342.13</v>
       </c>
       <c r="L215" t="inlineStr">
         <is>
@@ -13387,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
-        <v>1674.78</v>
+        <v>1697.4</v>
       </c>
       <c r="L225" t="inlineStr">
         <is>
@@ -13601,7 +13613,7 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>1795.33</v>
+        <v>1817.95</v>
       </c>
       <c r="L229" t="inlineStr">
         <is>
@@ -13650,7 +13662,7 @@
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>1119.69</v>
+        <v>1142.32</v>
       </c>
       <c r="L230" t="inlineStr">
         <is>
@@ -14139,7 +14151,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>728.58</v>
+        <v>751.2</v>
       </c>
       <c r="L239" t="inlineStr">
         <is>
@@ -14188,7 +14200,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>1840.48</v>
+        <v>1863.1</v>
       </c>
       <c r="L240" t="inlineStr">
         <is>
@@ -14237,7 +14249,7 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>399.02</v>
+        <v>421.64</v>
       </c>
       <c r="L241" t="inlineStr">
         <is>
@@ -14396,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>-93.09999999999999</v>
+        <v>-70.48</v>
       </c>
       <c r="L244" t="inlineStr">
         <is>
@@ -14665,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="K249" t="n">
-        <v>470.58</v>
+        <v>493.2</v>
       </c>
       <c r="L249" t="inlineStr">
         <is>
@@ -14934,7 +14946,7 @@
         <v>0</v>
       </c>
       <c r="K254" t="n">
-        <v>122.16</v>
+        <v>144.78</v>
       </c>
       <c r="L254" t="inlineStr">
         <is>
@@ -15038,7 +15050,7 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>92.29000000000001</v>
+        <v>114.92</v>
       </c>
       <c r="L256" t="inlineStr">
         <is>
@@ -15197,7 +15209,7 @@
         <v>0</v>
       </c>
       <c r="K259" t="n">
-        <v>1610.61</v>
+        <v>1633.24</v>
       </c>
       <c r="L259" t="inlineStr">
         <is>
@@ -15466,7 +15478,7 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>-5.04</v>
+        <v>17.58</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -15790,7 +15802,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>1919.86</v>
+        <v>1942.49</v>
       </c>
       <c r="L270" t="inlineStr">
         <is>
@@ -15894,7 +15906,7 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>1419.78</v>
+        <v>1442.41</v>
       </c>
       <c r="L272" t="inlineStr">
         <is>
@@ -15943,7 +15955,7 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>1891.04</v>
+        <v>1913.66</v>
       </c>
       <c r="L273" t="inlineStr">
         <is>
@@ -15992,7 +16004,7 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>6.96</v>
+        <v>29.58</v>
       </c>
       <c r="L274" t="inlineStr">
         <is>
@@ -16041,7 +16053,7 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>1636.74</v>
+        <v>1659.36</v>
       </c>
       <c r="L275" t="inlineStr">
         <is>
@@ -16145,7 +16157,7 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>966.59</v>
+        <v>989.21</v>
       </c>
       <c r="L277" t="inlineStr">
         <is>
@@ -16194,7 +16206,7 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>337.17</v>
+        <v>359.79</v>
       </c>
       <c r="L278" t="inlineStr">
         <is>
@@ -16518,7 +16530,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>1425.56</v>
+        <v>1448.18</v>
       </c>
       <c r="L284" t="inlineStr">
         <is>
@@ -17062,7 +17074,7 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>1100.78</v>
+        <v>1123.4</v>
       </c>
       <c r="L294" t="inlineStr">
         <is>
@@ -17221,7 +17233,7 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>153.11</v>
+        <v>175.73</v>
       </c>
       <c r="L297" t="inlineStr">
         <is>
@@ -17380,7 +17392,7 @@
         <v>0</v>
       </c>
       <c r="K300" t="n">
-        <v>215.95</v>
+        <v>238.58</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -17759,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>-51.99</v>
+        <v>-29.37</v>
       </c>
       <c r="L307" t="inlineStr">
         <is>
@@ -17808,7 +17820,7 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>173.02</v>
+        <v>195.64</v>
       </c>
       <c r="L308" t="inlineStr">
         <is>
@@ -18132,7 +18144,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>1564.78</v>
+        <v>1587.41</v>
       </c>
       <c r="L314" t="inlineStr">
         <is>
@@ -18181,7 +18193,7 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>248.08</v>
+        <v>270.7</v>
       </c>
       <c r="L315" t="inlineStr">
         <is>
@@ -18285,7 +18297,7 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>-17.09</v>
+        <v>5.53</v>
       </c>
       <c r="L317" t="inlineStr">
         <is>
@@ -18389,7 +18401,7 @@
         <v>0</v>
       </c>
       <c r="K319" t="n">
-        <v>968.22</v>
+        <v>990.85</v>
       </c>
       <c r="L319" t="inlineStr">
         <is>
@@ -18823,7 +18835,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>1074.58</v>
+        <v>1097.21</v>
       </c>
       <c r="L327" t="inlineStr">
         <is>
@@ -18982,7 +18994,7 @@
         <v>0</v>
       </c>
       <c r="K330" t="n">
-        <v>-11.4</v>
+        <v>11.22</v>
       </c>
       <c r="L330" t="inlineStr">
         <is>
@@ -19086,7 +19098,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>22.9</v>
+        <v>45.52</v>
       </c>
       <c r="L332" t="inlineStr">
         <is>
@@ -19135,7 +19147,7 @@
         <v>0</v>
       </c>
       <c r="K333" t="n">
-        <v>120.56</v>
+        <v>143.19</v>
       </c>
       <c r="L333" t="inlineStr">
         <is>
@@ -19151,41 +19163,47 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>PO-10491</t>
+          <t>PO-10493</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-10-25T05:37:27.996462+00:00</t>
+          <t>2026-10-21T05:25:11.128426+00:00</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-10-27T08:02:34.590398+00:00</t>
-        </is>
-      </c>
-      <c r="F334" t="inlineStr"/>
+          <t>2026-10-22T05:25:01.117148+00:00</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>2026-10-23T07:54:24.007634+00:00</t>
+        </is>
+      </c>
       <c r="G334" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="H334" t="inlineStr"/>
-      <c r="I334" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="H334" t="n">
+        <v>26.49</v>
+      </c>
+      <c r="I334" t="n">
+        <v>50.49</v>
+      </c>
       <c r="J334" t="b">
-        <v>0</v>
-      </c>
-      <c r="K334" t="n">
-        <v>-38.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -19205,56 +19223,62 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>PO-10492</t>
+          <t>PO-10494</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-26T03:50:58.864173+00:00</t>
+          <t>2026-09-29T02:40:09.192998+00:00</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2026-08-27T06:21:25.808022+00:00</t>
-        </is>
-      </c>
-      <c r="F335" t="inlineStr"/>
+          <t>2026-09-29T22:43:10.604029+00:00</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>2026-10-01T07:21:18.334554+00:00</t>
+        </is>
+      </c>
       <c r="G335" t="n">
-        <v>26.51</v>
-      </c>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
+        <v>20.05</v>
+      </c>
+      <c r="H335" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="I335" t="n">
+        <v>52.69</v>
+      </c>
       <c r="J335" t="b">
-        <v>0</v>
-      </c>
-      <c r="K335" t="n">
-        <v>1403.7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PO-10493</t>
+          <t>PO-10495</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -19264,27 +19288,27 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-10-16T03:52:16.212326+00:00</t>
+          <t>2026-10-15T23:15:50.765955+00:00</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2026-10-17T04:22:59.430445+00:00</t>
+          <t>2026-10-17T14:29:52.455450+00:00</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>2026-10-21T16:10:29.868179+00:00</t>
+          <t>2026-10-20T07:31:52.945602+00:00</t>
         </is>
       </c>
       <c r="G336" t="n">
-        <v>24.51</v>
+        <v>39.23</v>
       </c>
       <c r="H336" t="n">
-        <v>107.79</v>
+        <v>65.03</v>
       </c>
       <c r="I336" t="n">
-        <v>132.3</v>
+        <v>104.27</v>
       </c>
       <c r="J336" t="b">
         <v>1</v>
@@ -19304,49 +19328,55 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>PO-10494</t>
+          <t>PO-10496</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-10-20T15:15:50.765955+00:00</t>
+          <t>2026-08-17T02:44:59.622168+00:00</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2026-10-24T01:54:25.370615+00:00</t>
-        </is>
-      </c>
-      <c r="F337" t="inlineStr"/>
+          <t>2026-08-19T04:28:49.068780+00:00</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>2026-08-25T02:55:53.600196+00:00</t>
+        </is>
+      </c>
       <c r="G337" t="n">
-        <v>82.64</v>
-      </c>
-      <c r="H337" t="inlineStr"/>
-      <c r="I337" t="inlineStr"/>
+        <v>49.73</v>
+      </c>
+      <c r="H337" t="n">
+        <v>142.45</v>
+      </c>
+      <c r="I337" t="n">
+        <v>192.18</v>
+      </c>
       <c r="J337" t="b">
-        <v>0</v>
-      </c>
-      <c r="K337" t="n">
-        <v>72.29000000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -19358,7 +19388,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>PO-10495</t>
+          <t>PO-10499</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -19368,27 +19398,27 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-17T02:44:59.622168+00:00</t>
+          <t>2026-08-09T21:32:15.767073+00:00</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2026-08-19T04:28:49.068780+00:00</t>
+          <t>2026-08-10T09:39:03.862803+00:00</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>2026-08-25T02:55:53.600196+00:00</t>
+          <t>2026-08-11T16:15:08.874292+00:00</t>
         </is>
       </c>
       <c r="G338" t="n">
-        <v>49.73</v>
+        <v>12.11</v>
       </c>
       <c r="H338" t="n">
-        <v>142.45</v>
+        <v>30.6</v>
       </c>
       <c r="I338" t="n">
-        <v>192.18</v>
+        <v>42.71</v>
       </c>
       <c r="J338" t="b">
         <v>1</v>
@@ -19401,62 +19431,56 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PO-10498</t>
+          <t>PO-10501</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-09T21:32:15.767073+00:00</t>
+          <t>2026-10-08T06:19:53.378460+00:00</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2026-08-10T09:39:03.862803+00:00</t>
-        </is>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>2026-08-11T16:15:08.874292+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-10T05:16:07.339986+00:00</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr"/>
       <c r="G339" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="H339" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="I339" t="n">
-        <v>42.71</v>
-      </c>
+        <v>46.94</v>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr"/>
       <c r="J339" t="b">
-        <v>1</v>
-      </c>
-      <c r="K339" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K339" t="n">
+        <v>391.84</v>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
@@ -19468,56 +19492,62 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>PO-10500</t>
+          <t>PO-10502</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-10-08T06:19:53.378460+00:00</t>
+          <t>2026-08-30T04:08:07.198697+00:00</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2026-10-10T05:16:07.339986+00:00</t>
-        </is>
-      </c>
-      <c r="F340" t="inlineStr"/>
+          <t>2026-08-30T10:30:08.904663+00:00</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>2026-09-02T16:32:14.750148+00:00</t>
+        </is>
+      </c>
       <c r="G340" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="H340" t="inlineStr"/>
-      <c r="I340" t="inlineStr"/>
+        <v>6.37</v>
+      </c>
+      <c r="H340" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="I340" t="n">
+        <v>84.40000000000001</v>
+      </c>
       <c r="J340" t="b">
-        <v>0</v>
-      </c>
-      <c r="K340" t="n">
-        <v>369.22</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>PO-10501</t>
+          <t>PO-10506</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -19527,27 +19557,27 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-30T04:08:07.198697+00:00</t>
+          <t>2026-09-28T11:14:25.063087+00:00</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>2026-08-30T10:30:08.904663+00:00</t>
+          <t>2026-09-28T15:49:16.866453+00:00</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>2026-09-02T16:32:14.750148+00:00</t>
+          <t>2026-09-30T13:49:09.557627+00:00</t>
         </is>
       </c>
       <c r="G341" t="n">
-        <v>6.37</v>
+        <v>4.58</v>
       </c>
       <c r="H341" t="n">
-        <v>78.03</v>
+        <v>46</v>
       </c>
       <c r="I341" t="n">
-        <v>84.40000000000001</v>
+        <v>50.58</v>
       </c>
       <c r="J341" t="b">
         <v>1</v>
@@ -19555,108 +19585,108 @@
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>PO-10505</t>
+          <t>PO-10507</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-28T11:14:25.063087+00:00</t>
+          <t>2026-10-18T02:25:38.642571+00:00</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2026-09-28T15:49:16.866453+00:00</t>
-        </is>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>2026-09-30T13:49:09.557627+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-18T15:37:57.938546+00:00</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr"/>
       <c r="G342" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="H342" t="n">
-        <v>46</v>
-      </c>
-      <c r="I342" t="n">
-        <v>50.58</v>
-      </c>
+        <v>13.21</v>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr"/>
       <c r="J342" t="b">
-        <v>1</v>
-      </c>
-      <c r="K342" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K342" t="n">
+        <v>155.75</v>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PO-10506</t>
+          <t>PO-10509</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-10-18T02:25:38.642571+00:00</t>
+          <t>2026-10-03T12:51:42.139011+00:00</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-10-18T15:37:57.938546+00:00</t>
-        </is>
-      </c>
-      <c r="F343" t="inlineStr"/>
+          <t>2026-10-07T03:12:43.342414+00:00</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>2026-10-13T00:45:54.797117+00:00</t>
+        </is>
+      </c>
       <c r="G343" t="n">
-        <v>13.21</v>
-      </c>
-      <c r="H343" t="inlineStr"/>
-      <c r="I343" t="inlineStr"/>
+        <v>86.34999999999999</v>
+      </c>
+      <c r="H343" t="n">
+        <v>141.55</v>
+      </c>
+      <c r="I343" t="n">
+        <v>227.9</v>
+      </c>
       <c r="J343" t="b">
-        <v>0</v>
-      </c>
-      <c r="K343" t="n">
-        <v>133.12</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -19664,54 +19694,48 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PO-10508</t>
+          <t>PO-10510</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-10-03T12:51:42.139011+00:00</t>
+          <t>2026-10-26T19:53:28.650435+00:00</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2026-10-07T03:12:43.342414+00:00</t>
-        </is>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>2026-10-13T00:45:54.797117+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-30T00:12:56.107253+00:00</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr"/>
       <c r="G344" t="n">
-        <v>86.34999999999999</v>
-      </c>
-      <c r="H344" t="n">
-        <v>141.55</v>
-      </c>
-      <c r="I344" t="n">
-        <v>227.9</v>
-      </c>
+        <v>76.31999999999999</v>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr"/>
       <c r="J344" t="b">
-        <v>1</v>
-      </c>
-      <c r="K344" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K344" t="n">
+        <v>-53.72</v>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -19719,56 +19743,62 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S44</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PO-10509</t>
+          <t>PO-10511</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-10-21T10:53:28.650435+00:00</t>
+          <t>2026-09-01T08:03:23.465215+00:00</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-10-24T15:12:56.107253+00:00</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr"/>
+          <t>2026-09-03T05:03:35.233319+00:00</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>2026-09-06T09:51:38.460550+00:00</t>
+        </is>
+      </c>
       <c r="G345" t="n">
-        <v>76.31999999999999</v>
-      </c>
-      <c r="H345" t="inlineStr"/>
-      <c r="I345" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="H345" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I345" t="n">
+        <v>121.8</v>
+      </c>
       <c r="J345" t="b">
-        <v>0</v>
-      </c>
-      <c r="K345" t="n">
-        <v>52.66</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19810,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PO-10510</t>
+          <t>PO-10512</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -19790,27 +19820,27 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-01T08:03:23.465215+00:00</t>
+          <t>2026-08-23T05:45:37.462891+00:00</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-09-03T05:03:35.233319+00:00</t>
+          <t>2026-08-24T08:46:24.840641+00:00</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>2026-09-06T09:51:38.460550+00:00</t>
+          <t>2026-08-29T10:54:04.473455+00:00</t>
         </is>
       </c>
       <c r="G346" t="n">
-        <v>45</v>
+        <v>27.01</v>
       </c>
       <c r="H346" t="n">
-        <v>76.8</v>
+        <v>122.13</v>
       </c>
       <c r="I346" t="n">
-        <v>121.8</v>
+        <v>149.14</v>
       </c>
       <c r="J346" t="b">
         <v>1</v>
@@ -19818,24 +19848,24 @@
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PO-10511</t>
+          <t>PO-10514</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -19845,27 +19875,27 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-23T05:45:37.462891+00:00</t>
+          <t>2026-09-03T11:25:33.495098+00:00</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2026-08-24T08:46:24.840641+00:00</t>
+          <t>2026-09-03T16:38:32.266915+00:00</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2026-08-29T10:54:04.473455+00:00</t>
+          <t>2026-09-08T11:15:10.888701+00:00</t>
         </is>
       </c>
       <c r="G347" t="n">
-        <v>27.01</v>
+        <v>5.22</v>
       </c>
       <c r="H347" t="n">
-        <v>122.13</v>
+        <v>114.61</v>
       </c>
       <c r="I347" t="n">
-        <v>149.14</v>
+        <v>119.83</v>
       </c>
       <c r="J347" t="b">
         <v>1</v>
@@ -19873,24 +19903,24 @@
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>PO-10513</t>
+          <t>PO-10515</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -19900,27 +19930,27 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-03T11:25:33.495098+00:00</t>
+          <t>2026-09-18T12:27:20.859241+00:00</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>2026-09-03T16:38:32.266915+00:00</t>
+          <t>2026-09-18T15:45:07.848708+00:00</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>2026-09-08T11:15:10.888701+00:00</t>
+          <t>2026-09-22T00:28:12.771882+00:00</t>
         </is>
       </c>
       <c r="G348" t="n">
-        <v>5.22</v>
+        <v>3.3</v>
       </c>
       <c r="H348" t="n">
-        <v>114.61</v>
+        <v>80.72</v>
       </c>
       <c r="I348" t="n">
-        <v>119.83</v>
+        <v>84.01000000000001</v>
       </c>
       <c r="J348" t="b">
         <v>1</v>
@@ -19933,19 +19963,19 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>PO-10514</t>
+          <t>PO-10519</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -19955,27 +19985,27 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-18T12:27:20.859241+00:00</t>
+          <t>2026-09-04T20:17:44.545188+00:00</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>2026-09-18T15:45:07.848708+00:00</t>
+          <t>2026-09-05T10:10:40.749824+00:00</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>2026-09-22T00:28:12.771882+00:00</t>
+          <t>2026-09-08T02:48:51.034616+00:00</t>
         </is>
       </c>
       <c r="G349" t="n">
-        <v>3.3</v>
+        <v>13.88</v>
       </c>
       <c r="H349" t="n">
-        <v>80.72</v>
+        <v>64.64</v>
       </c>
       <c r="I349" t="n">
-        <v>84.01000000000001</v>
+        <v>78.52</v>
       </c>
       <c r="J349" t="b">
         <v>1</v>
@@ -19988,19 +20018,19 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>PO-10518</t>
+          <t>PO-10521</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -20010,27 +20040,27 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-04T20:17:44.545188+00:00</t>
+          <t>2026-10-08T19:25:58.442739+00:00</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>2026-09-05T10:10:40.749824+00:00</t>
+          <t>2026-10-10T04:23:28.455671+00:00</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>2026-09-08T02:48:51.034616+00:00</t>
+          <t>2026-10-15T08:31:19.903061+00:00</t>
         </is>
       </c>
       <c r="G350" t="n">
-        <v>13.88</v>
+        <v>32.96</v>
       </c>
       <c r="H350" t="n">
-        <v>64.64</v>
+        <v>124.13</v>
       </c>
       <c r="I350" t="n">
-        <v>78.52</v>
+        <v>157.09</v>
       </c>
       <c r="J350" t="b">
         <v>1</v>
@@ -20038,24 +20068,24 @@
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>PO-10520</t>
+          <t>PO-10522</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -20065,27 +20095,27 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-10-08T19:25:58.442739+00:00</t>
+          <t>2026-08-28T12:35:00.419074+00:00</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2026-10-10T04:23:28.455671+00:00</t>
+          <t>2026-08-30T18:07:11.901792+00:00</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>2026-10-15T08:31:19.903061+00:00</t>
+          <t>2026-08-30T23:33:48.431347+00:00</t>
         </is>
       </c>
       <c r="G351" t="n">
-        <v>32.96</v>
+        <v>53.54</v>
       </c>
       <c r="H351" t="n">
-        <v>124.13</v>
+        <v>5.44</v>
       </c>
       <c r="I351" t="n">
-        <v>157.09</v>
+        <v>58.98</v>
       </c>
       <c r="J351" t="b">
         <v>1</v>
@@ -20093,24 +20123,24 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>PO-10521</t>
+          <t>PO-10523</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -20120,27 +20150,27 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-08-28T12:35:00.419074+00:00</t>
+          <t>2026-09-25T09:27:22.946834+00:00</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>2026-08-30T18:07:11.901792+00:00</t>
+          <t>2026-09-26T15:01:10.819219+00:00</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>2026-08-30T23:33:48.431347+00:00</t>
+          <t>2026-09-28T09:45:20.374206+00:00</t>
         </is>
       </c>
       <c r="G352" t="n">
-        <v>53.54</v>
+        <v>29.56</v>
       </c>
       <c r="H352" t="n">
-        <v>5.44</v>
+        <v>42.74</v>
       </c>
       <c r="I352" t="n">
-        <v>58.98</v>
+        <v>72.3</v>
       </c>
       <c r="J352" t="b">
         <v>1</v>
@@ -20148,79 +20178,73 @@
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>PO-10522</t>
+          <t>PO-10524</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-25T09:27:22.946834+00:00</t>
+          <t>2026-08-17T22:27:11.867127+00:00</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2026-09-26T15:01:10.819219+00:00</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>2026-09-28T09:45:20.374206+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-20T09:21:31.781331+00:00</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
       <c r="G353" t="n">
-        <v>29.56</v>
-      </c>
-      <c r="H353" t="n">
-        <v>42.74</v>
-      </c>
-      <c r="I353" t="n">
-        <v>72.3</v>
-      </c>
+        <v>58.91</v>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr"/>
       <c r="J353" t="b">
-        <v>1</v>
-      </c>
-      <c r="K353" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K353" t="n">
+        <v>1623.72</v>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>PO-10523</t>
+          <t>PO-10525</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -20230,17 +20254,17 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-17T22:27:11.867127+00:00</t>
+          <t>2026-10-16T12:34:27.465371+00:00</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>2026-08-20T09:21:31.781331+00:00</t>
+          <t>2026-10-18T16:57:31.108975+00:00</t>
         </is>
       </c>
       <c r="F354" t="inlineStr"/>
       <c r="G354" t="n">
-        <v>58.91</v>
+        <v>52.38</v>
       </c>
       <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
@@ -20248,57 +20272,63 @@
         <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>1601.1</v>
+        <v>193.6</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>PO-10524</t>
+          <t>PO-10526</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-10-16T12:34:27.465371+00:00</t>
+          <t>2026-10-16T01:56:53.297424+00:00</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>2026-10-18T16:57:31.108975+00:00</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr"/>
+          <t>2026-10-17T20:53:26.914789+00:00</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>2026-10-20T20:50:51.927809+00:00</t>
+        </is>
+      </c>
       <c r="G355" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="H355" t="inlineStr"/>
-      <c r="I355" t="inlineStr"/>
+        <v>42.94</v>
+      </c>
+      <c r="H355" t="n">
+        <v>71.95999999999999</v>
+      </c>
+      <c r="I355" t="n">
+        <v>114.9</v>
+      </c>
       <c r="J355" t="b">
-        <v>0</v>
-      </c>
-      <c r="K355" t="n">
-        <v>170.98</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -20313,12 +20343,12 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PO-10525</t>
+          <t>PO-10530</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -20328,27 +20358,27 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-10-16T01:56:53.297424+00:00</t>
+          <t>2026-09-27T16:50:10.552600+00:00</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2026-10-17T20:53:26.914789+00:00</t>
+          <t>2026-09-30T05:18:28.626985+00:00</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>2026-10-20T20:50:51.927809+00:00</t>
+          <t>2026-10-05T17:59:18.943459+00:00</t>
         </is>
       </c>
       <c r="G356" t="n">
-        <v>42.94</v>
+        <v>60.47</v>
       </c>
       <c r="H356" t="n">
-        <v>71.95999999999999</v>
+        <v>132.68</v>
       </c>
       <c r="I356" t="n">
-        <v>114.9</v>
+        <v>193.15</v>
       </c>
       <c r="J356" t="b">
         <v>1</v>
@@ -20356,24 +20386,24 @@
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PO-10529</t>
+          <t>PO-10532</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -20383,27 +20413,27 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-09-27T16:50:10.552600+00:00</t>
+          <t>2026-10-02T22:35:17.352603+00:00</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>2026-09-30T05:18:28.626985+00:00</t>
+          <t>2026-10-04T20:01:44.146283+00:00</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>2026-10-05T17:59:18.943459+00:00</t>
+          <t>2026-10-07T09:51:20.314283+00:00</t>
         </is>
       </c>
       <c r="G357" t="n">
-        <v>60.47</v>
+        <v>45.44</v>
       </c>
       <c r="H357" t="n">
-        <v>132.68</v>
+        <v>61.83</v>
       </c>
       <c r="I357" t="n">
-        <v>193.15</v>
+        <v>107.27</v>
       </c>
       <c r="J357" t="b">
         <v>1</v>
@@ -20411,24 +20441,24 @@
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PO-10531</t>
+          <t>PO-10534</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -20438,27 +20468,27 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-10-02T22:35:17.352603+00:00</t>
+          <t>2026-09-12T16:52:35.514610+00:00</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2026-10-04T20:01:44.146283+00:00</t>
+          <t>2026-09-14T13:29:33.628539+00:00</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>2026-10-07T09:51:20.314283+00:00</t>
+          <t>2026-09-18T11:19:02.240835+00:00</t>
         </is>
       </c>
       <c r="G358" t="n">
-        <v>45.44</v>
+        <v>44.62</v>
       </c>
       <c r="H358" t="n">
-        <v>61.83</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="I358" t="n">
-        <v>107.27</v>
+        <v>138.44</v>
       </c>
       <c r="J358" t="b">
         <v>1</v>
@@ -20466,67 +20496,61 @@
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PO-10533</t>
+          <t>PO-10535</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-09-12T16:52:35.514610+00:00</t>
+          <t>2026-08-18T03:44:04.743671+00:00</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-09-14T13:29:33.628539+00:00</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>2026-09-18T11:19:02.240835+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-18T08:29:02.648842+00:00</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr"/>
       <c r="G359" t="n">
-        <v>44.62</v>
-      </c>
-      <c r="H359" t="n">
-        <v>93.81999999999999</v>
-      </c>
-      <c r="I359" t="n">
-        <v>138.44</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr"/>
       <c r="J359" t="b">
-        <v>1</v>
-      </c>
-      <c r="K359" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K359" t="n">
+        <v>1618.44</v>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
@@ -20538,27 +20562,27 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>PO-10534</t>
+          <t>PO-10537</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-18T03:44:04.743671+00:00</t>
+          <t>2026-08-10T09:18:03.411993+00:00</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>2026-08-18T08:29:02.648842+00:00</t>
+          <t>2026-08-12T16:20:47.711713+00:00</t>
         </is>
       </c>
       <c r="F360" t="inlineStr"/>
       <c r="G360" t="n">
-        <v>4.75</v>
+        <v>55.05</v>
       </c>
       <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr"/>
@@ -20566,7 +20590,7 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1595.82</v>
+        <v>1804.87</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
@@ -20575,19 +20599,19 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S33</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>PO-10536</t>
+          <t>PO-10540</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -20597,17 +20621,17 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-10T09:18:03.411993+00:00</t>
+          <t>2026-09-23T04:38:34.711594+00:00</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>2026-08-12T16:20:47.711713+00:00</t>
+          <t>2026-09-24T07:05:45.030204+00:00</t>
         </is>
       </c>
       <c r="F361" t="inlineStr"/>
       <c r="G361" t="n">
-        <v>55.05</v>
+        <v>26.45</v>
       </c>
       <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr"/>
@@ -20615,16 +20639,16 @@
         <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>1782.25</v>
+        <v>753.53</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -20636,50 +20660,44 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PO-10539</t>
+          <t>PO-10542</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-16T02:01:54.885863+00:00</t>
+          <t>2026-10-04T11:17:51.631426+00:00</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-08-16T21:09:23.207688+00:00</t>
-        </is>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>2026-08-18T02:22:56.590571+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-06T01:52:06.543167+00:00</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr"/>
       <c r="G362" t="n">
-        <v>19.12</v>
-      </c>
-      <c r="H362" t="n">
-        <v>29.23</v>
-      </c>
-      <c r="I362" t="n">
-        <v>48.35</v>
-      </c>
+        <v>38.57</v>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr"/>
       <c r="J362" t="b">
-        <v>1</v>
-      </c>
-      <c r="K362" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K362" t="n">
+        <v>482.88</v>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -20691,44 +20709,50 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PO-10540</t>
+          <t>PO-10544</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-16T11:32:17.062607+00:00</t>
+          <t>2026-10-02T03:06:52.204713+00:00</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>2026-08-18T13:57:29.497866+00:00</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr"/>
+          <t>2026-10-04T11:10:54.963814+00:00</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>2026-10-07T23:20:58.806418+00:00</t>
+        </is>
+      </c>
       <c r="G363" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="H363" t="inlineStr"/>
-      <c r="I363" t="inlineStr"/>
+        <v>56.07</v>
+      </c>
+      <c r="H363" t="n">
+        <v>84.17</v>
+      </c>
+      <c r="I363" t="n">
+        <v>140.24</v>
+      </c>
       <c r="J363" t="b">
-        <v>0</v>
-      </c>
-      <c r="K363" t="n">
-        <v>1636.01</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>2026-S33</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -20740,27 +20764,27 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PO-10541</t>
+          <t>PO-10545</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-10-21T07:37:24.813696+00:00</t>
+          <t>2026-10-21T18:43:47.673652+00:00</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>2026-10-22T10:14:27.377903+00:00</t>
+          <t>2026-10-23T10:59:10.070951+00:00</t>
         </is>
       </c>
       <c r="F364" t="inlineStr"/>
       <c r="G364" t="n">
-        <v>26.62</v>
+        <v>40.26</v>
       </c>
       <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr"/>
@@ -20768,7 +20792,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>55.93</v>
+        <v>67.45</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
@@ -20784,61 +20808,67 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PO-10542</t>
+          <t>PO-10546</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-10-21T18:43:47.673652+00:00</t>
+          <t>2026-08-19T08:02:45.499478+00:00</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>2026-10-23T10:59:10.070951+00:00</t>
-        </is>
-      </c>
-      <c r="F365" t="inlineStr"/>
+          <t>2026-08-21T20:11:07.711374+00:00</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>2026-08-25T23:36:16.530907+00:00</t>
+        </is>
+      </c>
       <c r="G365" t="n">
-        <v>40.26</v>
-      </c>
-      <c r="H365" t="inlineStr"/>
-      <c r="I365" t="inlineStr"/>
+        <v>60.14</v>
+      </c>
+      <c r="H365" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="I365" t="n">
+        <v>159.56</v>
+      </c>
       <c r="J365" t="b">
-        <v>0</v>
-      </c>
-      <c r="K365" t="n">
-        <v>44.82</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PO-10543</t>
+          <t>PO-10548</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -20848,27 +20878,27 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-19T08:02:45.499478+00:00</t>
+          <t>2026-09-26T16:56:19.752404+00:00</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>2026-08-21T20:11:07.711374+00:00</t>
+          <t>2026-09-28T01:34:26.259134+00:00</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>2026-08-25T23:36:16.530907+00:00</t>
+          <t>2026-09-30T18:59:17.189186+00:00</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>60.14</v>
+        <v>32.64</v>
       </c>
       <c r="H366" t="n">
-        <v>99.42</v>
+        <v>65.41</v>
       </c>
       <c r="I366" t="n">
-        <v>159.56</v>
+        <v>98.05</v>
       </c>
       <c r="J366" t="b">
         <v>1</v>
@@ -20876,24 +20906,24 @@
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>PO-10545</t>
+          <t>PO-10549</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -20903,27 +20933,27 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-09-26T16:56:19.752404+00:00</t>
+          <t>2026-08-30T13:56:23.291599+00:00</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>2026-09-28T01:34:26.259134+00:00</t>
+          <t>2026-09-03T05:27:59.726504+00:00</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>2026-09-30T18:59:17.189186+00:00</t>
+          <t>2026-09-05T12:17:10.132584+00:00</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>32.64</v>
+        <v>87.53</v>
       </c>
       <c r="H367" t="n">
-        <v>65.41</v>
+        <v>54.82</v>
       </c>
       <c r="I367" t="n">
-        <v>98.05</v>
+        <v>142.35</v>
       </c>
       <c r="J367" t="b">
         <v>1</v>
@@ -20931,24 +20961,24 @@
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>PO-10546</t>
+          <t>PO-10550</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -20958,27 +20988,27 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-08-30T13:56:23.291599+00:00</t>
+          <t>2026-09-23T06:12:07.616449+00:00</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-09-03T05:27:59.726504+00:00</t>
+          <t>2026-09-24T15:52:37.551670+00:00</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-09-05T12:17:10.132584+00:00</t>
+          <t>2026-09-27T00:23:00.657506+00:00</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>87.53</v>
+        <v>33.67</v>
       </c>
       <c r="H368" t="n">
-        <v>54.82</v>
+        <v>56.51</v>
       </c>
       <c r="I368" t="n">
-        <v>142.35</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="J368" t="b">
         <v>1</v>
@@ -20986,12 +21016,12 @@
       <c r="K368" t="inlineStr"/>
       <c r="L368" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -21003,99 +21033,99 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>PO-10547</t>
+          <t>PO-10552</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-09-23T06:12:07.616449+00:00</t>
+          <t>2026-10-15T14:59:13.458924+00:00</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-09-24T15:52:37.551670+00:00</t>
-        </is>
-      </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>2026-09-27T00:23:00.657506+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-16T21:47:55.886881+00:00</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr"/>
       <c r="G369" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="H369" t="n">
-        <v>56.51</v>
-      </c>
-      <c r="I369" t="n">
-        <v>90.18000000000001</v>
-      </c>
+        <v>30.81</v>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr"/>
       <c r="J369" t="b">
-        <v>1</v>
-      </c>
-      <c r="K369" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K369" t="n">
+        <v>215.19</v>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>PO-10549</t>
+          <t>PO-10553</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-10-15T14:59:13.458924+00:00</t>
+          <t>2026-09-30T16:51:26.731151+00:00</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-10-16T21:47:55.886881+00:00</t>
-        </is>
-      </c>
-      <c r="F370" t="inlineStr"/>
+          <t>2026-10-04T07:32:29.826345+00:00</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>2026-10-07T06:32:54.729961+00:00</t>
+        </is>
+      </c>
       <c r="G370" t="n">
-        <v>30.81</v>
-      </c>
-      <c r="H370" t="inlineStr"/>
-      <c r="I370" t="inlineStr"/>
+        <v>86.68000000000001</v>
+      </c>
+      <c r="H370" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="I370" t="n">
+        <v>157.69</v>
+      </c>
       <c r="J370" t="b">
-        <v>0</v>
-      </c>
-      <c r="K370" t="n">
-        <v>192.56</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -21107,7 +21137,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>PO-10550</t>
+          <t>PO-10554</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -21117,27 +21147,27 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-30T16:51:26.731151+00:00</t>
+          <t>2026-10-09T10:15:44.580551+00:00</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-10-04T07:32:29.826345+00:00</t>
+          <t>2026-10-10T00:07:58.109611+00:00</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>2026-10-07T06:32:54.729961+00:00</t>
+          <t>2026-10-12T03:36:07.895992+00:00</t>
         </is>
       </c>
       <c r="G371" t="n">
-        <v>86.68000000000001</v>
+        <v>13.87</v>
       </c>
       <c r="H371" t="n">
-        <v>71.01000000000001</v>
+        <v>51.47</v>
       </c>
       <c r="I371" t="n">
-        <v>157.69</v>
+        <v>65.34</v>
       </c>
       <c r="J371" t="b">
         <v>1</v>
@@ -21145,24 +21175,24 @@
       <c r="K371" t="inlineStr"/>
       <c r="L371" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>PO-10551</t>
+          <t>PO-10555</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -21172,27 +21202,27 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-10-09T10:15:44.580551+00:00</t>
+          <t>2026-10-07T09:57:50.147511+00:00</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-10-10T00:07:58.109611+00:00</t>
+          <t>2026-10-09T11:39:59.246568+00:00</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-10-12T03:36:07.895992+00:00</t>
+          <t>2026-10-12T17:36:00.867516+00:00</t>
         </is>
       </c>
       <c r="G372" t="n">
-        <v>13.87</v>
+        <v>49.7</v>
       </c>
       <c r="H372" t="n">
-        <v>51.47</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="I372" t="n">
-        <v>65.34</v>
+        <v>127.64</v>
       </c>
       <c r="J372" t="b">
         <v>1</v>
@@ -21212,159 +21242,153 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>PO-10552</t>
+          <t>PO-10556</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-10-07T09:57:50.147511+00:00</t>
+          <t>2026-09-15T17:04:16.078411+00:00</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>2026-10-09T11:39:59.246568+00:00</t>
-        </is>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>2026-10-12T17:36:00.867516+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-17T07:04:14.427206+00:00</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr"/>
       <c r="G373" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="H373" t="n">
-        <v>77.93000000000001</v>
-      </c>
-      <c r="I373" t="n">
-        <v>127.64</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr"/>
       <c r="J373" t="b">
-        <v>1</v>
-      </c>
-      <c r="K373" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K373" t="n">
+        <v>933.1</v>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>PO-10553</t>
+          <t>PO-10557</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-09-15T17:04:16.078411+00:00</t>
+          <t>2026-08-28T06:27:56.812254+00:00</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-09-17T07:04:14.427206+00:00</t>
-        </is>
-      </c>
-      <c r="F374" t="inlineStr"/>
+          <t>2026-08-31T12:20:00.151268+00:00</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2026-09-03T08:09:46.557253+00:00</t>
+        </is>
+      </c>
       <c r="G374" t="n">
-        <v>38</v>
-      </c>
-      <c r="H374" t="inlineStr"/>
-      <c r="I374" t="inlineStr"/>
+        <v>77.87</v>
+      </c>
+      <c r="H374" t="n">
+        <v>67.83</v>
+      </c>
+      <c r="I374" t="n">
+        <v>145.7</v>
+      </c>
       <c r="J374" t="b">
-        <v>0</v>
-      </c>
-      <c r="K374" t="n">
-        <v>910.48</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PO-10554</t>
+          <t>PO-10559</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-28T06:27:56.812254+00:00</t>
+          <t>2026-10-23T04:41:09.252173+00:00</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-08-31T12:20:00.151268+00:00</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>2026-09-03T08:09:46.557253+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-23T12:19:01.282468+00:00</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr"/>
       <c r="G375" t="n">
-        <v>77.87</v>
-      </c>
-      <c r="H375" t="n">
-        <v>67.83</v>
-      </c>
-      <c r="I375" t="n">
-        <v>145.7</v>
-      </c>
+        <v>7.63</v>
+      </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr"/>
       <c r="J375" t="b">
-        <v>1</v>
-      </c>
-      <c r="K375" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>33.49</v>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
@@ -21376,44 +21400,50 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>PO-10556</t>
+          <t>PO-10562</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-10-23T04:41:09.252173+00:00</t>
+          <t>2026-08-25T10:48:32.733828+00:00</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-10-23T12:19:01.282468+00:00</t>
-        </is>
-      </c>
-      <c r="F376" t="inlineStr"/>
+          <t>2026-08-26T21:43:48.732261+00:00</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>2026-08-27T21:54:57.128563+00:00</t>
+        </is>
+      </c>
       <c r="G376" t="n">
-        <v>7.63</v>
-      </c>
-      <c r="H376" t="inlineStr"/>
-      <c r="I376" t="inlineStr"/>
+        <v>34.92</v>
+      </c>
+      <c r="H376" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="I376" t="n">
+        <v>59.11</v>
+      </c>
       <c r="J376" t="b">
-        <v>0</v>
-      </c>
-      <c r="K376" t="n">
-        <v>10.86</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
@@ -21425,91 +21455,91 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>PO-10559</t>
+          <t>PO-10563</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-08-25T10:48:32.733828+00:00</t>
+          <t>2026-10-13T03:02:49.669800+00:00</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2026-08-26T21:43:48.732261+00:00</t>
-        </is>
-      </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>2026-08-27T21:54:57.128563+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-14T14:15:28.972878+00:00</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr"/>
       <c r="G377" t="n">
-        <v>34.92</v>
-      </c>
-      <c r="H377" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="I377" t="n">
-        <v>59.11</v>
-      </c>
+        <v>35.21</v>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
       <c r="J377" t="b">
-        <v>1</v>
-      </c>
-      <c r="K377" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K377" t="n">
+        <v>275.13</v>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S42</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>PO-10560</t>
+          <t>PO-10564</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-10-13T03:02:49.669800+00:00</t>
+          <t>2026-10-01T01:34:58.328543+00:00</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2026-10-14T14:15:28.972878+00:00</t>
-        </is>
-      </c>
-      <c r="F378" t="inlineStr"/>
+          <t>2026-10-01T08:49:19.134062+00:00</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>2026-10-01T22:37:14.930137+00:00</t>
+        </is>
+      </c>
       <c r="G378" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="H378" t="inlineStr"/>
-      <c r="I378" t="inlineStr"/>
+        <v>7.24</v>
+      </c>
+      <c r="H378" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I378" t="n">
+        <v>21.04</v>
+      </c>
       <c r="J378" t="b">
-        <v>0</v>
-      </c>
-      <c r="K378" t="n">
-        <v>252.5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -21517,19 +21547,19 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>2026-S42</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>PO-10561</t>
+          <t>PO-10565</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -21539,27 +21569,27 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-10-01T01:34:58.328543+00:00</t>
+          <t>2026-09-29T07:38:45.123436+00:00</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>2026-10-01T08:49:19.134062+00:00</t>
+          <t>2026-10-01T02:19:46.942968+00:00</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2026-10-01T22:37:14.930137+00:00</t>
+          <t>2026-10-04T15:16:49.058324+00:00</t>
         </is>
       </c>
       <c r="G379" t="n">
-        <v>7.24</v>
+        <v>42.68</v>
       </c>
       <c r="H379" t="n">
-        <v>13.8</v>
+        <v>84.95</v>
       </c>
       <c r="I379" t="n">
-        <v>21.04</v>
+        <v>127.63</v>
       </c>
       <c r="J379" t="b">
         <v>1</v>
@@ -21567,7 +21597,7 @@
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M379" t="inlineStr">
@@ -21579,12 +21609,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>PO-10562</t>
+          <t>PO-10569</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -21594,27 +21624,27 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-09-29T07:38:45.123436+00:00</t>
+          <t>2026-08-18T08:18:23.601518+00:00</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-10-01T02:19:46.942968+00:00</t>
+          <t>2026-08-20T04:18:48.318982+00:00</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>2026-10-04T15:16:49.058324+00:00</t>
+          <t>2026-08-23T08:15:22.520821+00:00</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>42.68</v>
+        <v>44.01</v>
       </c>
       <c r="H380" t="n">
-        <v>84.95</v>
+        <v>75.94</v>
       </c>
       <c r="I380" t="n">
-        <v>127.63</v>
+        <v>119.95</v>
       </c>
       <c r="J380" t="b">
         <v>1</v>
@@ -21622,24 +21652,24 @@
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>PO-10566</t>
+          <t>PO-10570</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -21649,27 +21679,27 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-08-18T08:18:23.601518+00:00</t>
+          <t>2026-08-21T01:10:17.136890+00:00</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2026-08-20T04:18:48.318982+00:00</t>
+          <t>2026-08-22T23:02:34.077777+00:00</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>2026-08-23T08:15:22.520821+00:00</t>
+          <t>2026-08-24T10:24:44.895786+00:00</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>44.01</v>
+        <v>45.87</v>
       </c>
       <c r="H381" t="n">
-        <v>75.94</v>
+        <v>35.37</v>
       </c>
       <c r="I381" t="n">
-        <v>119.95</v>
+        <v>81.23999999999999</v>
       </c>
       <c r="J381" t="b">
         <v>1</v>
@@ -21694,7 +21724,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>PO-10567</t>
+          <t>PO-10572</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -21704,27 +21734,27 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-21T01:10:17.136890+00:00</t>
+          <t>2026-09-29T01:31:35.007610+00:00</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>2026-08-22T23:02:34.077777+00:00</t>
+          <t>2026-09-29T13:24:00.117735+00:00</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>2026-08-24T10:24:44.895786+00:00</t>
+          <t>2026-10-01T06:55:42.864711+00:00</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>45.87</v>
+        <v>11.87</v>
       </c>
       <c r="H382" t="n">
-        <v>35.37</v>
+        <v>41.53</v>
       </c>
       <c r="I382" t="n">
-        <v>81.23999999999999</v>
+        <v>53.4</v>
       </c>
       <c r="J382" t="b">
         <v>1</v>
@@ -21732,12 +21762,12 @@
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
@@ -21749,195 +21779,195 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>PO-10569</t>
+          <t>PO-10573</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-29T01:31:35.007610+00:00</t>
+          <t>2026-10-23T06:28:51.601950+00:00</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2026-09-29T13:24:00.117735+00:00</t>
-        </is>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>2026-10-01T06:55:42.864711+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-24T18:46:15.585581+00:00</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr"/>
       <c r="G383" t="n">
-        <v>11.87</v>
-      </c>
-      <c r="H383" t="n">
-        <v>41.53</v>
-      </c>
-      <c r="I383" t="n">
-        <v>53.4</v>
-      </c>
+        <v>36.29</v>
+      </c>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
       <c r="J383" t="b">
-        <v>1</v>
-      </c>
-      <c r="K383" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>31.69</v>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>PO-10570</t>
+          <t>PO-10577</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-10-23T06:28:51.601950+00:00</t>
+          <t>2026-09-22T22:49:57.786697+00:00</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>2026-10-24T18:46:15.585581+00:00</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr"/>
+          <t>2026-09-24T10:41:20.139185+00:00</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>2026-09-29T04:10:36.889140+00:00</t>
+        </is>
+      </c>
       <c r="G384" t="n">
-        <v>36.29</v>
-      </c>
-      <c r="H384" t="inlineStr"/>
-      <c r="I384" t="inlineStr"/>
+        <v>35.86</v>
+      </c>
+      <c r="H384" t="n">
+        <v>113.49</v>
+      </c>
+      <c r="I384" t="n">
+        <v>149.34</v>
+      </c>
       <c r="J384" t="b">
-        <v>0</v>
-      </c>
-      <c r="K384" t="n">
-        <v>9.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K384" t="inlineStr"/>
       <c r="L384" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Fluxo Denim</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>PO-10574</t>
+          <t>PO-10578</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Associado</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-22T22:49:57.786697+00:00</t>
+          <t>2026-08-26T00:10:17.513362+00:00</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-09-24T10:41:20.139185+00:00</t>
-        </is>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>2026-09-29T04:10:36.889140+00:00</t>
-        </is>
-      </c>
+          <t>2026-08-26T17:02:14.582750+00:00</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
       <c r="G385" t="n">
-        <v>35.86</v>
-      </c>
-      <c r="H385" t="n">
-        <v>113.49</v>
-      </c>
-      <c r="I385" t="n">
-        <v>149.34</v>
-      </c>
+        <v>16.87</v>
+      </c>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
       <c r="J385" t="b">
-        <v>1</v>
-      </c>
-      <c r="K385" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K385" t="n">
+        <v>1430</v>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S35</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Fluxo Denim</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>PO-10575</t>
+          <t>PO-10579</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Associado</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-26T00:10:17.513362+00:00</t>
+          <t>2026-08-08T11:15:58.813417+00:00</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2026-08-26T17:02:14.582750+00:00</t>
-        </is>
-      </c>
-      <c r="F386" t="inlineStr"/>
+          <t>2026-08-08T14:56:53.887078+00:00</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>2026-08-10T21:10:27.076616+00:00</t>
+        </is>
+      </c>
       <c r="G386" t="n">
-        <v>16.87</v>
-      </c>
-      <c r="H386" t="inlineStr"/>
-      <c r="I386" t="inlineStr"/>
+        <v>3.68</v>
+      </c>
+      <c r="H386" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="I386" t="n">
+        <v>57.91</v>
+      </c>
       <c r="J386" t="b">
-        <v>0</v>
-      </c>
-      <c r="K386" t="n">
-        <v>1407.38</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr">
         <is>
           <t>2026-08</t>
@@ -21945,19 +21975,19 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>2026-S35</t>
+          <t>2026-S32</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PO-10576</t>
+          <t>PO-10580</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -21967,27 +21997,27 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-08-08T11:15:58.813417+00:00</t>
+          <t>2026-09-09T03:48:36.013567+00:00</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-08-08T14:56:53.887078+00:00</t>
+          <t>2026-09-11T04:29:50.524995+00:00</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>2026-08-10T21:10:27.076616+00:00</t>
+          <t>2026-09-14T02:58:22.220455+00:00</t>
         </is>
       </c>
       <c r="G387" t="n">
-        <v>3.68</v>
+        <v>48.69</v>
       </c>
       <c r="H387" t="n">
-        <v>54.23</v>
+        <v>70.48</v>
       </c>
       <c r="I387" t="n">
-        <v>57.91</v>
+        <v>119.16</v>
       </c>
       <c r="J387" t="b">
         <v>1</v>
@@ -21995,24 +22025,24 @@
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>2026-S32</t>
+          <t>2026-S37</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PO-10577</t>
+          <t>PO-10584</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -22022,27 +22052,27 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-09T03:48:36.013567+00:00</t>
+          <t>2026-09-17T14:30:34.313777+00:00</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-09-11T04:29:50.524995+00:00</t>
+          <t>2026-09-19T07:06:39.336574+00:00</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>2026-09-14T02:58:22.220455+00:00</t>
+          <t>2026-09-21T05:03:03.900005+00:00</t>
         </is>
       </c>
       <c r="G388" t="n">
-        <v>48.69</v>
+        <v>40.6</v>
       </c>
       <c r="H388" t="n">
-        <v>70.48</v>
+        <v>45.94</v>
       </c>
       <c r="I388" t="n">
-        <v>119.16</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="J388" t="b">
         <v>1</v>
@@ -22055,103 +22085,103 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>2026-S37</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>PO-10581</t>
+          <t>PO-10585</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Pendente</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-17T14:30:34.313777+00:00</t>
+          <t>2026-10-22T03:30:06.447096+00:00</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-09-19T07:06:39.336574+00:00</t>
-        </is>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>2026-09-21T05:03:03.900005+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-25T04:59:17.955405+00:00</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
       <c r="G389" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="H389" t="n">
-        <v>45.94</v>
-      </c>
-      <c r="I389" t="n">
-        <v>86.54000000000001</v>
-      </c>
+        <v>73.48999999999999</v>
+      </c>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
       <c r="J389" t="b">
-        <v>1</v>
-      </c>
-      <c r="K389" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K389" t="n">
+        <v>58.67</v>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S43</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>PO-10582</t>
+          <t>PO-10586</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-10-22T03:30:06.447096+00:00</t>
+          <t>2026-10-08T04:08:28.630454+00:00</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2026-10-25T04:59:17.955405+00:00</t>
-        </is>
-      </c>
-      <c r="F390" t="inlineStr"/>
+          <t>2026-10-10T19:47:22.368743+00:00</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>2026-10-14T13:55:52.426386+00:00</t>
+        </is>
+      </c>
       <c r="G390" t="n">
-        <v>73.48999999999999</v>
-      </c>
-      <c r="H390" t="inlineStr"/>
-      <c r="I390" t="inlineStr"/>
+        <v>63.65</v>
+      </c>
+      <c r="H390" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="I390" t="n">
+        <v>153.79</v>
+      </c>
       <c r="J390" t="b">
-        <v>0</v>
-      </c>
-      <c r="K390" t="n">
-        <v>36.05</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr">
         <is>
           <t>2026-10</t>
@@ -22159,19 +22189,19 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>2026-S43</t>
+          <t>2026-S41</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>PO-10583</t>
+          <t>PO-10587</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -22181,27 +22211,27 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-10-08T04:08:28.630454+00:00</t>
+          <t>2026-09-06T00:18:04.568172+00:00</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2026-10-10T19:47:22.368743+00:00</t>
+          <t>2026-09-07T16:35:20.792467+00:00</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>2026-10-14T13:55:52.426386+00:00</t>
+          <t>2026-09-07T21:52:02.080409+00:00</t>
         </is>
       </c>
       <c r="G391" t="n">
-        <v>63.65</v>
+        <v>40.29</v>
       </c>
       <c r="H391" t="n">
-        <v>90.14</v>
+        <v>5.28</v>
       </c>
       <c r="I391" t="n">
-        <v>153.79</v>
+        <v>45.57</v>
       </c>
       <c r="J391" t="b">
         <v>1</v>
@@ -22209,116 +22239,116 @@
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>2026-S41</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Eterna Beleza</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>PO-10584</t>
+          <t>PO-10588</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-06T00:18:04.568172+00:00</t>
+          <t>2026-10-01T18:14:03.540413+00:00</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>2026-09-07T16:35:20.792467+00:00</t>
-        </is>
-      </c>
-      <c r="F392" t="inlineStr">
-        <is>
-          <t>2026-09-07T21:52:02.080409+00:00</t>
-        </is>
-      </c>
+          <t>2026-10-03T22:10:52.328796+00:00</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
       <c r="G392" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="H392" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="I392" t="n">
-        <v>45.57</v>
-      </c>
+        <v>51.95</v>
+      </c>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
       <c r="J392" t="b">
-        <v>1</v>
-      </c>
-      <c r="K392" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K392" t="n">
+        <v>547.9400000000001</v>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S40</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Eterna Beleza</t>
+          <t>Delta Sports</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>PO-10585</t>
+          <t>PO-10590</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-10-01T18:14:03.540413+00:00</t>
+          <t>2026-09-21T11:43:40.218265+00:00</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-10-03T22:10:52.328796+00:00</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr"/>
+          <t>2026-09-22T16:42:43.675081+00:00</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>2026-09-28T10:42:23.181875+00:00</t>
+        </is>
+      </c>
       <c r="G393" t="n">
-        <v>51.95</v>
-      </c>
-      <c r="H393" t="inlineStr"/>
-      <c r="I393" t="inlineStr"/>
+        <v>28.98</v>
+      </c>
+      <c r="H393" t="n">
+        <v>137.99</v>
+      </c>
+      <c r="I393" t="n">
+        <v>166.98</v>
+      </c>
       <c r="J393" t="b">
-        <v>0</v>
-      </c>
-      <c r="K393" t="n">
-        <v>525.3200000000001</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K393" t="inlineStr"/>
       <c r="L393" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>2026-S40</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22360,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>PO-10587</t>
+          <t>PO-10591</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -22340,27 +22370,27 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-21T11:43:40.218265+00:00</t>
+          <t>2026-09-16T22:32:09.599556+00:00</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-09-22T16:42:43.675081+00:00</t>
+          <t>2026-09-18T18:42:54.145985+00:00</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>2026-09-28T10:42:23.181875+00:00</t>
+          <t>2026-09-21T08:13:42.147403+00:00</t>
         </is>
       </c>
       <c r="G394" t="n">
-        <v>28.98</v>
+        <v>44.18</v>
       </c>
       <c r="H394" t="n">
-        <v>137.99</v>
+        <v>61.51</v>
       </c>
       <c r="I394" t="n">
-        <v>166.98</v>
+        <v>105.69</v>
       </c>
       <c r="J394" t="b">
         <v>1</v>
@@ -22373,19 +22403,19 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>2026-S39</t>
+          <t>2026-S38</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Delta Sports</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>PO-10588</t>
+          <t>PO-10594</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -22395,27 +22425,27 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-09-16T22:32:09.599556+00:00</t>
+          <t>2026-08-23T00:23:09.845408+00:00</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-09-18T18:42:54.145985+00:00</t>
+          <t>2026-08-24T13:57:23.901980+00:00</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>2026-09-21T08:13:42.147403+00:00</t>
+          <t>2026-08-25T12:08:11.844181+00:00</t>
         </is>
       </c>
       <c r="G395" t="n">
-        <v>44.18</v>
+        <v>37.57</v>
       </c>
       <c r="H395" t="n">
-        <v>61.51</v>
+        <v>22.18</v>
       </c>
       <c r="I395" t="n">
-        <v>105.69</v>
+        <v>59.75</v>
       </c>
       <c r="J395" t="b">
         <v>1</v>
@@ -22423,24 +22453,24 @@
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>2026-S38</t>
+          <t>2026-S34</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Cedro Kids</t>
+          <t>Alpha Moda</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PO-10591</t>
+          <t>PO-10595</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -22450,27 +22480,27 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-23T00:23:09.845408+00:00</t>
+          <t>2026-09-06T01:22:54.855884+00:00</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-08-24T13:57:23.901980+00:00</t>
+          <t>2026-09-06T23:41:23.435126+00:00</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>2026-08-25T12:08:11.844181+00:00</t>
+          <t>2026-09-07T09:47:48.263323+00:00</t>
         </is>
       </c>
       <c r="G396" t="n">
-        <v>37.57</v>
+        <v>22.31</v>
       </c>
       <c r="H396" t="n">
-        <v>22.18</v>
+        <v>10.11</v>
       </c>
       <c r="I396" t="n">
-        <v>59.75</v>
+        <v>32.41</v>
       </c>
       <c r="J396" t="b">
         <v>1</v>
@@ -22478,59 +22508,53 @@
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>2026-S34</t>
+          <t>2026-S36</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Alpha Moda</t>
+          <t>Bravo Casa</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PO-10592</t>
+          <t>PO-10598</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Aprovado</t>
+          <t>Em avaliação</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-06T01:22:54.855884+00:00</t>
+          <t>2026-09-27T00:18:24.785515+00:00</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-09-06T23:41:23.435126+00:00</t>
-        </is>
-      </c>
-      <c r="F397" t="inlineStr">
-        <is>
-          <t>2026-09-07T09:47:48.263323+00:00</t>
-        </is>
-      </c>
+          <t>2026-09-27T09:52:49.421779+00:00</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
       <c r="G397" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="H397" t="n">
-        <v>10.11</v>
-      </c>
-      <c r="I397" t="n">
-        <v>32.41</v>
-      </c>
+        <v>9.57</v>
+      </c>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
       <c r="J397" t="b">
-        <v>1</v>
-      </c>
-      <c r="K397" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>661.87</v>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>2026-09</t>
@@ -22538,166 +22562,62 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>2026-S36</t>
+          <t>2026-S39</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Bravo Casa</t>
+          <t>Cedro Kids</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PO-10595</t>
+          <t>PO-10599</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Em avaliação</t>
+          <t>Aprovado</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-27T00:18:24.785515+00:00</t>
+          <t>2026-10-17T04:57:04.670864+00:00</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-09-27T09:52:49.421779+00:00</t>
-        </is>
-      </c>
-      <c r="F398" t="inlineStr"/>
+          <t>2026-10-19T05:59:28.926443+00:00</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>2026-10-20T20:43:38.935908+00:00</t>
+        </is>
+      </c>
       <c r="G398" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="H398" t="inlineStr"/>
-      <c r="I398" t="inlineStr"/>
+        <v>49.04</v>
+      </c>
+      <c r="H398" t="n">
+        <v>38.74</v>
+      </c>
+      <c r="I398" t="n">
+        <v>87.78</v>
+      </c>
       <c r="J398" t="b">
-        <v>0</v>
-      </c>
-      <c r="K398" t="n">
-        <v>639.24</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>2026-S39</t>
-        </is>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Cedro Kids</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>PO-10596</t>
-        </is>
-      </c>
-      <c r="C399" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>2026-10-17T04:57:04.670864+00:00</t>
-        </is>
-      </c>
-      <c r="E399" t="inlineStr">
-        <is>
-          <t>2026-10-19T05:59:28.926443+00:00</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>2026-10-20T20:43:38.935908+00:00</t>
-        </is>
-      </c>
-      <c r="G399" t="n">
-        <v>49.04</v>
-      </c>
-      <c r="H399" t="n">
-        <v>38.74</v>
-      </c>
-      <c r="I399" t="n">
-        <v>87.78</v>
-      </c>
-      <c r="J399" t="b">
-        <v>1</v>
-      </c>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="M399" t="inlineStr">
-        <is>
           <t>2026-S42</t>
-        </is>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Delta Sports</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>PO-10597</t>
-        </is>
-      </c>
-      <c r="C400" t="inlineStr">
-        <is>
-          <t>Aprovado</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>2026-09-16T19:58:00.010793+00:00</t>
-        </is>
-      </c>
-      <c r="E400" t="inlineStr">
-        <is>
-          <t>2026-09-17T22:47:05.024616+00:00</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>2026-09-23T05:41:28.322060+00:00</t>
-        </is>
-      </c>
-      <c r="G400" t="n">
-        <v>26.82</v>
-      </c>
-      <c r="H400" t="n">
-        <v>126.91</v>
-      </c>
-      <c r="I400" t="n">
-        <v>153.72</v>
-      </c>
-      <c r="J400" t="b">
-        <v>1</v>
-      </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="M400" t="inlineStr">
-        <is>
-          <t>2026-S38</t>
         </is>
       </c>
     </row>
